--- a/reports/latest_test_report.xlsx
+++ b/reports/latest_test_report.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R665b44d98d8c4df1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R33ad33b1b4174005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R92289695f3404946"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Re5fe06773bd24350"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="R4bc0295909994954"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R8fd7812d018141f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R5f835862f1b24db2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R66bd42e6f7514829"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="R95b3651c8b324ea1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Rf239ae32030a4d9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H201" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H204" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J201" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J204" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="运行时间"/>
     <x:tableColumn id="2" name="Git Commit"/>
@@ -977,7 +977,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T09:35:06+08:00  |  Git：a119c6647feaf019e381fcb12c094d447b019655</x:v>
+        <x:v>运行时间：2026-08-13T09:58:19+08:00  |  Git：04c22a0c496dd4d31d2314616e7e4c714f29303f</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1007,22 +1007,22 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="74" t="n">
-        <x:f>COUNTA('测试明细'!$A$5:$A$201)</x:f>
-        <x:v>197</x:v>
+        <x:f>COUNTA('测试明细'!$A$5:$A$204)</x:f>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B5" s="75"/>
       <x:c r="C5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$201,"通过")</x:f>
-        <x:v>197</x:v>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$204,"通过")</x:f>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D5" s="75"/>
       <x:c r="E5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$201,"失败")+COUNTIF('测试明细'!$E$5:$E$201,"错误")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$204,"失败")+COUNTIF('测试明细'!$E$5:$E$204,"错误")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="75"/>
       <x:c r="G5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$201,"跳过")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$204,"跳过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="76"/>
@@ -1062,8 +1062,8 @@
       </x:c>
       <x:c r="B9" s="108"/>
       <x:c r="C9" s="109" t="n">
-        <x:f>SUM('测试明细'!$F$5:$F$201)</x:f>
-        <x:v>256.2999999999999</x:v>
+        <x:f>SUM('测试明细'!$F$5:$F$204)</x:f>
+        <x:v>185.2360000000001</x:v>
       </x:c>
       <x:c r="D9" s="109"/>
       <x:c r="E9" s="110" t="n">
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="F9" s="110"/>
       <x:c r="G9" s="110" t="n">
-        <x:f>COUNTIF('用例说明'!$J$5:$J$201,"未登记")</x:f>
+        <x:f>COUNTIF('用例说明'!$J$5:$J$204,"未登记")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="111"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T09:35:06+08:00  |  Git：a119c6647feaf019e381fcb12c094d447b019655</x:v>
+        <x:v>运行时间：2026-08-13T09:58:19+08:00  |  Git：04c22a0c496dd4d31d2314616e7e4c714f29303f</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1280,7 +1280,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
         <x:v>确认旧基线与当前候选实现使用完全相同的能力模块，保证能力对比口径一致。</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F6" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
         <x:v>确认当前实现相对旧基线确实提升关键确定性能力的准确率。</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>验证动态查询规划不会为简单问题创建多余检索词，同时保持规划准确。</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F8" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>验证基准报告能同时给出基线值、候选值和差值。</x:v>
@@ -1376,7 +1376,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F9" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
         <x:v>验证离线基准能准确统计成功/失败调用以及输入、输出和总 Token。</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F10" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
         <x:v>验证离线基准能够量化统一 Tool 层的协议、错误和恢复能力。</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F11" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
         <x:v>验证离线 Benchmark 对比单源基线与多源候选的覆盖、去重和故障恢复。</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F12" s="32" t="n">
-        <x:v>0.206</x:v>
+        <x:v>0.214</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
         <x:v>验证完整能力基准报告可以用 UTF-8 JSON 保存并重新读取。</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F13" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G13" s="35" t="str">
         <x:v>验证基准工具拒绝不存在的运行配置名称。</x:v>
@@ -1496,7 +1496,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F14" s="32" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.053</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str">
         <x:v>验证候选评测能从 OpenAlex 等二级来源的 DOI 中提取待验证 arXiv 身份。</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
-        <x:v>0.029</x:v>
+        <x:v>0.036</x:v>
       </x:c>
       <x:c r="G15" s="35" t="str">
         <x:v>验证联合重放只把普通 DOI 交给 Crossref，排除 arXiv DOI。</x:v>
@@ -1544,7 +1544,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F16" s="32" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="G16" s="35" t="str">
         <x:v>验证成功取得的规范元数据会缓存，快照重放不会重复消耗网络请求。</x:v>
@@ -1568,7 +1568,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="G17" s="35" t="str">
         <x:v>验证 SSL、超时等临时失败不会被当成永久缓存结果。</x:v>
@@ -1592,7 +1592,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.032</x:v>
       </x:c>
       <x:c r="G18" s="35" t="str">
         <x:v>验证 Crossref 成功记录和明确查无均可重复使用。</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G19" s="35" t="str">
         <x:v>验证 DOI authority 网络失败不会写入成功缓存。</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="G20" s="35" t="str">
         <x:v>验证本轮候选实验只查询 v2 实际隔离过的身份，控制外部请求成本。</x:v>
@@ -1664,7 +1664,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
-        <x:v>0.029</x:v>
+        <x:v>0.058</x:v>
       </x:c>
       <x:c r="G21" s="35" t="str">
         <x:v>验证规范元数据候选只有在三份完整独立快照、权威覆盖完整且逐题无回归时才通过晋升门槛。</x:v>
@@ -1688,7 +1688,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F22" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G22" s="35" t="str">
         <x:v>验证 Crossref 相对仅 arXiv canonical 没有指标变化时不得宣称质量提升。</x:v>
@@ -1712,7 +1712,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F23" s="32" t="n">
-        <x:v>0.026</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="G23" s="35" t="str">
         <x:v>验证普通 DOI 候选评测只使用所有独立快照都出现的非 arXiv DOI。</x:v>
@@ -1760,7 +1760,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F25" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G25" s="35" t="str">
         <x:v>验证普通 DOI 样本按注册前缀轮转抽取，避免单一高频前缀垄断评测集。</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F27" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G27" s="35" t="str">
         <x:v>验证 DOI 校验在固定污染、缺失、近似、查无和失败场景中达到阶段止损条件。</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F28" s="32" t="n">
-        <x:v>0.109</x:v>
+        <x:v>0.146</x:v>
       </x:c>
       <x:c r="G28" s="35" t="str">
         <x:v>验证普通研究问题按完整 Agentic RAG 节点顺序执行。</x:v>
@@ -1856,7 +1856,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F29" s="32" t="n">
-        <x:v>0.088</x:v>
+        <x:v>0.111</x:v>
       </x:c>
       <x:c r="G29" s="35" t="str">
         <x:v>验证已有 PDF 的请求不会重复进行外部查询规划和检索。</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F30" s="32" t="n">
-        <x:v>0.081</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="G30" s="35" t="str">
         <x:v>验证问候类输入在进入 RAG 与 LLM 节点前本地结束。</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F31" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G31" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1928,7 +1928,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F32" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G32" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1976,7 +1976,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F34" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G34" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -2096,7 +2096,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F39" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G39" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2192,7 +2192,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F43" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G43" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2216,7 +2216,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F44" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G44" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2240,7 +2240,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F45" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G45" s="35" t="str">
         <x:v>验证意图匹配前只清理空格、大小写和末尾标点等表面差异。</x:v>
@@ -2288,7 +2288,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F47" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G47" s="35" t="str">
         <x:v>验证能读取 LangChain 标准 usage_metadata Token 字段。</x:v>
@@ -2312,7 +2312,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F48" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G48" s="35" t="str">
         <x:v>验证能读取 OpenAI 兼容响应中的 token_usage 字段。</x:v>
@@ -2336,7 +2336,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F49" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G49" s="35" t="str">
         <x:v>验证模型未返回 Token 数据时系统明确标记缺失而不伪造估算值。</x:v>
@@ -2360,7 +2360,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F50" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G50" s="35" t="str">
         <x:v>验证成功 LLM 调用会记录节点、模型、Token、成功状态和延迟。</x:v>
@@ -2384,7 +2384,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F51" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G51" s="35" t="str">
         <x:v>验证 LLM 调用失败时仍保留失败类型和耗时记录。</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F55" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G55" s="35" t="str">
         <x:v>验证检索评估节点启用 LLM 时记录评分与用量。</x:v>
@@ -2504,7 +2504,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F56" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G56" s="35" t="str">
         <x:v>验证答案生成节点记录实际生成结果和模型用量。</x:v>
@@ -2528,7 +2528,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F57" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G57" s="35" t="str">
         <x:v>验证关闭 LLM 评估时只使用规则评分且不创建虚假调用记录。</x:v>
@@ -2552,7 +2552,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F58" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G58" s="35" t="str">
         <x:v>验证 BM25 基线能把中文问题与英文术语、数字混合分词。</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F61" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G61" s="35" t="str">
         <x:v>用手工可计算的排名验证本地 RAG Recall、MRR 与 nDCG 公式。</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F63" s="32" t="n">
-        <x:v>0.081</x:v>
+        <x:v>0.064</x:v>
       </x:c>
       <x:c r="G63" s="35" t="str">
         <x:v>验证代表论文来源清单生成 Manifest 时保留语料版本、论文身份和内容哈希。</x:v>
@@ -2696,7 +2696,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F64" s="32" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="G64" s="35" t="str">
         <x:v>验证来源清单声明的 PDF 缺失时立即失败，而不是静默生成不完整语料。</x:v>
@@ -2751,15 +2751,15 @@
       </x:c>
       <x:c r="H66" s="35" t="str"/>
     </x:row>
-    <x:row r="67" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="67" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A67" s="26" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense.py</x:v>
       </x:c>
       <x:c r="C67" s="35" t="str">
-        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
+        <x:v>test_dense_index_cache_round_trips_vectors_and_invalidates_changed_corpus</x:v>
       </x:c>
       <x:c r="D67" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2768,22 +2768,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F67" s="32" t="n">
-        <x:v>61.22</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="G67" s="35" t="str">
-        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
+        <x:v>验证 Dense 向量缓存可以无损加载，并在语料文本、模型或处理版本变化后使用不同指纹。</x:v>
       </x:c>
       <x:c r="H67" s="35" t="str"/>
     </x:row>
-    <x:row r="68" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="68" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A68" s="26" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense.py</x:v>
       </x:c>
       <x:c r="C68" s="35" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_retriever_reuses_cached_vectors_without_document_embedding</x:v>
       </x:c>
       <x:c r="D68" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2795,19 +2795,19 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G68" s="35" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证缓存命中时 DenseRetriever 不会重新编码全部论文，只对查询生成向量。</x:v>
       </x:c>
       <x:c r="H68" s="35" t="str"/>
     </x:row>
-    <x:row r="69" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="69" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A69" s="26" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_cache_compare.py</x:v>
       </x:c>
       <x:c r="C69" s="35" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_dense_cache_comparison_requires_same_quality_and_faster_warm_build</x:v>
       </x:c>
       <x:c r="D69" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2816,10 +2816,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F69" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="G69" s="35" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
       </x:c>
       <x:c r="H69" s="35" t="str"/>
     </x:row>
@@ -2828,10 +2828,10 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_compare.py</x:v>
       </x:c>
       <x:c r="C70" s="35" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
       </x:c>
       <x:c r="D70" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2840,10 +2840,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F70" s="32" t="n">
-        <x:v>0.036</x:v>
+        <x:v>64.649</x:v>
       </x:c>
       <x:c r="G70" s="35" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
       </x:c>
       <x:c r="H70" s="35" t="str"/>
     </x:row>
@@ -2855,7 +2855,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C71" s="35" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D71" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2864,22 +2864,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F71" s="32" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G71" s="35" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="H71" s="35" t="str"/>
     </x:row>
-    <x:row r="72" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="72" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A72" s="26" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C72" s="35" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D72" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2888,10 +2888,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F72" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G72" s="35" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="H72" s="35" t="str"/>
     </x:row>
@@ -2900,10 +2900,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C73" s="35" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D73" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2912,22 +2912,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F73" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="G73" s="35" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="H73" s="35" t="str"/>
     </x:row>
-    <x:row r="74" ht="132" hidden="0" customHeight="1">
+    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A74" s="26" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" s="35" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C74" s="35" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D74" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2936,22 +2936,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F74" s="32" t="n">
-        <x:v>56.235</x:v>
+        <x:v>0.053</x:v>
       </x:c>
       <x:c r="G74" s="35" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="H74" s="35" t="str"/>
     </x:row>
-    <x:row r="75" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="75" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A75" s="26" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C75" s="35" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D75" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2960,22 +2960,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F75" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G75" s="35" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="H75" s="35" t="str"/>
     </x:row>
-    <x:row r="76" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="76" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A76" s="26" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C76" s="35" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D76" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2984,22 +2984,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F76" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G76" s="35" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="H76" s="35" t="str"/>
     </x:row>
-    <x:row r="77" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="77" ht="132" hidden="0" customHeight="1">
       <x:c r="A77" s="26" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C77" s="35" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D77" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3008,22 +3008,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F77" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>48.557</x:v>
       </x:c>
       <x:c r="G77" s="35" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="H77" s="35" t="str"/>
     </x:row>
-    <x:row r="78" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="78" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A78" s="26" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C78" s="35" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D78" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3032,22 +3032,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F78" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G78" s="35" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="H78" s="35" t="str"/>
     </x:row>
-    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="79" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A79" s="26" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C79" s="35" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D79" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3056,22 +3056,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F79" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G79" s="35" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="H79" s="35" t="str"/>
     </x:row>
-    <x:row r="80" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="80" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A80" s="26" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C80" s="35" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D80" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3083,11 +3083,11 @@
         <x:v>0.004</x:v>
       </x:c>
       <x:c r="G80" s="35" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="H80" s="35" t="str"/>
     </x:row>
-    <x:row r="81" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A81" s="26" t="n">
         <x:v>77</x:v>
       </x:c>
@@ -3095,7 +3095,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C81" s="35" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D81" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3104,14 +3104,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F81" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G81" s="35" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="H81" s="35" t="str"/>
     </x:row>
-    <x:row r="82" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="82" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A82" s="26" t="n">
         <x:v>78</x:v>
       </x:c>
@@ -3119,7 +3119,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C82" s="35" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D82" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3128,14 +3128,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F82" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G82" s="35" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="H82" s="35" t="str"/>
     </x:row>
-    <x:row r="83" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="83" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A83" s="26" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -3143,7 +3143,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C83" s="35" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D83" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3152,14 +3152,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F83" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G83" s="35" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="H83" s="35" t="str"/>
     </x:row>
-    <x:row r="84" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="84" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A84" s="26" t="n">
         <x:v>80</x:v>
       </x:c>
@@ -3167,7 +3167,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C84" s="35" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D84" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3176,22 +3176,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F84" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G84" s="35" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="H84" s="35" t="str"/>
     </x:row>
-    <x:row r="85" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="85" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A85" s="26" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C85" s="35" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D85" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3200,22 +3200,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F85" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G85" s="35" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="H85" s="35" t="str"/>
     </x:row>
-    <x:row r="86" ht="132" hidden="0" customHeight="1">
+    <x:row r="86" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A86" s="26" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="35" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D86" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3224,22 +3224,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F86" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G86" s="35" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="H86" s="35" t="str"/>
     </x:row>
-    <x:row r="87" ht="132" hidden="0" customHeight="1">
+    <x:row r="87" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A87" s="26" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="35" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D87" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3248,10 +3248,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F87" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G87" s="35" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="H87" s="35" t="str"/>
     </x:row>
@@ -3263,7 +3263,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C88" s="35" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D88" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3272,14 +3272,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F88" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G88" s="35" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="H88" s="35" t="str"/>
     </x:row>
-    <x:row r="89" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="89" ht="132" hidden="0" customHeight="1">
       <x:c r="A89" s="26" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -3287,7 +3287,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C89" s="35" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D89" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3296,14 +3296,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F89" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G89" s="35" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="H89" s="35" t="str"/>
     </x:row>
-    <x:row r="90" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="90" ht="132" hidden="0" customHeight="1">
       <x:c r="A90" s="26" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -3311,7 +3311,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C90" s="35" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D90" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3320,14 +3320,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F90" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G90" s="35" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="H90" s="35" t="str"/>
     </x:row>
-    <x:row r="91" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="91" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A91" s="26" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -3335,7 +3335,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C91" s="35" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D91" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3344,10 +3344,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F91" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G91" s="35" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="H91" s="35" t="str"/>
     </x:row>
@@ -3356,10 +3356,10 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" s="35" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C92" s="35" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D92" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3368,22 +3368,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F92" s="32" t="n">
-        <x:v>2.385</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G92" s="35" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="H92" s="35" t="str"/>
     </x:row>
-    <x:row r="93" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="93" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A93" s="26" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B93" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="35" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D93" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3392,22 +3392,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F93" s="32" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G93" s="35" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="H93" s="35" t="str"/>
     </x:row>
-    <x:row r="94" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="94" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A94" s="26" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B94" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="35" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D94" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3416,22 +3416,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F94" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G94" s="35" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="H94" s="35" t="str"/>
     </x:row>
-    <x:row r="95" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="95" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A95" s="26" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C95" s="35" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D95" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3440,14 +3440,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F95" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>2.365</x:v>
       </x:c>
       <x:c r="G95" s="35" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="H95" s="35" t="str"/>
     </x:row>
-    <x:row r="96" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="96" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A96" s="26" t="n">
         <x:v>92</x:v>
       </x:c>
@@ -3455,7 +3455,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C96" s="35" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D96" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3464,22 +3464,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F96" s="32" t="n">
-        <x:v>1.213</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="G96" s="35" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="H96" s="35" t="str"/>
     </x:row>
-    <x:row r="97" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="97" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A97" s="26" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C97" s="35" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D97" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3488,10 +3488,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F97" s="32" t="n">
-        <x:v>0.211</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G97" s="35" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="H97" s="35" t="str"/>
     </x:row>
@@ -3500,10 +3500,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C98" s="35" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D98" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3512,22 +3512,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F98" s="32" t="n">
-        <x:v>0.114</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G98" s="35" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="H98" s="35" t="str"/>
     </x:row>
-    <x:row r="99" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="99" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A99" s="26" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B99" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C99" s="35" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D99" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3536,14 +3536,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F99" s="32" t="n">
-        <x:v>0.057</x:v>
+        <x:v>1.156</x:v>
       </x:c>
       <x:c r="G99" s="35" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="H99" s="35" t="str"/>
     </x:row>
-    <x:row r="100" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="100" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A100" s="26" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -3551,7 +3551,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C100" s="35" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D100" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3560,22 +3560,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F100" s="32" t="n">
-        <x:v>0.096</x:v>
+        <x:v>0.196</x:v>
       </x:c>
       <x:c r="G100" s="35" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="H100" s="35" t="str"/>
     </x:row>
-    <x:row r="101" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A101" s="26" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="35" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C101" s="35" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D101" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3584,22 +3584,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F101" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.088</x:v>
       </x:c>
       <x:c r="G101" s="35" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="H101" s="35" t="str"/>
     </x:row>
-    <x:row r="102" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="102" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A102" s="26" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C102" s="35" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D102" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3608,34 +3608,34 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F102" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="G102" s="35" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="H102" s="35" t="str"/>
     </x:row>
-    <x:row r="103" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="103" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A103" s="26" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C103" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D103" s="35" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E103" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F103" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="G103" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="H103" s="35" t="str"/>
     </x:row>
@@ -3644,26 +3644,26 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C104" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D104" s="35" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E104" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F104" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G104" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="H104" s="35" t="str"/>
     </x:row>
-    <x:row r="105" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="105" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A105" s="26" t="n">
         <x:v>101</x:v>
       </x:c>
@@ -3671,19 +3671,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C105" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D105" s="35" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E105" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F105" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G105" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="H105" s="35" t="str"/>
     </x:row>
@@ -3695,16 +3695,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C106" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D106" s="35" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E106" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F106" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G106" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3719,23 +3719,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C107" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D107" s="35" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E107" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F107" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G107" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H107" s="35" t="str"/>
     </x:row>
-    <x:row r="108" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="108" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A108" s="26" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -3743,10 +3743,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C108" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D108" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E108" s="26" t="str">
         <x:v>通过</x:v>
@@ -3755,11 +3755,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G108" s="35" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H108" s="35" t="str"/>
     </x:row>
-    <x:row r="109" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="109" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A109" s="26" t="n">
         <x:v>105</x:v>
       </x:c>
@@ -3767,23 +3767,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C109" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D109" s="35" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F109" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G109" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H109" s="35" t="str"/>
     </x:row>
-    <x:row r="110" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="110" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A110" s="26" t="n">
         <x:v>106</x:v>
       </x:c>
@@ -3791,19 +3791,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D110" s="35" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E110" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F110" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G110" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H110" s="35" t="str"/>
     </x:row>
@@ -3815,19 +3815,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D111" s="35" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E111" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F111" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G111" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="H111" s="35" t="str"/>
     </x:row>
@@ -3839,16 +3839,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D112" s="35" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E112" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F112" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G112" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -3863,23 +3863,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D113" s="35" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F113" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G113" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H113" s="35" t="str"/>
     </x:row>
-    <x:row r="114" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="114" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A114" s="26" t="n">
         <x:v>110</x:v>
       </x:c>
@@ -3887,23 +3887,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D114" s="35" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E114" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F114" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G114" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H114" s="35" t="str"/>
     </x:row>
-    <x:row r="115" ht="66" hidden="0" customHeight="1">
+    <x:row r="115" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A115" s="26" t="n">
         <x:v>111</x:v>
       </x:c>
@@ -3911,19 +3911,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="35" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D115" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F115" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G115" s="35" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H115" s="35" t="str"/>
     </x:row>
@@ -3935,55 +3935,55 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="35" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D116" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E116" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F116" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G116" s="35" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H116" s="35" t="str"/>
     </x:row>
-    <x:row r="117" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="117" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A117" s="26" t="n">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B117" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="35" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D117" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F117" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G117" s="35" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H117" s="35" t="str"/>
     </x:row>
-    <x:row r="118" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="118" ht="66" hidden="0" customHeight="1">
       <x:c r="A118" s="26" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B118" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="35" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D118" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3995,19 +3995,19 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G118" s="35" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="H118" s="35" t="str"/>
     </x:row>
-    <x:row r="119" ht="132" hidden="0" customHeight="1">
+    <x:row r="119" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A119" s="26" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B119" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="35" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D119" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4016,10 +4016,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F119" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G119" s="35" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="H119" s="35" t="str"/>
     </x:row>
@@ -4031,7 +4031,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C120" s="35" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D120" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4043,19 +4043,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G120" s="35" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="H120" s="35" t="str"/>
     </x:row>
-    <x:row r="121" ht="132" hidden="0" customHeight="1">
+    <x:row r="121" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A121" s="26" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B121" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C121" s="35" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D121" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4064,22 +4064,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F121" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G121" s="35" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="H121" s="35" t="str"/>
     </x:row>
-    <x:row r="122" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="122" ht="132" hidden="0" customHeight="1">
       <x:c r="A122" s="26" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B122" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C122" s="35" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D122" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4088,10 +4088,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F122" s="32" t="n">
-        <x:v>32.086</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G122" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="H122" s="35" t="str"/>
     </x:row>
@@ -4100,10 +4100,10 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B123" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C123" s="35" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D123" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4112,10 +4112,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F123" s="32" t="n">
-        <x:v>31.47</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G123" s="35" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="H123" s="35" t="str"/>
     </x:row>
@@ -4124,10 +4124,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C124" s="35" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D124" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4136,22 +4136,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F124" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G124" s="35" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="H124" s="35" t="str"/>
     </x:row>
-    <x:row r="125" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A125" s="26" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C125" s="35" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D125" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4160,22 +4160,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F125" s="32" t="n">
-        <x:v>38.108</x:v>
+        <x:v>15.585</x:v>
       </x:c>
       <x:c r="G125" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="H125" s="35" t="str"/>
     </x:row>
-    <x:row r="126" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="126" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A126" s="26" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C126" s="35" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D126" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4184,22 +4184,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F126" s="32" t="n">
-        <x:v>30.793</x:v>
+        <x:v>15.492</x:v>
       </x:c>
       <x:c r="G126" s="35" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="H126" s="35" t="str"/>
     </x:row>
-    <x:row r="127" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="127" ht="132" hidden="0" customHeight="1">
       <x:c r="A127" s="26" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C127" s="35" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D127" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4208,22 +4208,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F127" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G127" s="35" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="H127" s="35" t="str"/>
     </x:row>
-    <x:row r="128" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="128" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A128" s="26" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C128" s="35" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D128" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4232,22 +4232,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F128" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>19.508</x:v>
       </x:c>
       <x:c r="G128" s="35" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="H128" s="35" t="str"/>
     </x:row>
-    <x:row r="129" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="129" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A129" s="26" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="35" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D129" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4256,14 +4256,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F129" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>15.364</x:v>
       </x:c>
       <x:c r="G129" s="35" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="H129" s="35" t="str"/>
     </x:row>
-    <x:row r="130" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="130" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A130" s="26" t="n">
         <x:v>126</x:v>
       </x:c>
@@ -4271,7 +4271,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C130" s="35" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D130" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4280,10 +4280,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F130" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G130" s="35" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="H130" s="35" t="str"/>
     </x:row>
@@ -4295,7 +4295,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C131" s="35" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D131" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4304,10 +4304,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F131" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G131" s="35" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="H131" s="35" t="str"/>
     </x:row>
@@ -4319,7 +4319,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C132" s="35" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D132" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4331,7 +4331,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G132" s="35" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="H132" s="35" t="str"/>
     </x:row>
@@ -4343,7 +4343,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C133" s="35" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D133" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4352,14 +4352,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F133" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G133" s="35" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="H133" s="35" t="str"/>
     </x:row>
-    <x:row r="134" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="134" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A134" s="26" t="n">
         <x:v>130</x:v>
       </x:c>
@@ -4367,7 +4367,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C134" s="35" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D134" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4379,7 +4379,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G134" s="35" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="H134" s="35" t="str"/>
     </x:row>
@@ -4391,7 +4391,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D135" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4400,14 +4400,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F135" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G135" s="35" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="H135" s="35" t="str"/>
     </x:row>
-    <x:row r="136" ht="132" hidden="0" customHeight="1">
+    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A136" s="26" t="n">
         <x:v>132</x:v>
       </x:c>
@@ -4415,7 +4415,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D136" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4424,10 +4424,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F136" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G136" s="35" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="H136" s="35" t="str"/>
     </x:row>
@@ -4439,7 +4439,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="35" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D137" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4451,7 +4451,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G137" s="35" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="H137" s="35" t="str"/>
     </x:row>
@@ -4463,7 +4463,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="35" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D138" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4472,14 +4472,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F138" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G138" s="35" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="H138" s="35" t="str"/>
     </x:row>
-    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="139" ht="132" hidden="0" customHeight="1">
       <x:c r="A139" s="26" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -4487,7 +4487,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="35" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D139" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4496,22 +4496,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F139" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G139" s="35" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="H139" s="35" t="str"/>
     </x:row>
-    <x:row r="140" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A140" s="26" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B140" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="35" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D140" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4520,22 +4520,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F140" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G140" s="35" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="H140" s="35" t="str"/>
     </x:row>
-    <x:row r="141" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="141" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A141" s="26" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B141" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="35" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D141" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4544,10 +4544,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F141" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G141" s="35" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="H141" s="35" t="str"/>
     </x:row>
@@ -4556,10 +4556,10 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B142" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D142" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4568,14 +4568,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F142" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G142" s="35" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="H142" s="35" t="str"/>
     </x:row>
-    <x:row r="143" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="143" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A143" s="26" t="n">
         <x:v>139</x:v>
       </x:c>
@@ -4583,7 +4583,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C143" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D143" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4595,7 +4595,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G143" s="35" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="H143" s="35" t="str"/>
     </x:row>
@@ -4607,7 +4607,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C144" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D144" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4616,10 +4616,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F144" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G144" s="35" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="H144" s="35" t="str"/>
     </x:row>
@@ -4631,7 +4631,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C145" s="35" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D145" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4640,14 +4640,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F145" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G145" s="35" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="H145" s="35" t="str"/>
     </x:row>
-    <x:row r="146" ht="66" hidden="0" customHeight="1">
+    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A146" s="26" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -4655,7 +4655,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C146" s="35" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D146" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4664,14 +4664,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F146" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G146" s="35" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="H146" s="35" t="str"/>
     </x:row>
-    <x:row r="147" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A147" s="26" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -4679,7 +4679,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C147" s="35" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D147" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4688,22 +4688,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F147" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G147" s="35" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="H147" s="35" t="str"/>
     </x:row>
-    <x:row r="148" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="148" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A148" s="26" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B148" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="35" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D148" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4712,22 +4712,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F148" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G148" s="35" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="H148" s="35" t="str"/>
     </x:row>
-    <x:row r="149" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="149" ht="66" hidden="0" customHeight="1">
       <x:c r="A149" s="26" t="n">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B149" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="35" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D149" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4736,22 +4736,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F149" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G149" s="35" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="H149" s="35" t="str"/>
     </x:row>
-    <x:row r="150" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="150" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A150" s="26" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B150" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="35" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D150" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4763,11 +4763,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G150" s="35" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="H150" s="35" t="str"/>
     </x:row>
-    <x:row r="151" ht="132" hidden="0" customHeight="1">
+    <x:row r="151" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A151" s="26" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -4775,7 +4775,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C151" s="35" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D151" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4784,14 +4784,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F151" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G151" s="35" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="H151" s="35" t="str"/>
     </x:row>
-    <x:row r="152" ht="132" hidden="0" customHeight="1">
+    <x:row r="152" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A152" s="26" t="n">
         <x:v>148</x:v>
       </x:c>
@@ -4799,7 +4799,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C152" s="35" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D152" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4808,14 +4808,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F152" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G152" s="35" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="H152" s="35" t="str"/>
     </x:row>
-    <x:row r="153" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A153" s="26" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -4823,7 +4823,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C153" s="35" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D153" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4832,14 +4832,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F153" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G153" s="35" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="H153" s="35" t="str"/>
     </x:row>
-    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="154" ht="132" hidden="0" customHeight="1">
       <x:c r="A154" s="26" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -4847,7 +4847,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C154" s="35" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D154" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4856,14 +4856,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F154" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G154" s="35" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="H154" s="35" t="str"/>
     </x:row>
-    <x:row r="155" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="155" ht="132" hidden="0" customHeight="1">
       <x:c r="A155" s="26" t="n">
         <x:v>151</x:v>
       </x:c>
@@ -4871,7 +4871,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C155" s="35" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D155" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4880,14 +4880,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F155" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G155" s="35" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="H155" s="35" t="str"/>
     </x:row>
-    <x:row r="156" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="156" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A156" s="26" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -4895,7 +4895,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="35" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D156" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4904,14 +4904,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F156" s="32" t="n">
-        <x:v>0.149</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G156" s="35" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="H156" s="35" t="str"/>
     </x:row>
-    <x:row r="157" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="157" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A157" s="26" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -4919,7 +4919,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="35" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D157" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4928,14 +4928,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F157" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G157" s="35" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H157" s="35" t="str"/>
     </x:row>
-    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="158" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A158" s="26" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -4943,7 +4943,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="35" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D158" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4952,14 +4952,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F158" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G158" s="35" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="H158" s="35" t="str"/>
     </x:row>
-    <x:row r="159" ht="132" hidden="0" customHeight="1">
+    <x:row r="159" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A159" s="26" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -4967,7 +4967,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4976,14 +4976,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F159" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="G159" s="35" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="H159" s="35" t="str"/>
     </x:row>
-    <x:row r="160" ht="132" hidden="0" customHeight="1">
+    <x:row r="160" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A160" s="26" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -4991,7 +4991,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5000,10 +5000,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F160" s="32" t="n">
-        <x:v>0.218</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G160" s="35" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="H160" s="35" t="str"/>
     </x:row>
@@ -5015,7 +5015,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5024,14 +5024,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F161" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="G161" s="35" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="H161" s="35" t="str"/>
     </x:row>
-    <x:row r="162" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="162" ht="132" hidden="0" customHeight="1">
       <x:c r="A162" s="26" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -5039,7 +5039,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5048,14 +5048,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F162" s="32" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G162" s="35" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="H162" s="35" t="str"/>
     </x:row>
-    <x:row r="163" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="163" ht="132" hidden="0" customHeight="1">
       <x:c r="A163" s="26" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -5063,7 +5063,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5072,22 +5072,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F163" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.164</x:v>
       </x:c>
       <x:c r="G163" s="35" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="H163" s="35" t="str"/>
     </x:row>
-    <x:row r="164" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A164" s="26" t="n">
         <x:v>160</x:v>
       </x:c>
       <x:c r="B164" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5096,22 +5096,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F164" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G164" s="35" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="H164" s="35" t="str"/>
     </x:row>
-    <x:row r="165" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A165" s="26" t="n">
         <x:v>161</x:v>
       </x:c>
       <x:c r="B165" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5120,22 +5120,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F165" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G165" s="35" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="H165" s="35" t="str"/>
     </x:row>
-    <x:row r="166" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="166" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A166" s="26" t="n">
         <x:v>162</x:v>
       </x:c>
       <x:c r="B166" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5144,14 +5144,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F166" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G166" s="35" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="H166" s="35" t="str"/>
     </x:row>
-    <x:row r="167" ht="66" hidden="0" customHeight="1">
+    <x:row r="167" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A167" s="26" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -5159,7 +5159,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C167" s="35" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D167" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5168,22 +5168,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F167" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G167" s="35" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="H167" s="35" t="str"/>
     </x:row>
-    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="168" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A168" s="26" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B168" s="35" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C168" s="35" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D168" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5195,19 +5195,19 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G168" s="35" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="H168" s="35" t="str"/>
     </x:row>
-    <x:row r="169" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="169" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A169" s="26" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B169" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C169" s="35" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D169" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5216,22 +5216,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F169" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G169" s="35" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="H169" s="35" t="str"/>
     </x:row>
-    <x:row r="170" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="170" ht="66" hidden="0" customHeight="1">
       <x:c r="A170" s="26" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B170" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C170" s="35" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D170" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5240,10 +5240,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F170" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G170" s="35" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="H170" s="35" t="str"/>
     </x:row>
@@ -5252,10 +5252,10 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B171" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="35" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D171" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5267,19 +5267,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G171" s="35" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="H171" s="35" t="str"/>
     </x:row>
-    <x:row r="172" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="172" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A172" s="26" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C172" s="35" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D172" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5288,22 +5288,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F172" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G172" s="35" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="H172" s="35" t="str"/>
     </x:row>
-    <x:row r="173" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="173" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A173" s="26" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B173" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C173" s="35" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D173" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5312,22 +5312,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F173" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G173" s="35" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="H173" s="35" t="str"/>
     </x:row>
-    <x:row r="174" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="174" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A174" s="26" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C174" s="35" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D174" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5339,19 +5339,19 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G174" s="35" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="H174" s="35" t="str"/>
     </x:row>
-    <x:row r="175" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="175" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A175" s="26" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C175" s="35" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D175" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5360,22 +5360,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F175" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G175" s="35" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="H175" s="35" t="str"/>
     </x:row>
-    <x:row r="176" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="176" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A176" s="26" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C176" s="35" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D176" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5384,10 +5384,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F176" s="32" t="n">
-        <x:v>0.047</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G176" s="35" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="H176" s="35" t="str"/>
     </x:row>
@@ -5399,7 +5399,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C177" s="35" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D177" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5408,22 +5408,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F177" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G177" s="35" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="H177" s="35" t="str"/>
     </x:row>
-    <x:row r="178" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="178" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A178" s="26" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C178" s="35" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D178" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5432,10 +5432,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F178" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G178" s="35" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="H178" s="35" t="str"/>
     </x:row>
@@ -5444,10 +5444,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5456,22 +5456,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F179" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="G179" s="35" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="H179" s="35" t="str"/>
     </x:row>
-    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="180" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A180" s="26" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="35" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C180" s="35" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D180" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5480,22 +5480,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F180" s="32" t="n">
-        <x:v>0.355</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G180" s="35" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="H180" s="35" t="str"/>
     </x:row>
-    <x:row r="181" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="181" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A181" s="26" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C181" s="35" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D181" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5504,10 +5504,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F181" s="32" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G181" s="35" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="H181" s="35" t="str"/>
     </x:row>
@@ -5516,10 +5516,10 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5528,22 +5528,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F182" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G182" s="35" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H182" s="35" t="str"/>
     </x:row>
-    <x:row r="183" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A183" s="26" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5552,22 +5552,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F183" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.181</x:v>
       </x:c>
       <x:c r="G183" s="35" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="H183" s="35" t="str"/>
     </x:row>
-    <x:row r="184" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="184" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A184" s="26" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C184" s="35" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D184" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5576,22 +5576,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F184" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G184" s="35" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="H184" s="35" t="str"/>
     </x:row>
-    <x:row r="185" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="185" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A185" s="26" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C185" s="35" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D185" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5600,10 +5600,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F185" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G185" s="35" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="H185" s="35" t="str"/>
     </x:row>
@@ -5615,7 +5615,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C186" s="35" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D186" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5624,14 +5624,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F186" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G186" s="35" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="H186" s="35" t="str"/>
     </x:row>
-    <x:row r="187" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="187" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A187" s="26" t="n">
         <x:v>183</x:v>
       </x:c>
@@ -5639,7 +5639,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5648,10 +5648,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F187" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G187" s="35" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="H187" s="35" t="str"/>
     </x:row>
@@ -5663,7 +5663,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C188" s="35" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D188" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5672,10 +5672,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F188" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G188" s="35" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="H188" s="35" t="str"/>
     </x:row>
@@ -5687,7 +5687,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5696,10 +5696,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F189" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G189" s="35" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="H189" s="35" t="str"/>
     </x:row>
@@ -5711,7 +5711,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C190" s="35" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D190" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5720,14 +5720,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F190" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G190" s="35" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="H190" s="35" t="str"/>
     </x:row>
-    <x:row r="191" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A191" s="26" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -5735,7 +5735,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5744,14 +5744,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F191" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G191" s="35" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="H191" s="35" t="str"/>
     </x:row>
-    <x:row r="192" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="192" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A192" s="26" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -5759,7 +5759,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="35" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D192" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5768,10 +5768,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F192" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G192" s="35" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="H192" s="35" t="str"/>
     </x:row>
@@ -5783,7 +5783,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="35" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D193" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5792,10 +5792,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F193" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G193" s="35" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="H193" s="35" t="str"/>
     </x:row>
@@ -5807,7 +5807,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5816,14 +5816,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F194" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="G194" s="35" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="H194" s="35" t="str"/>
     </x:row>
-    <x:row r="195" ht="132" hidden="0" customHeight="1">
+    <x:row r="195" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A195" s="26" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -5831,7 +5831,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5840,14 +5840,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F195" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G195" s="35" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="H195" s="35" t="str"/>
     </x:row>
-    <x:row r="196" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="196" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A196" s="26" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -5855,7 +5855,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5864,14 +5864,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F196" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G196" s="35" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="H196" s="35" t="str"/>
     </x:row>
-    <x:row r="197" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="197" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A197" s="26" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -5879,7 +5879,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5891,7 +5891,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G197" s="35" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="H197" s="35" t="str"/>
     </x:row>
@@ -5903,7 +5903,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5912,14 +5912,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F198" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G198" s="35" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="H198" s="35" t="str"/>
     </x:row>
-    <x:row r="199" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="199" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A199" s="26" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -5927,7 +5927,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5936,14 +5936,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F199" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G199" s="35" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="H199" s="35" t="str"/>
     </x:row>
-    <x:row r="200" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="200" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A200" s="26" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -5951,52 +5951,124 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D200" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E200" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F200" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G200" s="35" t="str">
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+      </x:c>
+      <x:c r="H200" s="35" t="str"/>
+    </x:row>
+    <x:row r="201" ht="132" hidden="0" customHeight="1">
+      <x:c r="A201" s="26" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B201" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C201" s="35" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D201" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E201" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F201" s="32" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="G201" s="35" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="H201" s="35" t="str"/>
+    </x:row>
+    <x:row r="202" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A202" s="26" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B202" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C202" s="35" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D202" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E202" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F202" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G202" s="35" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="H202" s="35" t="str"/>
+    </x:row>
+    <x:row r="203" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A203" s="26" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B203" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C203" s="35" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D200" s="35" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E200" s="26" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F200" s="32" t="n">
-        <x:v>0.003</x:v>
-      </x:c>
-      <x:c r="G200" s="35" t="str">
+      <x:c r="D203" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E203" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F203" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G203" s="35" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="H200" s="35" t="str"/>
-    </x:row>
-    <x:row r="201" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A201" s="27" t="n">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B201" s="36" t="str">
+      <x:c r="H203" s="35" t="str"/>
+    </x:row>
+    <x:row r="204" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A204" s="27" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B204" s="36" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C201" s="36" t="str">
+      <x:c r="C204" s="36" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D201" s="36" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E201" s="27" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F201" s="33" t="n">
-        <x:v>0.007</x:v>
-      </x:c>
-      <x:c r="G201" s="36" t="str">
+      <x:c r="D204" s="36" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E204" s="27" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F204" s="33" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="G204" s="36" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="H201" s="36" t="str"/>
+      <x:c r="H204" s="36" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E5:E201">
+  <x:conditionalFormatting sqref="E5:E204">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="错误"/>
@@ -6004,7 +6076,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5ff250144524c8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abbd3b80baa4a1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6111,7 +6183,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I5" s="54" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="J5" s="57" t="str">
         <x:v>已登记</x:v>
@@ -6143,7 +6215,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I6" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J6" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6175,7 +6247,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I7" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="J7" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6207,7 +6279,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I8" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J8" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6239,7 +6311,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I9" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J9" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6271,7 +6343,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I10" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J10" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6303,7 +6375,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I11" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J11" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6335,7 +6407,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I12" s="55" t="n">
-        <x:v>0.206</x:v>
+        <x:v>0.214</x:v>
       </x:c>
       <x:c r="J12" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6367,7 +6439,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I13" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J13" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6399,7 +6471,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I14" s="55" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.053</x:v>
       </x:c>
       <x:c r="J14" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6431,7 +6503,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I15" s="55" t="n">
-        <x:v>0.029</x:v>
+        <x:v>0.036</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6463,7 +6535,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I16" s="55" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="J16" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6495,7 +6567,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I17" s="55" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="J17" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6527,7 +6599,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I18" s="55" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.032</x:v>
       </x:c>
       <x:c r="J18" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6559,7 +6631,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I19" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J19" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6591,7 +6663,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I20" s="55" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="J20" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6623,7 +6695,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I21" s="55" t="n">
-        <x:v>0.029</x:v>
+        <x:v>0.058</x:v>
       </x:c>
       <x:c r="J21" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6655,7 +6727,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I22" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J22" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6687,7 +6759,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I23" s="55" t="n">
-        <x:v>0.026</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="J23" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6751,7 +6823,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I25" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J25" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6815,7 +6887,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I27" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J27" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6847,7 +6919,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I28" s="55" t="n">
-        <x:v>0.109</x:v>
+        <x:v>0.146</x:v>
       </x:c>
       <x:c r="J28" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6879,7 +6951,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I29" s="55" t="n">
-        <x:v>0.088</x:v>
+        <x:v>0.111</x:v>
       </x:c>
       <x:c r="J29" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6911,7 +6983,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I30" s="55" t="n">
-        <x:v>0.081</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="J30" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6943,7 +7015,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I31" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J31" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6975,7 +7047,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I32" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J32" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7039,7 +7111,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I34" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J34" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7199,7 +7271,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I39" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J39" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7327,7 +7399,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I43" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J43" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7359,7 +7431,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I44" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J44" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7391,7 +7463,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I45" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J45" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7455,7 +7527,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I47" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J47" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7487,7 +7559,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I48" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J48" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7519,7 +7591,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I49" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J49" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7551,7 +7623,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I50" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J50" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7583,7 +7655,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I51" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J51" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7711,7 +7783,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I55" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J55" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7743,7 +7815,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I56" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J56" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7775,7 +7847,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I57" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J57" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7807,7 +7879,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I58" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J58" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7903,7 +7975,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I61" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J61" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7967,7 +8039,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I63" s="55" t="n">
-        <x:v>0.081</x:v>
+        <x:v>0.064</x:v>
       </x:c>
       <x:c r="J63" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7999,7 +8071,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I64" s="55" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="J64" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8069,59 +8141,59 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="211.1999969482422" hidden="0" customHeight="1">
+    <x:row r="67" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A67" s="42" t="n">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B67" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense.py</x:v>
       </x:c>
       <x:c r="C67" s="49" t="str">
-        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
+        <x:v>test_dense_index_cache_round_trips_vectors_and_invalidates_changed_corpus</x:v>
       </x:c>
       <x:c r="D67" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E67" s="49" t="str">
-        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
+        <x:v>验证 Dense 向量缓存可以无损加载，并在语料文本、模型或处理版本变化后使用不同指纹。</x:v>
       </x:c>
       <x:c r="F67" s="49" t="str">
-        <x:v>保留集 Recall@5 提升 20 个百分点且 nDCG 为正，但存在 3 个逐题回归，超过最多 2 个的门槛，因此候选晋升和生产默认均保持关闭。</x:v>
+        <x:v>加载向量保持单位长度；变更语料不会错误命中旧缓存。</x:v>
       </x:c>
       <x:c r="G67" s="49" t="str">
-        <x:v>系统可能再次依据开发集拟合晋升，或未经重复验证就直接改动生产检索路径。</x:v>
+        <x:v>陈旧向量可能与当前 Chunk 错位，使评测和生产检索返回不可追踪的错误证据。</x:v>
       </x:c>
       <x:c r="H67" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I67" s="55" t="n">
-        <x:v>61.22</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="J67" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="68" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A68" s="42" t="n">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B68" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense.py</x:v>
       </x:c>
       <x:c r="C68" s="49" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_retriever_reuses_cached_vectors_without_document_embedding</x:v>
       </x:c>
       <x:c r="D68" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E68" s="49" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证缓存命中时 DenseRetriever 不会重新编码全部论文，只对查询生成向量。</x:v>
       </x:c>
       <x:c r="F68" s="49" t="str">
-        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
+        <x:v>构造阶段复用缓存，搜索阶段仅调用一次查询 Embedding。</x:v>
       </x:c>
       <x:c r="G68" s="49" t="str">
-        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
+        <x:v>每次启动仍重复编码 1098 个 Chunk，持久化缓存无法降低冷启动成本。</x:v>
       </x:c>
       <x:c r="H68" s="52" t="str">
         <x:v>通过</x:v>
@@ -8133,65 +8205,65 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="69" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A69" s="42" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_cache_compare.py</x:v>
       </x:c>
       <x:c r="C69" s="49" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_dense_cache_comparison_requires_same_quality_and_faster_warm_build</x:v>
       </x:c>
       <x:c r="D69" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E69" s="49" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
       </x:c>
       <x:c r="F69" s="49" t="str">
-        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
+        <x:v>缓存被确认只改变启动成本，不改变 Recall、MRR、nDCG 或生产开关。</x:v>
       </x:c>
       <x:c r="G69" s="49" t="str">
-        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
+        <x:v>缓存可能悄悄改变排序结果，或速度收益不足却被错误判定为可用。</x:v>
       </x:c>
       <x:c r="H69" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I69" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="J69" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="70" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A70" s="42" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_compare.py</x:v>
       </x:c>
       <x:c r="C70" s="49" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
       </x:c>
       <x:c r="D70" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E70" s="49" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
       </x:c>
       <x:c r="F70" s="49" t="str">
-        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
+        <x:v>保留集 Recall@5 提升 20 个百分点且 nDCG 为正，但存在 3 个逐题回归，超过最多 2 个的门槛，因此候选晋升和生产默认均保持关闭。</x:v>
       </x:c>
       <x:c r="G70" s="49" t="str">
-        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
+        <x:v>系统可能再次依据开发集拟合晋升，或未经重复验证就直接改动生产检索路径。</x:v>
       </x:c>
       <x:c r="H70" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I70" s="55" t="n">
-        <x:v>0.036</x:v>
+        <x:v>64.649</x:v>
       </x:c>
       <x:c r="J70" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8205,57 +8277,57 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C71" s="49" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D71" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E71" s="49" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="F71" s="49" t="str">
-        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
+        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
       </x:c>
       <x:c r="G71" s="49" t="str">
-        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
+        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
       </x:c>
       <x:c r="H71" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I71" s="55" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J71" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="72" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A72" s="42" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C72" s="49" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D72" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E72" s="49" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="F72" s="49" t="str">
-        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
+        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
       </x:c>
       <x:c r="G72" s="49" t="str">
-        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
+        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
       </x:c>
       <x:c r="H72" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I72" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J72" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8266,220 +8338,220 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C73" s="49" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D73" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E73" s="49" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="F73" s="49" t="str">
-        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
+        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
       </x:c>
       <x:c r="G73" s="49" t="str">
-        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
+        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
       </x:c>
       <x:c r="H73" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I73" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="J73" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="132" hidden="0" customHeight="1">
+    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A74" s="42" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" s="49" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C74" s="49" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D74" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E74" s="49" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="F74" s="49" t="str">
-        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
+        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
       </x:c>
       <x:c r="G74" s="49" t="str">
-        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
+        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
       </x:c>
       <x:c r="H74" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I74" s="55" t="n">
-        <x:v>56.235</x:v>
+        <x:v>0.053</x:v>
       </x:c>
       <x:c r="J74" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="132" hidden="0" customHeight="1">
+    <x:row r="75" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A75" s="42" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C75" s="49" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D75" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E75" s="49" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="F75" s="49" t="str">
-        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
+        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
       </x:c>
       <x:c r="G75" s="49" t="str">
-        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
+        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
       </x:c>
       <x:c r="H75" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I75" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J75" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="76" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A76" s="42" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C76" s="49" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D76" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E76" s="49" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="F76" s="49" t="str">
-        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
+        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
       </x:c>
       <x:c r="G76" s="49" t="str">
-        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
+        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
       </x:c>
       <x:c r="H76" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I76" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J76" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="77" ht="132" hidden="0" customHeight="1">
       <x:c r="A77" s="42" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C77" s="49" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D77" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E77" s="49" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="F77" s="49" t="str">
-        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
+        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
       </x:c>
       <x:c r="G77" s="49" t="str">
-        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
+        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
       </x:c>
       <x:c r="H77" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I77" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>48.557</x:v>
       </x:c>
       <x:c r="J77" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="78" ht="132" hidden="0" customHeight="1">
       <x:c r="A78" s="42" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C78" s="49" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D78" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E78" s="49" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="F78" s="49" t="str">
-        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
+        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
       </x:c>
       <x:c r="G78" s="49" t="str">
-        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
+        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
       </x:c>
       <x:c r="H78" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I78" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J78" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="79" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A79" s="42" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C79" s="49" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D79" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E79" s="49" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="F79" s="49" t="str">
-        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
+        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
       </x:c>
       <x:c r="G79" s="49" t="str">
-        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
+        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
       </x:c>
       <x:c r="H79" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I79" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J79" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8490,22 +8562,22 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C80" s="49" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D80" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E80" s="49" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="F80" s="49" t="str">
-        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
+        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
       </x:c>
       <x:c r="G80" s="49" t="str">
-        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
+        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
       </x:c>
       <x:c r="H80" s="52" t="str">
         <x:v>通过</x:v>
@@ -8517,7 +8589,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A81" s="42" t="n">
         <x:v>77</x:v>
       </x:c>
@@ -8525,31 +8597,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C81" s="49" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D81" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E81" s="49" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="F81" s="49" t="str">
-        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
+        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
       </x:c>
       <x:c r="G81" s="49" t="str">
-        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
+        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
       </x:c>
       <x:c r="H81" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I81" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J81" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="132" hidden="0" customHeight="1">
+    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A82" s="42" t="n">
         <x:v>78</x:v>
       </x:c>
@@ -8557,31 +8629,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C82" s="49" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D82" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E82" s="49" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="F82" s="49" t="str">
-        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
+        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
       </x:c>
       <x:c r="G82" s="49" t="str">
-        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
+        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
       </x:c>
       <x:c r="H82" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I82" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J82" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="83" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A83" s="42" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -8589,31 +8661,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C83" s="49" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D83" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E83" s="49" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="F83" s="49" t="str">
-        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
+        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
       </x:c>
       <x:c r="G83" s="49" t="str">
-        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
+        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
       </x:c>
       <x:c r="H83" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I83" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J83" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="84" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A84" s="42" t="n">
         <x:v>80</x:v>
       </x:c>
@@ -8621,127 +8693,127 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C84" s="49" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D84" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E84" s="49" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="F84" s="49" t="str">
-        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
+        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
       </x:c>
       <x:c r="G84" s="49" t="str">
-        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
+        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
       </x:c>
       <x:c r="H84" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I84" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J84" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="85" ht="132" hidden="0" customHeight="1">
       <x:c r="A85" s="42" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C85" s="49" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D85" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E85" s="49" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="F85" s="49" t="str">
-        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
+        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
       </x:c>
       <x:c r="G85" s="49" t="str">
-        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
+        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
       </x:c>
       <x:c r="H85" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I85" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J85" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="132" hidden="0" customHeight="1">
+    <x:row r="86" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A86" s="42" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="49" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D86" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E86" s="49" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="F86" s="49" t="str">
-        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
+        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
       </x:c>
       <x:c r="G86" s="49" t="str">
-        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
+        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
       </x:c>
       <x:c r="H86" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I86" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J86" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="132" hidden="0" customHeight="1">
+    <x:row r="87" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A87" s="42" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="49" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D87" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E87" s="49" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="F87" s="49" t="str">
-        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
+        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
       </x:c>
       <x:c r="G87" s="49" t="str">
-        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
+        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
       </x:c>
       <x:c r="H87" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I87" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J87" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="88" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A88" s="42" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -8749,31 +8821,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C88" s="49" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D88" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E88" s="49" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="F88" s="49" t="str">
-        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
+        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
       </x:c>
       <x:c r="G88" s="49" t="str">
-        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
+        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
       </x:c>
       <x:c r="H88" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I88" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J88" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="89" ht="132" hidden="0" customHeight="1">
       <x:c r="A89" s="42" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -8781,31 +8853,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C89" s="49" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D89" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E89" s="49" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="F89" s="49" t="str">
-        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
+        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
       </x:c>
       <x:c r="G89" s="49" t="str">
-        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
+        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
       </x:c>
       <x:c r="H89" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I89" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J89" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="90" ht="132" hidden="0" customHeight="1">
       <x:c r="A90" s="42" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -8813,31 +8885,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C90" s="49" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D90" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E90" s="49" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="F90" s="49" t="str">
-        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
+        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
       </x:c>
       <x:c r="G90" s="49" t="str">
-        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
+        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
       </x:c>
       <x:c r="H90" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I90" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J90" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="91" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A91" s="42" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -8845,57 +8917,57 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C91" s="49" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D91" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E91" s="49" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="F91" s="49" t="str">
-        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
+        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
       </x:c>
       <x:c r="G91" s="49" t="str">
-        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
+        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
       </x:c>
       <x:c r="H91" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I91" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J91" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="92" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A92" s="42" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" s="49" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C92" s="49" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D92" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E92" s="49" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="F92" s="49" t="str">
-        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
+        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
       </x:c>
       <x:c r="G92" s="49" t="str">
-        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
+        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
       </x:c>
       <x:c r="H92" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I92" s="55" t="n">
-        <x:v>2.385</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J92" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8906,92 +8978,92 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B93" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="49" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D93" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E93" s="49" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="F93" s="49" t="str">
-        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
+        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
       </x:c>
       <x:c r="G93" s="49" t="str">
-        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
+        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
       </x:c>
       <x:c r="H93" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I93" s="55" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J93" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="94" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A94" s="42" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B94" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="49" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D94" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E94" s="49" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="F94" s="49" t="str">
-        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
+        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
       </x:c>
       <x:c r="G94" s="49" t="str">
-        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
+        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
       </x:c>
       <x:c r="H94" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I94" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J94" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="95" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A95" s="42" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C95" s="49" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D95" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E95" s="49" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="F95" s="49" t="str">
-        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
+        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
       </x:c>
       <x:c r="G95" s="49" t="str">
-        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
+        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
       </x:c>
       <x:c r="H95" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I95" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>2.365</x:v>
       </x:c>
       <x:c r="J95" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9005,25 +9077,25 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C96" s="49" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D96" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E96" s="49" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="F96" s="49" t="str">
-        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
+        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
       </x:c>
       <x:c r="G96" s="49" t="str">
-        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
+        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
       </x:c>
       <x:c r="H96" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I96" s="55" t="n">
-        <x:v>1.213</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="J96" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9034,98 +9106,98 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C97" s="49" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D97" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E97" s="49" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="F97" s="49" t="str">
-        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
+        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
       </x:c>
       <x:c r="G97" s="49" t="str">
-        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
+        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
       </x:c>
       <x:c r="H97" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I97" s="55" t="n">
-        <x:v>0.211</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J97" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="98" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A98" s="42" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C98" s="49" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D98" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E98" s="49" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="F98" s="49" t="str">
-        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
+        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
       </x:c>
       <x:c r="G98" s="49" t="str">
-        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
+        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
       </x:c>
       <x:c r="H98" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I98" s="55" t="n">
-        <x:v>0.114</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J98" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="99" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A99" s="42" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B99" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C99" s="49" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D99" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E99" s="49" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="F99" s="49" t="str">
-        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
+        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
       </x:c>
       <x:c r="G99" s="49" t="str">
-        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
+        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
       </x:c>
       <x:c r="H99" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I99" s="55" t="n">
-        <x:v>0.057</x:v>
+        <x:v>1.156</x:v>
       </x:c>
       <x:c r="J99" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="100" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A100" s="42" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -9133,57 +9205,57 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C100" s="49" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D100" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E100" s="49" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="F100" s="49" t="str">
-        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
+        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
       </x:c>
       <x:c r="G100" s="49" t="str">
-        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
+        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
       </x:c>
       <x:c r="H100" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I100" s="55" t="n">
-        <x:v>0.096</x:v>
+        <x:v>0.196</x:v>
       </x:c>
       <x:c r="J100" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="132" hidden="0" customHeight="1">
+    <x:row r="101" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A101" s="42" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="49" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C101" s="49" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D101" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E101" s="49" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="F101" s="49" t="str">
-        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
+        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
       </x:c>
       <x:c r="G101" s="49" t="str">
-        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
+        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
       </x:c>
       <x:c r="H101" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I101" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.088</x:v>
       </x:c>
       <x:c r="J101" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9194,98 +9266,98 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C102" s="49" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D102" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E102" s="49" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="F102" s="49" t="str">
-        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
+        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
       </x:c>
       <x:c r="G102" s="49" t="str">
-        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
+        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
       </x:c>
       <x:c r="H102" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I102" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="J102" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="103" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A103" s="42" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C103" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D103" s="49" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E103" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="F103" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
       </x:c>
       <x:c r="G103" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
       </x:c>
       <x:c r="H103" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I103" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="J103" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="104" ht="132" hidden="0" customHeight="1">
       <x:c r="A104" s="42" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C104" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D104" s="49" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E104" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="F104" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
       </x:c>
       <x:c r="G104" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
       </x:c>
       <x:c r="H104" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I104" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J104" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="105" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A105" s="42" t="n">
         <x:v>101</x:v>
       </x:c>
@@ -9293,25 +9365,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C105" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D105" s="49" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E105" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="F105" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
       </x:c>
       <x:c r="G105" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
       </x:c>
       <x:c r="H105" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I105" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J105" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9325,10 +9397,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C106" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D106" s="49" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E106" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9343,7 +9415,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I106" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J106" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9357,10 +9429,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C107" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D107" s="49" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E107" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9375,13 +9447,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I107" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J107" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="108" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A108" s="42" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -9389,19 +9461,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C108" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D108" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E108" s="49" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F108" s="49" t="str">
-        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G108" s="49" t="str">
-        <x:v>查询改写异常可能导致完全不检索。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H108" s="52" t="str">
         <x:v>通过</x:v>
@@ -9421,25 +9493,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C109" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D109" s="49" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E109" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F109" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G109" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H109" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I109" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J109" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9453,31 +9525,31 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D110" s="49" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E110" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F110" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G110" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H110" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I110" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J110" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="111" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A111" s="42" t="n">
         <x:v>107</x:v>
       </x:c>
@@ -9485,25 +9557,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D111" s="49" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E111" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="F111" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
       </x:c>
       <x:c r="G111" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>查询改写异常可能导致完全不检索。</x:v>
       </x:c>
       <x:c r="H111" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I111" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J111" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9517,10 +9589,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D112" s="49" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E112" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9535,7 +9607,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I112" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J112" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9549,10 +9621,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D113" s="49" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E113" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9567,7 +9639,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I113" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J113" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9581,10 +9653,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D114" s="49" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E114" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9599,13 +9671,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I114" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J114" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="115" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A115" s="42" t="n">
         <x:v>111</x:v>
       </x:c>
@@ -9613,25 +9685,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="49" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D115" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E115" s="49" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F115" s="49" t="str">
-        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G115" s="49" t="str">
-        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H115" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I115" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J115" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9645,25 +9717,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="49" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D116" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E116" s="49" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F116" s="49" t="str">
-        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G116" s="49" t="str">
-        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H116" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I116" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J116" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9674,54 +9746,54 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B117" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="49" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D117" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E117" s="49" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F117" s="49" t="str">
-        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G117" s="49" t="str">
-        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H117" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I117" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J117" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="118" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A118" s="42" t="n">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B118" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="49" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D118" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E118" s="49" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="F118" s="49" t="str">
-        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
+        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
       </x:c>
       <x:c r="G118" s="49" t="str">
-        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
+        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
       </x:c>
       <x:c r="H118" s="52" t="str">
         <x:v>通过</x:v>
@@ -9733,39 +9805,39 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="132" hidden="0" customHeight="1">
+    <x:row r="119" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A119" s="42" t="n">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B119" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="49" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D119" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E119" s="49" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="F119" s="49" t="str">
-        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
+        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
       </x:c>
       <x:c r="G119" s="49" t="str">
-        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
+        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
       </x:c>
       <x:c r="H119" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I119" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J119" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="120" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A120" s="42" t="n">
         <x:v>116</x:v>
       </x:c>
@@ -9773,19 +9845,19 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C120" s="49" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D120" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E120" s="49" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="F120" s="49" t="str">
-        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
+        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
       </x:c>
       <x:c r="G120" s="49" t="str">
-        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
+        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
       </x:c>
       <x:c r="H120" s="52" t="str">
         <x:v>通过</x:v>
@@ -9797,97 +9869,97 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="132" hidden="0" customHeight="1">
+    <x:row r="121" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A121" s="42" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B121" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C121" s="49" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D121" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E121" s="49" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="F121" s="49" t="str">
-        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
+        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
       </x:c>
       <x:c r="G121" s="49" t="str">
-        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
+        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
       </x:c>
       <x:c r="H121" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I121" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J121" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="122" ht="132" hidden="0" customHeight="1">
       <x:c r="A122" s="42" t="n">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B122" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C122" s="49" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D122" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E122" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="F122" s="49" t="str">
-        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
+        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
       </x:c>
       <x:c r="G122" s="49" t="str">
-        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
+        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
       </x:c>
       <x:c r="H122" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I122" s="55" t="n">
-        <x:v>32.086</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J122" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="123" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A123" s="42" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B123" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C123" s="49" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D123" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E123" s="49" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="F123" s="49" t="str">
-        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
+        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
       </x:c>
       <x:c r="G123" s="49" t="str">
-        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
+        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
       </x:c>
       <x:c r="H123" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I123" s="55" t="n">
-        <x:v>31.47</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J123" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9898,124 +9970,124 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C124" s="49" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D124" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E124" s="49" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="F124" s="49" t="str">
-        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
+        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
       </x:c>
       <x:c r="G124" s="49" t="str">
-        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
+        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
       </x:c>
       <x:c r="H124" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I124" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J124" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A125" s="42" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C125" s="49" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D125" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E125" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="F125" s="49" t="str">
-        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
+        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
       </x:c>
       <x:c r="G125" s="49" t="str">
-        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
+        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
       </x:c>
       <x:c r="H125" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I125" s="55" t="n">
-        <x:v>38.108</x:v>
+        <x:v>15.585</x:v>
       </x:c>
       <x:c r="J125" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="126" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A126" s="42" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C126" s="49" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D126" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E126" s="49" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="F126" s="49" t="str">
-        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
+        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
       </x:c>
       <x:c r="G126" s="49" t="str">
-        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
+        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
       </x:c>
       <x:c r="H126" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I126" s="55" t="n">
-        <x:v>30.793</x:v>
+        <x:v>15.492</x:v>
       </x:c>
       <x:c r="J126" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="127" ht="132" hidden="0" customHeight="1">
       <x:c r="A127" s="42" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C127" s="49" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D127" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E127" s="49" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="F127" s="49" t="str">
-        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
+        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
       </x:c>
       <x:c r="G127" s="49" t="str">
-        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
+        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
       </x:c>
       <x:c r="H127" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I127" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J127" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10026,66 +10098,66 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C128" s="49" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D128" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E128" s="49" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="F128" s="49" t="str">
-        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
+        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
       </x:c>
       <x:c r="G128" s="49" t="str">
-        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
+        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
       </x:c>
       <x:c r="H128" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I128" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>19.508</x:v>
       </x:c>
       <x:c r="J128" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="129" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A129" s="42" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="49" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D129" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E129" s="49" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="F129" s="49" t="str">
-        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
+        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
       </x:c>
       <x:c r="G129" s="49" t="str">
-        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
+        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
       </x:c>
       <x:c r="H129" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I129" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>15.364</x:v>
       </x:c>
       <x:c r="J129" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="130" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A130" s="42" t="n">
         <x:v>126</x:v>
       </x:c>
@@ -10093,31 +10165,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C130" s="49" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D130" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E130" s="49" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="F130" s="49" t="str">
-        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
+        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
       </x:c>
       <x:c r="G130" s="49" t="str">
-        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
+        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
       </x:c>
       <x:c r="H130" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I130" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J130" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="131" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A131" s="42" t="n">
         <x:v>127</x:v>
       </x:c>
@@ -10125,31 +10197,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C131" s="49" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D131" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E131" s="49" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="F131" s="49" t="str">
-        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
+        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
       </x:c>
       <x:c r="G131" s="49" t="str">
-        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
+        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
       </x:c>
       <x:c r="H131" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I131" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J131" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="132" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A132" s="42" t="n">
         <x:v>128</x:v>
       </x:c>
@@ -10157,19 +10229,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C132" s="49" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D132" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E132" s="49" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="F132" s="49" t="str">
-        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
+        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
       </x:c>
       <x:c r="G132" s="49" t="str">
-        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
+        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
       </x:c>
       <x:c r="H132" s="52" t="str">
         <x:v>通过</x:v>
@@ -10181,7 +10253,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="133" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A133" s="42" t="n">
         <x:v>129</x:v>
       </x:c>
@@ -10189,25 +10261,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C133" s="49" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D133" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E133" s="49" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="F133" s="49" t="str">
-        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
+        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
       </x:c>
       <x:c r="G133" s="49" t="str">
-        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
+        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
       </x:c>
       <x:c r="H133" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I133" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J133" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10221,19 +10293,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C134" s="49" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D134" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E134" s="49" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="F134" s="49" t="str">
-        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
+        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
       </x:c>
       <x:c r="G134" s="49" t="str">
-        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
+        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
       </x:c>
       <x:c r="H134" s="52" t="str">
         <x:v>通过</x:v>
@@ -10245,7 +10317,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="135" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A135" s="42" t="n">
         <x:v>131</x:v>
       </x:c>
@@ -10253,31 +10325,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D135" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E135" s="49" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="F135" s="49" t="str">
-        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
+        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
       </x:c>
       <x:c r="G135" s="49" t="str">
-        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
+        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
       </x:c>
       <x:c r="H135" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I135" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J135" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="132" hidden="0" customHeight="1">
+    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A136" s="42" t="n">
         <x:v>132</x:v>
       </x:c>
@@ -10285,25 +10357,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D136" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E136" s="49" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="F136" s="49" t="str">
-        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
+        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
       </x:c>
       <x:c r="G136" s="49" t="str">
-        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
+        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
       </x:c>
       <x:c r="H136" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I136" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J136" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10317,19 +10389,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="49" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D137" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E137" s="49" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="F137" s="49" t="str">
-        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
+        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
       </x:c>
       <x:c r="G137" s="49" t="str">
-        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
+        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
       </x:c>
       <x:c r="H137" s="52" t="str">
         <x:v>通过</x:v>
@@ -10349,31 +10421,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="49" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D138" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E138" s="49" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="F138" s="49" t="str">
-        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
+        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
       </x:c>
       <x:c r="G138" s="49" t="str">
-        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
+        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
       </x:c>
       <x:c r="H138" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I138" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J138" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="139" ht="132" hidden="0" customHeight="1">
       <x:c r="A139" s="42" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -10381,89 +10453,89 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="49" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D139" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E139" s="49" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="F139" s="49" t="str">
-        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
+        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
       </x:c>
       <x:c r="G139" s="49" t="str">
-        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
+        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
       </x:c>
       <x:c r="H139" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I139" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J139" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A140" s="42" t="n">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B140" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="49" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D140" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E140" s="49" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="F140" s="49" t="str">
-        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
+        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
       </x:c>
       <x:c r="G140" s="49" t="str">
-        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
+        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
       </x:c>
       <x:c r="H140" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I140" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J140" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="141" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A141" s="42" t="n">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B141" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="49" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D141" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E141" s="49" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="F141" s="49" t="str">
-        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
+        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
       </x:c>
       <x:c r="G141" s="49" t="str">
-        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
+        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
       </x:c>
       <x:c r="H141" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I141" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J141" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10474,34 +10546,34 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B142" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D142" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E142" s="49" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="F142" s="49" t="str">
-        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
+        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
       </x:c>
       <x:c r="G142" s="49" t="str">
-        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
+        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
       </x:c>
       <x:c r="H142" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I142" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J142" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A143" s="42" t="n">
         <x:v>139</x:v>
       </x:c>
@@ -10509,19 +10581,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C143" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D143" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E143" s="49" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="F143" s="49" t="str">
-        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
+        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
       </x:c>
       <x:c r="G143" s="49" t="str">
-        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
+        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
       </x:c>
       <x:c r="H143" s="52" t="str">
         <x:v>通过</x:v>
@@ -10541,25 +10613,25 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C144" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D144" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E144" s="49" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="F144" s="49" t="str">
-        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
+        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
       </x:c>
       <x:c r="G144" s="49" t="str">
-        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
+        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
       </x:c>
       <x:c r="H144" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I144" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J144" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10573,31 +10645,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C145" s="49" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D145" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E145" s="49" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="F145" s="49" t="str">
-        <x:v>两条无去重键文档均被保留。</x:v>
+        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
       </x:c>
       <x:c r="G145" s="49" t="str">
-        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
+        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
       </x:c>
       <x:c r="H145" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I145" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J145" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A146" s="42" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -10605,31 +10677,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C146" s="49" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D146" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E146" s="49" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="F146" s="49" t="str">
-        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
+        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
       </x:c>
       <x:c r="G146" s="49" t="str">
-        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
+        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
       </x:c>
       <x:c r="H146" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I146" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J146" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A147" s="42" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -10637,57 +10709,57 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C147" s="49" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D147" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E147" s="49" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="F147" s="49" t="str">
-        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
+        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
       </x:c>
       <x:c r="G147" s="49" t="str">
-        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
+        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
       </x:c>
       <x:c r="H147" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I147" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J147" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="148" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A148" s="42" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B148" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="49" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D148" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E148" s="49" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="F148" s="49" t="str">
-        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
+        <x:v>两条无去重键文档均被保留。</x:v>
       </x:c>
       <x:c r="G148" s="49" t="str">
-        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
+        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
       </x:c>
       <x:c r="H148" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I148" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J148" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10698,54 +10770,54 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B149" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="49" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D149" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E149" s="49" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="F149" s="49" t="str">
-        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
+        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
       </x:c>
       <x:c r="G149" s="49" t="str">
-        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
+        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
       </x:c>
       <x:c r="H149" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I149" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J149" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="150" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A150" s="42" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B150" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="49" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D150" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E150" s="49" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="F150" s="49" t="str">
-        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
+        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
       </x:c>
       <x:c r="G150" s="49" t="str">
-        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
+        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
       </x:c>
       <x:c r="H150" s="52" t="str">
         <x:v>通过</x:v>
@@ -10757,7 +10829,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="132" hidden="0" customHeight="1">
+    <x:row r="151" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A151" s="42" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -10765,31 +10837,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C151" s="49" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D151" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E151" s="49" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="F151" s="49" t="str">
-        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
+        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
       </x:c>
       <x:c r="G151" s="49" t="str">
-        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
+        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
       </x:c>
       <x:c r="H151" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I151" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J151" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="132" hidden="0" customHeight="1">
+    <x:row r="152" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A152" s="42" t="n">
         <x:v>148</x:v>
       </x:c>
@@ -10797,31 +10869,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C152" s="49" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D152" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E152" s="49" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="F152" s="49" t="str">
-        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
+        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
       </x:c>
       <x:c r="G152" s="49" t="str">
-        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
+        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
       </x:c>
       <x:c r="H152" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I152" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J152" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A153" s="42" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -10829,31 +10901,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C153" s="49" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D153" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E153" s="49" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="F153" s="49" t="str">
-        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
+        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
       </x:c>
       <x:c r="G153" s="49" t="str">
-        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
+        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
       </x:c>
       <x:c r="H153" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I153" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J153" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="154" ht="132" hidden="0" customHeight="1">
       <x:c r="A154" s="42" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -10861,31 +10933,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C154" s="49" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D154" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E154" s="49" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="F154" s="49" t="str">
-        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
+        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
       </x:c>
       <x:c r="G154" s="49" t="str">
-        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
+        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
       </x:c>
       <x:c r="H154" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I154" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J154" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="155" ht="132" hidden="0" customHeight="1">
       <x:c r="A155" s="42" t="n">
         <x:v>151</x:v>
       </x:c>
@@ -10893,31 +10965,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C155" s="49" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D155" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E155" s="49" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="F155" s="49" t="str">
-        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
+        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
       </x:c>
       <x:c r="G155" s="49" t="str">
-        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
+        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
       </x:c>
       <x:c r="H155" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I155" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J155" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="156" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A156" s="42" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -10925,31 +10997,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="49" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D156" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E156" s="49" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="F156" s="49" t="str">
-        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
+        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
       </x:c>
       <x:c r="G156" s="49" t="str">
-        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
+        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
       </x:c>
       <x:c r="H156" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I156" s="55" t="n">
-        <x:v>0.149</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J156" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="157" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A157" s="42" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -10957,31 +11029,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="49" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D157" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E157" s="49" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F157" s="49" t="str">
-        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
+        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
       </x:c>
       <x:c r="G157" s="49" t="str">
-        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
+        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
       </x:c>
       <x:c r="H157" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I157" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J157" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="158" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A158" s="42" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -10989,31 +11061,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="49" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D158" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E158" s="49" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="F158" s="49" t="str">
-        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
+        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
       </x:c>
       <x:c r="G158" s="49" t="str">
-        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
+        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
       </x:c>
       <x:c r="H158" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I158" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J158" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="159" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A159" s="42" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -11021,31 +11093,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="49" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D159" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E159" s="49" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="F159" s="49" t="str">
-        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
+        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
       </x:c>
       <x:c r="G159" s="49" t="str">
-        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
+        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
       </x:c>
       <x:c r="H159" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I159" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="J159" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="132" hidden="0" customHeight="1">
+    <x:row r="160" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A160" s="42" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -11053,31 +11125,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="49" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D160" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E160" s="49" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="F160" s="49" t="str">
-        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
+        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
       </x:c>
       <x:c r="G160" s="49" t="str">
-        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
+        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
       </x:c>
       <x:c r="H160" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I160" s="55" t="n">
-        <x:v>0.218</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J160" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="161" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A161" s="42" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -11085,31 +11157,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="49" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D161" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E161" s="49" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="F161" s="49" t="str">
-        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
+        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
       </x:c>
       <x:c r="G161" s="49" t="str">
-        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
+        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
       </x:c>
       <x:c r="H161" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I161" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="J161" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="162" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A162" s="42" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -11117,31 +11189,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="49" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D162" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E162" s="49" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="F162" s="49" t="str">
-        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
+        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
       </x:c>
       <x:c r="G162" s="49" t="str">
-        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
+        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
       </x:c>
       <x:c r="H162" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I162" s="55" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J162" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="163" ht="132" hidden="0" customHeight="1">
       <x:c r="A163" s="42" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -11149,89 +11221,89 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="49" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D163" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E163" s="49" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="F163" s="49" t="str">
-        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
+        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
       </x:c>
       <x:c r="G163" s="49" t="str">
-        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
+        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
       </x:c>
       <x:c r="H163" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I163" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.164</x:v>
       </x:c>
       <x:c r="J163" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="164" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A164" s="42" t="n">
         <x:v>160</x:v>
       </x:c>
       <x:c r="B164" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="49" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D164" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E164" s="49" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="F164" s="49" t="str">
-        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
+        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
       </x:c>
       <x:c r="G164" s="49" t="str">
-        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
+        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
       </x:c>
       <x:c r="H164" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I164" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J164" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A165" s="42" t="n">
         <x:v>161</x:v>
       </x:c>
       <x:c r="B165" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="49" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D165" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E165" s="49" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="F165" s="49" t="str">
-        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
+        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
       </x:c>
       <x:c r="G165" s="49" t="str">
-        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
+        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
       </x:c>
       <x:c r="H165" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I165" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J165" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11242,34 +11314,34 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="B166" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="49" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D166" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E166" s="49" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="F166" s="49" t="str">
-        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
+        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
       </x:c>
       <x:c r="G166" s="49" t="str">
-        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
+        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
       </x:c>
       <x:c r="H166" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I166" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J166" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="167" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A167" s="42" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -11277,51 +11349,51 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C167" s="49" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D167" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E167" s="49" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="F167" s="49" t="str">
-        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
+        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
       </x:c>
       <x:c r="G167" s="49" t="str">
-        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
+        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
       </x:c>
       <x:c r="H167" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I167" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J167" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A168" s="42" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B168" s="49" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C168" s="49" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D168" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E168" s="49" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="F168" s="49" t="str">
-        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
+        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
       </x:c>
       <x:c r="G168" s="49" t="str">
-        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
+        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
       </x:c>
       <x:c r="H168" s="52" t="str">
         <x:v>通过</x:v>
@@ -11338,86 +11410,86 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B169" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C169" s="49" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D169" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E169" s="49" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="F169" s="49" t="str">
-        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
+        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
       </x:c>
       <x:c r="G169" s="49" t="str">
-        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
+        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
       </x:c>
       <x:c r="H169" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I169" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J169" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="170" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A170" s="42" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B170" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C170" s="49" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D170" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E170" s="49" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="F170" s="49" t="str">
-        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
+        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
       </x:c>
       <x:c r="G170" s="49" t="str">
-        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
+        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
       </x:c>
       <x:c r="H170" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I170" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J170" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="171" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A171" s="42" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B171" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="49" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D171" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E171" s="49" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="F171" s="49" t="str">
-        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
+        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
       </x:c>
       <x:c r="G171" s="49" t="str">
-        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
+        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
       </x:c>
       <x:c r="H171" s="52" t="str">
         <x:v>通过</x:v>
@@ -11434,60 +11506,60 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C172" s="49" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D172" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E172" s="49" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="F172" s="49" t="str">
-        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
+        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
       </x:c>
       <x:c r="G172" s="49" t="str">
-        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
+        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
       </x:c>
       <x:c r="H172" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I172" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J172" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="173" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A173" s="42" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B173" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C173" s="49" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D173" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E173" s="49" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="F173" s="49" t="str">
-        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
+        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
       </x:c>
       <x:c r="G173" s="49" t="str">
-        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
+        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
       </x:c>
       <x:c r="H173" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I173" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J173" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11498,22 +11570,22 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C174" s="49" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D174" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E174" s="49" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="F174" s="49" t="str">
-        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
+        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
       </x:c>
       <x:c r="G174" s="49" t="str">
-        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
+        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
       </x:c>
       <x:c r="H174" s="52" t="str">
         <x:v>通过</x:v>
@@ -11525,33 +11597,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="175" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A175" s="42" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C175" s="49" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D175" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E175" s="49" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="F175" s="49" t="str">
-        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
+        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
       </x:c>
       <x:c r="G175" s="49" t="str">
-        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
+        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
       </x:c>
       <x:c r="H175" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I175" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J175" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11562,34 +11634,34 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C176" s="49" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D176" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E176" s="49" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="F176" s="49" t="str">
-        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
+        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
       </x:c>
       <x:c r="G176" s="49" t="str">
-        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
+        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
       </x:c>
       <x:c r="H176" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I176" s="55" t="n">
-        <x:v>0.047</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J176" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="177" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A177" s="42" t="n">
         <x:v>173</x:v>
       </x:c>
@@ -11597,57 +11669,57 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C177" s="49" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D177" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E177" s="49" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="F177" s="49" t="str">
-        <x:v>单子查询继续走直接调用路径。</x:v>
+        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
       </x:c>
       <x:c r="G177" s="49" t="str">
-        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
+        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
       </x:c>
       <x:c r="H177" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I177" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J177" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="178" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A178" s="42" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C178" s="49" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D178" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E178" s="49" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="F178" s="49" t="str">
-        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
+        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
       </x:c>
       <x:c r="G178" s="49" t="str">
-        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
+        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
       </x:c>
       <x:c r="H178" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I178" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J178" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11658,226 +11730,226 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C179" s="49" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D179" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E179" s="49" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="F179" s="49" t="str">
-        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
+        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
       </x:c>
       <x:c r="G179" s="49" t="str">
-        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
+        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
       </x:c>
       <x:c r="H179" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I179" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="J179" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="180" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A180" s="42" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="49" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C180" s="49" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D180" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E180" s="49" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="F180" s="49" t="str">
-        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
+        <x:v>单子查询继续走直接调用路径。</x:v>
       </x:c>
       <x:c r="G180" s="49" t="str">
-        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
+        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
       </x:c>
       <x:c r="H180" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I180" s="55" t="n">
-        <x:v>0.355</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J180" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="181" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A181" s="42" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C181" s="49" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D181" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E181" s="49" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="F181" s="49" t="str">
-        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
+        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
       </x:c>
       <x:c r="G181" s="49" t="str">
-        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
+        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
       </x:c>
       <x:c r="H181" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I181" s="55" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J181" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="132" hidden="0" customHeight="1">
+    <x:row r="182" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A182" s="42" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C182" s="49" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D182" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E182" s="49" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F182" s="49" t="str">
-        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
+        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
       </x:c>
       <x:c r="G182" s="49" t="str">
-        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
+        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
       </x:c>
       <x:c r="H182" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I182" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J182" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="132" hidden="0" customHeight="1">
+    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A183" s="42" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C183" s="49" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D183" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E183" s="49" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="F183" s="49" t="str">
-        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
+        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
       </x:c>
       <x:c r="G183" s="49" t="str">
-        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
+        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
       </x:c>
       <x:c r="H183" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I183" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.181</x:v>
       </x:c>
       <x:c r="J183" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A184" s="42" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C184" s="49" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D184" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E184" s="49" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="F184" s="49" t="str">
-        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
+        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
       </x:c>
       <x:c r="G184" s="49" t="str">
-        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
+        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
       </x:c>
       <x:c r="H184" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I184" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J184" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="185" ht="132" hidden="0" customHeight="1">
       <x:c r="A185" s="42" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C185" s="49" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D185" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E185" s="49" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="F185" s="49" t="str">
-        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
+        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
       </x:c>
       <x:c r="G185" s="49" t="str">
-        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
+        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
       </x:c>
       <x:c r="H185" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I185" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J185" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="186" ht="132" hidden="0" customHeight="1">
       <x:c r="A186" s="42" t="n">
         <x:v>182</x:v>
       </x:c>
@@ -11885,31 +11957,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C186" s="49" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D186" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E186" s="49" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="F186" s="49" t="str">
-        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
+        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
       </x:c>
       <x:c r="G186" s="49" t="str">
-        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
+        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
       </x:c>
       <x:c r="H186" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I186" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J186" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="187" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A187" s="42" t="n">
         <x:v>183</x:v>
       </x:c>
@@ -11917,25 +11989,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C187" s="49" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D187" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E187" s="49" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="F187" s="49" t="str">
-        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
+        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
       </x:c>
       <x:c r="G187" s="49" t="str">
-        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
+        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
       </x:c>
       <x:c r="H187" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I187" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J187" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11949,25 +12021,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C188" s="49" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D188" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E188" s="49" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="F188" s="49" t="str">
-        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
+        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
       </x:c>
       <x:c r="G188" s="49" t="str">
-        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
+        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
       </x:c>
       <x:c r="H188" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I188" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J188" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11981,31 +12053,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C189" s="49" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D189" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E189" s="49" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="F189" s="49" t="str">
-        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
+        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
       </x:c>
       <x:c r="G189" s="49" t="str">
-        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
+        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
       </x:c>
       <x:c r="H189" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I189" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J189" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="190" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A190" s="42" t="n">
         <x:v>186</x:v>
       </x:c>
@@ -12013,31 +12085,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C190" s="49" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D190" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E190" s="49" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="F190" s="49" t="str">
-        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
+        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
       </x:c>
       <x:c r="G190" s="49" t="str">
-        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
+        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
       </x:c>
       <x:c r="H190" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I190" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J190" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A191" s="42" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -12045,31 +12117,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="49" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D191" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E191" s="49" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="F191" s="49" t="str">
-        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
+        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
       </x:c>
       <x:c r="G191" s="49" t="str">
-        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
+        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
       </x:c>
       <x:c r="H191" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I191" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J191" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="192" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A192" s="42" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -12077,31 +12149,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="49" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D192" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E192" s="49" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="F192" s="49" t="str">
-        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
+        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
       </x:c>
       <x:c r="G192" s="49" t="str">
-        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
+        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
       </x:c>
       <x:c r="H192" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I192" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J192" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A193" s="42" t="n">
         <x:v>189</x:v>
       </x:c>
@@ -12109,25 +12181,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="49" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D193" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E193" s="49" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="F193" s="49" t="str">
-        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
+        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
       </x:c>
       <x:c r="G193" s="49" t="str">
-        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
+        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
       </x:c>
       <x:c r="H193" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I193" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J193" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12141,31 +12213,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="49" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D194" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E194" s="49" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="F194" s="49" t="str">
-        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
+        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
       </x:c>
       <x:c r="G194" s="49" t="str">
-        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
+        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
       </x:c>
       <x:c r="H194" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I194" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="J194" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="132" hidden="0" customHeight="1">
+    <x:row r="195" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A195" s="42" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -12173,31 +12245,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="49" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D195" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E195" s="49" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="F195" s="49" t="str">
-        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
+        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
       </x:c>
       <x:c r="G195" s="49" t="str">
-        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
+        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
       </x:c>
       <x:c r="H195" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I195" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J195" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="196" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A196" s="42" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -12205,31 +12277,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="49" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D196" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E196" s="49" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="F196" s="49" t="str">
-        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
+        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
       </x:c>
       <x:c r="G196" s="49" t="str">
-        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
+        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
       </x:c>
       <x:c r="H196" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I196" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J196" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="197" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A197" s="42" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -12237,19 +12309,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="49" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D197" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E197" s="49" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="F197" s="49" t="str">
-        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
       </x:c>
       <x:c r="G197" s="49" t="str">
-        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
       </x:c>
       <x:c r="H197" s="52" t="str">
         <x:v>通过</x:v>
@@ -12269,31 +12341,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="49" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D198" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E198" s="49" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="F198" s="49" t="str">
-        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
       </x:c>
       <x:c r="G198" s="49" t="str">
-        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
       </x:c>
       <x:c r="H198" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I198" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J198" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="199" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A199" s="42" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -12301,31 +12373,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="49" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D199" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E199" s="49" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="F199" s="49" t="str">
-        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G199" s="49" t="str">
-        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
       </x:c>
       <x:c r="H199" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I199" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J199" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="200" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A200" s="42" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -12333,59 +12405,155 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="49" t="str">
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D200" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E200" s="49" t="str">
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+      </x:c>
+      <x:c r="F200" s="49" t="str">
+        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+      </x:c>
+      <x:c r="G200" s="49" t="str">
+        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+      </x:c>
+      <x:c r="H200" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I200" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J200" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" ht="132" hidden="0" customHeight="1">
+      <x:c r="A201" s="42" t="n">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B201" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C201" s="49" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D201" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E201" s="49" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="F201" s="49" t="str">
+        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+      </x:c>
+      <x:c r="G201" s="49" t="str">
+        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+      </x:c>
+      <x:c r="H201" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I201" s="55" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="J201" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A202" s="42" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B202" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C202" s="49" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D202" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E202" s="49" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="F202" s="49" t="str">
+        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+      </x:c>
+      <x:c r="G202" s="49" t="str">
+        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+      </x:c>
+      <x:c r="H202" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I202" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J202" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A203" s="42" t="n">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B203" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C203" s="49" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D200" s="49" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E200" s="49" t="str">
+      <x:c r="D203" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E203" s="49" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="F200" s="49" t="str">
+      <x:c r="F203" s="49" t="str">
         <x:v>限流进入可重试失败类别，不被误记为论文查无。</x:v>
       </x:c>
-      <x:c r="G200" s="49" t="str">
+      <x:c r="G203" s="49" t="str">
         <x:v>匿名访问限流可能污染覆盖率并错误触发论文隔离。</x:v>
       </x:c>
-      <x:c r="H200" s="52" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I200" s="55" t="n">
-        <x:v>0.003</x:v>
-      </x:c>
-      <x:c r="J200" s="58" t="str">
-        <x:v>已登记</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" ht="132" hidden="0" customHeight="1">
-      <x:c r="A201" s="45" t="n">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="B201" s="50" t="str">
+      <x:c r="H203" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I203" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J203" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="132" hidden="0" customHeight="1">
+      <x:c r="A204" s="45" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B204" s="50" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C201" s="50" t="str">
+      <x:c r="C204" s="50" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D201" s="50" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E201" s="50" t="str">
+      <x:c r="D204" s="50" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E204" s="50" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="F201" s="50" t="str">
+      <x:c r="F204" s="50" t="str">
         <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
       </x:c>
-      <x:c r="G201" s="50" t="str">
+      <x:c r="G204" s="50" t="str">
         <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
       </x:c>
-      <x:c r="H201" s="53" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I201" s="56" t="n">
-        <x:v>0.007</x:v>
-      </x:c>
-      <x:c r="J201" s="59" t="str">
+      <x:c r="H204" s="53" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I204" s="56" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="J204" s="59" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
@@ -12394,18 +12562,18 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H201">
+  <x:conditionalFormatting sqref="H5:H204">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="错误"/>
     <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="跳过"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J201">
+  <x:conditionalFormatting sqref="J5:J204">
     <x:cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="未登记"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e4f3415a38a4bea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a41c5f1382d4b45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13694,34 +13862,66 @@
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="128" t="n">
+      <x:c r="A40" s="127" t="n">
         <x:v>46247.399375</x:v>
       </x:c>
-      <x:c r="B40" s="24" t="str">
+      <x:c r="B40" s="23" t="str">
         <x:v>a119c6647fea</x:v>
       </x:c>
-      <x:c r="C40" s="24" t="n">
+      <x:c r="C40" s="23" t="n">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="D40" s="24" t="n">
+      <x:c r="D40" s="23" t="n">
         <x:v>197</x:v>
       </x:c>
-      <x:c r="E40" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F40" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H40" s="131" t="n">
+      <x:c r="E40" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F40" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G40" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" s="130" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I40" s="30" t="n">
+      <x:c r="I40" s="29" t="n">
         <x:v>256.3</x:v>
       </x:c>
-      <x:c r="J40" s="24" t="n">
+      <x:c r="J40" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="128" t="n">
+        <x:v>46247.415497685186</x:v>
+      </x:c>
+      <x:c r="B41" s="24" t="str">
+        <x:v>04c22a0c496d</x:v>
+      </x:c>
+      <x:c r="C41" s="24" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D41" s="24" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="E41" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F41" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G41" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I41" s="30" t="n">
+        <x:v>185.236</x:v>
+      </x:c>
+      <x:c r="J41" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -13731,7 +13931,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa3081f4b2394f3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda7c9ce43ff248f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/latest_test_report.xlsx
+++ b/reports/latest_test_report.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R8fd7812d018141f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R5f835862f1b24db2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R66bd42e6f7514829"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="R95b3651c8b324ea1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Rf239ae32030a4d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R0b644514fbdf4b75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="Rd8f0e49bff0740e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R05c7234a48854c40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Re6d2c39b3a2f4926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Rb1c6e542297a43bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H204" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H205" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J204" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J205" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="运行时间"/>
     <x:tableColumn id="2" name="Git Commit"/>
@@ -977,7 +977,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T09:58:19+08:00  |  Git：04c22a0c496dd4d31d2314616e7e4c714f29303f</x:v>
+        <x:v>运行时间：2026-08-13T10:15:24+08:00  |  Git：7f436ea669c287c481594a4c8fcd0ab51f997c89</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1007,22 +1007,22 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="74" t="n">
-        <x:f>COUNTA('测试明细'!$A$5:$A$204)</x:f>
-        <x:v>200</x:v>
+        <x:f>COUNTA('测试明细'!$A$5:$A$205)</x:f>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B5" s="75"/>
       <x:c r="C5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$204,"通过")</x:f>
-        <x:v>200</x:v>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$205,"通过")</x:f>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D5" s="75"/>
       <x:c r="E5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$204,"失败")+COUNTIF('测试明细'!$E$5:$E$204,"错误")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$205,"失败")+COUNTIF('测试明细'!$E$5:$E$205,"错误")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="75"/>
       <x:c r="G5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$204,"跳过")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$205,"跳过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="76"/>
@@ -1062,8 +1062,8 @@
       </x:c>
       <x:c r="B9" s="108"/>
       <x:c r="C9" s="109" t="n">
-        <x:f>SUM('测试明细'!$F$5:$F$204)</x:f>
-        <x:v>185.2360000000001</x:v>
+        <x:f>SUM('测试明细'!$F$5:$F$205)</x:f>
+        <x:v>133.3509999999996</x:v>
       </x:c>
       <x:c r="D9" s="109"/>
       <x:c r="E9" s="110" t="n">
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="F9" s="110"/>
       <x:c r="G9" s="110" t="n">
-        <x:f>COUNTIF('用例说明'!$J$5:$J$204,"未登记")</x:f>
+        <x:f>COUNTIF('用例说明'!$J$5:$J$205,"未登记")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="111"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T09:58:19+08:00  |  Git：04c22a0c496dd4d31d2314616e7e4c714f29303f</x:v>
+        <x:v>运行时间：2026-08-13T10:15:24+08:00  |  Git：7f436ea669c287c481594a4c8fcd0ab51f997c89</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1304,7 +1304,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F6" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
         <x:v>确认当前实现相对旧基线确实提升关键确定性能力的准确率。</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>验证动态查询规划不会为简单问题创建多余检索词，同时保持规划准确。</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F8" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>验证基准报告能同时给出基线值、候选值和差值。</x:v>
@@ -1376,7 +1376,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F9" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
         <x:v>验证离线基准能准确统计成功/失败调用以及输入、输出和总 Token。</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F10" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
         <x:v>验证离线基准能够量化统一 Tool 层的协议、错误和恢复能力。</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F11" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
         <x:v>验证离线 Benchmark 对比单源基线与多源候选的覆盖、去重和故障恢复。</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F12" s="32" t="n">
-        <x:v>0.214</x:v>
+        <x:v>0.171</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
         <x:v>验证完整能力基准报告可以用 UTF-8 JSON 保存并重新读取。</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F13" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G13" s="35" t="str">
         <x:v>验证基准工具拒绝不存在的运行配置名称。</x:v>
@@ -1496,7 +1496,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F14" s="32" t="n">
-        <x:v>0.053</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str">
         <x:v>验证候选评测能从 OpenAlex 等二级来源的 DOI 中提取待验证 arXiv 身份。</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
-        <x:v>0.036</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="G15" s="35" t="str">
         <x:v>验证联合重放只把普通 DOI 交给 Crossref，排除 arXiv DOI。</x:v>
@@ -1544,7 +1544,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F16" s="32" t="n">
-        <x:v>0.022</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="G16" s="35" t="str">
         <x:v>验证成功取得的规范元数据会缓存，快照重放不会重复消耗网络请求。</x:v>
@@ -1568,7 +1568,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G17" s="35" t="str">
         <x:v>验证 SSL、超时等临时失败不会被当成永久缓存结果。</x:v>
@@ -1592,7 +1592,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>0.032</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="G18" s="35" t="str">
         <x:v>验证 Crossref 成功记录和明确查无均可重复使用。</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G19" s="35" t="str">
         <x:v>验证 DOI authority 网络失败不会写入成功缓存。</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="G20" s="35" t="str">
         <x:v>验证本轮候选实验只查询 v2 实际隔离过的身份，控制外部请求成本。</x:v>
@@ -1664,7 +1664,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
-        <x:v>0.058</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="G21" s="35" t="str">
         <x:v>验证规范元数据候选只有在三份完整独立快照、权威覆盖完整且逐题无回归时才通过晋升门槛。</x:v>
@@ -1688,7 +1688,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F22" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G22" s="35" t="str">
         <x:v>验证 Crossref 相对仅 arXiv canonical 没有指标变化时不得宣称质量提升。</x:v>
@@ -1712,7 +1712,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F23" s="32" t="n">
-        <x:v>0.028</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G23" s="35" t="str">
         <x:v>验证普通 DOI 候选评测只使用所有独立快照都出现的非 arXiv DOI。</x:v>
@@ -1736,7 +1736,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F24" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G24" s="35" t="str">
         <x:v>验证 Crossref 评测严格区分标题匹配、标题冲突、规范查无和网络失败。</x:v>
@@ -1760,7 +1760,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F25" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G25" s="35" t="str">
         <x:v>验证普通 DOI 样本按注册前缀轮转抽取，避免单一高频前缀垄断评测集。</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F26" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G26" s="35" t="str">
         <x:v>验证 provider 一致率只使用双方均成功返回标题的 DOI。</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F27" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G27" s="35" t="str">
         <x:v>验证 DOI 校验在固定污染、缺失、近似、查无和失败场景中达到阶段止损条件。</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F28" s="32" t="n">
-        <x:v>0.146</x:v>
+        <x:v>0.071</x:v>
       </x:c>
       <x:c r="G28" s="35" t="str">
         <x:v>验证普通研究问题按完整 Agentic RAG 节点顺序执行。</x:v>
@@ -1856,7 +1856,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F29" s="32" t="n">
-        <x:v>0.111</x:v>
+        <x:v>0.046</x:v>
       </x:c>
       <x:c r="G29" s="35" t="str">
         <x:v>验证已有 PDF 的请求不会重复进行外部查询规划和检索。</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F30" s="32" t="n">
-        <x:v>0.094</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="G30" s="35" t="str">
         <x:v>验证问候类输入在进入 RAG 与 LLM 节点前本地结束。</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F31" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G31" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1928,7 +1928,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F32" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G32" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1952,7 +1952,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F33" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G33" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1976,7 +1976,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F34" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G34" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -2000,7 +2000,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F35" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G35" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2024,7 +2024,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F36" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G36" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2048,7 +2048,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F37" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G37" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2072,7 +2072,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F38" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G38" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2096,7 +2096,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F39" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G39" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2120,7 +2120,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F40" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G40" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F41" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G41" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2168,7 +2168,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F42" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G42" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2192,7 +2192,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F43" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G43" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2216,7 +2216,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F44" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G44" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2240,7 +2240,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F45" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G45" s="35" t="str">
         <x:v>验证意图匹配前只清理空格、大小写和末尾标点等表面差异。</x:v>
@@ -2264,7 +2264,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F46" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G46" s="35" t="str">
         <x:v>验证本地闲聊响应不会破坏已有状态和请求元数据。</x:v>
@@ -2312,7 +2312,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F48" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G48" s="35" t="str">
         <x:v>验证能读取 OpenAI 兼容响应中的 token_usage 字段。</x:v>
@@ -2336,7 +2336,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F49" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G49" s="35" t="str">
         <x:v>验证模型未返回 Token 数据时系统明确标记缺失而不伪造估算值。</x:v>
@@ -2360,7 +2360,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F50" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G50" s="35" t="str">
         <x:v>验证成功 LLM 调用会记录节点、模型、Token、成功状态和延迟。</x:v>
@@ -2384,7 +2384,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F51" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G51" s="35" t="str">
         <x:v>验证 LLM 调用失败时仍保留失败类型和耗时记录。</x:v>
@@ -2408,7 +2408,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F52" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G52" s="35" t="str">
         <x:v>验证多个节点的 LLM 用量可以累加且不会重复计数。</x:v>
@@ -2432,7 +2432,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F53" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G53" s="35" t="str">
         <x:v>验证指标节点既能按节点分组，又能提供全流程总量与缺失用量统计。</x:v>
@@ -2456,7 +2456,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F54" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G54" s="35" t="str">
         <x:v>验证推理节点启用 LLM 时会写入统一用量记录。</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F55" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G55" s="35" t="str">
         <x:v>验证检索评估节点启用 LLM 时记录评分与用量。</x:v>
@@ -2504,7 +2504,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F56" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G56" s="35" t="str">
         <x:v>验证答案生成节点记录实际生成结果和模型用量。</x:v>
@@ -2528,7 +2528,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F57" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G57" s="35" t="str">
         <x:v>验证关闭 LLM 评估时只使用规则评分且不创建虚假调用记录。</x:v>
@@ -2552,7 +2552,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F58" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G58" s="35" t="str">
         <x:v>验证 BM25 基线能把中文问题与英文术语、数字混合分词。</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F59" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G59" s="35" t="str">
         <x:v>验证 BM25 将包含查询词的文本块排在无关块之前，且重复运行排名与分数一致。</x:v>
@@ -2600,7 +2600,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F60" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G60" s="35" t="str">
         <x:v>验证 BM25 拒绝空语料和非正数返回条数。</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F61" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G61" s="35" t="str">
         <x:v>用手工可计算的排名验证本地 RAG Recall、MRR 与 nDCG 公式。</x:v>
@@ -2648,7 +2648,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F62" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G62" s="35" t="str">
         <x:v>验证同一相关 PDF 页返回多个 Chunk 时，page-level 指标只计算首次命中。</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F63" s="32" t="n">
-        <x:v>0.064</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="G63" s="35" t="str">
         <x:v>验证代表论文来源清单生成 Manifest 时保留语料版本、论文身份和内容哈希。</x:v>
@@ -2696,7 +2696,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F64" s="32" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="G64" s="35" t="str">
         <x:v>验证来源清单声明的 PDF 缺失时立即失败，而不是静默生成不完整语料。</x:v>
@@ -2720,7 +2720,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F65" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G65" s="35" t="str">
         <x:v>验证 Dense 检索显式归一化向量，并按余弦相似度将语义匹配块排在前面。</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F66" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G66" s="35" t="str">
         <x:v>验证 Dense 检索拒绝零向量和空语料。</x:v>
@@ -2768,7 +2768,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F67" s="32" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="G67" s="35" t="str">
         <x:v>验证 Dense 向量缓存可以无损加载，并在语料文本、模型或处理版本变化后使用不同指纹。</x:v>
@@ -2792,7 +2792,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F68" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G68" s="35" t="str">
         <x:v>验证缓存命中时 DenseRetriever 不会重新编码全部论文，只对查询生成向量。</x:v>
@@ -2816,7 +2816,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F69" s="32" t="n">
-        <x:v>0.028</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G69" s="35" t="str">
         <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
@@ -2840,22 +2840,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F70" s="32" t="n">
-        <x:v>64.649</x:v>
+        <x:v>30.836</x:v>
       </x:c>
       <x:c r="G70" s="35" t="str">
         <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
       </x:c>
       <x:c r="H70" s="35" t="str"/>
     </x:row>
-    <x:row r="71" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="71" ht="198" hidden="0" customHeight="1">
       <x:c r="A71" s="26" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C71" s="35" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
       </x:c>
       <x:c r="D71" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2864,14 +2864,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F71" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="G71" s="35" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
       </x:c>
       <x:c r="H71" s="35" t="str"/>
     </x:row>
-    <x:row r="72" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="72" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A72" s="26" t="n">
         <x:v>68</x:v>
       </x:c>
@@ -2879,7 +2879,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C72" s="35" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D72" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2888,14 +2888,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F72" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G72" s="35" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="H72" s="35" t="str"/>
     </x:row>
-    <x:row r="73" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="73" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A73" s="26" t="n">
         <x:v>69</x:v>
       </x:c>
@@ -2903,7 +2903,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C73" s="35" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D73" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2912,14 +2912,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F73" s="32" t="n">
-        <x:v>0.038</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G73" s="35" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="H73" s="35" t="str"/>
     </x:row>
-    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="74" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A74" s="26" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -2927,7 +2927,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C74" s="35" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D74" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2936,22 +2936,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F74" s="32" t="n">
-        <x:v>0.053</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="G74" s="35" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="H74" s="35" t="str"/>
     </x:row>
-    <x:row r="75" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="75" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A75" s="26" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C75" s="35" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D75" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2960,10 +2960,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F75" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="G75" s="35" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="H75" s="35" t="str"/>
     </x:row>
@@ -2975,7 +2975,7 @@
         <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C76" s="35" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D76" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2984,22 +2984,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F76" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G76" s="35" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="H76" s="35" t="str"/>
     </x:row>
-    <x:row r="77" ht="132" hidden="0" customHeight="1">
+    <x:row r="77" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A77" s="26" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="35" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C77" s="35" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D77" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3008,22 +3008,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F77" s="32" t="n">
-        <x:v>48.557</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G77" s="35" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="H77" s="35" t="str"/>
     </x:row>
-    <x:row r="78" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="78" ht="132" hidden="0" customHeight="1">
       <x:c r="A78" s="26" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C78" s="35" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D78" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3032,14 +3032,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F78" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>30.236</x:v>
       </x:c>
       <x:c r="G78" s="35" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="H78" s="35" t="str"/>
     </x:row>
-    <x:row r="79" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A79" s="26" t="n">
         <x:v>75</x:v>
       </x:c>
@@ -3047,7 +3047,7 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C79" s="35" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D79" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3056,14 +3056,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F79" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G79" s="35" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="H79" s="35" t="str"/>
     </x:row>
-    <x:row r="80" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="80" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A80" s="26" t="n">
         <x:v>76</x:v>
       </x:c>
@@ -3071,7 +3071,7 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C80" s="35" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D80" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3080,22 +3080,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F80" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G80" s="35" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="H80" s="35" t="str"/>
     </x:row>
-    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="81" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A81" s="26" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C81" s="35" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D81" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3104,14 +3104,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F81" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G81" s="35" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="H81" s="35" t="str"/>
     </x:row>
-    <x:row r="82" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A82" s="26" t="n">
         <x:v>78</x:v>
       </x:c>
@@ -3119,7 +3119,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C82" s="35" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D82" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3128,14 +3128,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F82" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G82" s="35" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="H82" s="35" t="str"/>
     </x:row>
-    <x:row r="83" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="83" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A83" s="26" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -3143,7 +3143,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C83" s="35" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D83" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3155,11 +3155,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G83" s="35" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="H83" s="35" t="str"/>
     </x:row>
-    <x:row r="84" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="84" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A84" s="26" t="n">
         <x:v>80</x:v>
       </x:c>
@@ -3167,7 +3167,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C84" s="35" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D84" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3176,10 +3176,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F84" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G84" s="35" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="H84" s="35" t="str"/>
     </x:row>
@@ -3191,7 +3191,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C85" s="35" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D85" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3203,11 +3203,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G85" s="35" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="H85" s="35" t="str"/>
     </x:row>
-    <x:row r="86" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="86" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A86" s="26" t="n">
         <x:v>82</x:v>
       </x:c>
@@ -3215,7 +3215,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="35" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D86" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3224,10 +3224,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F86" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G86" s="35" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="H86" s="35" t="str"/>
     </x:row>
@@ -3239,7 +3239,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="35" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D87" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3248,10 +3248,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F87" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G87" s="35" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="H87" s="35" t="str"/>
     </x:row>
@@ -3260,10 +3260,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="35" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D88" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3272,14 +3272,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F88" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G88" s="35" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="H88" s="35" t="str"/>
     </x:row>
-    <x:row r="89" ht="132" hidden="0" customHeight="1">
+    <x:row r="89" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A89" s="26" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -3287,7 +3287,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C89" s="35" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D89" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3296,10 +3296,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F89" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G89" s="35" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="H89" s="35" t="str"/>
     </x:row>
@@ -3311,7 +3311,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C90" s="35" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D90" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3323,11 +3323,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G90" s="35" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="H90" s="35" t="str"/>
     </x:row>
-    <x:row r="91" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="91" ht="132" hidden="0" customHeight="1">
       <x:c r="A91" s="26" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -3335,7 +3335,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C91" s="35" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D91" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3347,11 +3347,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G91" s="35" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="H91" s="35" t="str"/>
     </x:row>
-    <x:row r="92" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="92" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A92" s="26" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -3359,7 +3359,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C92" s="35" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D92" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3371,7 +3371,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G92" s="35" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="H92" s="35" t="str"/>
     </x:row>
@@ -3383,7 +3383,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="35" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D93" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3395,11 +3395,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G93" s="35" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="H93" s="35" t="str"/>
     </x:row>
-    <x:row r="94" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="94" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A94" s="26" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -3407,7 +3407,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="35" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D94" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3416,22 +3416,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F94" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G94" s="35" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="H94" s="35" t="str"/>
     </x:row>
-    <x:row r="95" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="95" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A95" s="26" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="35" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="35" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D95" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3440,22 +3440,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F95" s="32" t="n">
-        <x:v>2.365</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G95" s="35" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="H95" s="35" t="str"/>
     </x:row>
-    <x:row r="96" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="96" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A96" s="26" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C96" s="35" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D96" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3464,10 +3464,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F96" s="32" t="n">
-        <x:v>0.039</x:v>
+        <x:v>2.386</x:v>
       </x:c>
       <x:c r="G96" s="35" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="H96" s="35" t="str"/>
     </x:row>
@@ -3479,7 +3479,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C97" s="35" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D97" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3488,14 +3488,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F97" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="G97" s="35" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="H97" s="35" t="str"/>
     </x:row>
-    <x:row r="98" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="98" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A98" s="26" t="n">
         <x:v>94</x:v>
       </x:c>
@@ -3503,7 +3503,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C98" s="35" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D98" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3512,14 +3512,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F98" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G98" s="35" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="H98" s="35" t="str"/>
     </x:row>
-    <x:row r="99" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="99" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A99" s="26" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -3527,7 +3527,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C99" s="35" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D99" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3536,22 +3536,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F99" s="32" t="n">
-        <x:v>1.156</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G99" s="35" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="H99" s="35" t="str"/>
     </x:row>
-    <x:row r="100" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="100" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A100" s="26" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C100" s="35" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D100" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3560,14 +3560,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F100" s="32" t="n">
-        <x:v>0.196</x:v>
+        <x:v>1.128</x:v>
       </x:c>
       <x:c r="G100" s="35" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="H100" s="35" t="str"/>
     </x:row>
-    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="101" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A101" s="26" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -3575,7 +3575,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C101" s="35" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D101" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3584,14 +3584,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F101" s="32" t="n">
-        <x:v>0.088</x:v>
+        <x:v>0.188</x:v>
       </x:c>
       <x:c r="G101" s="35" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="H101" s="35" t="str"/>
     </x:row>
-    <x:row r="102" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="102" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A102" s="26" t="n">
         <x:v>98</x:v>
       </x:c>
@@ -3599,7 +3599,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C102" s="35" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D102" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3608,14 +3608,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F102" s="32" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.106</x:v>
       </x:c>
       <x:c r="G102" s="35" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="H102" s="35" t="str"/>
     </x:row>
-    <x:row r="103" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="103" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A103" s="26" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -3623,7 +3623,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C103" s="35" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D103" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3632,22 +3632,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F103" s="32" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.056</x:v>
       </x:c>
       <x:c r="G103" s="35" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="H103" s="35" t="str"/>
     </x:row>
-    <x:row r="104" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="104" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A104" s="26" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="35" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C104" s="35" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D104" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3656,22 +3656,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F104" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="G104" s="35" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="H104" s="35" t="str"/>
     </x:row>
-    <x:row r="105" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="105" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A105" s="26" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C105" s="35" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D105" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3683,11 +3683,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G105" s="35" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="H105" s="35" t="str"/>
     </x:row>
-    <x:row r="106" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="106" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A106" s="26" t="n">
         <x:v>102</x:v>
       </x:c>
@@ -3695,10 +3695,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C106" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D106" s="35" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E106" s="26" t="str">
         <x:v>通过</x:v>
@@ -3707,7 +3707,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G106" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="H106" s="35" t="str"/>
     </x:row>
@@ -3719,10 +3719,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C107" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D107" s="35" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E107" s="26" t="str">
         <x:v>通过</x:v>
@@ -3743,16 +3743,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C108" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D108" s="35" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E108" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F108" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G108" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3767,16 +3767,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C109" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D109" s="35" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F109" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G109" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3791,10 +3791,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D110" s="35" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E110" s="26" t="str">
         <x:v>通过</x:v>
@@ -3807,7 +3807,7 @@
       </x:c>
       <x:c r="H110" s="35" t="str"/>
     </x:row>
-    <x:row r="111" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="111" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A111" s="26" t="n">
         <x:v>107</x:v>
       </x:c>
@@ -3815,10 +3815,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D111" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E111" s="26" t="str">
         <x:v>通过</x:v>
@@ -3827,7 +3827,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G111" s="35" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H111" s="35" t="str"/>
     </x:row>
@@ -3839,19 +3839,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D112" s="35" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E112" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F112" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G112" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="H112" s="35" t="str"/>
     </x:row>
@@ -3863,10 +3863,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D113" s="35" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
         <x:v>通过</x:v>
@@ -3887,10 +3887,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D114" s="35" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E114" s="26" t="str">
         <x:v>通过</x:v>
@@ -3911,16 +3911,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D115" s="35" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F115" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G115" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -3935,10 +3935,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D116" s="35" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E116" s="26" t="str">
         <x:v>通过</x:v>
@@ -3951,7 +3951,7 @@
       </x:c>
       <x:c r="H116" s="35" t="str"/>
     </x:row>
-    <x:row r="117" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="117" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A117" s="26" t="n">
         <x:v>113</x:v>
       </x:c>
@@ -3959,10 +3959,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D117" s="35" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
         <x:v>通过</x:v>
@@ -3975,7 +3975,7 @@
       </x:c>
       <x:c r="H117" s="35" t="str"/>
     </x:row>
-    <x:row r="118" ht="66" hidden="0" customHeight="1">
+    <x:row r="118" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A118" s="26" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -3983,23 +3983,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="35" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D118" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E118" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F118" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G118" s="35" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H118" s="35" t="str"/>
     </x:row>
-    <x:row r="119" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="119" ht="66" hidden="0" customHeight="1">
       <x:c r="A119" s="26" t="n">
         <x:v>115</x:v>
       </x:c>
@@ -4007,7 +4007,7 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="35" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D119" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4019,19 +4019,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G119" s="35" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="H119" s="35" t="str"/>
     </x:row>
-    <x:row r="120" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="120" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A120" s="26" t="n">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B120" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="35" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D120" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4040,14 +4040,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F120" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G120" s="35" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="H120" s="35" t="str"/>
     </x:row>
-    <x:row r="121" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="121" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A121" s="26" t="n">
         <x:v>117</x:v>
       </x:c>
@@ -4055,7 +4055,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C121" s="35" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D121" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4067,11 +4067,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G121" s="35" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="H121" s="35" t="str"/>
     </x:row>
-    <x:row r="122" ht="132" hidden="0" customHeight="1">
+    <x:row r="122" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A122" s="26" t="n">
         <x:v>118</x:v>
       </x:c>
@@ -4079,7 +4079,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C122" s="35" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D122" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4088,14 +4088,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F122" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G122" s="35" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="H122" s="35" t="str"/>
     </x:row>
-    <x:row r="123" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="123" ht="132" hidden="0" customHeight="1">
       <x:c r="A123" s="26" t="n">
         <x:v>119</x:v>
       </x:c>
@@ -4103,7 +4103,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C123" s="35" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D123" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4112,22 +4112,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F123" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G123" s="35" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="H123" s="35" t="str"/>
     </x:row>
-    <x:row r="124" ht="132" hidden="0" customHeight="1">
+    <x:row r="124" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A124" s="26" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C124" s="35" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D124" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4136,14 +4136,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F124" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G124" s="35" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="H124" s="35" t="str"/>
     </x:row>
-    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="125" ht="132" hidden="0" customHeight="1">
       <x:c r="A125" s="26" t="n">
         <x:v>121</x:v>
       </x:c>
@@ -4151,7 +4151,7 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C125" s="35" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D125" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4160,10 +4160,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F125" s="32" t="n">
-        <x:v>15.585</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G125" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="H125" s="35" t="str"/>
     </x:row>
@@ -4175,7 +4175,7 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C126" s="35" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D126" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4184,22 +4184,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F126" s="32" t="n">
-        <x:v>15.492</x:v>
+        <x:v>14.87</x:v>
       </x:c>
       <x:c r="G126" s="35" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="H126" s="35" t="str"/>
     </x:row>
-    <x:row r="127" ht="132" hidden="0" customHeight="1">
+    <x:row r="127" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A127" s="26" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C127" s="35" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D127" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4208,14 +4208,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F127" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>14.978</x:v>
       </x:c>
       <x:c r="G127" s="35" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="H127" s="35" t="str"/>
     </x:row>
-    <x:row r="128" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="128" ht="132" hidden="0" customHeight="1">
       <x:c r="A128" s="26" t="n">
         <x:v>124</x:v>
       </x:c>
@@ -4223,7 +4223,7 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C128" s="35" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D128" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4232,14 +4232,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F128" s="32" t="n">
-        <x:v>19.508</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G128" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="H128" s="35" t="str"/>
     </x:row>
-    <x:row r="129" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="129" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A129" s="26" t="n">
         <x:v>125</x:v>
       </x:c>
@@ -4247,7 +4247,7 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="35" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D129" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4256,22 +4256,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F129" s="32" t="n">
-        <x:v>15.364</x:v>
+        <x:v>18.845</x:v>
       </x:c>
       <x:c r="G129" s="35" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="H129" s="35" t="str"/>
     </x:row>
-    <x:row r="130" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="130" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A130" s="26" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C130" s="35" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D130" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4280,14 +4280,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F130" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>17.713</x:v>
       </x:c>
       <x:c r="G130" s="35" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="H130" s="35" t="str"/>
     </x:row>
-    <x:row r="131" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="131" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A131" s="26" t="n">
         <x:v>127</x:v>
       </x:c>
@@ -4295,7 +4295,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C131" s="35" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D131" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4304,14 +4304,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F131" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G131" s="35" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="H131" s="35" t="str"/>
     </x:row>
-    <x:row r="132" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="132" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A132" s="26" t="n">
         <x:v>128</x:v>
       </x:c>
@@ -4319,7 +4319,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C132" s="35" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D132" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4331,11 +4331,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G132" s="35" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="H132" s="35" t="str"/>
     </x:row>
-    <x:row r="133" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="133" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A133" s="26" t="n">
         <x:v>129</x:v>
       </x:c>
@@ -4343,7 +4343,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C133" s="35" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D133" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4352,10 +4352,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F133" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G133" s="35" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="H133" s="35" t="str"/>
     </x:row>
@@ -4367,7 +4367,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C134" s="35" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D134" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4379,11 +4379,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G134" s="35" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="H134" s="35" t="str"/>
     </x:row>
-    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="135" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A135" s="26" t="n">
         <x:v>131</x:v>
       </x:c>
@@ -4391,7 +4391,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="35" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D135" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4400,14 +4400,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F135" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G135" s="35" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="H135" s="35" t="str"/>
     </x:row>
-    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="136" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A136" s="26" t="n">
         <x:v>132</x:v>
       </x:c>
@@ -4415,7 +4415,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="35" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D136" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4424,14 +4424,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F136" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G136" s="35" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="H136" s="35" t="str"/>
     </x:row>
-    <x:row r="137" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="137" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A137" s="26" t="n">
         <x:v>133</x:v>
       </x:c>
@@ -4439,7 +4439,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="35" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D137" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4448,10 +4448,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F137" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G137" s="35" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="H137" s="35" t="str"/>
     </x:row>
@@ -4463,7 +4463,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D138" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4472,14 +4472,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F138" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G138" s="35" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="H138" s="35" t="str"/>
     </x:row>
-    <x:row r="139" ht="132" hidden="0" customHeight="1">
+    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A139" s="26" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -4487,7 +4487,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D139" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4496,14 +4496,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F139" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G139" s="35" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="H139" s="35" t="str"/>
     </x:row>
-    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="140" ht="132" hidden="0" customHeight="1">
       <x:c r="A140" s="26" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -4511,7 +4511,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="35" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D140" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4520,10 +4520,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F140" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G140" s="35" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="H140" s="35" t="str"/>
     </x:row>
@@ -4535,7 +4535,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="35" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D141" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4544,14 +4544,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F141" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G141" s="35" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="H141" s="35" t="str"/>
     </x:row>
-    <x:row r="142" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A142" s="26" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -4559,7 +4559,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="35" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D142" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4568,22 +4568,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F142" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G142" s="35" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="H142" s="35" t="str"/>
     </x:row>
-    <x:row r="143" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A143" s="26" t="n">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B143" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="35" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D143" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4592,14 +4592,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F143" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G143" s="35" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="H143" s="35" t="str"/>
     </x:row>
-    <x:row r="144" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="144" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A144" s="26" t="n">
         <x:v>140</x:v>
       </x:c>
@@ -4607,7 +4607,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C144" s="35" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D144" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4616,10 +4616,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F144" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G144" s="35" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="H144" s="35" t="str"/>
     </x:row>
@@ -4631,7 +4631,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C145" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D145" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4640,14 +4640,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F145" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G145" s="35" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="H145" s="35" t="str"/>
     </x:row>
-    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="146" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A146" s="26" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -4655,7 +4655,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C146" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D146" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4664,14 +4664,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F146" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G146" s="35" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="H146" s="35" t="str"/>
     </x:row>
-    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="147" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A147" s="26" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -4679,7 +4679,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C147" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D147" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4688,10 +4688,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F147" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G147" s="35" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="H147" s="35" t="str"/>
     </x:row>
@@ -4703,7 +4703,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="35" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D148" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4712,14 +4712,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F148" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G148" s="35" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="H148" s="35" t="str"/>
     </x:row>
-    <x:row r="149" ht="66" hidden="0" customHeight="1">
+    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A149" s="26" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -4727,7 +4727,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="35" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D149" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4736,14 +4736,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F149" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G149" s="35" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="H149" s="35" t="str"/>
     </x:row>
-    <x:row r="150" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="150" ht="66" hidden="0" customHeight="1">
       <x:c r="A150" s="26" t="n">
         <x:v>146</x:v>
       </x:c>
@@ -4751,7 +4751,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="35" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D150" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4763,19 +4763,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G150" s="35" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="H150" s="35" t="str"/>
     </x:row>
-    <x:row r="151" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="151" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A151" s="26" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B151" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="35" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D151" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4787,11 +4787,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G151" s="35" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="H151" s="35" t="str"/>
     </x:row>
-    <x:row r="152" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="152" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A152" s="26" t="n">
         <x:v>148</x:v>
       </x:c>
@@ -4799,7 +4799,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C152" s="35" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D152" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4808,14 +4808,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F152" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G152" s="35" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="H152" s="35" t="str"/>
     </x:row>
-    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="153" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A153" s="26" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -4823,7 +4823,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C153" s="35" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D153" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4832,14 +4832,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F153" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G153" s="35" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="H153" s="35" t="str"/>
     </x:row>
-    <x:row r="154" ht="132" hidden="0" customHeight="1">
+    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A154" s="26" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -4847,7 +4847,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C154" s="35" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D154" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4859,7 +4859,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G154" s="35" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="H154" s="35" t="str"/>
     </x:row>
@@ -4871,7 +4871,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C155" s="35" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D155" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4880,14 +4880,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F155" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G155" s="35" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="H155" s="35" t="str"/>
     </x:row>
-    <x:row r="156" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="156" ht="132" hidden="0" customHeight="1">
       <x:c r="A156" s="26" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -4895,7 +4895,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="35" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D156" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4904,14 +4904,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F156" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G156" s="35" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="H156" s="35" t="str"/>
     </x:row>
-    <x:row r="157" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="157" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A157" s="26" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -4919,7 +4919,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="35" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D157" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4931,11 +4931,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G157" s="35" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="H157" s="35" t="str"/>
     </x:row>
-    <x:row r="158" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A158" s="26" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -4943,7 +4943,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="35" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D158" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4952,10 +4952,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F158" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G158" s="35" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H158" s="35" t="str"/>
     </x:row>
@@ -4967,7 +4967,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4976,14 +4976,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F159" s="32" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G159" s="35" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="H159" s="35" t="str"/>
     </x:row>
-    <x:row r="160" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="160" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A160" s="26" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -4991,7 +4991,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5000,14 +5000,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F160" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.117</x:v>
       </x:c>
       <x:c r="G160" s="35" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="H160" s="35" t="str"/>
     </x:row>
-    <x:row r="161" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="161" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A161" s="26" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -5015,7 +5015,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5024,14 +5024,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F161" s="32" t="n">
-        <x:v>0.022</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G161" s="35" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="H161" s="35" t="str"/>
     </x:row>
-    <x:row r="162" ht="132" hidden="0" customHeight="1">
+    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A162" s="26" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -5039,7 +5039,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5048,10 +5048,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F162" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G162" s="35" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="H162" s="35" t="str"/>
     </x:row>
@@ -5063,7 +5063,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5072,14 +5072,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F163" s="32" t="n">
-        <x:v>0.164</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G163" s="35" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="H163" s="35" t="str"/>
     </x:row>
-    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="164" ht="132" hidden="0" customHeight="1">
       <x:c r="A164" s="26" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -5087,7 +5087,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5096,14 +5096,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F164" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.225</x:v>
       </x:c>
       <x:c r="G164" s="35" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="H164" s="35" t="str"/>
     </x:row>
-    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="165" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A165" s="26" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -5111,7 +5111,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5120,10 +5120,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F165" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G165" s="35" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="H165" s="35" t="str"/>
     </x:row>
@@ -5135,7 +5135,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5144,22 +5144,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F166" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G166" s="35" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="H166" s="35" t="str"/>
     </x:row>
-    <x:row r="167" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="167" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A167" s="26" t="n">
         <x:v>163</x:v>
       </x:c>
       <x:c r="B167" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="35" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D167" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5168,10 +5168,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F167" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G167" s="35" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="H167" s="35" t="str"/>
     </x:row>
@@ -5183,7 +5183,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C168" s="35" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D168" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5192,14 +5192,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F168" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G168" s="35" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="H168" s="35" t="str"/>
     </x:row>
-    <x:row r="169" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="169" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A169" s="26" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -5207,7 +5207,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C169" s="35" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D169" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5216,14 +5216,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F169" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G169" s="35" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="H169" s="35" t="str"/>
     </x:row>
-    <x:row r="170" ht="66" hidden="0" customHeight="1">
+    <x:row r="170" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A170" s="26" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -5231,7 +5231,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C170" s="35" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D170" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5240,22 +5240,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F170" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G170" s="35" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="H170" s="35" t="str"/>
     </x:row>
-    <x:row r="171" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="171" ht="66" hidden="0" customHeight="1">
       <x:c r="A171" s="26" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B171" s="35" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C171" s="35" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D171" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5264,10 +5264,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F171" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G171" s="35" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="H171" s="35" t="str"/>
     </x:row>
@@ -5276,10 +5276,10 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C172" s="35" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D172" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5288,10 +5288,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F172" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G172" s="35" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="H172" s="35" t="str"/>
     </x:row>
@@ -5303,7 +5303,7 @@
         <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C173" s="35" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D173" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5312,10 +5312,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F173" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G173" s="35" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="H173" s="35" t="str"/>
     </x:row>
@@ -5324,10 +5324,10 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C174" s="35" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D174" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5339,11 +5339,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G174" s="35" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="H174" s="35" t="str"/>
     </x:row>
-    <x:row r="175" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="175" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A175" s="26" t="n">
         <x:v>171</x:v>
       </x:c>
@@ -5351,7 +5351,7 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C175" s="35" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D175" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5360,14 +5360,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F175" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G175" s="35" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="H175" s="35" t="str"/>
     </x:row>
-    <x:row r="176" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="176" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A176" s="26" t="n">
         <x:v>172</x:v>
       </x:c>
@@ -5375,7 +5375,7 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C176" s="35" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D176" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5384,10 +5384,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F176" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G176" s="35" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="H176" s="35" t="str"/>
     </x:row>
@@ -5396,10 +5396,10 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B177" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C177" s="35" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D177" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5411,7 +5411,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G177" s="35" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="H177" s="35" t="str"/>
     </x:row>
@@ -5423,7 +5423,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C178" s="35" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D178" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5432,14 +5432,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F178" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G178" s="35" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="H178" s="35" t="str"/>
     </x:row>
-    <x:row r="179" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="179" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A179" s="26" t="n">
         <x:v>175</x:v>
       </x:c>
@@ -5447,7 +5447,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5456,14 +5456,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F179" s="32" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G179" s="35" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="H179" s="35" t="str"/>
     </x:row>
-    <x:row r="180" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="180" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A180" s="26" t="n">
         <x:v>176</x:v>
       </x:c>
@@ -5471,7 +5471,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C180" s="35" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D180" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5480,22 +5480,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F180" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="G180" s="35" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="H180" s="35" t="str"/>
     </x:row>
-    <x:row r="181" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="181" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A181" s="26" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C181" s="35" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D181" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5504,14 +5504,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F181" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G181" s="35" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="H181" s="35" t="str"/>
     </x:row>
-    <x:row r="182" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="182" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A182" s="26" t="n">
         <x:v>178</x:v>
       </x:c>
@@ -5519,7 +5519,7 @@
         <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5528,22 +5528,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F182" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G182" s="35" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="H182" s="35" t="str"/>
     </x:row>
-    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="183" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A183" s="26" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="35" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5552,22 +5552,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F183" s="32" t="n">
-        <x:v>0.181</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G183" s="35" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H183" s="35" t="str"/>
     </x:row>
-    <x:row r="184" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A184" s="26" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C184" s="35" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D184" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5576,10 +5576,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F184" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.308</x:v>
       </x:c>
       <x:c r="G184" s="35" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="H184" s="35" t="str"/>
     </x:row>
@@ -5591,7 +5591,7 @@
         <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C185" s="35" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D185" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5600,10 +5600,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F185" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="G185" s="35" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="H185" s="35" t="str"/>
     </x:row>
@@ -5612,10 +5612,10 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C186" s="35" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D186" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5624,14 +5624,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F186" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G186" s="35" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="H186" s="35" t="str"/>
     </x:row>
-    <x:row r="187" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="187" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A187" s="26" t="n">
         <x:v>183</x:v>
       </x:c>
@@ -5639,7 +5639,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5651,11 +5651,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G187" s="35" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="H187" s="35" t="str"/>
     </x:row>
-    <x:row r="188" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="188" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A188" s="26" t="n">
         <x:v>184</x:v>
       </x:c>
@@ -5663,7 +5663,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C188" s="35" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D188" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5672,14 +5672,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F188" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G188" s="35" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="H188" s="35" t="str"/>
     </x:row>
-    <x:row r="189" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="189" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A189" s="26" t="n">
         <x:v>185</x:v>
       </x:c>
@@ -5687,7 +5687,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5696,10 +5696,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F189" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G189" s="35" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="H189" s="35" t="str"/>
     </x:row>
@@ -5711,7 +5711,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C190" s="35" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D190" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5720,14 +5720,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F190" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G190" s="35" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="H190" s="35" t="str"/>
     </x:row>
-    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="191" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A191" s="26" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -5735,7 +5735,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5747,11 +5747,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G191" s="35" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="H191" s="35" t="str"/>
     </x:row>
-    <x:row r="192" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="192" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A192" s="26" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -5759,7 +5759,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="35" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D192" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5771,7 +5771,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G192" s="35" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="H192" s="35" t="str"/>
     </x:row>
@@ -5783,7 +5783,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="35" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D193" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5792,14 +5792,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F193" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G193" s="35" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="H193" s="35" t="str"/>
     </x:row>
-    <x:row r="194" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A194" s="26" t="n">
         <x:v>190</x:v>
       </x:c>
@@ -5807,7 +5807,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5816,10 +5816,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F194" s="32" t="n">
-        <x:v>0.014</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G194" s="35" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="H194" s="35" t="str"/>
     </x:row>
@@ -5831,7 +5831,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5840,14 +5840,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F195" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="G195" s="35" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="H195" s="35" t="str"/>
     </x:row>
-    <x:row r="196" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="196" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A196" s="26" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -5855,7 +5855,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5864,14 +5864,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F196" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G196" s="35" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="H196" s="35" t="str"/>
     </x:row>
-    <x:row r="197" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="197" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A197" s="26" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -5879,7 +5879,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5888,14 +5888,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F197" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G197" s="35" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="H197" s="35" t="str"/>
     </x:row>
-    <x:row r="198" ht="132" hidden="0" customHeight="1">
+    <x:row r="198" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A198" s="26" t="n">
         <x:v>194</x:v>
       </x:c>
@@ -5903,7 +5903,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5912,14 +5912,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F198" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G198" s="35" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="H198" s="35" t="str"/>
     </x:row>
-    <x:row r="199" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="199" ht="132" hidden="0" customHeight="1">
       <x:c r="A199" s="26" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -5927,7 +5927,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5936,10 +5936,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F199" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G199" s="35" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="H199" s="35" t="str"/>
     </x:row>
@@ -5951,7 +5951,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D200" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5960,14 +5960,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F200" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G200" s="35" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="H200" s="35" t="str"/>
     </x:row>
-    <x:row r="201" ht="132" hidden="0" customHeight="1">
+    <x:row r="201" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A201" s="26" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -5975,7 +5975,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="35" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D201" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5984,14 +5984,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F201" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G201" s="35" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="H201" s="35" t="str"/>
     </x:row>
-    <x:row r="202" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="202" ht="132" hidden="0" customHeight="1">
       <x:c r="A202" s="26" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -5999,7 +5999,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="35" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D202" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6008,14 +6008,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F202" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G202" s="35" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
       </x:c>
       <x:c r="H202" s="35" t="str"/>
     </x:row>
-    <x:row r="203" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="203" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A203" s="26" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -6023,52 +6023,76 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="35" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D203" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E203" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F203" s="32" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="G203" s="35" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="H203" s="35" t="str"/>
+    </x:row>
+    <x:row r="204" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A204" s="26" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B204" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C204" s="35" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D203" s="35" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E203" s="26" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F203" s="32" t="n">
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="G203" s="35" t="str">
+      <x:c r="D204" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E204" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F204" s="32" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="G204" s="35" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="H203" s="35" t="str"/>
-    </x:row>
-    <x:row r="204" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A204" s="27" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="B204" s="36" t="str">
+      <x:c r="H204" s="35" t="str"/>
+    </x:row>
+    <x:row r="205" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A205" s="27" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B205" s="36" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C204" s="36" t="str">
+      <x:c r="C205" s="36" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D204" s="36" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E204" s="27" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F204" s="33" t="n">
-        <x:v>0.004</x:v>
-      </x:c>
-      <x:c r="G204" s="36" t="str">
+      <x:c r="D205" s="36" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E205" s="27" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F205" s="33" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="G205" s="36" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="H204" s="36" t="str"/>
+      <x:c r="H205" s="36" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E5:E204">
+  <x:conditionalFormatting sqref="E5:E205">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="错误"/>
@@ -6076,7 +6100,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abbd3b80baa4a1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7830910ede384edb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6215,7 +6239,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I6" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J6" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6247,7 +6271,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I7" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J7" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6279,7 +6303,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I8" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J8" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6311,7 +6335,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I9" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J9" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6343,7 +6367,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I10" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J10" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6375,7 +6399,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I11" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J11" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6407,7 +6431,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I12" s="55" t="n">
-        <x:v>0.214</x:v>
+        <x:v>0.171</x:v>
       </x:c>
       <x:c r="J12" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6439,7 +6463,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I13" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J13" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6471,7 +6495,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I14" s="55" t="n">
-        <x:v>0.053</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="J14" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6503,7 +6527,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I15" s="55" t="n">
-        <x:v>0.036</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6535,7 +6559,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I16" s="55" t="n">
-        <x:v>0.022</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="J16" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6567,7 +6591,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I17" s="55" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J17" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6599,7 +6623,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I18" s="55" t="n">
-        <x:v>0.032</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="J18" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6631,7 +6655,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I19" s="55" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J19" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6663,7 +6687,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I20" s="55" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="J20" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6695,7 +6719,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I21" s="55" t="n">
-        <x:v>0.058</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="J21" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6727,7 +6751,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I22" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J22" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6759,7 +6783,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I23" s="55" t="n">
-        <x:v>0.028</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J23" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6791,7 +6815,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I24" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J24" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6823,7 +6847,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I25" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J25" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6855,7 +6879,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I26" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J26" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6887,7 +6911,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I27" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J27" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6919,7 +6943,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I28" s="55" t="n">
-        <x:v>0.146</x:v>
+        <x:v>0.071</x:v>
       </x:c>
       <x:c r="J28" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6951,7 +6975,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I29" s="55" t="n">
-        <x:v>0.111</x:v>
+        <x:v>0.046</x:v>
       </x:c>
       <x:c r="J29" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6983,7 +7007,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I30" s="55" t="n">
-        <x:v>0.094</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="J30" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7015,7 +7039,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I31" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J31" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7047,7 +7071,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I32" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J32" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7079,7 +7103,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I33" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J33" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7111,7 +7135,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I34" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J34" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7143,7 +7167,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I35" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J35" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7175,7 +7199,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I36" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J36" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7207,7 +7231,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I37" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J37" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7239,7 +7263,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I38" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J38" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7271,7 +7295,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I39" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J39" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7303,7 +7327,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I40" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J40" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7335,7 +7359,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I41" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J41" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7367,7 +7391,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I42" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J42" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7399,7 +7423,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I43" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J43" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7431,7 +7455,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I44" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J44" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7463,7 +7487,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I45" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J45" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7495,7 +7519,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I46" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J46" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7559,7 +7583,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I48" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J48" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7591,7 +7615,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I49" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J49" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7623,7 +7647,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I50" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J50" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7655,7 +7679,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I51" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J51" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7687,7 +7711,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I52" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J52" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7719,7 +7743,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I53" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J53" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7751,7 +7775,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I54" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J54" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7783,7 +7807,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I55" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J55" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7815,7 +7839,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I56" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J56" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7847,7 +7871,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I57" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J57" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7879,7 +7903,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I58" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J58" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7911,7 +7935,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I59" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J59" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7943,7 +7967,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I60" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J60" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7975,7 +7999,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I61" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J61" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8007,7 +8031,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I62" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J62" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8039,7 +8063,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I63" s="55" t="n">
-        <x:v>0.064</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="J63" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8071,7 +8095,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I64" s="55" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="J64" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8103,7 +8127,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I65" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J65" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8135,7 +8159,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I66" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J66" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8167,7 +8191,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I67" s="55" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="J67" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8199,7 +8223,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I68" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J68" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8231,7 +8255,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I69" s="55" t="n">
-        <x:v>0.028</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J69" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8263,45 +8287,45 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I70" s="55" t="n">
-        <x:v>64.649</x:v>
+        <x:v>30.836</x:v>
       </x:c>
       <x:c r="J70" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="71" ht="198" hidden="0" customHeight="1">
       <x:c r="A71" s="42" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C71" s="49" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
       </x:c>
       <x:c r="D71" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E71" s="49" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
       </x:c>
       <x:c r="F71" s="49" t="str">
-        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
+        <x:v>三个运行的检索结果完全一致，查询延迟变异系数不超过 50%，但生产开关仍保持关闭。</x:v>
       </x:c>
       <x:c r="G71" s="49" t="str">
-        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
+        <x:v>单次偶然结果或不稳定排名可能被错误当成可复现能力，导致后续模型对照失去公平基线。</x:v>
       </x:c>
       <x:c r="H71" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I71" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="J71" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="72" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A72" s="42" t="n">
         <x:v>68</x:v>
       </x:c>
@@ -8309,31 +8333,31 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C72" s="49" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D72" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E72" s="49" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="F72" s="49" t="str">
-        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
+        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
       </x:c>
       <x:c r="G72" s="49" t="str">
-        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
+        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
       </x:c>
       <x:c r="H72" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I72" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J72" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="73" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A73" s="42" t="n">
         <x:v>69</x:v>
       </x:c>
@@ -8341,31 +8365,31 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C73" s="49" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D73" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E73" s="49" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="F73" s="49" t="str">
-        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
+        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
       </x:c>
       <x:c r="G73" s="49" t="str">
-        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
+        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
       </x:c>
       <x:c r="H73" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I73" s="55" t="n">
-        <x:v>0.038</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J73" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="74" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A74" s="42" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -8373,57 +8397,57 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C74" s="49" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D74" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E74" s="49" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="F74" s="49" t="str">
-        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
+        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
       </x:c>
       <x:c r="G74" s="49" t="str">
-        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
+        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
       </x:c>
       <x:c r="H74" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I74" s="55" t="n">
-        <x:v>0.053</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="J74" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="75" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A75" s="42" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C75" s="49" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D75" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E75" s="49" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="F75" s="49" t="str">
-        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
+        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
       </x:c>
       <x:c r="G75" s="49" t="str">
-        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
+        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
       </x:c>
       <x:c r="H75" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I75" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="J75" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8437,57 +8461,57 @@
         <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C76" s="49" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D76" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E76" s="49" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="F76" s="49" t="str">
-        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
+        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
       </x:c>
       <x:c r="G76" s="49" t="str">
-        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
+        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
       </x:c>
       <x:c r="H76" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I76" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J76" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="132" hidden="0" customHeight="1">
+    <x:row r="77" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A77" s="42" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="49" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C77" s="49" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D77" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E77" s="49" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="F77" s="49" t="str">
-        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
+        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
       </x:c>
       <x:c r="G77" s="49" t="str">
-        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
+        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
       </x:c>
       <x:c r="H77" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I77" s="55" t="n">
-        <x:v>48.557</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J77" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8498,34 +8522,34 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C78" s="49" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D78" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E78" s="49" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="F78" s="49" t="str">
-        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
+        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
       </x:c>
       <x:c r="G78" s="49" t="str">
-        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
+        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
       </x:c>
       <x:c r="H78" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I78" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>30.236</x:v>
       </x:c>
       <x:c r="J78" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="79" ht="132" hidden="0" customHeight="1">
       <x:c r="A79" s="42" t="n">
         <x:v>75</x:v>
       </x:c>
@@ -8533,31 +8557,31 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C79" s="49" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D79" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E79" s="49" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="F79" s="49" t="str">
-        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
+        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
       </x:c>
       <x:c r="G79" s="49" t="str">
-        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
+        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
       </x:c>
       <x:c r="H79" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I79" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J79" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="80" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A80" s="42" t="n">
         <x:v>76</x:v>
       </x:c>
@@ -8565,25 +8589,25 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C80" s="49" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D80" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E80" s="49" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="F80" s="49" t="str">
-        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
+        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
       </x:c>
       <x:c r="G80" s="49" t="str">
-        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
+        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
       </x:c>
       <x:c r="H80" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I80" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J80" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8594,28 +8618,28 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C81" s="49" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D81" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E81" s="49" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="F81" s="49" t="str">
-        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
+        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
       </x:c>
       <x:c r="G81" s="49" t="str">
-        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
+        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
       </x:c>
       <x:c r="H81" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I81" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J81" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8629,25 +8653,25 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C82" s="49" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D82" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E82" s="49" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="F82" s="49" t="str">
-        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
+        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
       </x:c>
       <x:c r="G82" s="49" t="str">
-        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
+        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
       </x:c>
       <x:c r="H82" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I82" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J82" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8661,19 +8685,19 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C83" s="49" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D83" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E83" s="49" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="F83" s="49" t="str">
-        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
+        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
       </x:c>
       <x:c r="G83" s="49" t="str">
-        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
+        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
       </x:c>
       <x:c r="H83" s="52" t="str">
         <x:v>通过</x:v>
@@ -8685,7 +8709,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="84" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A84" s="42" t="n">
         <x:v>80</x:v>
       </x:c>
@@ -8693,31 +8717,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C84" s="49" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D84" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E84" s="49" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="F84" s="49" t="str">
-        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
+        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
       </x:c>
       <x:c r="G84" s="49" t="str">
-        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
+        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
       </x:c>
       <x:c r="H84" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I84" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J84" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="132" hidden="0" customHeight="1">
+    <x:row r="85" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A85" s="42" t="n">
         <x:v>81</x:v>
       </x:c>
@@ -8725,19 +8749,19 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C85" s="49" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D85" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E85" s="49" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="F85" s="49" t="str">
-        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
+        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
       </x:c>
       <x:c r="G85" s="49" t="str">
-        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
+        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
       </x:c>
       <x:c r="H85" s="52" t="str">
         <x:v>通过</x:v>
@@ -8749,7 +8773,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="86" ht="132" hidden="0" customHeight="1">
       <x:c r="A86" s="42" t="n">
         <x:v>82</x:v>
       </x:c>
@@ -8757,25 +8781,25 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="49" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D86" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E86" s="49" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="F86" s="49" t="str">
-        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
+        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
       </x:c>
       <x:c r="G86" s="49" t="str">
-        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
+        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
       </x:c>
       <x:c r="H86" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I86" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J86" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8789,63 +8813,63 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="49" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D87" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E87" s="49" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="F87" s="49" t="str">
-        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
+        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
       </x:c>
       <x:c r="G87" s="49" t="str">
-        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
+        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
       </x:c>
       <x:c r="H87" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I87" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J87" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="88" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A88" s="42" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="49" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D88" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E88" s="49" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="F88" s="49" t="str">
-        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
+        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
       </x:c>
       <x:c r="G88" s="49" t="str">
-        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
+        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
       </x:c>
       <x:c r="H88" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I88" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J88" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="132" hidden="0" customHeight="1">
+    <x:row r="89" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A89" s="42" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -8853,25 +8877,25 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C89" s="49" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D89" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E89" s="49" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="F89" s="49" t="str">
-        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
+        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
       </x:c>
       <x:c r="G89" s="49" t="str">
-        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
+        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
       </x:c>
       <x:c r="H89" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I89" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J89" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8885,19 +8909,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C90" s="49" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D90" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E90" s="49" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="F90" s="49" t="str">
-        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
+        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
       </x:c>
       <x:c r="G90" s="49" t="str">
-        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
+        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
       </x:c>
       <x:c r="H90" s="52" t="str">
         <x:v>通过</x:v>
@@ -8909,7 +8933,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="91" ht="132" hidden="0" customHeight="1">
       <x:c r="A91" s="42" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -8917,19 +8941,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C91" s="49" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D91" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E91" s="49" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="F91" s="49" t="str">
-        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
+        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
       </x:c>
       <x:c r="G91" s="49" t="str">
-        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
+        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
       </x:c>
       <x:c r="H91" s="52" t="str">
         <x:v>通过</x:v>
@@ -8941,7 +8965,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="92" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A92" s="42" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -8949,19 +8973,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C92" s="49" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D92" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E92" s="49" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="F92" s="49" t="str">
-        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
+        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
       </x:c>
       <x:c r="G92" s="49" t="str">
-        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
+        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
       </x:c>
       <x:c r="H92" s="52" t="str">
         <x:v>通过</x:v>
@@ -8973,7 +8997,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="93" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A93" s="42" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -8981,19 +9005,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="49" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D93" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E93" s="49" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="F93" s="49" t="str">
-        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
+        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
       </x:c>
       <x:c r="G93" s="49" t="str">
-        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
+        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
       </x:c>
       <x:c r="H93" s="52" t="str">
         <x:v>通过</x:v>
@@ -9005,7 +9029,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="94" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A94" s="42" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -9013,89 +9037,89 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="49" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D94" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E94" s="49" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="F94" s="49" t="str">
-        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
+        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
       </x:c>
       <x:c r="G94" s="49" t="str">
-        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
+        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
       </x:c>
       <x:c r="H94" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I94" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J94" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="95" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A95" s="42" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="49" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="49" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D95" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E95" s="49" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="F95" s="49" t="str">
-        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
+        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
       </x:c>
       <x:c r="G95" s="49" t="str">
-        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
+        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
       </x:c>
       <x:c r="H95" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I95" s="55" t="n">
-        <x:v>2.365</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J95" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="96" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A96" s="42" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C96" s="49" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D96" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E96" s="49" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="F96" s="49" t="str">
-        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
+        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
       </x:c>
       <x:c r="G96" s="49" t="str">
-        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
+        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
       </x:c>
       <x:c r="H96" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I96" s="55" t="n">
-        <x:v>0.039</x:v>
+        <x:v>2.386</x:v>
       </x:c>
       <x:c r="J96" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9109,31 +9133,31 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C97" s="49" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D97" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E97" s="49" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="F97" s="49" t="str">
-        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
+        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
       </x:c>
       <x:c r="G97" s="49" t="str">
-        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
+        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
       </x:c>
       <x:c r="H97" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I97" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="J97" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="98" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A98" s="42" t="n">
         <x:v>94</x:v>
       </x:c>
@@ -9141,31 +9165,31 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C98" s="49" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D98" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E98" s="49" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="F98" s="49" t="str">
-        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
+        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
       </x:c>
       <x:c r="G98" s="49" t="str">
-        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
+        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
       </x:c>
       <x:c r="H98" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I98" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J98" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="99" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A99" s="42" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -9173,25 +9197,25 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C99" s="49" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D99" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E99" s="49" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="F99" s="49" t="str">
-        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
+        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
       </x:c>
       <x:c r="G99" s="49" t="str">
-        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
+        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
       </x:c>
       <x:c r="H99" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I99" s="55" t="n">
-        <x:v>1.156</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J99" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9202,34 +9226,34 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C100" s="49" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D100" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E100" s="49" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="F100" s="49" t="str">
-        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
+        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
       </x:c>
       <x:c r="G100" s="49" t="str">
-        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
+        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
       </x:c>
       <x:c r="H100" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I100" s="55" t="n">
-        <x:v>0.196</x:v>
+        <x:v>1.128</x:v>
       </x:c>
       <x:c r="J100" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="101" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A101" s="42" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -9237,31 +9261,31 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C101" s="49" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D101" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E101" s="49" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="F101" s="49" t="str">
-        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
+        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
       </x:c>
       <x:c r="G101" s="49" t="str">
-        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
+        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
       </x:c>
       <x:c r="H101" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I101" s="55" t="n">
-        <x:v>0.088</x:v>
+        <x:v>0.188</x:v>
       </x:c>
       <x:c r="J101" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="102" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A102" s="42" t="n">
         <x:v>98</x:v>
       </x:c>
@@ -9269,31 +9293,31 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C102" s="49" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D102" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E102" s="49" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="F102" s="49" t="str">
-        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
+        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
       </x:c>
       <x:c r="G102" s="49" t="str">
-        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
+        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
       </x:c>
       <x:c r="H102" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I102" s="55" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.106</x:v>
       </x:c>
       <x:c r="J102" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="103" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A103" s="42" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -9301,83 +9325,83 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C103" s="49" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D103" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E103" s="49" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="F103" s="49" t="str">
-        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
+        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
       </x:c>
       <x:c r="G103" s="49" t="str">
-        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
+        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
       </x:c>
       <x:c r="H103" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I103" s="55" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.056</x:v>
       </x:c>
       <x:c r="J103" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="132" hidden="0" customHeight="1">
+    <x:row r="104" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A104" s="42" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="49" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C104" s="49" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D104" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E104" s="49" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="F104" s="49" t="str">
-        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
+        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
       </x:c>
       <x:c r="G104" s="49" t="str">
-        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
+        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
       </x:c>
       <x:c r="H104" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I104" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="J104" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="105" ht="132" hidden="0" customHeight="1">
       <x:c r="A105" s="42" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C105" s="49" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D105" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E105" s="49" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="F105" s="49" t="str">
-        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
+        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
       </x:c>
       <x:c r="G105" s="49" t="str">
-        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
+        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
       </x:c>
       <x:c r="H105" s="52" t="str">
         <x:v>通过</x:v>
@@ -9389,7 +9413,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="106" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A106" s="42" t="n">
         <x:v>102</x:v>
       </x:c>
@@ -9397,19 +9421,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C106" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D106" s="49" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E106" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="F106" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
       </x:c>
       <x:c r="G106" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
       </x:c>
       <x:c r="H106" s="52" t="str">
         <x:v>通过</x:v>
@@ -9429,10 +9453,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C107" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D107" s="49" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E107" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9461,10 +9485,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C108" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D108" s="49" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E108" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9479,7 +9503,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I108" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J108" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9493,10 +9517,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C109" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D109" s="49" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E109" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9511,7 +9535,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I109" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J109" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9525,10 +9549,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D110" s="49" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E110" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9549,7 +9573,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="111" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A111" s="42" t="n">
         <x:v>107</x:v>
       </x:c>
@@ -9557,19 +9581,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D111" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E111" s="49" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F111" s="49" t="str">
-        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G111" s="49" t="str">
-        <x:v>查询改写异常可能导致完全不检索。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H111" s="52" t="str">
         <x:v>通过</x:v>
@@ -9581,7 +9605,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="112" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A112" s="42" t="n">
         <x:v>108</x:v>
       </x:c>
@@ -9589,25 +9613,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D112" s="49" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E112" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="F112" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
       </x:c>
       <x:c r="G112" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>查询改写异常可能导致完全不检索。</x:v>
       </x:c>
       <x:c r="H112" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I112" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J112" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9621,10 +9645,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D113" s="49" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E113" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9653,10 +9677,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D114" s="49" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E114" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9685,10 +9709,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D115" s="49" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E115" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9703,7 +9727,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I115" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J115" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9717,10 +9741,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D116" s="49" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E116" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9749,10 +9773,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D117" s="49" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E117" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9773,7 +9797,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="118" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A118" s="42" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -9781,31 +9805,31 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="49" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D118" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E118" s="49" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F118" s="49" t="str">
-        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G118" s="49" t="str">
-        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H118" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I118" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J118" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="119" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A119" s="42" t="n">
         <x:v>115</x:v>
       </x:c>
@@ -9813,19 +9837,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="49" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D119" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E119" s="49" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="F119" s="49" t="str">
-        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
+        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
       </x:c>
       <x:c r="G119" s="49" t="str">
-        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
+        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
       </x:c>
       <x:c r="H119" s="52" t="str">
         <x:v>通过</x:v>
@@ -9842,28 +9866,28 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B120" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="49" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D120" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E120" s="49" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="F120" s="49" t="str">
-        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
+        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
       </x:c>
       <x:c r="G120" s="49" t="str">
-        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
+        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
       </x:c>
       <x:c r="H120" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I120" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J120" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9877,19 +9901,19 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C121" s="49" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D121" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E121" s="49" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="F121" s="49" t="str">
-        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
+        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
       </x:c>
       <x:c r="G121" s="49" t="str">
-        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
+        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
       </x:c>
       <x:c r="H121" s="52" t="str">
         <x:v>通过</x:v>
@@ -9901,7 +9925,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="132" hidden="0" customHeight="1">
+    <x:row r="122" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A122" s="42" t="n">
         <x:v>118</x:v>
       </x:c>
@@ -9909,31 +9933,31 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C122" s="49" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D122" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E122" s="49" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="F122" s="49" t="str">
-        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
+        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
       </x:c>
       <x:c r="G122" s="49" t="str">
-        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
+        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
       </x:c>
       <x:c r="H122" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I122" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J122" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="123" ht="132" hidden="0" customHeight="1">
       <x:c r="A123" s="42" t="n">
         <x:v>119</x:v>
       </x:c>
@@ -9941,63 +9965,63 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C123" s="49" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D123" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E123" s="49" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="F123" s="49" t="str">
-        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
+        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
       </x:c>
       <x:c r="G123" s="49" t="str">
-        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
+        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
       </x:c>
       <x:c r="H123" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I123" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J123" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="132" hidden="0" customHeight="1">
+    <x:row r="124" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A124" s="42" t="n">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C124" s="49" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D124" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E124" s="49" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="F124" s="49" t="str">
-        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
+        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
       </x:c>
       <x:c r="G124" s="49" t="str">
-        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
+        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
       </x:c>
       <x:c r="H124" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I124" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J124" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="125" ht="132" hidden="0" customHeight="1">
       <x:c r="A125" s="42" t="n">
         <x:v>121</x:v>
       </x:c>
@@ -10005,25 +10029,25 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C125" s="49" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D125" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E125" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="F125" s="49" t="str">
-        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
+        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
       </x:c>
       <x:c r="G125" s="49" t="str">
-        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
+        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
       </x:c>
       <x:c r="H125" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I125" s="55" t="n">
-        <x:v>15.585</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J125" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10037,63 +10061,63 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C126" s="49" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D126" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E126" s="49" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="F126" s="49" t="str">
-        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
+        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
       </x:c>
       <x:c r="G126" s="49" t="str">
-        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
+        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
       </x:c>
       <x:c r="H126" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I126" s="55" t="n">
-        <x:v>15.492</x:v>
+        <x:v>14.87</x:v>
       </x:c>
       <x:c r="J126" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="132" hidden="0" customHeight="1">
+    <x:row r="127" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A127" s="42" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C127" s="49" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D127" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E127" s="49" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="F127" s="49" t="str">
-        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
+        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
       </x:c>
       <x:c r="G127" s="49" t="str">
-        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
+        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
       </x:c>
       <x:c r="H127" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I127" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>14.978</x:v>
       </x:c>
       <x:c r="J127" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="128" ht="132" hidden="0" customHeight="1">
       <x:c r="A128" s="42" t="n">
         <x:v>124</x:v>
       </x:c>
@@ -10101,25 +10125,25 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C128" s="49" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D128" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E128" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="F128" s="49" t="str">
-        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
+        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
       </x:c>
       <x:c r="G128" s="49" t="str">
-        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
+        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
       </x:c>
       <x:c r="H128" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I128" s="55" t="n">
-        <x:v>19.508</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J128" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10133,63 +10157,63 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="49" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D129" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E129" s="49" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="F129" s="49" t="str">
-        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
+        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
       </x:c>
       <x:c r="G129" s="49" t="str">
-        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
+        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
       </x:c>
       <x:c r="H129" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I129" s="55" t="n">
-        <x:v>15.364</x:v>
+        <x:v>18.845</x:v>
       </x:c>
       <x:c r="J129" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="130" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A130" s="42" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C130" s="49" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D130" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E130" s="49" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="F130" s="49" t="str">
-        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
+        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
       </x:c>
       <x:c r="G130" s="49" t="str">
-        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
+        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
       </x:c>
       <x:c r="H130" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I130" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>17.713</x:v>
       </x:c>
       <x:c r="J130" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="131" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A131" s="42" t="n">
         <x:v>127</x:v>
       </x:c>
@@ -10197,31 +10221,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C131" s="49" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D131" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E131" s="49" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="F131" s="49" t="str">
-        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
+        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
       </x:c>
       <x:c r="G131" s="49" t="str">
-        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
+        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
       </x:c>
       <x:c r="H131" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I131" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J131" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="132" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A132" s="42" t="n">
         <x:v>128</x:v>
       </x:c>
@@ -10229,19 +10253,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C132" s="49" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D132" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E132" s="49" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="F132" s="49" t="str">
-        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
+        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
       </x:c>
       <x:c r="G132" s="49" t="str">
-        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
+        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
       </x:c>
       <x:c r="H132" s="52" t="str">
         <x:v>通过</x:v>
@@ -10261,25 +10285,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C133" s="49" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D133" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E133" s="49" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="F133" s="49" t="str">
-        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
+        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
       </x:c>
       <x:c r="G133" s="49" t="str">
-        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
+        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
       </x:c>
       <x:c r="H133" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I133" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J133" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10293,19 +10317,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C134" s="49" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D134" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E134" s="49" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="F134" s="49" t="str">
-        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
+        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
       </x:c>
       <x:c r="G134" s="49" t="str">
-        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
+        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
       </x:c>
       <x:c r="H134" s="52" t="str">
         <x:v>通过</x:v>
@@ -10317,7 +10341,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A135" s="42" t="n">
         <x:v>131</x:v>
       </x:c>
@@ -10325,31 +10349,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="49" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D135" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E135" s="49" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="F135" s="49" t="str">
-        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
+        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
       </x:c>
       <x:c r="G135" s="49" t="str">
-        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
+        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
       </x:c>
       <x:c r="H135" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I135" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J135" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="136" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A136" s="42" t="n">
         <x:v>132</x:v>
       </x:c>
@@ -10357,31 +10381,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="49" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D136" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E136" s="49" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="F136" s="49" t="str">
-        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
+        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
       </x:c>
       <x:c r="G136" s="49" t="str">
-        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
+        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
       </x:c>
       <x:c r="H136" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I136" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J136" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="137" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A137" s="42" t="n">
         <x:v>133</x:v>
       </x:c>
@@ -10389,25 +10413,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="49" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D137" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E137" s="49" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="F137" s="49" t="str">
-        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
+        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
       </x:c>
       <x:c r="G137" s="49" t="str">
-        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
+        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
       </x:c>
       <x:c r="H137" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I137" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J137" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10421,31 +10445,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D138" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E138" s="49" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="F138" s="49" t="str">
-        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
+        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
       </x:c>
       <x:c r="G138" s="49" t="str">
-        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
+        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
       </x:c>
       <x:c r="H138" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I138" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J138" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="132" hidden="0" customHeight="1">
+    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A139" s="42" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -10453,31 +10477,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D139" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E139" s="49" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="F139" s="49" t="str">
-        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
+        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
       </x:c>
       <x:c r="G139" s="49" t="str">
-        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
+        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
       </x:c>
       <x:c r="H139" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I139" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J139" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="140" ht="132" hidden="0" customHeight="1">
       <x:c r="A140" s="42" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -10485,25 +10509,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="49" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D140" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E140" s="49" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="F140" s="49" t="str">
-        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
+        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
       </x:c>
       <x:c r="G140" s="49" t="str">
-        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
+        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
       </x:c>
       <x:c r="H140" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I140" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J140" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10517,31 +10541,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="49" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D141" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E141" s="49" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="F141" s="49" t="str">
-        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
+        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
       </x:c>
       <x:c r="G141" s="49" t="str">
-        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
+        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
       </x:c>
       <x:c r="H141" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I141" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J141" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A142" s="42" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -10549,25 +10573,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="49" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D142" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E142" s="49" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="F142" s="49" t="str">
-        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
+        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
       </x:c>
       <x:c r="G142" s="49" t="str">
-        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
+        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
       </x:c>
       <x:c r="H142" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I142" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J142" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10578,28 +10602,28 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B143" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="49" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D143" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E143" s="49" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="F143" s="49" t="str">
-        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
+        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
       </x:c>
       <x:c r="G143" s="49" t="str">
-        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
+        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
       </x:c>
       <x:c r="H143" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I143" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J143" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10613,25 +10637,25 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C144" s="49" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D144" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E144" s="49" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="F144" s="49" t="str">
-        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
+        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
       </x:c>
       <x:c r="G144" s="49" t="str">
-        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
+        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
       </x:c>
       <x:c r="H144" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I144" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J144" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10645,31 +10669,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C145" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D145" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E145" s="49" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="F145" s="49" t="str">
-        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
+        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
       </x:c>
       <x:c r="G145" s="49" t="str">
-        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
+        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
       </x:c>
       <x:c r="H145" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I145" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J145" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="146" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A146" s="42" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -10677,31 +10701,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C146" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D146" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E146" s="49" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="F146" s="49" t="str">
-        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
+        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
       </x:c>
       <x:c r="G146" s="49" t="str">
-        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
+        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
       </x:c>
       <x:c r="H146" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I146" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J146" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="147" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A147" s="42" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -10709,25 +10733,25 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C147" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D147" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E147" s="49" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="F147" s="49" t="str">
-        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
+        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
       </x:c>
       <x:c r="G147" s="49" t="str">
-        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
+        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
       </x:c>
       <x:c r="H147" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I147" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J147" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10741,31 +10765,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="49" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D148" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E148" s="49" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="F148" s="49" t="str">
-        <x:v>两条无去重键文档均被保留。</x:v>
+        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
       </x:c>
       <x:c r="G148" s="49" t="str">
-        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
+        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
       </x:c>
       <x:c r="H148" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I148" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J148" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A149" s="42" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -10773,25 +10797,25 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="49" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D149" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E149" s="49" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="F149" s="49" t="str">
-        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
+        <x:v>两条无去重键文档均被保留。</x:v>
       </x:c>
       <x:c r="G149" s="49" t="str">
-        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
+        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
       </x:c>
       <x:c r="H149" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I149" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J149" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10805,19 +10829,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="49" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D150" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E150" s="49" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="F150" s="49" t="str">
-        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
+        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
       </x:c>
       <x:c r="G150" s="49" t="str">
-        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
+        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
       </x:c>
       <x:c r="H150" s="52" t="str">
         <x:v>通过</x:v>
@@ -10829,27 +10853,27 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="151" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A151" s="42" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B151" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="49" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D151" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E151" s="49" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="F151" s="49" t="str">
-        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
+        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
       </x:c>
       <x:c r="G151" s="49" t="str">
-        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
+        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
       </x:c>
       <x:c r="H151" s="52" t="str">
         <x:v>通过</x:v>
@@ -10861,7 +10885,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="152" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A152" s="42" t="n">
         <x:v>148</x:v>
       </x:c>
@@ -10869,31 +10893,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C152" s="49" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D152" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E152" s="49" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="F152" s="49" t="str">
-        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
+        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
       </x:c>
       <x:c r="G152" s="49" t="str">
-        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
+        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
       </x:c>
       <x:c r="H152" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I152" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J152" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="153" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A153" s="42" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -10901,31 +10925,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C153" s="49" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D153" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E153" s="49" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="F153" s="49" t="str">
-        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
+        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
       </x:c>
       <x:c r="G153" s="49" t="str">
-        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
+        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
       </x:c>
       <x:c r="H153" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I153" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J153" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="132" hidden="0" customHeight="1">
+    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A154" s="42" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -10933,19 +10957,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C154" s="49" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D154" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E154" s="49" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="F154" s="49" t="str">
-        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
+        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
       </x:c>
       <x:c r="G154" s="49" t="str">
-        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
+        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
       </x:c>
       <x:c r="H154" s="52" t="str">
         <x:v>通过</x:v>
@@ -10965,31 +10989,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C155" s="49" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D155" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E155" s="49" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="F155" s="49" t="str">
-        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
+        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
       </x:c>
       <x:c r="G155" s="49" t="str">
-        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
+        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
       </x:c>
       <x:c r="H155" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I155" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J155" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="156" ht="132" hidden="0" customHeight="1">
       <x:c r="A156" s="42" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -10997,31 +11021,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="49" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D156" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E156" s="49" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="F156" s="49" t="str">
-        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
+        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
       </x:c>
       <x:c r="G156" s="49" t="str">
-        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
+        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
       </x:c>
       <x:c r="H156" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I156" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J156" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="157" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A157" s="42" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -11029,19 +11053,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="49" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D157" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E157" s="49" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="F157" s="49" t="str">
-        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
+        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
       </x:c>
       <x:c r="G157" s="49" t="str">
-        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
+        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
       </x:c>
       <x:c r="H157" s="52" t="str">
         <x:v>通过</x:v>
@@ -11053,7 +11077,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A158" s="42" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -11061,25 +11085,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="49" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D158" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E158" s="49" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F158" s="49" t="str">
-        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
+        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
       </x:c>
       <x:c r="G158" s="49" t="str">
-        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
+        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
       </x:c>
       <x:c r="H158" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I158" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J158" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11093,25 +11117,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="49" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D159" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E159" s="49" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="F159" s="49" t="str">
-        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
+        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
       </x:c>
       <x:c r="G159" s="49" t="str">
-        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
+        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
       </x:c>
       <x:c r="H159" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I159" s="55" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J159" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11125,31 +11149,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="49" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D160" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E160" s="49" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="F160" s="49" t="str">
-        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
+        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
       </x:c>
       <x:c r="G160" s="49" t="str">
-        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
+        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
       </x:c>
       <x:c r="H160" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I160" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.117</x:v>
       </x:c>
       <x:c r="J160" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="161" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A161" s="42" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -11157,31 +11181,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="49" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D161" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E161" s="49" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="F161" s="49" t="str">
-        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
+        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
       </x:c>
       <x:c r="G161" s="49" t="str">
-        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
+        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
       </x:c>
       <x:c r="H161" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I161" s="55" t="n">
-        <x:v>0.022</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J161" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A162" s="42" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -11189,31 +11213,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="49" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D162" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E162" s="49" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="F162" s="49" t="str">
-        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
+        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
       </x:c>
       <x:c r="G162" s="49" t="str">
-        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
+        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
       </x:c>
       <x:c r="H162" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I162" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J162" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="132" hidden="0" customHeight="1">
+    <x:row r="163" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A163" s="42" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -11221,31 +11245,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="49" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D163" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E163" s="49" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="F163" s="49" t="str">
-        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
+        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
       </x:c>
       <x:c r="G163" s="49" t="str">
-        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
+        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
       </x:c>
       <x:c r="H163" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I163" s="55" t="n">
-        <x:v>0.164</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J163" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="164" ht="132" hidden="0" customHeight="1">
       <x:c r="A164" s="42" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -11253,25 +11277,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="49" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D164" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E164" s="49" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="F164" s="49" t="str">
-        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
+        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
       </x:c>
       <x:c r="G164" s="49" t="str">
-        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
+        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
       </x:c>
       <x:c r="H164" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I164" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.225</x:v>
       </x:c>
       <x:c r="J164" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11285,25 +11309,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="49" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D165" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E165" s="49" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="F165" s="49" t="str">
-        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
+        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
       </x:c>
       <x:c r="G165" s="49" t="str">
-        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
+        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
       </x:c>
       <x:c r="H165" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I165" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J165" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11317,63 +11341,63 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="49" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D166" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E166" s="49" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="F166" s="49" t="str">
-        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
+        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
       </x:c>
       <x:c r="G166" s="49" t="str">
-        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
+        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
       </x:c>
       <x:c r="H166" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I166" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J166" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="167" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A167" s="42" t="n">
         <x:v>163</x:v>
       </x:c>
       <x:c r="B167" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="49" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D167" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E167" s="49" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="F167" s="49" t="str">
-        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
+        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
       </x:c>
       <x:c r="G167" s="49" t="str">
-        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
+        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
       </x:c>
       <x:c r="H167" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I167" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J167" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="168" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A168" s="42" t="n">
         <x:v>164</x:v>
       </x:c>
@@ -11381,31 +11405,31 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C168" s="49" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D168" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E168" s="49" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="F168" s="49" t="str">
-        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
+        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
       </x:c>
       <x:c r="G168" s="49" t="str">
-        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
+        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
       </x:c>
       <x:c r="H168" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I168" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J168" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="169" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A169" s="42" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -11413,31 +11437,31 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C169" s="49" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D169" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E169" s="49" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="F169" s="49" t="str">
-        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
+        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
       </x:c>
       <x:c r="G169" s="49" t="str">
-        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
+        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
       </x:c>
       <x:c r="H169" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I169" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J169" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A170" s="42" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -11445,89 +11469,89 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C170" s="49" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D170" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E170" s="49" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="F170" s="49" t="str">
-        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
+        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
       </x:c>
       <x:c r="G170" s="49" t="str">
-        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
+        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
       </x:c>
       <x:c r="H170" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I170" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J170" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="171" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A171" s="42" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B171" s="49" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C171" s="49" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D171" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E171" s="49" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="F171" s="49" t="str">
-        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
+        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
       </x:c>
       <x:c r="G171" s="49" t="str">
-        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
+        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
       </x:c>
       <x:c r="H171" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I171" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J171" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="172" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A172" s="42" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C172" s="49" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D172" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E172" s="49" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="F172" s="49" t="str">
-        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
+        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
       </x:c>
       <x:c r="G172" s="49" t="str">
-        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
+        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
       </x:c>
       <x:c r="H172" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I172" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J172" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11541,25 +11565,25 @@
         <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C173" s="49" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D173" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E173" s="49" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="F173" s="49" t="str">
-        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
+        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
       </x:c>
       <x:c r="G173" s="49" t="str">
-        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
+        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
       </x:c>
       <x:c r="H173" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I173" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J173" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11570,22 +11594,22 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C174" s="49" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D174" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E174" s="49" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="F174" s="49" t="str">
-        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
+        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
       </x:c>
       <x:c r="G174" s="49" t="str">
-        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
+        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
       </x:c>
       <x:c r="H174" s="52" t="str">
         <x:v>通过</x:v>
@@ -11605,31 +11629,31 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C175" s="49" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D175" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E175" s="49" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="F175" s="49" t="str">
-        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
+        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
       </x:c>
       <x:c r="G175" s="49" t="str">
-        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
+        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
       </x:c>
       <x:c r="H175" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I175" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J175" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="176" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A176" s="42" t="n">
         <x:v>172</x:v>
       </x:c>
@@ -11637,51 +11661,51 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C176" s="49" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D176" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E176" s="49" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="F176" s="49" t="str">
-        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
+        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
       </x:c>
       <x:c r="G176" s="49" t="str">
-        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
+        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
       </x:c>
       <x:c r="H176" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I176" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J176" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="177" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A177" s="42" t="n">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B177" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C177" s="49" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D177" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E177" s="49" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="F177" s="49" t="str">
-        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
+        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
       </x:c>
       <x:c r="G177" s="49" t="str">
-        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
+        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
       </x:c>
       <x:c r="H177" s="52" t="str">
         <x:v>通过</x:v>
@@ -11693,7 +11717,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="178" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A178" s="42" t="n">
         <x:v>174</x:v>
       </x:c>
@@ -11701,25 +11725,25 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C178" s="49" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D178" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E178" s="49" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="F178" s="49" t="str">
-        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
+        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
       </x:c>
       <x:c r="G178" s="49" t="str">
-        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
+        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
       </x:c>
       <x:c r="H178" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I178" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J178" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11733,31 +11757,31 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C179" s="49" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D179" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E179" s="49" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="F179" s="49" t="str">
-        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
+        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
       </x:c>
       <x:c r="G179" s="49" t="str">
-        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
+        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
       </x:c>
       <x:c r="H179" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I179" s="55" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J179" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A180" s="42" t="n">
         <x:v>176</x:v>
       </x:c>
@@ -11765,63 +11789,63 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C180" s="49" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D180" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E180" s="49" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="F180" s="49" t="str">
-        <x:v>单子查询继续走直接调用路径。</x:v>
+        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
       </x:c>
       <x:c r="G180" s="49" t="str">
-        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
+        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
       </x:c>
       <x:c r="H180" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I180" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="J180" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="181" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A181" s="42" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C181" s="49" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D181" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E181" s="49" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="F181" s="49" t="str">
-        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
+        <x:v>单子查询继续走直接调用路径。</x:v>
       </x:c>
       <x:c r="G181" s="49" t="str">
-        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
+        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
       </x:c>
       <x:c r="H181" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I181" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J181" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="182" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A182" s="42" t="n">
         <x:v>178</x:v>
       </x:c>
@@ -11829,25 +11853,25 @@
         <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C182" s="49" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D182" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E182" s="49" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="F182" s="49" t="str">
-        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
+        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
       </x:c>
       <x:c r="G182" s="49" t="str">
-        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
+        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
       </x:c>
       <x:c r="H182" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I182" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J182" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11858,28 +11882,28 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="49" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C183" s="49" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D183" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E183" s="49" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F183" s="49" t="str">
-        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
+        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
       </x:c>
       <x:c r="G183" s="49" t="str">
-        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
+        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
       </x:c>
       <x:c r="H183" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I183" s="55" t="n">
-        <x:v>0.181</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J183" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11890,34 +11914,34 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C184" s="49" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D184" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E184" s="49" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="F184" s="49" t="str">
-        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
+        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
       </x:c>
       <x:c r="G184" s="49" t="str">
-        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
+        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
       </x:c>
       <x:c r="H184" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I184" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.308</x:v>
       </x:c>
       <x:c r="J184" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="132" hidden="0" customHeight="1">
+    <x:row r="185" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A185" s="42" t="n">
         <x:v>181</x:v>
       </x:c>
@@ -11925,25 +11949,25 @@
         <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C185" s="49" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D185" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E185" s="49" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="F185" s="49" t="str">
-        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
+        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
       </x:c>
       <x:c r="G185" s="49" t="str">
-        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
+        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
       </x:c>
       <x:c r="H185" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I185" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="J185" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11954,34 +11978,34 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C186" s="49" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D186" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E186" s="49" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="F186" s="49" t="str">
-        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
+        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
       </x:c>
       <x:c r="G186" s="49" t="str">
-        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
+        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
       </x:c>
       <x:c r="H186" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I186" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J186" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="187" ht="132" hidden="0" customHeight="1">
       <x:c r="A187" s="42" t="n">
         <x:v>183</x:v>
       </x:c>
@@ -11989,19 +12013,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C187" s="49" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D187" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E187" s="49" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="F187" s="49" t="str">
-        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
+        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
       </x:c>
       <x:c r="G187" s="49" t="str">
-        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
+        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
       </x:c>
       <x:c r="H187" s="52" t="str">
         <x:v>通过</x:v>
@@ -12013,7 +12037,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="188" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A188" s="42" t="n">
         <x:v>184</x:v>
       </x:c>
@@ -12021,25 +12045,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C188" s="49" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D188" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E188" s="49" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="F188" s="49" t="str">
-        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
+        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
       </x:c>
       <x:c r="G188" s="49" t="str">
-        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
+        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
       </x:c>
       <x:c r="H188" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I188" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J188" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12053,31 +12077,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C189" s="49" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D189" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E189" s="49" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="F189" s="49" t="str">
-        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
+        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
       </x:c>
       <x:c r="G189" s="49" t="str">
-        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
+        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
       </x:c>
       <x:c r="H189" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I189" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J189" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="190" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A190" s="42" t="n">
         <x:v>186</x:v>
       </x:c>
@@ -12085,31 +12109,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C190" s="49" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D190" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E190" s="49" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="F190" s="49" t="str">
-        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
+        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
       </x:c>
       <x:c r="G190" s="49" t="str">
-        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
+        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
       </x:c>
       <x:c r="H190" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I190" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J190" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="191" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A191" s="42" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -12117,19 +12141,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="49" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D191" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E191" s="49" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="F191" s="49" t="str">
-        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
+        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
       </x:c>
       <x:c r="G191" s="49" t="str">
-        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
+        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
       </x:c>
       <x:c r="H191" s="52" t="str">
         <x:v>通过</x:v>
@@ -12149,19 +12173,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="49" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D192" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E192" s="49" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="F192" s="49" t="str">
-        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
+        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
       </x:c>
       <x:c r="G192" s="49" t="str">
-        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
+        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
       </x:c>
       <x:c r="H192" s="52" t="str">
         <x:v>通过</x:v>
@@ -12181,31 +12205,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="49" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D193" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E193" s="49" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="F193" s="49" t="str">
-        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
+        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
       </x:c>
       <x:c r="G193" s="49" t="str">
-        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
+        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
       </x:c>
       <x:c r="H193" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I193" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J193" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="194" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A194" s="42" t="n">
         <x:v>190</x:v>
       </x:c>
@@ -12213,31 +12237,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="49" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D194" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E194" s="49" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="F194" s="49" t="str">
-        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
+        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
       </x:c>
       <x:c r="G194" s="49" t="str">
-        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
+        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
       </x:c>
       <x:c r="H194" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I194" s="55" t="n">
-        <x:v>0.014</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J194" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="195" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A195" s="42" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -12245,31 +12269,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="49" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D195" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E195" s="49" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="F195" s="49" t="str">
-        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
+        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
       </x:c>
       <x:c r="G195" s="49" t="str">
-        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
+        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
       </x:c>
       <x:c r="H195" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I195" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="J195" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="196" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A196" s="42" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -12277,25 +12301,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="49" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D196" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E196" s="49" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="F196" s="49" t="str">
-        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
+        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
       </x:c>
       <x:c r="G196" s="49" t="str">
-        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
+        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
       </x:c>
       <x:c r="H196" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I196" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J196" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12309,31 +12333,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="49" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D197" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E197" s="49" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="F197" s="49" t="str">
-        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
+        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
       </x:c>
       <x:c r="G197" s="49" t="str">
-        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
+        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
       </x:c>
       <x:c r="H197" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I197" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J197" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" ht="132" hidden="0" customHeight="1">
+    <x:row r="198" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A198" s="42" t="n">
         <x:v>194</x:v>
       </x:c>
@@ -12341,31 +12365,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="49" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D198" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E198" s="49" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="F198" s="49" t="str">
-        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
+        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
       </x:c>
       <x:c r="G198" s="49" t="str">
-        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
+        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
       </x:c>
       <x:c r="H198" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I198" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J198" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="199" ht="132" hidden="0" customHeight="1">
       <x:c r="A199" s="42" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -12373,25 +12397,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="49" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D199" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E199" s="49" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="F199" s="49" t="str">
-        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
+        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
       </x:c>
       <x:c r="G199" s="49" t="str">
-        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
+        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
       </x:c>
       <x:c r="H199" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I199" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J199" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12405,31 +12429,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="49" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D200" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E200" s="49" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="F200" s="49" t="str">
-        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G200" s="49" t="str">
-        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
       </x:c>
       <x:c r="H200" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I200" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J200" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="132" hidden="0" customHeight="1">
+    <x:row r="201" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A201" s="42" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -12437,31 +12461,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="49" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D201" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E201" s="49" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="F201" s="49" t="str">
-        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
       </x:c>
       <x:c r="G201" s="49" t="str">
-        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
       </x:c>
       <x:c r="H201" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I201" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J201" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="202" ht="132" hidden="0" customHeight="1">
       <x:c r="A202" s="42" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -12469,31 +12493,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="49" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D202" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E202" s="49" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
       </x:c>
       <x:c r="F202" s="49" t="str">
-        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G202" s="49" t="str">
-        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
       </x:c>
       <x:c r="H202" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I202" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J202" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="203" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A203" s="42" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -12501,59 +12525,91 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="49" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D203" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E203" s="49" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="F203" s="49" t="str">
+        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+      </x:c>
+      <x:c r="G203" s="49" t="str">
+        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+      </x:c>
+      <x:c r="H203" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I203" s="55" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="J203" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A204" s="42" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B204" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C204" s="49" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D203" s="49" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E203" s="49" t="str">
+      <x:c r="D204" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E204" s="49" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="F203" s="49" t="str">
+      <x:c r="F204" s="49" t="str">
         <x:v>限流进入可重试失败类别，不被误记为论文查无。</x:v>
       </x:c>
-      <x:c r="G203" s="49" t="str">
+      <x:c r="G204" s="49" t="str">
         <x:v>匿名访问限流可能污染覆盖率并错误触发论文隔离。</x:v>
       </x:c>
-      <x:c r="H203" s="52" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I203" s="55" t="n">
-        <x:v>0.001</x:v>
-      </x:c>
-      <x:c r="J203" s="58" t="str">
-        <x:v>已登记</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" ht="132" hidden="0" customHeight="1">
-      <x:c r="A204" s="45" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="B204" s="50" t="str">
+      <x:c r="H204" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I204" s="55" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="J204" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="132" hidden="0" customHeight="1">
+      <x:c r="A205" s="45" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B205" s="50" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C204" s="50" t="str">
+      <x:c r="C205" s="50" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D204" s="50" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E204" s="50" t="str">
+      <x:c r="D205" s="50" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E205" s="50" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="F204" s="50" t="str">
+      <x:c r="F205" s="50" t="str">
         <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
       </x:c>
-      <x:c r="G204" s="50" t="str">
+      <x:c r="G205" s="50" t="str">
         <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
       </x:c>
-      <x:c r="H204" s="53" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I204" s="56" t="n">
-        <x:v>0.004</x:v>
-      </x:c>
-      <x:c r="J204" s="59" t="str">
+      <x:c r="H205" s="53" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I205" s="56" t="n">
+        <x:v>0.007</x:v>
+      </x:c>
+      <x:c r="J205" s="59" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
@@ -12562,18 +12618,18 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H204">
+  <x:conditionalFormatting sqref="H5:H205">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="错误"/>
     <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="跳过"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J204">
+  <x:conditionalFormatting sqref="J5:J205">
     <x:cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="未登记"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a41c5f1382d4b45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4057c0d7c65648e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13894,34 +13950,66 @@
       </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="128" t="n">
+      <x:c r="A41" s="127" t="n">
         <x:v>46247.415497685186</x:v>
       </x:c>
-      <x:c r="B41" s="24" t="str">
+      <x:c r="B41" s="23" t="str">
         <x:v>04c22a0c496d</x:v>
       </x:c>
-      <x:c r="C41" s="24" t="n">
+      <x:c r="C41" s="23" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D41" s="24" t="n">
+      <x:c r="D41" s="23" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="E41" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F41" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G41" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H41" s="131" t="n">
+      <x:c r="E41" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F41" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G41" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H41" s="130" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I41" s="30" t="n">
+      <x:c r="I41" s="29" t="n">
         <x:v>185.236</x:v>
       </x:c>
-      <x:c r="J41" s="24" t="n">
+      <x:c r="J41" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="128" t="n">
+        <x:v>46247.42736111111</x:v>
+      </x:c>
+      <x:c r="B42" s="24" t="str">
+        <x:v>7f436ea669c2</x:v>
+      </x:c>
+      <x:c r="C42" s="24" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D42" s="24" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="E42" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F42" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I42" s="30" t="n">
+        <x:v>133.351</x:v>
+      </x:c>
+      <x:c r="J42" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -13931,7 +14019,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda7c9ce43ff248f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc064e4197625492a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/latest_test_report.xlsx
+++ b/reports/latest_test_report.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R0b644514fbdf4b75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="Rd8f0e49bff0740e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R05c7234a48854c40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Re6d2c39b3a2f4926"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Rb1c6e542297a43bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R124317e12eed4df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R7ecbdd235ddc4dba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R674d873db6d24725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Ra9804720c4044f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="R5274b0e0a02d40e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H205" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H207" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J205" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J207" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="运行时间"/>
     <x:tableColumn id="2" name="Git Commit"/>
@@ -977,7 +977,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T10:15:24+08:00  |  Git：7f436ea669c287c481594a4c8fcd0ab51f997c89</x:v>
+        <x:v>运行时间：2026-08-13T10:44:57+08:00  |  Git：fa64c7c71283159548fa054dfd35b184c218c305</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1007,22 +1007,22 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="74" t="n">
-        <x:f>COUNTA('测试明细'!$A$5:$A$205)</x:f>
-        <x:v>201</x:v>
+        <x:f>COUNTA('测试明细'!$A$5:$A$207)</x:f>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B5" s="75"/>
       <x:c r="C5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$205,"通过")</x:f>
-        <x:v>201</x:v>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$207,"通过")</x:f>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D5" s="75"/>
       <x:c r="E5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$205,"失败")+COUNTIF('测试明细'!$E$5:$E$205,"错误")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$207,"失败")+COUNTIF('测试明细'!$E$5:$E$207,"错误")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="75"/>
       <x:c r="G5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$205,"跳过")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$207,"跳过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="76"/>
@@ -1062,8 +1062,8 @@
       </x:c>
       <x:c r="B9" s="108"/>
       <x:c r="C9" s="109" t="n">
-        <x:f>SUM('测试明细'!$F$5:$F$205)</x:f>
-        <x:v>133.3509999999996</x:v>
+        <x:f>SUM('测试明细'!$F$5:$F$207)</x:f>
+        <x:v>266.50499999999937</x:v>
       </x:c>
       <x:c r="D9" s="109"/>
       <x:c r="E9" s="110" t="n">
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="F9" s="110"/>
       <x:c r="G9" s="110" t="n">
-        <x:f>COUNTIF('用例说明'!$J$5:$J$205,"未登记")</x:f>
+        <x:f>COUNTIF('用例说明'!$J$5:$J$207,"未登记")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="111"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T10:15:24+08:00  |  Git：7f436ea669c287c481594a4c8fcd0ab51f997c89</x:v>
+        <x:v>运行时间：2026-08-13T10:44:57+08:00  |  Git：fa64c7c71283159548fa054dfd35b184c218c305</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1280,7 +1280,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
         <x:v>确认旧基线与当前候选实现使用完全相同的能力模块，保证能力对比口径一致。</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F6" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
         <x:v>确认当前实现相对旧基线确实提升关键确定性能力的准确率。</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.036</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>验证动态查询规划不会为简单问题创建多余检索词，同时保持规划准确。</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F8" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>验证基准报告能同时给出基线值、候选值和差值。</x:v>
@@ -1376,7 +1376,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F9" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
         <x:v>验证离线基准能准确统计成功/失败调用以及输入、输出和总 Token。</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F10" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
         <x:v>验证离线基准能够量化统一 Tool 层的协议、错误和恢复能力。</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F11" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
         <x:v>验证离线 Benchmark 对比单源基线与多源候选的覆盖、去重和故障恢复。</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F12" s="32" t="n">
-        <x:v>0.171</x:v>
+        <x:v>0.231</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
         <x:v>验证完整能力基准报告可以用 UTF-8 JSON 保存并重新读取。</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F13" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G13" s="35" t="str">
         <x:v>验证基准工具拒绝不存在的运行配置名称。</x:v>
@@ -1496,7 +1496,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F14" s="32" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.029</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str">
         <x:v>验证候选评测能从 OpenAlex 等二级来源的 DOI 中提取待验证 arXiv 身份。</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.032</x:v>
       </x:c>
       <x:c r="G15" s="35" t="str">
         <x:v>验证联合重放只把普通 DOI 交给 Crossref，排除 arXiv DOI。</x:v>
@@ -1544,7 +1544,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F16" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="G16" s="35" t="str">
         <x:v>验证成功取得的规范元数据会缓存，快照重放不会重复消耗网络请求。</x:v>
@@ -1568,7 +1568,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.042</x:v>
       </x:c>
       <x:c r="G17" s="35" t="str">
         <x:v>验证 SSL、超时等临时失败不会被当成永久缓存结果。</x:v>
@@ -1592,7 +1592,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="G18" s="35" t="str">
         <x:v>验证 Crossref 成功记录和明确查无均可重复使用。</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G19" s="35" t="str">
         <x:v>验证 DOI authority 网络失败不会写入成功缓存。</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="G20" s="35" t="str">
         <x:v>验证本轮候选实验只查询 v2 实际隔离过的身份，控制外部请求成本。</x:v>
@@ -1664,7 +1664,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.057</x:v>
       </x:c>
       <x:c r="G21" s="35" t="str">
         <x:v>验证规范元数据候选只有在三份完整独立快照、权威覆盖完整且逐题无回归时才通过晋升门槛。</x:v>
@@ -1688,7 +1688,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F22" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G22" s="35" t="str">
         <x:v>验证 Crossref 相对仅 arXiv canonical 没有指标变化时不得宣称质量提升。</x:v>
@@ -1712,7 +1712,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F23" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="G23" s="35" t="str">
         <x:v>验证普通 DOI 候选评测只使用所有独立快照都出现的非 arXiv DOI。</x:v>
@@ -1736,7 +1736,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F24" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G24" s="35" t="str">
         <x:v>验证 Crossref 评测严格区分标题匹配、标题冲突、规范查无和网络失败。</x:v>
@@ -1760,7 +1760,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F25" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G25" s="35" t="str">
         <x:v>验证普通 DOI 样本按注册前缀轮转抽取，避免单一高频前缀垄断评测集。</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F26" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G26" s="35" t="str">
         <x:v>验证 provider 一致率只使用双方均成功返回标题的 DOI。</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F27" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G27" s="35" t="str">
         <x:v>验证 DOI 校验在固定污染、缺失、近似、查无和失败场景中达到阶段止损条件。</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F28" s="32" t="n">
-        <x:v>0.071</x:v>
+        <x:v>0.142</x:v>
       </x:c>
       <x:c r="G28" s="35" t="str">
         <x:v>验证普通研究问题按完整 Agentic RAG 节点顺序执行。</x:v>
@@ -1856,7 +1856,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F29" s="32" t="n">
-        <x:v>0.046</x:v>
+        <x:v>0.107</x:v>
       </x:c>
       <x:c r="G29" s="35" t="str">
         <x:v>验证已有 PDF 的请求不会重复进行外部查询规划和检索。</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F30" s="32" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="G30" s="35" t="str">
         <x:v>验证问候类输入在进入 RAG 与 LLM 节点前本地结束。</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F31" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G31" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1928,7 +1928,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F32" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G32" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1952,7 +1952,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F33" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G33" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1976,7 +1976,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F34" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G34" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -2000,7 +2000,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F35" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G35" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2024,7 +2024,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F36" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G36" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2048,7 +2048,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F37" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G37" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2072,7 +2072,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F38" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G38" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2096,7 +2096,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F39" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G39" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2120,7 +2120,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F40" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G40" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F41" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G41" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2168,7 +2168,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F42" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G42" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2192,7 +2192,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F43" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G43" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2216,7 +2216,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F44" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G44" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2240,7 +2240,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F45" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G45" s="35" t="str">
         <x:v>验证意图匹配前只清理空格、大小写和末尾标点等表面差异。</x:v>
@@ -2264,7 +2264,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F46" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G46" s="35" t="str">
         <x:v>验证本地闲聊响应不会破坏已有状态和请求元数据。</x:v>
@@ -2288,7 +2288,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F47" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G47" s="35" t="str">
         <x:v>验证能读取 LangChain 标准 usage_metadata Token 字段。</x:v>
@@ -2312,7 +2312,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F48" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G48" s="35" t="str">
         <x:v>验证能读取 OpenAI 兼容响应中的 token_usage 字段。</x:v>
@@ -2336,7 +2336,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F49" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G49" s="35" t="str">
         <x:v>验证模型未返回 Token 数据时系统明确标记缺失而不伪造估算值。</x:v>
@@ -2360,7 +2360,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F50" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G50" s="35" t="str">
         <x:v>验证成功 LLM 调用会记录节点、模型、Token、成功状态和延迟。</x:v>
@@ -2384,7 +2384,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F51" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G51" s="35" t="str">
         <x:v>验证 LLM 调用失败时仍保留失败类型和耗时记录。</x:v>
@@ -2408,7 +2408,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F52" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G52" s="35" t="str">
         <x:v>验证多个节点的 LLM 用量可以累加且不会重复计数。</x:v>
@@ -2432,7 +2432,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F53" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G53" s="35" t="str">
         <x:v>验证指标节点既能按节点分组，又能提供全流程总量与缺失用量统计。</x:v>
@@ -2456,7 +2456,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F54" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G54" s="35" t="str">
         <x:v>验证推理节点启用 LLM 时会写入统一用量记录。</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F55" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G55" s="35" t="str">
         <x:v>验证检索评估节点启用 LLM 时记录评分与用量。</x:v>
@@ -2504,7 +2504,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F56" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G56" s="35" t="str">
         <x:v>验证答案生成节点记录实际生成结果和模型用量。</x:v>
@@ -2528,7 +2528,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F57" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G57" s="35" t="str">
         <x:v>验证关闭 LLM 评估时只使用规则评分且不创建虚假调用记录。</x:v>
@@ -2552,7 +2552,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F58" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G58" s="35" t="str">
         <x:v>验证 BM25 基线能把中文问题与英文术语、数字混合分词。</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F59" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G59" s="35" t="str">
         <x:v>验证 BM25 将包含查询词的文本块排在无关块之前，且重复运行排名与分数一致。</x:v>
@@ -2600,7 +2600,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F60" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G60" s="35" t="str">
         <x:v>验证 BM25 拒绝空语料和非正数返回条数。</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F61" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G61" s="35" t="str">
         <x:v>用手工可计算的排名验证本地 RAG Recall、MRR 与 nDCG 公式。</x:v>
@@ -2648,7 +2648,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F62" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G62" s="35" t="str">
         <x:v>验证同一相关 PDF 页返回多个 Chunk 时，page-level 指标只计算首次命中。</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F63" s="32" t="n">
-        <x:v>0.065</x:v>
+        <x:v>0.079</x:v>
       </x:c>
       <x:c r="G63" s="35" t="str">
         <x:v>验证代表论文来源清单生成 Manifest 时保留语料版本、论文身份和内容哈希。</x:v>
@@ -2696,7 +2696,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F64" s="32" t="n">
-        <x:v>0.014</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="G64" s="35" t="str">
         <x:v>验证来源清单声明的 PDF 缺失时立即失败，而不是静默生成不完整语料。</x:v>
@@ -2720,7 +2720,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F65" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G65" s="35" t="str">
         <x:v>验证 Dense 检索显式归一化向量，并按余弦相似度将语义匹配块排在前面。</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F66" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G66" s="35" t="str">
         <x:v>验证 Dense 检索拒绝零向量和空语料。</x:v>
@@ -2768,7 +2768,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F67" s="32" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="G67" s="35" t="str">
         <x:v>验证 Dense 向量缓存可以无损加载，并在语料文本、模型或处理版本变化后使用不同指纹。</x:v>
@@ -2792,7 +2792,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F68" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G68" s="35" t="str">
         <x:v>验证缓存命中时 DenseRetriever 不会重新编码全部论文，只对查询生成向量。</x:v>
@@ -2816,7 +2816,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F69" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="G69" s="35" t="str">
         <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
@@ -2840,22 +2840,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F70" s="32" t="n">
-        <x:v>30.836</x:v>
+        <x:v>62.614</x:v>
       </x:c>
       <x:c r="G70" s="35" t="str">
         <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
       </x:c>
       <x:c r="H70" s="35" t="str"/>
     </x:row>
-    <x:row r="71" ht="198" hidden="0" customHeight="1">
+    <x:row r="71" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A71" s="26" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_stability.py</x:v>
+        <x:v>tests/test_local_rag_dense_model_compare.py</x:v>
       </x:c>
       <x:c r="C71" s="35" t="str">
-        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
+        <x:v>test_dense_model_comparison_prefers_quality_gain_without_excess_regression</x:v>
       </x:c>
       <x:c r="D71" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2864,22 +2864,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F71" s="32" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="G71" s="35" t="str">
-        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
+        <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
       </x:c>
       <x:c r="H71" s="35" t="str"/>
     </x:row>
-    <x:row r="72" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="72" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A72" s="26" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_models.py</x:v>
       </x:c>
       <x:c r="C72" s="35" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_model_matrix_changes_only_declared_embedding_properties</x:v>
       </x:c>
       <x:c r="D72" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2888,22 +2888,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F72" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>1.891</x:v>
       </x:c>
       <x:c r="G72" s="35" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
       </x:c>
       <x:c r="H72" s="35" t="str"/>
     </x:row>
-    <x:row r="73" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="73" ht="198" hidden="0" customHeight="1">
       <x:c r="A73" s="26" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C73" s="35" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
       </x:c>
       <x:c r="D73" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2912,14 +2912,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F73" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.051</x:v>
       </x:c>
       <x:c r="G73" s="35" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
       </x:c>
       <x:c r="H73" s="35" t="str"/>
     </x:row>
-    <x:row r="74" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A74" s="26" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -2927,7 +2927,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C74" s="35" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D74" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2936,14 +2936,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F74" s="32" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G74" s="35" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="H74" s="35" t="str"/>
     </x:row>
-    <x:row r="75" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="75" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A75" s="26" t="n">
         <x:v>71</x:v>
       </x:c>
@@ -2951,7 +2951,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C75" s="35" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D75" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2960,10 +2960,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F75" s="32" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G75" s="35" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="H75" s="35" t="str"/>
     </x:row>
@@ -2972,10 +2972,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C76" s="35" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D76" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2984,22 +2984,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F76" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="G76" s="35" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="H76" s="35" t="str"/>
     </x:row>
-    <x:row r="77" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="77" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A77" s="26" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C77" s="35" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D77" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3008,22 +3008,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F77" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.055</x:v>
       </x:c>
       <x:c r="G77" s="35" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="H77" s="35" t="str"/>
     </x:row>
-    <x:row r="78" ht="132" hidden="0" customHeight="1">
+    <x:row r="78" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A78" s="26" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="35" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C78" s="35" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D78" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3032,22 +3032,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F78" s="32" t="n">
-        <x:v>30.236</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G78" s="35" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="H78" s="35" t="str"/>
     </x:row>
-    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="79" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A79" s="26" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C79" s="35" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D79" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3056,22 +3056,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F79" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G79" s="35" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="H79" s="35" t="str"/>
     </x:row>
-    <x:row r="80" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="80" ht="132" hidden="0" customHeight="1">
       <x:c r="A80" s="26" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C80" s="35" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D80" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3080,10 +3080,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F80" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>62.618</x:v>
       </x:c>
       <x:c r="G80" s="35" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="H80" s="35" t="str"/>
     </x:row>
@@ -3095,7 +3095,7 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C81" s="35" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D81" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3107,19 +3107,19 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G81" s="35" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="H81" s="35" t="str"/>
     </x:row>
-    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="82" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A82" s="26" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C82" s="35" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D82" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3128,10 +3128,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F82" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G82" s="35" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="H82" s="35" t="str"/>
     </x:row>
@@ -3140,10 +3140,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C83" s="35" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D83" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3152,10 +3152,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F83" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G83" s="35" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="H83" s="35" t="str"/>
     </x:row>
@@ -3167,7 +3167,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C84" s="35" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D84" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3176,14 +3176,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F84" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G84" s="35" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="H84" s="35" t="str"/>
     </x:row>
-    <x:row r="85" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="85" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A85" s="26" t="n">
         <x:v>81</x:v>
       </x:c>
@@ -3191,7 +3191,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C85" s="35" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D85" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3200,14 +3200,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F85" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G85" s="35" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="H85" s="35" t="str"/>
     </x:row>
-    <x:row r="86" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="86" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A86" s="26" t="n">
         <x:v>82</x:v>
       </x:c>
@@ -3215,7 +3215,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="35" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D86" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3224,14 +3224,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F86" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G86" s="35" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="H86" s="35" t="str"/>
     </x:row>
-    <x:row r="87" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="87" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A87" s="26" t="n">
         <x:v>83</x:v>
       </x:c>
@@ -3239,7 +3239,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="35" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D87" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3248,14 +3248,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F87" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G87" s="35" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="H87" s="35" t="str"/>
     </x:row>
-    <x:row r="88" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="88" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A88" s="26" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -3263,7 +3263,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="35" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D88" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3272,10 +3272,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F88" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G88" s="35" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="H88" s="35" t="str"/>
     </x:row>
@@ -3284,10 +3284,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C89" s="35" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D89" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3296,22 +3296,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F89" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G89" s="35" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="H89" s="35" t="str"/>
     </x:row>
-    <x:row r="90" ht="132" hidden="0" customHeight="1">
+    <x:row r="90" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A90" s="26" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C90" s="35" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D90" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3320,14 +3320,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F90" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.016</x:v>
       </x:c>
       <x:c r="G90" s="35" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="H90" s="35" t="str"/>
     </x:row>
-    <x:row r="91" ht="132" hidden="0" customHeight="1">
+    <x:row r="91" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A91" s="26" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -3335,7 +3335,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C91" s="35" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D91" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3344,14 +3344,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F91" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G91" s="35" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="H91" s="35" t="str"/>
     </x:row>
-    <x:row r="92" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="92" ht="132" hidden="0" customHeight="1">
       <x:c r="A92" s="26" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -3359,7 +3359,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C92" s="35" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D92" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3371,11 +3371,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G92" s="35" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="H92" s="35" t="str"/>
     </x:row>
-    <x:row r="93" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="93" ht="132" hidden="0" customHeight="1">
       <x:c r="A93" s="26" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -3383,7 +3383,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="35" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D93" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3392,14 +3392,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F93" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G93" s="35" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="H93" s="35" t="str"/>
     </x:row>
-    <x:row r="94" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="94" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A94" s="26" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -3407,7 +3407,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="35" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D94" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3416,14 +3416,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F94" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G94" s="35" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="H94" s="35" t="str"/>
     </x:row>
-    <x:row r="95" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="95" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A95" s="26" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -3431,7 +3431,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="35" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D95" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3440,10 +3440,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F95" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G95" s="35" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="H95" s="35" t="str"/>
     </x:row>
@@ -3452,10 +3452,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" s="35" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C96" s="35" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D96" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3464,22 +3464,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F96" s="32" t="n">
-        <x:v>2.386</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G96" s="35" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="H96" s="35" t="str"/>
     </x:row>
-    <x:row r="97" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="97" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A97" s="26" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C97" s="35" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D97" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3488,22 +3488,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F97" s="32" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G97" s="35" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="H97" s="35" t="str"/>
     </x:row>
-    <x:row r="98" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="98" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A98" s="26" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C98" s="35" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D98" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3512,14 +3512,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F98" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>2.352</x:v>
       </x:c>
       <x:c r="G98" s="35" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="H98" s="35" t="str"/>
     </x:row>
-    <x:row r="99" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="99" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A99" s="26" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -3527,7 +3527,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C99" s="35" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D99" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3536,14 +3536,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F99" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.046</x:v>
       </x:c>
       <x:c r="G99" s="35" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="H99" s="35" t="str"/>
     </x:row>
-    <x:row r="100" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="100" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A100" s="26" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -3551,7 +3551,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C100" s="35" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D100" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3560,22 +3560,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F100" s="32" t="n">
-        <x:v>1.128</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G100" s="35" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="H100" s="35" t="str"/>
     </x:row>
-    <x:row r="101" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A101" s="26" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C101" s="35" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D101" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3584,22 +3584,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F101" s="32" t="n">
-        <x:v>0.188</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G101" s="35" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="H101" s="35" t="str"/>
     </x:row>
-    <x:row r="102" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="102" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A102" s="26" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C102" s="35" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D102" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3608,10 +3608,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F102" s="32" t="n">
-        <x:v>0.106</x:v>
+        <x:v>1.166</x:v>
       </x:c>
       <x:c r="G102" s="35" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="H102" s="35" t="str"/>
     </x:row>
@@ -3623,7 +3623,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C103" s="35" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D103" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3632,14 +3632,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F103" s="32" t="n">
-        <x:v>0.056</x:v>
+        <x:v>0.192</x:v>
       </x:c>
       <x:c r="G103" s="35" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="H103" s="35" t="str"/>
     </x:row>
-    <x:row r="104" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="104" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A104" s="26" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -3647,7 +3647,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C104" s="35" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D104" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3656,22 +3656,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F104" s="32" t="n">
-        <x:v>0.094</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="G104" s="35" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="H104" s="35" t="str"/>
     </x:row>
-    <x:row r="105" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="105" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A105" s="26" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="35" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C105" s="35" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D105" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3680,10 +3680,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F105" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="G105" s="35" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="H105" s="35" t="str"/>
     </x:row>
@@ -3692,10 +3692,10 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C106" s="35" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D106" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3704,10 +3704,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F106" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="G106" s="35" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="H106" s="35" t="str"/>
     </x:row>
@@ -3716,26 +3716,26 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C107" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D107" s="35" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E107" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F107" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G107" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="H107" s="35" t="str"/>
     </x:row>
-    <x:row r="108" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="108" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A108" s="26" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -3743,19 +3743,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C108" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D108" s="35" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E108" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F108" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G108" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="H108" s="35" t="str"/>
     </x:row>
@@ -3767,16 +3767,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C109" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D109" s="35" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F109" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G109" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3791,16 +3791,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D110" s="35" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E110" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F110" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G110" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3815,23 +3815,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D111" s="35" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E111" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F111" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G111" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H111" s="35" t="str"/>
     </x:row>
-    <x:row r="112" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="112" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A112" s="26" t="n">
         <x:v>108</x:v>
       </x:c>
@@ -3839,23 +3839,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D112" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E112" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F112" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G112" s="35" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H112" s="35" t="str"/>
     </x:row>
-    <x:row r="113" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="113" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A113" s="26" t="n">
         <x:v>109</x:v>
       </x:c>
@@ -3863,19 +3863,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D113" s="35" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F113" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G113" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H113" s="35" t="str"/>
     </x:row>
@@ -3887,19 +3887,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D114" s="35" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E114" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F114" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G114" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="H114" s="35" t="str"/>
     </x:row>
@@ -3911,16 +3911,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D115" s="35" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F115" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G115" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -3935,16 +3935,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D116" s="35" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E116" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F116" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G116" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -3959,23 +3959,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D117" s="35" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F117" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G117" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H117" s="35" t="str"/>
     </x:row>
-    <x:row r="118" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="118" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A118" s="26" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -3983,23 +3983,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D118" s="35" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E118" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F118" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G118" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H118" s="35" t="str"/>
     </x:row>
-    <x:row r="119" ht="66" hidden="0" customHeight="1">
+    <x:row r="119" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A119" s="26" t="n">
         <x:v>115</x:v>
       </x:c>
@@ -4007,23 +4007,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="35" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D119" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E119" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F119" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G119" s="35" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H119" s="35" t="str"/>
     </x:row>
-    <x:row r="120" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="120" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A120" s="26" t="n">
         <x:v>116</x:v>
       </x:c>
@@ -4031,31 +4031,31 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="35" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D120" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E120" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F120" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G120" s="35" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H120" s="35" t="str"/>
     </x:row>
-    <x:row r="121" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="121" ht="66" hidden="0" customHeight="1">
       <x:c r="A121" s="26" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B121" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="35" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D121" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4067,7 +4067,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G121" s="35" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="H121" s="35" t="str"/>
     </x:row>
@@ -4076,10 +4076,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B122" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="35" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D122" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4091,11 +4091,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G122" s="35" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="H122" s="35" t="str"/>
     </x:row>
-    <x:row r="123" ht="132" hidden="0" customHeight="1">
+    <x:row r="123" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A123" s="26" t="n">
         <x:v>119</x:v>
       </x:c>
@@ -4103,7 +4103,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C123" s="35" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D123" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4112,14 +4112,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F123" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G123" s="35" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="H123" s="35" t="str"/>
     </x:row>
-    <x:row r="124" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="124" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A124" s="26" t="n">
         <x:v>120</x:v>
       </x:c>
@@ -4127,7 +4127,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C124" s="35" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D124" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4139,7 +4139,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G124" s="35" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="H124" s="35" t="str"/>
     </x:row>
@@ -4148,10 +4148,10 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C125" s="35" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D125" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4160,10 +4160,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F125" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G125" s="35" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="H125" s="35" t="str"/>
     </x:row>
@@ -4172,10 +4172,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C126" s="35" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D126" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4184,14 +4184,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F126" s="32" t="n">
-        <x:v>14.87</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G126" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="H126" s="35" t="str"/>
     </x:row>
-    <x:row r="127" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="127" ht="132" hidden="0" customHeight="1">
       <x:c r="A127" s="26" t="n">
         <x:v>123</x:v>
       </x:c>
@@ -4199,7 +4199,7 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C127" s="35" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D127" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4208,22 +4208,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F127" s="32" t="n">
-        <x:v>14.978</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G127" s="35" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="H127" s="35" t="str"/>
     </x:row>
-    <x:row r="128" ht="132" hidden="0" customHeight="1">
+    <x:row r="128" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A128" s="26" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C128" s="35" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D128" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4232,22 +4232,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F128" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>32.145</x:v>
       </x:c>
       <x:c r="G128" s="35" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="H128" s="35" t="str"/>
     </x:row>
-    <x:row r="129" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="129" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A129" s="26" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="35" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D129" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4256,14 +4256,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F129" s="32" t="n">
-        <x:v>18.845</x:v>
+        <x:v>31.502</x:v>
       </x:c>
       <x:c r="G129" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="H129" s="35" t="str"/>
     </x:row>
-    <x:row r="130" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="130" ht="132" hidden="0" customHeight="1">
       <x:c r="A130" s="26" t="n">
         <x:v>126</x:v>
       </x:c>
@@ -4271,7 +4271,7 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C130" s="35" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D130" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4280,10 +4280,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F130" s="32" t="n">
-        <x:v>17.713</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G130" s="35" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="H130" s="35" t="str"/>
     </x:row>
@@ -4292,10 +4292,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C131" s="35" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D131" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4304,10 +4304,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F131" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>38.998</x:v>
       </x:c>
       <x:c r="G131" s="35" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="H131" s="35" t="str"/>
     </x:row>
@@ -4316,10 +4316,10 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C132" s="35" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D132" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4328,14 +4328,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F132" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>30.151</x:v>
       </x:c>
       <x:c r="G132" s="35" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="H132" s="35" t="str"/>
     </x:row>
-    <x:row r="133" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="133" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A133" s="26" t="n">
         <x:v>129</x:v>
       </x:c>
@@ -4343,7 +4343,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C133" s="35" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D133" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4352,10 +4352,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F133" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G133" s="35" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="H133" s="35" t="str"/>
     </x:row>
@@ -4367,7 +4367,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C134" s="35" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D134" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4376,14 +4376,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F134" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G134" s="35" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="H134" s="35" t="str"/>
     </x:row>
-    <x:row r="135" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A135" s="26" t="n">
         <x:v>131</x:v>
       </x:c>
@@ -4391,7 +4391,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="35" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D135" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4403,11 +4403,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G135" s="35" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="H135" s="35" t="str"/>
     </x:row>
-    <x:row r="136" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A136" s="26" t="n">
         <x:v>132</x:v>
       </x:c>
@@ -4415,7 +4415,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="35" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D136" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4427,7 +4427,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G136" s="35" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="H136" s="35" t="str"/>
     </x:row>
@@ -4439,7 +4439,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="35" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D137" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4451,7 +4451,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G137" s="35" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="H137" s="35" t="str"/>
     </x:row>
@@ -4463,7 +4463,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="35" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D138" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4475,11 +4475,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G138" s="35" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="H138" s="35" t="str"/>
     </x:row>
-    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A139" s="26" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -4487,7 +4487,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D139" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4499,11 +4499,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G139" s="35" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="H139" s="35" t="str"/>
     </x:row>
-    <x:row r="140" ht="132" hidden="0" customHeight="1">
+    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A140" s="26" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -4511,7 +4511,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D140" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4523,7 +4523,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G140" s="35" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="H140" s="35" t="str"/>
     </x:row>
@@ -4535,7 +4535,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="35" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D141" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4544,14 +4544,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F141" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G141" s="35" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="H141" s="35" t="str"/>
     </x:row>
-    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="142" ht="132" hidden="0" customHeight="1">
       <x:c r="A142" s="26" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -4559,7 +4559,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="35" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D142" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4571,11 +4571,11 @@
         <x:v>0.004</x:v>
       </x:c>
       <x:c r="G142" s="35" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="H142" s="35" t="str"/>
     </x:row>
-    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="143" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A143" s="26" t="n">
         <x:v>139</x:v>
       </x:c>
@@ -4583,7 +4583,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="35" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D143" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4595,19 +4595,19 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G143" s="35" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="H143" s="35" t="str"/>
     </x:row>
-    <x:row r="144" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="144" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A144" s="26" t="n">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B144" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="35" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D144" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4616,10 +4616,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F144" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G144" s="35" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="H144" s="35" t="str"/>
     </x:row>
@@ -4628,10 +4628,10 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B145" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="35" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D145" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4640,14 +4640,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F145" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G145" s="35" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="H145" s="35" t="str"/>
     </x:row>
-    <x:row r="146" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="146" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A146" s="26" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -4655,7 +4655,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C146" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D146" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4664,14 +4664,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F146" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G146" s="35" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="H146" s="35" t="str"/>
     </x:row>
-    <x:row r="147" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A147" s="26" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -4679,7 +4679,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C147" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D147" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4688,10 +4688,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F147" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G147" s="35" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="H147" s="35" t="str"/>
     </x:row>
@@ -4703,7 +4703,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D148" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4712,14 +4712,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F148" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G148" s="35" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="H148" s="35" t="str"/>
     </x:row>
-    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="149" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A149" s="26" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -4727,7 +4727,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="35" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D149" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4739,11 +4739,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G149" s="35" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="H149" s="35" t="str"/>
     </x:row>
-    <x:row r="150" ht="66" hidden="0" customHeight="1">
+    <x:row r="150" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A150" s="26" t="n">
         <x:v>146</x:v>
       </x:c>
@@ -4751,7 +4751,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="35" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D150" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4760,14 +4760,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F150" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G150" s="35" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="H150" s="35" t="str"/>
     </x:row>
-    <x:row r="151" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A151" s="26" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -4775,7 +4775,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="35" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D151" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4787,19 +4787,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G151" s="35" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="H151" s="35" t="str"/>
     </x:row>
-    <x:row r="152" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="152" ht="66" hidden="0" customHeight="1">
       <x:c r="A152" s="26" t="n">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B152" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C152" s="35" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D152" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4808,10 +4808,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F152" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G152" s="35" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="H152" s="35" t="str"/>
     </x:row>
@@ -4820,10 +4820,10 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B153" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="35" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D153" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4832,14 +4832,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F153" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G153" s="35" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="H153" s="35" t="str"/>
     </x:row>
-    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="154" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A154" s="26" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -4847,7 +4847,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C154" s="35" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D154" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4856,14 +4856,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F154" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G154" s="35" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="H154" s="35" t="str"/>
     </x:row>
-    <x:row r="155" ht="132" hidden="0" customHeight="1">
+    <x:row r="155" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A155" s="26" t="n">
         <x:v>151</x:v>
       </x:c>
@@ -4871,7 +4871,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C155" s="35" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D155" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4880,14 +4880,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F155" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G155" s="35" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="H155" s="35" t="str"/>
     </x:row>
-    <x:row r="156" ht="132" hidden="0" customHeight="1">
+    <x:row r="156" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A156" s="26" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -4895,7 +4895,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="35" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D156" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4904,14 +4904,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F156" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G156" s="35" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="H156" s="35" t="str"/>
     </x:row>
-    <x:row r="157" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="157" ht="132" hidden="0" customHeight="1">
       <x:c r="A157" s="26" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -4919,7 +4919,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="35" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D157" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4928,14 +4928,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F157" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G157" s="35" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="H157" s="35" t="str"/>
     </x:row>
-    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="158" ht="132" hidden="0" customHeight="1">
       <x:c r="A158" s="26" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -4943,7 +4943,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="35" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D158" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4952,14 +4952,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F158" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G158" s="35" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="H158" s="35" t="str"/>
     </x:row>
-    <x:row r="159" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="159" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A159" s="26" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -4967,7 +4967,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4976,14 +4976,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F159" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G159" s="35" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="H159" s="35" t="str"/>
     </x:row>
-    <x:row r="160" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A160" s="26" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -4991,7 +4991,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5000,14 +5000,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F160" s="32" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G160" s="35" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H160" s="35" t="str"/>
     </x:row>
-    <x:row r="161" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="161" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A161" s="26" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -5015,7 +5015,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5024,14 +5024,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F161" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G161" s="35" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="H161" s="35" t="str"/>
     </x:row>
-    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="162" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A162" s="26" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -5039,7 +5039,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5048,14 +5048,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F162" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.157</x:v>
       </x:c>
       <x:c r="G162" s="35" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="H162" s="35" t="str"/>
     </x:row>
-    <x:row r="163" ht="132" hidden="0" customHeight="1">
+    <x:row r="163" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A163" s="26" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -5063,7 +5063,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5072,14 +5072,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F163" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G163" s="35" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="H163" s="35" t="str"/>
     </x:row>
-    <x:row r="164" ht="132" hidden="0" customHeight="1">
+    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A164" s="26" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -5087,7 +5087,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5096,14 +5096,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F164" s="32" t="n">
-        <x:v>0.225</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="G164" s="35" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="H164" s="35" t="str"/>
     </x:row>
-    <x:row r="165" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="165" ht="132" hidden="0" customHeight="1">
       <x:c r="A165" s="26" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -5111,7 +5111,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5120,14 +5120,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F165" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G165" s="35" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="H165" s="35" t="str"/>
     </x:row>
-    <x:row r="166" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="166" ht="132" hidden="0" customHeight="1">
       <x:c r="A166" s="26" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -5135,7 +5135,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5144,14 +5144,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F166" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.294</x:v>
       </x:c>
       <x:c r="G166" s="35" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="H166" s="35" t="str"/>
     </x:row>
-    <x:row r="167" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="167" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A167" s="26" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -5159,7 +5159,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="35" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D167" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5168,22 +5168,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F167" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G167" s="35" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="H167" s="35" t="str"/>
     </x:row>
-    <x:row r="168" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="168" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A168" s="26" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B168" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="35" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D168" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5192,22 +5192,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F168" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="G168" s="35" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="H168" s="35" t="str"/>
     </x:row>
-    <x:row r="169" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="169" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A169" s="26" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B169" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="35" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D169" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5216,14 +5216,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F169" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G169" s="35" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="H169" s="35" t="str"/>
     </x:row>
-    <x:row r="170" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="170" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A170" s="26" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -5231,7 +5231,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C170" s="35" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D170" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5243,11 +5243,11 @@
         <x:v>0.004</x:v>
       </x:c>
       <x:c r="G170" s="35" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="H170" s="35" t="str"/>
     </x:row>
-    <x:row r="171" ht="66" hidden="0" customHeight="1">
+    <x:row r="171" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A171" s="26" t="n">
         <x:v>167</x:v>
       </x:c>
@@ -5255,7 +5255,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C171" s="35" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D171" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5264,22 +5264,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F171" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G171" s="35" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="H171" s="35" t="str"/>
     </x:row>
-    <x:row r="172" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="172" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A172" s="26" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="35" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C172" s="35" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D172" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5288,22 +5288,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F172" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G172" s="35" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="H172" s="35" t="str"/>
     </x:row>
-    <x:row r="173" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="173" ht="66" hidden="0" customHeight="1">
       <x:c r="A173" s="26" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B173" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C173" s="35" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D173" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5312,10 +5312,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F173" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G173" s="35" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="H173" s="35" t="str"/>
     </x:row>
@@ -5324,10 +5324,10 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C174" s="35" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D174" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5336,10 +5336,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F174" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G174" s="35" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="H174" s="35" t="str"/>
     </x:row>
@@ -5348,10 +5348,10 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C175" s="35" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D175" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5360,22 +5360,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F175" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G175" s="35" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="H175" s="35" t="str"/>
     </x:row>
-    <x:row r="176" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="176" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A176" s="26" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C176" s="35" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D176" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5387,11 +5387,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G176" s="35" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="H176" s="35" t="str"/>
     </x:row>
-    <x:row r="177" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="177" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A177" s="26" t="n">
         <x:v>173</x:v>
       </x:c>
@@ -5399,7 +5399,7 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C177" s="35" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D177" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5408,22 +5408,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F177" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G177" s="35" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="H177" s="35" t="str"/>
     </x:row>
-    <x:row r="178" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="178" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A178" s="26" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C178" s="35" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D178" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5435,7 +5435,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G178" s="35" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="H178" s="35" t="str"/>
     </x:row>
@@ -5444,10 +5444,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5456,14 +5456,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F179" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G179" s="35" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="H179" s="35" t="str"/>
     </x:row>
-    <x:row r="180" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="180" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A180" s="26" t="n">
         <x:v>176</x:v>
       </x:c>
@@ -5471,7 +5471,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C180" s="35" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D180" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5480,10 +5480,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F180" s="32" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G180" s="35" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="H180" s="35" t="str"/>
     </x:row>
@@ -5495,7 +5495,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C181" s="35" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D181" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5504,22 +5504,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F181" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G181" s="35" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="H181" s="35" t="str"/>
     </x:row>
-    <x:row r="182" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="182" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A182" s="26" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5528,22 +5528,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F182" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="G182" s="35" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="H182" s="35" t="str"/>
     </x:row>
-    <x:row r="183" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="183" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A183" s="26" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5552,22 +5552,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F183" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G183" s="35" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="H183" s="35" t="str"/>
     </x:row>
-    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="184" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A184" s="26" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="35" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C184" s="35" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D184" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5576,10 +5576,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F184" s="32" t="n">
-        <x:v>0.308</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G184" s="35" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="H184" s="35" t="str"/>
     </x:row>
@@ -5588,10 +5588,10 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C185" s="35" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D185" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5600,22 +5600,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F185" s="32" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G185" s="35" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H185" s="35" t="str"/>
     </x:row>
-    <x:row r="186" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="186" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A186" s="26" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C186" s="35" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D186" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5624,10 +5624,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F186" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="G186" s="35" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="H186" s="35" t="str"/>
     </x:row>
@@ -5636,10 +5636,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B187" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5648,22 +5648,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F187" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="G187" s="35" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="H187" s="35" t="str"/>
     </x:row>
-    <x:row r="188" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="188" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A188" s="26" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C188" s="35" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D188" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5675,11 +5675,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G188" s="35" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="H188" s="35" t="str"/>
     </x:row>
-    <x:row r="189" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="189" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A189" s="26" t="n">
         <x:v>185</x:v>
       </x:c>
@@ -5687,7 +5687,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5696,14 +5696,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F189" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G189" s="35" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="H189" s="35" t="str"/>
     </x:row>
-    <x:row r="190" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="190" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A190" s="26" t="n">
         <x:v>186</x:v>
       </x:c>
@@ -5711,7 +5711,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C190" s="35" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D190" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5720,14 +5720,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F190" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G190" s="35" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="H190" s="35" t="str"/>
     </x:row>
-    <x:row r="191" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A191" s="26" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -5735,7 +5735,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5744,14 +5744,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F191" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G191" s="35" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="H191" s="35" t="str"/>
     </x:row>
-    <x:row r="192" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="192" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A192" s="26" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -5759,7 +5759,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="35" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D192" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5771,7 +5771,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G192" s="35" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="H192" s="35" t="str"/>
     </x:row>
@@ -5783,7 +5783,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="35" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D193" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5792,14 +5792,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F193" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G193" s="35" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="H193" s="35" t="str"/>
     </x:row>
-    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="194" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A194" s="26" t="n">
         <x:v>190</x:v>
       </x:c>
@@ -5807,7 +5807,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5819,11 +5819,11 @@
         <x:v>0.006</x:v>
       </x:c>
       <x:c r="G194" s="35" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="H194" s="35" t="str"/>
     </x:row>
-    <x:row r="195" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="195" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A195" s="26" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -5831,7 +5831,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5840,14 +5840,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F195" s="32" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G195" s="35" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="H195" s="35" t="str"/>
     </x:row>
-    <x:row r="196" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="196" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A196" s="26" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -5855,7 +5855,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5864,14 +5864,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F196" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G196" s="35" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="H196" s="35" t="str"/>
     </x:row>
-    <x:row r="197" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="197" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A197" s="26" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -5879,7 +5879,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5888,10 +5888,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F197" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="G197" s="35" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="H197" s="35" t="str"/>
     </x:row>
@@ -5903,7 +5903,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5912,14 +5912,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F198" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G198" s="35" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="H198" s="35" t="str"/>
     </x:row>
-    <x:row r="199" ht="132" hidden="0" customHeight="1">
+    <x:row r="199" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A199" s="26" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -5927,7 +5927,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5939,11 +5939,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G199" s="35" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="H199" s="35" t="str"/>
     </x:row>
-    <x:row r="200" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="200" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A200" s="26" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -5951,7 +5951,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D200" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5960,14 +5960,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F200" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G200" s="35" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="H200" s="35" t="str"/>
     </x:row>
-    <x:row r="201" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="201" ht="132" hidden="0" customHeight="1">
       <x:c r="A201" s="26" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -5975,7 +5975,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="35" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D201" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5984,14 +5984,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F201" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G201" s="35" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="H201" s="35" t="str"/>
     </x:row>
-    <x:row r="202" ht="132" hidden="0" customHeight="1">
+    <x:row r="202" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A202" s="26" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -5999,7 +5999,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="35" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D202" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6008,14 +6008,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F202" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G202" s="35" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="H202" s="35" t="str"/>
     </x:row>
-    <x:row r="203" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="203" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A203" s="26" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -6023,7 +6023,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="35" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D203" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6032,14 +6032,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F203" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G203" s="35" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="H203" s="35" t="str"/>
     </x:row>
-    <x:row r="204" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="204" ht="132" hidden="0" customHeight="1">
       <x:c r="A204" s="26" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -6047,52 +6047,100 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="35" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D204" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E204" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F204" s="32" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="G204" s="35" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="H204" s="35" t="str"/>
+    </x:row>
+    <x:row r="205" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A205" s="26" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B205" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C205" s="35" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D205" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E205" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F205" s="32" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="G205" s="35" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="H205" s="35" t="str"/>
+    </x:row>
+    <x:row r="206" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A206" s="26" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B206" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C206" s="35" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D204" s="35" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E204" s="26" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F204" s="32" t="n">
-        <x:v>0.003</x:v>
-      </x:c>
-      <x:c r="G204" s="35" t="str">
+      <x:c r="D206" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E206" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F206" s="32" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="G206" s="35" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="H204" s="35" t="str"/>
-    </x:row>
-    <x:row r="205" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A205" s="27" t="n">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="B205" s="36" t="str">
+      <x:c r="H206" s="35" t="str"/>
+    </x:row>
+    <x:row r="207" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A207" s="27" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B207" s="36" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C205" s="36" t="str">
+      <x:c r="C207" s="36" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D205" s="36" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E205" s="27" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F205" s="33" t="n">
-        <x:v>0.007</x:v>
-      </x:c>
-      <x:c r="G205" s="36" t="str">
+      <x:c r="D207" s="36" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E207" s="27" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F207" s="33" t="n">
+        <x:v>0.009</x:v>
+      </x:c>
+      <x:c r="G207" s="36" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="H205" s="36" t="str"/>
+      <x:c r="H207" s="36" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E5:E205">
+  <x:conditionalFormatting sqref="E5:E207">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="错误"/>
@@ -6100,7 +6148,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7830910ede384edb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R919e2d24181d4deb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6207,7 +6255,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I5" s="54" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J5" s="57" t="str">
         <x:v>已登记</x:v>
@@ -6239,7 +6287,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I6" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J6" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6271,7 +6319,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I7" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.036</x:v>
       </x:c>
       <x:c r="J7" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6303,7 +6351,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I8" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="J8" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6335,7 +6383,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I9" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J9" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6367,7 +6415,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I10" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="J10" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6399,7 +6447,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I11" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="J11" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6431,7 +6479,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I12" s="55" t="n">
-        <x:v>0.171</x:v>
+        <x:v>0.231</x:v>
       </x:c>
       <x:c r="J12" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6463,7 +6511,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I13" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J13" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6495,7 +6543,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I14" s="55" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.029</x:v>
       </x:c>
       <x:c r="J14" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6527,7 +6575,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I15" s="55" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.032</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6559,7 +6607,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I16" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="J16" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6591,7 +6639,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I17" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.042</x:v>
       </x:c>
       <x:c r="J17" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6623,7 +6671,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I18" s="55" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="J18" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6655,7 +6703,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I19" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J19" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6687,7 +6735,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I20" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="J20" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6719,7 +6767,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I21" s="55" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.057</x:v>
       </x:c>
       <x:c r="J21" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6751,7 +6799,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I22" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J22" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6783,7 +6831,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I23" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="J23" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6815,7 +6863,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I24" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J24" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6847,7 +6895,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I25" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J25" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6879,7 +6927,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I26" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J26" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6911,7 +6959,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I27" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J27" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6943,7 +6991,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I28" s="55" t="n">
-        <x:v>0.071</x:v>
+        <x:v>0.142</x:v>
       </x:c>
       <x:c r="J28" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6975,7 +7023,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I29" s="55" t="n">
-        <x:v>0.046</x:v>
+        <x:v>0.107</x:v>
       </x:c>
       <x:c r="J29" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7007,7 +7055,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I30" s="55" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="J30" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7039,7 +7087,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I31" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J31" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7071,7 +7119,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I32" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J32" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7103,7 +7151,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I33" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J33" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7135,7 +7183,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I34" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J34" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7167,7 +7215,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I35" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J35" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7199,7 +7247,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I36" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J36" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7231,7 +7279,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I37" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J37" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7263,7 +7311,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I38" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J38" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7295,7 +7343,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I39" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J39" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7327,7 +7375,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I40" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J40" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7359,7 +7407,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I41" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J41" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7391,7 +7439,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I42" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J42" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7423,7 +7471,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I43" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J43" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7455,7 +7503,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I44" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J44" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7487,7 +7535,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I45" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J45" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7519,7 +7567,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I46" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J46" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7551,7 +7599,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I47" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J47" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7583,7 +7631,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I48" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J48" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7615,7 +7663,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I49" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J49" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7647,7 +7695,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I50" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J50" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7679,7 +7727,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I51" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J51" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7711,7 +7759,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I52" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J52" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7743,7 +7791,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I53" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J53" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7775,7 +7823,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I54" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J54" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7807,7 +7855,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I55" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J55" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7839,7 +7887,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I56" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J56" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7871,7 +7919,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I57" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J57" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7903,7 +7951,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I58" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J58" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7935,7 +7983,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I59" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J59" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7967,7 +8015,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I60" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J60" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7999,7 +8047,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I61" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J61" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8031,7 +8079,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I62" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J62" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8063,7 +8111,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I63" s="55" t="n">
-        <x:v>0.065</x:v>
+        <x:v>0.079</x:v>
       </x:c>
       <x:c r="J63" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8095,7 +8143,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I64" s="55" t="n">
-        <x:v>0.014</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="J64" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8127,7 +8175,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I65" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J65" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8159,7 +8207,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I66" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J66" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8191,7 +8239,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I67" s="55" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="J67" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8223,7 +8271,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I68" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J68" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8255,7 +8303,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I69" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="J69" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8287,109 +8335,109 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I70" s="55" t="n">
-        <x:v>30.836</x:v>
+        <x:v>62.614</x:v>
       </x:c>
       <x:c r="J70" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="198" hidden="0" customHeight="1">
+    <x:row r="71" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A71" s="42" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_stability.py</x:v>
+        <x:v>tests/test_local_rag_dense_model_compare.py</x:v>
       </x:c>
       <x:c r="C71" s="49" t="str">
-        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
+        <x:v>test_dense_model_comparison_prefers_quality_gain_without_excess_regression</x:v>
       </x:c>
       <x:c r="D71" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E71" s="49" t="str">
-        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
+        <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
       </x:c>
       <x:c r="F71" s="49" t="str">
-        <x:v>三个运行的检索结果完全一致，查询延迟变异系数不超过 50%，但生产开关仍保持关闭。</x:v>
+        <x:v>模型候选可以晋升，但生产默认开关仍独立保持关闭。</x:v>
       </x:c>
       <x:c r="G71" s="49" t="str">
-        <x:v>单次偶然结果或不稳定排名可能被错误当成可复现能力，导致后续模型对照失去公平基线。</x:v>
+        <x:v>只看平均指标或速度可能掩盖逐题回归，或者把模型候选误当成生产上线。</x:v>
       </x:c>
       <x:c r="H71" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I71" s="55" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="J71" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="72" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A72" s="42" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_models.py</x:v>
       </x:c>
       <x:c r="C72" s="49" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_model_matrix_changes_only_declared_embedding_properties</x:v>
       </x:c>
       <x:c r="D72" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E72" s="49" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
       </x:c>
       <x:c r="F72" s="49" t="str">
-        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
+        <x:v>MiniLM 与 MPNet 共用语料、Chunker、相似度、缓存和指标逻辑，未知模型被拒绝。</x:v>
       </x:c>
       <x:c r="G72" s="49" t="str">
-        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
+        <x:v>复制评测代码或接受任意模型可能引入口径漂移，使模型质量对比失去单变量意义。</x:v>
       </x:c>
       <x:c r="H72" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I72" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>1.891</x:v>
       </x:c>
       <x:c r="J72" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="73" ht="198" hidden="0" customHeight="1">
       <x:c r="A73" s="42" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C73" s="49" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
       </x:c>
       <x:c r="D73" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E73" s="49" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
       </x:c>
       <x:c r="F73" s="49" t="str">
-        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
+        <x:v>三个运行的检索结果完全一致，查询延迟变异系数不超过 50%，但生产开关仍保持关闭。</x:v>
       </x:c>
       <x:c r="G73" s="49" t="str">
-        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
+        <x:v>单次偶然结果或不稳定排名可能被错误当成可复现能力，导致后续模型对照失去公平基线。</x:v>
       </x:c>
       <x:c r="H73" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I73" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.051</x:v>
       </x:c>
       <x:c r="J73" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A74" s="42" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -8397,31 +8445,31 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C74" s="49" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D74" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E74" s="49" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="F74" s="49" t="str">
-        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
+        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
       </x:c>
       <x:c r="G74" s="49" t="str">
-        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
+        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
       </x:c>
       <x:c r="H74" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I74" s="55" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J74" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="75" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A75" s="42" t="n">
         <x:v>71</x:v>
       </x:c>
@@ -8429,25 +8477,25 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C75" s="49" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D75" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E75" s="49" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="F75" s="49" t="str">
-        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
+        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
       </x:c>
       <x:c r="G75" s="49" t="str">
-        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
+        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
       </x:c>
       <x:c r="H75" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I75" s="55" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J75" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8458,162 +8506,162 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C76" s="49" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D76" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E76" s="49" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="F76" s="49" t="str">
-        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
+        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
       </x:c>
       <x:c r="G76" s="49" t="str">
-        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
+        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
       </x:c>
       <x:c r="H76" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I76" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="J76" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="77" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A77" s="42" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C77" s="49" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D77" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E77" s="49" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="F77" s="49" t="str">
-        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
+        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
       </x:c>
       <x:c r="G77" s="49" t="str">
-        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
+        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
       </x:c>
       <x:c r="H77" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I77" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.055</x:v>
       </x:c>
       <x:c r="J77" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="132" hidden="0" customHeight="1">
+    <x:row r="78" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A78" s="42" t="n">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="49" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C78" s="49" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D78" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E78" s="49" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="F78" s="49" t="str">
-        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
+        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
       </x:c>
       <x:c r="G78" s="49" t="str">
-        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
+        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
       </x:c>
       <x:c r="H78" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I78" s="55" t="n">
-        <x:v>30.236</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J78" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="132" hidden="0" customHeight="1">
+    <x:row r="79" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A79" s="42" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C79" s="49" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D79" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E79" s="49" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="F79" s="49" t="str">
-        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
+        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
       </x:c>
       <x:c r="G79" s="49" t="str">
-        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
+        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
       </x:c>
       <x:c r="H79" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I79" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J79" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="80" ht="132" hidden="0" customHeight="1">
       <x:c r="A80" s="42" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C80" s="49" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D80" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E80" s="49" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="F80" s="49" t="str">
-        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
+        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
       </x:c>
       <x:c r="G80" s="49" t="str">
-        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
+        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
       </x:c>
       <x:c r="H80" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I80" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>62.618</x:v>
       </x:c>
       <x:c r="J80" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="81" ht="132" hidden="0" customHeight="1">
       <x:c r="A81" s="42" t="n">
         <x:v>77</x:v>
       </x:c>
@@ -8621,19 +8669,19 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C81" s="49" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D81" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E81" s="49" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="F81" s="49" t="str">
-        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
+        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
       </x:c>
       <x:c r="G81" s="49" t="str">
-        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
+        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
       </x:c>
       <x:c r="H81" s="52" t="str">
         <x:v>通过</x:v>
@@ -8645,33 +8693,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="82" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A82" s="42" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C82" s="49" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D82" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E82" s="49" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="F82" s="49" t="str">
-        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
+        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
       </x:c>
       <x:c r="G82" s="49" t="str">
-        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
+        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
       </x:c>
       <x:c r="H82" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I82" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J82" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8682,28 +8730,28 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C83" s="49" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D83" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E83" s="49" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="F83" s="49" t="str">
-        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
+        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
       </x:c>
       <x:c r="G83" s="49" t="str">
-        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
+        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
       </x:c>
       <x:c r="H83" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I83" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J83" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8717,31 +8765,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C84" s="49" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D84" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E84" s="49" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="F84" s="49" t="str">
-        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
+        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
       </x:c>
       <x:c r="G84" s="49" t="str">
-        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
+        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
       </x:c>
       <x:c r="H84" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I84" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J84" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="85" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A85" s="42" t="n">
         <x:v>81</x:v>
       </x:c>
@@ -8749,31 +8797,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C85" s="49" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D85" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E85" s="49" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="F85" s="49" t="str">
-        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
+        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
       </x:c>
       <x:c r="G85" s="49" t="str">
-        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
+        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
       </x:c>
       <x:c r="H85" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I85" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J85" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="132" hidden="0" customHeight="1">
+    <x:row r="86" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A86" s="42" t="n">
         <x:v>82</x:v>
       </x:c>
@@ -8781,31 +8829,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="49" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D86" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E86" s="49" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="F86" s="49" t="str">
-        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
+        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
       </x:c>
       <x:c r="G86" s="49" t="str">
-        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
+        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
       </x:c>
       <x:c r="H86" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I86" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J86" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="87" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A87" s="42" t="n">
         <x:v>83</x:v>
       </x:c>
@@ -8813,31 +8861,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="49" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D87" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E87" s="49" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="F87" s="49" t="str">
-        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
+        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
       </x:c>
       <x:c r="G87" s="49" t="str">
-        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
+        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
       </x:c>
       <x:c r="H87" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I87" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J87" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="88" ht="132" hidden="0" customHeight="1">
       <x:c r="A88" s="42" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -8845,95 +8893,95 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="49" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D88" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E88" s="49" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="F88" s="49" t="str">
-        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
+        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
       </x:c>
       <x:c r="G88" s="49" t="str">
-        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
+        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
       </x:c>
       <x:c r="H88" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I88" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J88" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="89" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A89" s="42" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C89" s="49" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D89" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E89" s="49" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="F89" s="49" t="str">
-        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
+        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
       </x:c>
       <x:c r="G89" s="49" t="str">
-        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
+        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
       </x:c>
       <x:c r="H89" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I89" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J89" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="132" hidden="0" customHeight="1">
+    <x:row r="90" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A90" s="42" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C90" s="49" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D90" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E90" s="49" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="F90" s="49" t="str">
-        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
+        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
       </x:c>
       <x:c r="G90" s="49" t="str">
-        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
+        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
       </x:c>
       <x:c r="H90" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I90" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.016</x:v>
       </x:c>
       <x:c r="J90" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="132" hidden="0" customHeight="1">
+    <x:row r="91" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A91" s="42" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -8941,31 +8989,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C91" s="49" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D91" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E91" s="49" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="F91" s="49" t="str">
-        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
+        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
       </x:c>
       <x:c r="G91" s="49" t="str">
-        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
+        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
       </x:c>
       <x:c r="H91" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I91" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J91" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="92" ht="132" hidden="0" customHeight="1">
       <x:c r="A92" s="42" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -8973,19 +9021,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C92" s="49" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D92" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E92" s="49" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="F92" s="49" t="str">
-        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
+        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
       </x:c>
       <x:c r="G92" s="49" t="str">
-        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
+        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
       </x:c>
       <x:c r="H92" s="52" t="str">
         <x:v>通过</x:v>
@@ -8997,7 +9045,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="93" ht="132" hidden="0" customHeight="1">
       <x:c r="A93" s="42" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -9005,25 +9053,25 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="49" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D93" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E93" s="49" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="F93" s="49" t="str">
-        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
+        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
       </x:c>
       <x:c r="G93" s="49" t="str">
-        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
+        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
       </x:c>
       <x:c r="H93" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I93" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J93" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9037,25 +9085,25 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="49" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D94" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E94" s="49" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="F94" s="49" t="str">
-        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
+        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
       </x:c>
       <x:c r="G94" s="49" t="str">
-        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
+        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
       </x:c>
       <x:c r="H94" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I94" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J94" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9069,127 +9117,127 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="49" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D95" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E95" s="49" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="F95" s="49" t="str">
-        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
+        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
       </x:c>
       <x:c r="G95" s="49" t="str">
-        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
+        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
       </x:c>
       <x:c r="H95" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I95" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J95" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="96" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A96" s="42" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" s="49" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C96" s="49" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D96" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E96" s="49" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="F96" s="49" t="str">
-        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
+        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
       </x:c>
       <x:c r="G96" s="49" t="str">
-        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
+        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
       </x:c>
       <x:c r="H96" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I96" s="55" t="n">
-        <x:v>2.386</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J96" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="97" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A97" s="42" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C97" s="49" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D97" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E97" s="49" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="F97" s="49" t="str">
-        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
+        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
       </x:c>
       <x:c r="G97" s="49" t="str">
-        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
+        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
       </x:c>
       <x:c r="H97" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I97" s="55" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J97" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="98" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A98" s="42" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C98" s="49" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D98" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E98" s="49" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="F98" s="49" t="str">
-        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
+        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
       </x:c>
       <x:c r="G98" s="49" t="str">
-        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
+        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
       </x:c>
       <x:c r="H98" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I98" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>2.352</x:v>
       </x:c>
       <x:c r="J98" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="99" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A99" s="42" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -9197,25 +9245,25 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C99" s="49" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D99" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E99" s="49" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="F99" s="49" t="str">
-        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
+        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
       </x:c>
       <x:c r="G99" s="49" t="str">
-        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
+        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
       </x:c>
       <x:c r="H99" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I99" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.046</x:v>
       </x:c>
       <x:c r="J99" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9229,95 +9277,95 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C100" s="49" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D100" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E100" s="49" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="F100" s="49" t="str">
-        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
+        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
       </x:c>
       <x:c r="G100" s="49" t="str">
-        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
+        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
       </x:c>
       <x:c r="H100" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I100" s="55" t="n">
-        <x:v>1.128</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J100" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A101" s="42" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C101" s="49" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D101" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E101" s="49" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="F101" s="49" t="str">
-        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
+        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
       </x:c>
       <x:c r="G101" s="49" t="str">
-        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
+        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
       </x:c>
       <x:c r="H101" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I101" s="55" t="n">
-        <x:v>0.188</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J101" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="102" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A102" s="42" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C102" s="49" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D102" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E102" s="49" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="F102" s="49" t="str">
-        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
+        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
       </x:c>
       <x:c r="G102" s="49" t="str">
-        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
+        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
       </x:c>
       <x:c r="H102" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I102" s="55" t="n">
-        <x:v>0.106</x:v>
+        <x:v>1.166</x:v>
       </x:c>
       <x:c r="J102" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="103" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A103" s="42" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -9325,25 +9373,25 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C103" s="49" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D103" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E103" s="49" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="F103" s="49" t="str">
-        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
+        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
       </x:c>
       <x:c r="G103" s="49" t="str">
-        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
+        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
       </x:c>
       <x:c r="H103" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I103" s="55" t="n">
-        <x:v>0.056</x:v>
+        <x:v>0.192</x:v>
       </x:c>
       <x:c r="J103" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9357,127 +9405,127 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C104" s="49" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D104" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E104" s="49" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="F104" s="49" t="str">
-        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
+        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
       </x:c>
       <x:c r="G104" s="49" t="str">
-        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
+        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
       </x:c>
       <x:c r="H104" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I104" s="55" t="n">
-        <x:v>0.094</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="J104" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="132" hidden="0" customHeight="1">
+    <x:row r="105" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A105" s="42" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="49" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C105" s="49" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D105" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E105" s="49" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="F105" s="49" t="str">
-        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
+        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
       </x:c>
       <x:c r="G105" s="49" t="str">
-        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
+        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
       </x:c>
       <x:c r="H105" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I105" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="J105" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="106" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A106" s="42" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C106" s="49" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D106" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E106" s="49" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="F106" s="49" t="str">
-        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
+        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
       </x:c>
       <x:c r="G106" s="49" t="str">
-        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
+        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
       </x:c>
       <x:c r="H106" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I106" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="J106" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="107" ht="132" hidden="0" customHeight="1">
       <x:c r="A107" s="42" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C107" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D107" s="49" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E107" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="F107" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
       </x:c>
       <x:c r="G107" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
       </x:c>
       <x:c r="H107" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I107" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J107" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="108" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A108" s="42" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -9485,25 +9533,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C108" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D108" s="49" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E108" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="F108" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
       </x:c>
       <x:c r="G108" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
       </x:c>
       <x:c r="H108" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I108" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J108" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9517,10 +9565,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C109" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D109" s="49" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E109" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9535,7 +9583,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I109" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J109" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9549,10 +9597,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D110" s="49" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E110" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9567,7 +9615,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I110" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J110" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9581,10 +9629,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D111" s="49" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E111" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9599,13 +9647,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I111" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J111" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="112" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A112" s="42" t="n">
         <x:v>108</x:v>
       </x:c>
@@ -9613,25 +9661,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D112" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E112" s="49" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F112" s="49" t="str">
-        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G112" s="49" t="str">
-        <x:v>查询改写异常可能导致完全不检索。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H112" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I112" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J112" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9645,31 +9693,31 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D113" s="49" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E113" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F113" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G113" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H113" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I113" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J113" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="114" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A114" s="42" t="n">
         <x:v>110</x:v>
       </x:c>
@@ -9677,25 +9725,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D114" s="49" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E114" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="F114" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
       </x:c>
       <x:c r="G114" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>查询改写异常可能导致完全不检索。</x:v>
       </x:c>
       <x:c r="H114" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I114" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J114" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9709,10 +9757,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D115" s="49" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E115" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9727,7 +9775,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I115" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J115" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9741,10 +9789,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D116" s="49" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E116" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9759,7 +9807,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I116" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J116" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9773,10 +9821,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D117" s="49" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E117" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9791,7 +9839,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I117" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J117" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9805,10 +9853,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D118" s="49" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E118" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9823,13 +9871,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I118" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J118" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="119" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A119" s="42" t="n">
         <x:v>115</x:v>
       </x:c>
@@ -9837,25 +9885,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="49" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D119" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E119" s="49" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F119" s="49" t="str">
-        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G119" s="49" t="str">
-        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H119" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I119" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J119" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9869,51 +9917,51 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="49" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D120" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E120" s="49" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F120" s="49" t="str">
-        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G120" s="49" t="str">
-        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H120" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I120" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J120" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="121" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A121" s="42" t="n">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B121" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="49" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D121" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E121" s="49" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="F121" s="49" t="str">
-        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
+        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
       </x:c>
       <x:c r="G121" s="49" t="str">
-        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
+        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
       </x:c>
       <x:c r="H121" s="52" t="str">
         <x:v>通过</x:v>
@@ -9930,22 +9978,22 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B122" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="49" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D122" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E122" s="49" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="F122" s="49" t="str">
-        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
+        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
       </x:c>
       <x:c r="G122" s="49" t="str">
-        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
+        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
       </x:c>
       <x:c r="H122" s="52" t="str">
         <x:v>通过</x:v>
@@ -9957,7 +10005,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="132" hidden="0" customHeight="1">
+    <x:row r="123" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A123" s="42" t="n">
         <x:v>119</x:v>
       </x:c>
@@ -9965,31 +10013,31 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C123" s="49" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D123" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E123" s="49" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="F123" s="49" t="str">
-        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
+        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
       </x:c>
       <x:c r="G123" s="49" t="str">
-        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
+        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
       </x:c>
       <x:c r="H123" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I123" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J123" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="124" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A124" s="42" t="n">
         <x:v>120</x:v>
       </x:c>
@@ -9997,19 +10045,19 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C124" s="49" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D124" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E124" s="49" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="F124" s="49" t="str">
-        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
+        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
       </x:c>
       <x:c r="G124" s="49" t="str">
-        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
+        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
       </x:c>
       <x:c r="H124" s="52" t="str">
         <x:v>通过</x:v>
@@ -10026,66 +10074,66 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C125" s="49" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D125" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E125" s="49" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="F125" s="49" t="str">
-        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
+        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
       </x:c>
       <x:c r="G125" s="49" t="str">
-        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
+        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
       </x:c>
       <x:c r="H125" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I125" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J125" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="126" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A126" s="42" t="n">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C126" s="49" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D126" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E126" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="F126" s="49" t="str">
-        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
+        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
       </x:c>
       <x:c r="G126" s="49" t="str">
-        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
+        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
       </x:c>
       <x:c r="H126" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I126" s="55" t="n">
-        <x:v>14.87</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J126" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="127" ht="132" hidden="0" customHeight="1">
       <x:c r="A127" s="42" t="n">
         <x:v>123</x:v>
       </x:c>
@@ -10093,95 +10141,95 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C127" s="49" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D127" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E127" s="49" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="F127" s="49" t="str">
-        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
+        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
       </x:c>
       <x:c r="G127" s="49" t="str">
-        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
+        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
       </x:c>
       <x:c r="H127" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I127" s="55" t="n">
-        <x:v>14.978</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J127" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="132" hidden="0" customHeight="1">
+    <x:row r="128" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A128" s="42" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C128" s="49" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D128" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E128" s="49" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="F128" s="49" t="str">
-        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
+        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
       </x:c>
       <x:c r="G128" s="49" t="str">
-        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
+        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
       </x:c>
       <x:c r="H128" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I128" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>32.145</x:v>
       </x:c>
       <x:c r="J128" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="129" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A129" s="42" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="49" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D129" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E129" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="F129" s="49" t="str">
-        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
+        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
       </x:c>
       <x:c r="G129" s="49" t="str">
-        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
+        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
       </x:c>
       <x:c r="H129" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I129" s="55" t="n">
-        <x:v>18.845</x:v>
+        <x:v>31.502</x:v>
       </x:c>
       <x:c r="J129" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="130" ht="132" hidden="0" customHeight="1">
       <x:c r="A130" s="42" t="n">
         <x:v>126</x:v>
       </x:c>
@@ -10189,57 +10237,57 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C130" s="49" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D130" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E130" s="49" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="F130" s="49" t="str">
-        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
+        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
       </x:c>
       <x:c r="G130" s="49" t="str">
-        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
+        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
       </x:c>
       <x:c r="H130" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I130" s="55" t="n">
-        <x:v>17.713</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J130" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="131" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A131" s="42" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C131" s="49" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D131" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E131" s="49" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="F131" s="49" t="str">
-        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
+        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
       </x:c>
       <x:c r="G131" s="49" t="str">
-        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
+        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
       </x:c>
       <x:c r="H131" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I131" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>38.998</x:v>
       </x:c>
       <x:c r="J131" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10250,34 +10298,34 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C132" s="49" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D132" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E132" s="49" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="F132" s="49" t="str">
-        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
+        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
       </x:c>
       <x:c r="G132" s="49" t="str">
-        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
+        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
       </x:c>
       <x:c r="H132" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I132" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>30.151</x:v>
       </x:c>
       <x:c r="J132" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="133" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A133" s="42" t="n">
         <x:v>129</x:v>
       </x:c>
@@ -10285,31 +10333,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C133" s="49" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D133" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E133" s="49" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="F133" s="49" t="str">
-        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
+        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
       </x:c>
       <x:c r="G133" s="49" t="str">
-        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
+        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
       </x:c>
       <x:c r="H133" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I133" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J133" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="134" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A134" s="42" t="n">
         <x:v>130</x:v>
       </x:c>
@@ -10317,25 +10365,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C134" s="49" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D134" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E134" s="49" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="F134" s="49" t="str">
-        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
+        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
       </x:c>
       <x:c r="G134" s="49" t="str">
-        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
+        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
       </x:c>
       <x:c r="H134" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I134" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J134" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10349,19 +10397,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="49" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D135" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E135" s="49" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="F135" s="49" t="str">
-        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
+        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
       </x:c>
       <x:c r="G135" s="49" t="str">
-        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
+        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
       </x:c>
       <x:c r="H135" s="52" t="str">
         <x:v>通过</x:v>
@@ -10373,7 +10421,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="136" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A136" s="42" t="n">
         <x:v>132</x:v>
       </x:c>
@@ -10381,19 +10429,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="49" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D136" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E136" s="49" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="F136" s="49" t="str">
-        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
+        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
       </x:c>
       <x:c r="G136" s="49" t="str">
-        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
+        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
       </x:c>
       <x:c r="H136" s="52" t="str">
         <x:v>通过</x:v>
@@ -10405,7 +10453,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="137" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A137" s="42" t="n">
         <x:v>133</x:v>
       </x:c>
@@ -10413,19 +10461,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="49" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D137" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E137" s="49" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="F137" s="49" t="str">
-        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
+        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
       </x:c>
       <x:c r="G137" s="49" t="str">
-        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
+        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
       </x:c>
       <x:c r="H137" s="52" t="str">
         <x:v>通过</x:v>
@@ -10437,7 +10485,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="138" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A138" s="42" t="n">
         <x:v>134</x:v>
       </x:c>
@@ -10445,19 +10493,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="49" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D138" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E138" s="49" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="F138" s="49" t="str">
-        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
+        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
       </x:c>
       <x:c r="G138" s="49" t="str">
-        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
+        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
       </x:c>
       <x:c r="H138" s="52" t="str">
         <x:v>通过</x:v>
@@ -10469,7 +10517,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A139" s="42" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -10477,19 +10525,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D139" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E139" s="49" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="F139" s="49" t="str">
-        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
+        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
       </x:c>
       <x:c r="G139" s="49" t="str">
-        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
+        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
       </x:c>
       <x:c r="H139" s="52" t="str">
         <x:v>通过</x:v>
@@ -10501,7 +10549,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="132" hidden="0" customHeight="1">
+    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A140" s="42" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -10509,19 +10557,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D140" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E140" s="49" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="F140" s="49" t="str">
-        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
+        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
       </x:c>
       <x:c r="G140" s="49" t="str">
-        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
+        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
       </x:c>
       <x:c r="H140" s="52" t="str">
         <x:v>通过</x:v>
@@ -10541,31 +10589,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="49" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D141" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E141" s="49" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="F141" s="49" t="str">
-        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
+        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
       </x:c>
       <x:c r="G141" s="49" t="str">
-        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
+        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
       </x:c>
       <x:c r="H141" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I141" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J141" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="142" ht="132" hidden="0" customHeight="1">
       <x:c r="A142" s="42" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -10573,19 +10621,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="49" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D142" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E142" s="49" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="F142" s="49" t="str">
-        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
+        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
       </x:c>
       <x:c r="G142" s="49" t="str">
-        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
+        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
       </x:c>
       <x:c r="H142" s="52" t="str">
         <x:v>通过</x:v>
@@ -10597,7 +10645,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="143" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A143" s="42" t="n">
         <x:v>139</x:v>
       </x:c>
@@ -10605,19 +10653,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="49" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D143" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E143" s="49" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="F143" s="49" t="str">
-        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
+        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
       </x:c>
       <x:c r="G143" s="49" t="str">
-        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
+        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
       </x:c>
       <x:c r="H143" s="52" t="str">
         <x:v>通过</x:v>
@@ -10629,33 +10677,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="144" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A144" s="42" t="n">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B144" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="49" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D144" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E144" s="49" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="F144" s="49" t="str">
-        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
+        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
       </x:c>
       <x:c r="G144" s="49" t="str">
-        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
+        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
       </x:c>
       <x:c r="H144" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I144" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J144" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10666,28 +10714,28 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B145" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="49" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D145" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E145" s="49" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="F145" s="49" t="str">
-        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
+        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
       </x:c>
       <x:c r="G145" s="49" t="str">
-        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
+        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
       </x:c>
       <x:c r="H145" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I145" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J145" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10701,31 +10749,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C146" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D146" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E146" s="49" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="F146" s="49" t="str">
-        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
+        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
       </x:c>
       <x:c r="G146" s="49" t="str">
-        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
+        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
       </x:c>
       <x:c r="H146" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I146" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J146" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A147" s="42" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -10733,25 +10781,25 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C147" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D147" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E147" s="49" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="F147" s="49" t="str">
-        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
+        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
       </x:c>
       <x:c r="G147" s="49" t="str">
-        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
+        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
       </x:c>
       <x:c r="H147" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I147" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J147" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10765,31 +10813,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D148" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E148" s="49" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="F148" s="49" t="str">
-        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
+        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
       </x:c>
       <x:c r="G148" s="49" t="str">
-        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
+        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
       </x:c>
       <x:c r="H148" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I148" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J148" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="149" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A149" s="42" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -10797,19 +10845,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="49" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D149" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E149" s="49" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="F149" s="49" t="str">
-        <x:v>两条无去重键文档均被保留。</x:v>
+        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
       </x:c>
       <x:c r="G149" s="49" t="str">
-        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
+        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
       </x:c>
       <x:c r="H149" s="52" t="str">
         <x:v>通过</x:v>
@@ -10821,7 +10869,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="150" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A150" s="42" t="n">
         <x:v>146</x:v>
       </x:c>
@@ -10829,31 +10877,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="49" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D150" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E150" s="49" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="F150" s="49" t="str">
-        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
+        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
       </x:c>
       <x:c r="G150" s="49" t="str">
-        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
+        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
       </x:c>
       <x:c r="H150" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I150" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J150" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A151" s="42" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -10861,19 +10909,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="49" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D151" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E151" s="49" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="F151" s="49" t="str">
-        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
+        <x:v>两条无去重键文档均被保留。</x:v>
       </x:c>
       <x:c r="G151" s="49" t="str">
-        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
+        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
       </x:c>
       <x:c r="H151" s="52" t="str">
         <x:v>通过</x:v>
@@ -10885,33 +10933,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="152" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A152" s="42" t="n">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B152" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C152" s="49" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D152" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E152" s="49" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="F152" s="49" t="str">
-        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
+        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
       </x:c>
       <x:c r="G152" s="49" t="str">
-        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
+        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
       </x:c>
       <x:c r="H152" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I152" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J152" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10922,34 +10970,34 @@
         <x:v>149</x:v>
       </x:c>
       <x:c r="B153" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="49" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D153" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E153" s="49" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="F153" s="49" t="str">
-        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
+        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
       </x:c>
       <x:c r="G153" s="49" t="str">
-        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
+        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
       </x:c>
       <x:c r="H153" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I153" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J153" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="154" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A154" s="42" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -10957,31 +11005,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C154" s="49" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D154" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E154" s="49" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="F154" s="49" t="str">
-        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
+        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
       </x:c>
       <x:c r="G154" s="49" t="str">
-        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
+        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
       </x:c>
       <x:c r="H154" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I154" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J154" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="132" hidden="0" customHeight="1">
+    <x:row r="155" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A155" s="42" t="n">
         <x:v>151</x:v>
       </x:c>
@@ -10989,31 +11037,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C155" s="49" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D155" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E155" s="49" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="F155" s="49" t="str">
-        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
+        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
       </x:c>
       <x:c r="G155" s="49" t="str">
-        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
+        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
       </x:c>
       <x:c r="H155" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I155" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J155" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="132" hidden="0" customHeight="1">
+    <x:row r="156" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A156" s="42" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -11021,31 +11069,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="49" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D156" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E156" s="49" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="F156" s="49" t="str">
-        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
+        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
       </x:c>
       <x:c r="G156" s="49" t="str">
-        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
+        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
       </x:c>
       <x:c r="H156" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I156" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J156" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="157" ht="132" hidden="0" customHeight="1">
       <x:c r="A157" s="42" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -11053,31 +11101,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="49" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D157" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E157" s="49" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="F157" s="49" t="str">
-        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
+        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
       </x:c>
       <x:c r="G157" s="49" t="str">
-        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
+        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
       </x:c>
       <x:c r="H157" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I157" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J157" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="158" ht="132" hidden="0" customHeight="1">
       <x:c r="A158" s="42" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -11085,31 +11133,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="49" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D158" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E158" s="49" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="F158" s="49" t="str">
-        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
+        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
       </x:c>
       <x:c r="G158" s="49" t="str">
-        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
+        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
       </x:c>
       <x:c r="H158" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I158" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J158" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="159" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A159" s="42" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -11117,31 +11165,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="49" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D159" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E159" s="49" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="F159" s="49" t="str">
-        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
+        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
       </x:c>
       <x:c r="G159" s="49" t="str">
-        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
+        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
       </x:c>
       <x:c r="H159" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I159" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J159" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A160" s="42" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -11149,25 +11197,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="49" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D160" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E160" s="49" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F160" s="49" t="str">
-        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
+        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
       </x:c>
       <x:c r="G160" s="49" t="str">
-        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
+        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
       </x:c>
       <x:c r="H160" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I160" s="55" t="n">
-        <x:v>0.117</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J160" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11181,31 +11229,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="49" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D161" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E161" s="49" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="F161" s="49" t="str">
-        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
+        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
       </x:c>
       <x:c r="G161" s="49" t="str">
-        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
+        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
       </x:c>
       <x:c r="H161" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I161" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J161" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="162" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A162" s="42" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -11213,31 +11261,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="49" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D162" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E162" s="49" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="F162" s="49" t="str">
-        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
+        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
       </x:c>
       <x:c r="G162" s="49" t="str">
-        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
+        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
       </x:c>
       <x:c r="H162" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I162" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.157</x:v>
       </x:c>
       <x:c r="J162" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="163" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A163" s="42" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -11245,31 +11293,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="49" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D163" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E163" s="49" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="F163" s="49" t="str">
-        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
+        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
       </x:c>
       <x:c r="G163" s="49" t="str">
-        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
+        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
       </x:c>
       <x:c r="H163" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I163" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J163" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="132" hidden="0" customHeight="1">
+    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A164" s="42" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -11277,31 +11325,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="49" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D164" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E164" s="49" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="F164" s="49" t="str">
-        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
+        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
       </x:c>
       <x:c r="G164" s="49" t="str">
-        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
+        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
       </x:c>
       <x:c r="H164" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I164" s="55" t="n">
-        <x:v>0.225</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="J164" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="165" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A165" s="42" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -11309,31 +11357,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="49" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D165" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E165" s="49" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="F165" s="49" t="str">
-        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
+        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
       </x:c>
       <x:c r="G165" s="49" t="str">
-        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
+        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
       </x:c>
       <x:c r="H165" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I165" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J165" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="166" ht="132" hidden="0" customHeight="1">
       <x:c r="A166" s="42" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -11341,25 +11389,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="49" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D166" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E166" s="49" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="F166" s="49" t="str">
-        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
+        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
       </x:c>
       <x:c r="G166" s="49" t="str">
-        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
+        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
       </x:c>
       <x:c r="H166" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I166" s="55" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.294</x:v>
       </x:c>
       <x:c r="J166" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11373,95 +11421,95 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="49" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D167" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E167" s="49" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="F167" s="49" t="str">
-        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
+        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
       </x:c>
       <x:c r="G167" s="49" t="str">
-        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
+        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
       </x:c>
       <x:c r="H167" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I167" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J167" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="168" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A168" s="42" t="n">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B168" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="49" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D168" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E168" s="49" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="F168" s="49" t="str">
-        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
+        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
       </x:c>
       <x:c r="G168" s="49" t="str">
-        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
+        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
       </x:c>
       <x:c r="H168" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I168" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="J168" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="169" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A169" s="42" t="n">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B169" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="49" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D169" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E169" s="49" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="F169" s="49" t="str">
-        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
+        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
       </x:c>
       <x:c r="G169" s="49" t="str">
-        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
+        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
       </x:c>
       <x:c r="H169" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I169" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J169" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="170" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A170" s="42" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -11469,19 +11517,19 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C170" s="49" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D170" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E170" s="49" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="F170" s="49" t="str">
-        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
+        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
       </x:c>
       <x:c r="G170" s="49" t="str">
-        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
+        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
       </x:c>
       <x:c r="H170" s="52" t="str">
         <x:v>通过</x:v>
@@ -11501,121 +11549,121 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C171" s="49" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D171" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E171" s="49" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="F171" s="49" t="str">
-        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
+        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
       </x:c>
       <x:c r="G171" s="49" t="str">
-        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
+        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
       </x:c>
       <x:c r="H171" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I171" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J171" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A172" s="42" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="49" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C172" s="49" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D172" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E172" s="49" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="F172" s="49" t="str">
-        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
+        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
       </x:c>
       <x:c r="G172" s="49" t="str">
-        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
+        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
       </x:c>
       <x:c r="H172" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I172" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J172" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="173" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A173" s="42" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B173" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C173" s="49" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D173" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E173" s="49" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="F173" s="49" t="str">
-        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
+        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
       </x:c>
       <x:c r="G173" s="49" t="str">
-        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
+        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
       </x:c>
       <x:c r="H173" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I173" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J173" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="174" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A174" s="42" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C174" s="49" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D174" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E174" s="49" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="F174" s="49" t="str">
-        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
+        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
       </x:c>
       <x:c r="G174" s="49" t="str">
-        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
+        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
       </x:c>
       <x:c r="H174" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I174" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J174" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11626,28 +11674,28 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C175" s="49" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D175" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E175" s="49" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="F175" s="49" t="str">
-        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
+        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
       </x:c>
       <x:c r="G175" s="49" t="str">
-        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
+        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
       </x:c>
       <x:c r="H175" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I175" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J175" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11658,22 +11706,22 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C176" s="49" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D176" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E176" s="49" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="F176" s="49" t="str">
-        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
+        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
       </x:c>
       <x:c r="G176" s="49" t="str">
-        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
+        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
       </x:c>
       <x:c r="H176" s="52" t="str">
         <x:v>通过</x:v>
@@ -11685,7 +11733,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="177" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A177" s="42" t="n">
         <x:v>173</x:v>
       </x:c>
@@ -11693,25 +11741,25 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C177" s="49" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D177" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E177" s="49" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="F177" s="49" t="str">
-        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
+        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
       </x:c>
       <x:c r="G177" s="49" t="str">
-        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
+        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
       </x:c>
       <x:c r="H177" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I177" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J177" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11722,22 +11770,22 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C178" s="49" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D178" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E178" s="49" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="F178" s="49" t="str">
-        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
+        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
       </x:c>
       <x:c r="G178" s="49" t="str">
-        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
+        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
       </x:c>
       <x:c r="H178" s="52" t="str">
         <x:v>通过</x:v>
@@ -11754,34 +11802,34 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C179" s="49" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D179" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E179" s="49" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="F179" s="49" t="str">
-        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
+        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
       </x:c>
       <x:c r="G179" s="49" t="str">
-        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
+        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
       </x:c>
       <x:c r="H179" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I179" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J179" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="180" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A180" s="42" t="n">
         <x:v>176</x:v>
       </x:c>
@@ -11789,31 +11837,31 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C180" s="49" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D180" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E180" s="49" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="F180" s="49" t="str">
-        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
+        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
       </x:c>
       <x:c r="G180" s="49" t="str">
-        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
+        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
       </x:c>
       <x:c r="H180" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I180" s="55" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J180" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="181" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A181" s="42" t="n">
         <x:v>177</x:v>
       </x:c>
@@ -11821,121 +11869,121 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C181" s="49" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D181" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E181" s="49" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="F181" s="49" t="str">
-        <x:v>单子查询继续走直接调用路径。</x:v>
+        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
       </x:c>
       <x:c r="G181" s="49" t="str">
-        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
+        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
       </x:c>
       <x:c r="H181" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I181" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J181" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="182" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A182" s="42" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C182" s="49" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D182" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E182" s="49" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="F182" s="49" t="str">
-        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
+        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
       </x:c>
       <x:c r="G182" s="49" t="str">
-        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
+        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
       </x:c>
       <x:c r="H182" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I182" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="J182" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="183" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A183" s="42" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C183" s="49" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D183" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E183" s="49" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="F183" s="49" t="str">
-        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
+        <x:v>单子查询继续走直接调用路径。</x:v>
       </x:c>
       <x:c r="G183" s="49" t="str">
-        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
+        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
       </x:c>
       <x:c r="H183" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I183" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J183" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="184" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A184" s="42" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="49" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C184" s="49" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D184" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E184" s="49" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="F184" s="49" t="str">
-        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
+        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
       </x:c>
       <x:c r="G184" s="49" t="str">
-        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
+        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
       </x:c>
       <x:c r="H184" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I184" s="55" t="n">
-        <x:v>0.308</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J184" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11946,118 +11994,118 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C185" s="49" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D185" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E185" s="49" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F185" s="49" t="str">
-        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
+        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
       </x:c>
       <x:c r="G185" s="49" t="str">
-        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
+        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
       </x:c>
       <x:c r="H185" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I185" s="55" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J185" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="132" hidden="0" customHeight="1">
+    <x:row r="186" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A186" s="42" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C186" s="49" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D186" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E186" s="49" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="F186" s="49" t="str">
-        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
+        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
       </x:c>
       <x:c r="G186" s="49" t="str">
-        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
+        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
       </x:c>
       <x:c r="H186" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I186" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="J186" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="132" hidden="0" customHeight="1">
+    <x:row r="187" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A187" s="42" t="n">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B187" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C187" s="49" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D187" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E187" s="49" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="F187" s="49" t="str">
-        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
+        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
       </x:c>
       <x:c r="G187" s="49" t="str">
-        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
+        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
       </x:c>
       <x:c r="H187" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I187" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="J187" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="188" ht="132" hidden="0" customHeight="1">
       <x:c r="A188" s="42" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C188" s="49" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D188" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E188" s="49" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="F188" s="49" t="str">
-        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
+        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
       </x:c>
       <x:c r="G188" s="49" t="str">
-        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
+        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
       </x:c>
       <x:c r="H188" s="52" t="str">
         <x:v>通过</x:v>
@@ -12069,7 +12117,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="189" ht="132" hidden="0" customHeight="1">
       <x:c r="A189" s="42" t="n">
         <x:v>185</x:v>
       </x:c>
@@ -12077,31 +12125,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C189" s="49" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D189" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E189" s="49" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="F189" s="49" t="str">
-        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
+        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
       </x:c>
       <x:c r="G189" s="49" t="str">
-        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
+        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
       </x:c>
       <x:c r="H189" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I189" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J189" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="190" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A190" s="42" t="n">
         <x:v>186</x:v>
       </x:c>
@@ -12109,31 +12157,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C190" s="49" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D190" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E190" s="49" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="F190" s="49" t="str">
-        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
+        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
       </x:c>
       <x:c r="G190" s="49" t="str">
-        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
+        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
       </x:c>
       <x:c r="H190" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I190" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J190" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A191" s="42" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -12141,25 +12189,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="49" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D191" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E191" s="49" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="F191" s="49" t="str">
-        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
+        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
       </x:c>
       <x:c r="G191" s="49" t="str">
-        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
+        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
       </x:c>
       <x:c r="H191" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I191" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J191" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12173,19 +12221,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="49" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D192" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E192" s="49" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="F192" s="49" t="str">
-        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
+        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
       </x:c>
       <x:c r="G192" s="49" t="str">
-        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
+        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
       </x:c>
       <x:c r="H192" s="52" t="str">
         <x:v>通过</x:v>
@@ -12197,7 +12245,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="193" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A193" s="42" t="n">
         <x:v>189</x:v>
       </x:c>
@@ -12205,25 +12253,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="49" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D193" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E193" s="49" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="F193" s="49" t="str">
-        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
+        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
       </x:c>
       <x:c r="G193" s="49" t="str">
-        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
+        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
       </x:c>
       <x:c r="H193" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I193" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J193" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12237,19 +12285,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="49" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D194" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E194" s="49" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="F194" s="49" t="str">
-        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
+        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
       </x:c>
       <x:c r="G194" s="49" t="str">
-        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
+        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
       </x:c>
       <x:c r="H194" s="52" t="str">
         <x:v>通过</x:v>
@@ -12261,7 +12309,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="195" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A195" s="42" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -12269,31 +12317,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="49" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D195" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E195" s="49" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="F195" s="49" t="str">
-        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
+        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
       </x:c>
       <x:c r="G195" s="49" t="str">
-        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
+        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
       </x:c>
       <x:c r="H195" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I195" s="55" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J195" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="196" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A196" s="42" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -12301,25 +12349,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="49" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D196" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E196" s="49" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="F196" s="49" t="str">
-        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
+        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
       </x:c>
       <x:c r="G196" s="49" t="str">
-        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
+        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
       </x:c>
       <x:c r="H196" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I196" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J196" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12333,31 +12381,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="49" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D197" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E197" s="49" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="F197" s="49" t="str">
-        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
+        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
       </x:c>
       <x:c r="G197" s="49" t="str">
-        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
+        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
       </x:c>
       <x:c r="H197" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I197" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="J197" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="198" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A198" s="42" t="n">
         <x:v>194</x:v>
       </x:c>
@@ -12365,31 +12413,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="49" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D198" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E198" s="49" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="F198" s="49" t="str">
-        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
+        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
       </x:c>
       <x:c r="G198" s="49" t="str">
-        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
+        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
       </x:c>
       <x:c r="H198" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I198" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J198" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="132" hidden="0" customHeight="1">
+    <x:row r="199" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A199" s="42" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -12397,19 +12445,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="49" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D199" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E199" s="49" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="F199" s="49" t="str">
-        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
+        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
       </x:c>
       <x:c r="G199" s="49" t="str">
-        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
+        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
       </x:c>
       <x:c r="H199" s="52" t="str">
         <x:v>通过</x:v>
@@ -12421,7 +12469,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="200" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A200" s="42" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -12429,31 +12477,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="49" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D200" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E200" s="49" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="F200" s="49" t="str">
-        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
+        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
       </x:c>
       <x:c r="G200" s="49" t="str">
-        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
+        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
       </x:c>
       <x:c r="H200" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I200" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J200" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="201" ht="132" hidden="0" customHeight="1">
       <x:c r="A201" s="42" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -12461,31 +12509,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="49" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D201" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E201" s="49" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="F201" s="49" t="str">
-        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
       </x:c>
       <x:c r="G201" s="49" t="str">
-        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
       </x:c>
       <x:c r="H201" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I201" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J201" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="132" hidden="0" customHeight="1">
+    <x:row r="202" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A202" s="42" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -12493,31 +12541,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="49" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D202" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E202" s="49" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="F202" s="49" t="str">
-        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G202" s="49" t="str">
-        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
       </x:c>
       <x:c r="H202" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I202" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J202" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="203" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A203" s="42" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -12525,31 +12573,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="49" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D203" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E203" s="49" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="F203" s="49" t="str">
-        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
       </x:c>
       <x:c r="G203" s="49" t="str">
-        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
       </x:c>
       <x:c r="H203" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I203" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J203" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="204" ht="132" hidden="0" customHeight="1">
       <x:c r="A204" s="42" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -12557,59 +12605,123 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="49" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D204" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E204" s="49" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="F204" s="49" t="str">
+        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+      </x:c>
+      <x:c r="G204" s="49" t="str">
+        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+      </x:c>
+      <x:c r="H204" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I204" s="55" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="J204" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A205" s="42" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B205" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C205" s="49" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D205" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E205" s="49" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="F205" s="49" t="str">
+        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+      </x:c>
+      <x:c r="G205" s="49" t="str">
+        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+      </x:c>
+      <x:c r="H205" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I205" s="55" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="J205" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A206" s="42" t="n">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B206" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C206" s="49" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D204" s="49" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E204" s="49" t="str">
+      <x:c r="D206" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E206" s="49" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="F204" s="49" t="str">
+      <x:c r="F206" s="49" t="str">
         <x:v>限流进入可重试失败类别，不被误记为论文查无。</x:v>
       </x:c>
-      <x:c r="G204" s="49" t="str">
+      <x:c r="G206" s="49" t="str">
         <x:v>匿名访问限流可能污染覆盖率并错误触发论文隔离。</x:v>
       </x:c>
-      <x:c r="H204" s="52" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I204" s="55" t="n">
-        <x:v>0.003</x:v>
-      </x:c>
-      <x:c r="J204" s="58" t="str">
-        <x:v>已登记</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" ht="132" hidden="0" customHeight="1">
-      <x:c r="A205" s="45" t="n">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="B205" s="50" t="str">
+      <x:c r="H206" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I206" s="55" t="n">
+        <x:v>0.004</x:v>
+      </x:c>
+      <x:c r="J206" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="132" hidden="0" customHeight="1">
+      <x:c r="A207" s="45" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B207" s="50" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C205" s="50" t="str">
+      <x:c r="C207" s="50" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D205" s="50" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E205" s="50" t="str">
+      <x:c r="D207" s="50" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E207" s="50" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="F205" s="50" t="str">
+      <x:c r="F207" s="50" t="str">
         <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
       </x:c>
-      <x:c r="G205" s="50" t="str">
+      <x:c r="G207" s="50" t="str">
         <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
       </x:c>
-      <x:c r="H205" s="53" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I205" s="56" t="n">
-        <x:v>0.007</x:v>
-      </x:c>
-      <x:c r="J205" s="59" t="str">
+      <x:c r="H207" s="53" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I207" s="56" t="n">
+        <x:v>0.009</x:v>
+      </x:c>
+      <x:c r="J207" s="59" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
@@ -12618,18 +12730,18 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H205">
+  <x:conditionalFormatting sqref="H5:H207">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="错误"/>
     <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="跳过"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J205">
+  <x:conditionalFormatting sqref="J5:J207">
     <x:cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="未登记"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4057c0d7c65648e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R167d9a8028744dfa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13982,34 +14094,66 @@
       </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="128" t="n">
+      <x:c r="A42" s="127" t="n">
         <x:v>46247.42736111111</x:v>
       </x:c>
-      <x:c r="B42" s="24" t="str">
+      <x:c r="B42" s="23" t="str">
         <x:v>7f436ea669c2</x:v>
       </x:c>
-      <x:c r="C42" s="24" t="n">
+      <x:c r="C42" s="23" t="n">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="D42" s="24" t="n">
+      <x:c r="D42" s="23" t="n">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="E42" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F42" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G42" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="131" t="n">
+      <x:c r="E42" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F42" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="130" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I42" s="30" t="n">
+      <x:c r="I42" s="29" t="n">
         <x:v>133.351</x:v>
       </x:c>
-      <x:c r="J42" s="24" t="n">
+      <x:c r="J42" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="128" t="n">
+        <x:v>46247.44788194445</x:v>
+      </x:c>
+      <x:c r="B43" s="24" t="str">
+        <x:v>fa64c7c71283</x:v>
+      </x:c>
+      <x:c r="C43" s="24" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D43" s="24" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="E43" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F43" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G43" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I43" s="30" t="n">
+        <x:v>266.505</x:v>
+      </x:c>
+      <x:c r="J43" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -14019,7 +14163,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc064e4197625492a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92c795e84cb5497d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/latest_test_report.xlsx
+++ b/reports/latest_test_report.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R124317e12eed4df1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R7ecbdd235ddc4dba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R674d873db6d24725"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Ra9804720c4044f8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="R5274b0e0a02d40e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R18e549adb67b44cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R32182924db02494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R9136c57f12034b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="R47726ba19d1b4a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="R53a14c2706714391"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H207" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H209" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J207" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J209" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J43" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="运行时间"/>
     <x:tableColumn id="2" name="Git Commit"/>
@@ -977,7 +977,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T10:44:57+08:00  |  Git：fa64c7c71283159548fa054dfd35b184c218c305</x:v>
+        <x:v>运行时间：2026-08-13T11:12:50+08:00  |  Git：39a19fca1f844df50e7f0bf2f4be816c7b3c4672</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1007,22 +1007,22 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="74" t="n">
-        <x:f>COUNTA('测试明细'!$A$5:$A$207)</x:f>
-        <x:v>203</x:v>
+        <x:f>COUNTA('测试明细'!$A$5:$A$209)</x:f>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B5" s="75"/>
       <x:c r="C5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$207,"通过")</x:f>
-        <x:v>203</x:v>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$209,"通过")</x:f>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D5" s="75"/>
       <x:c r="E5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$207,"失败")+COUNTIF('测试明细'!$E$5:$E$207,"错误")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$209,"失败")+COUNTIF('测试明细'!$E$5:$E$209,"错误")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="75"/>
       <x:c r="G5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$207,"跳过")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$209,"跳过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="76"/>
@@ -1062,8 +1062,8 @@
       </x:c>
       <x:c r="B9" s="108"/>
       <x:c r="C9" s="109" t="n">
-        <x:f>SUM('测试明细'!$F$5:$F$207)</x:f>
-        <x:v>266.50499999999937</x:v>
+        <x:f>SUM('测试明细'!$F$5:$F$209)</x:f>
+        <x:v>133.42200000000025</x:v>
       </x:c>
       <x:c r="D9" s="109"/>
       <x:c r="E9" s="110" t="n">
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="F9" s="110"/>
       <x:c r="G9" s="110" t="n">
-        <x:f>COUNTIF('用例说明'!$J$5:$J$207,"未登记")</x:f>
+        <x:f>COUNTIF('用例说明'!$J$5:$J$209,"未登记")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="111"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T10:44:57+08:00  |  Git：fa64c7c71283159548fa054dfd35b184c218c305</x:v>
+        <x:v>运行时间：2026-08-13T11:12:50+08:00  |  Git：39a19fca1f844df50e7f0bf2f4be816c7b3c4672</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1280,7 +1280,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
         <x:v>确认旧基线与当前候选实现使用完全相同的能力模块，保证能力对比口径一致。</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F6" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
         <x:v>确认当前实现相对旧基线确实提升关键确定性能力的准确率。</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="32" t="n">
-        <x:v>0.036</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>验证动态查询规划不会为简单问题创建多余检索词，同时保持规划准确。</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F8" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>验证基准报告能同时给出基线值、候选值和差值。</x:v>
@@ -1376,7 +1376,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F9" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
         <x:v>验证离线基准能准确统计成功/失败调用以及输入、输出和总 Token。</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F10" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
         <x:v>验证离线基准能够量化统一 Tool 层的协议、错误和恢复能力。</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F11" s="32" t="n">
-        <x:v>0.014</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
         <x:v>验证离线 Benchmark 对比单源基线与多源候选的覆盖、去重和故障恢复。</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F12" s="32" t="n">
-        <x:v>0.231</x:v>
+        <x:v>0.185</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
         <x:v>验证完整能力基准报告可以用 UTF-8 JSON 保存并重新读取。</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F13" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G13" s="35" t="str">
         <x:v>验证基准工具拒绝不存在的运行配置名称。</x:v>
@@ -1496,7 +1496,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F14" s="32" t="n">
-        <x:v>0.029</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str">
         <x:v>验证候选评测能从 OpenAlex 等二级来源的 DOI 中提取待验证 arXiv 身份。</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
-        <x:v>0.032</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G15" s="35" t="str">
         <x:v>验证联合重放只把普通 DOI 交给 Crossref，排除 arXiv DOI。</x:v>
@@ -1544,7 +1544,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F16" s="32" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.031</x:v>
       </x:c>
       <x:c r="G16" s="35" t="str">
         <x:v>验证成功取得的规范元数据会缓存，快照重放不会重复消耗网络请求。</x:v>
@@ -1568,7 +1568,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
-        <x:v>0.042</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="G17" s="35" t="str">
         <x:v>验证 SSL、超时等临时失败不会被当成永久缓存结果。</x:v>
@@ -1592,7 +1592,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="G18" s="35" t="str">
         <x:v>验证 Crossref 成功记录和明确查无均可重复使用。</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="G19" s="35" t="str">
         <x:v>验证 DOI authority 网络失败不会写入成功缓存。</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="G20" s="35" t="str">
         <x:v>验证本轮候选实验只查询 v2 实际隔离过的身份，控制外部请求成本。</x:v>
@@ -1664,7 +1664,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
-        <x:v>0.057</x:v>
+        <x:v>0.124</x:v>
       </x:c>
       <x:c r="G21" s="35" t="str">
         <x:v>验证规范元数据候选只有在三份完整独立快照、权威覆盖完整且逐题无回归时才通过晋升门槛。</x:v>
@@ -1712,7 +1712,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F23" s="32" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="G23" s="35" t="str">
         <x:v>验证普通 DOI 候选评测只使用所有独立快照都出现的非 arXiv DOI。</x:v>
@@ -1736,7 +1736,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F24" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G24" s="35" t="str">
         <x:v>验证 Crossref 评测严格区分标题匹配、标题冲突、规范查无和网络失败。</x:v>
@@ -1760,7 +1760,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F25" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G25" s="35" t="str">
         <x:v>验证普通 DOI 样本按注册前缀轮转抽取，避免单一高频前缀垄断评测集。</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F26" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G26" s="35" t="str">
         <x:v>验证 provider 一致率只使用双方均成功返回标题的 DOI。</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F27" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G27" s="35" t="str">
         <x:v>验证 DOI 校验在固定污染、缺失、近似、查无和失败场景中达到阶段止损条件。</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F28" s="32" t="n">
-        <x:v>0.142</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="G28" s="35" t="str">
         <x:v>验证普通研究问题按完整 Agentic RAG 节点顺序执行。</x:v>
@@ -1856,7 +1856,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F29" s="32" t="n">
-        <x:v>0.107</x:v>
+        <x:v>0.067</x:v>
       </x:c>
       <x:c r="G29" s="35" t="str">
         <x:v>验证已有 PDF 的请求不会重复进行外部查询规划和检索。</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F30" s="32" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.066</x:v>
       </x:c>
       <x:c r="G30" s="35" t="str">
         <x:v>验证问候类输入在进入 RAG 与 LLM 节点前本地结束。</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F31" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G31" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1928,7 +1928,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F32" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G32" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1952,7 +1952,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F33" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G33" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -1976,7 +1976,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F34" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G34" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -2000,7 +2000,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F35" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G35" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2024,7 +2024,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F36" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G36" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2048,7 +2048,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F37" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G37" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2072,7 +2072,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F38" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G38" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2096,7 +2096,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F39" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G39" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2120,7 +2120,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F40" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G40" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F41" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G41" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2168,7 +2168,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F42" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G42" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2240,7 +2240,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F45" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G45" s="35" t="str">
         <x:v>验证意图匹配前只清理空格、大小写和末尾标点等表面差异。</x:v>
@@ -2264,7 +2264,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F46" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G46" s="35" t="str">
         <x:v>验证本地闲聊响应不会破坏已有状态和请求元数据。</x:v>
@@ -2288,7 +2288,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F47" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G47" s="35" t="str">
         <x:v>验证能读取 LangChain 标准 usage_metadata Token 字段。</x:v>
@@ -2312,7 +2312,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F48" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G48" s="35" t="str">
         <x:v>验证能读取 OpenAI 兼容响应中的 token_usage 字段。</x:v>
@@ -2336,7 +2336,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F49" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G49" s="35" t="str">
         <x:v>验证模型未返回 Token 数据时系统明确标记缺失而不伪造估算值。</x:v>
@@ -2360,7 +2360,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F50" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G50" s="35" t="str">
         <x:v>验证成功 LLM 调用会记录节点、模型、Token、成功状态和延迟。</x:v>
@@ -2384,7 +2384,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F51" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G51" s="35" t="str">
         <x:v>验证 LLM 调用失败时仍保留失败类型和耗时记录。</x:v>
@@ -2408,7 +2408,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F52" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G52" s="35" t="str">
         <x:v>验证多个节点的 LLM 用量可以累加且不会重复计数。</x:v>
@@ -2432,7 +2432,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F53" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G53" s="35" t="str">
         <x:v>验证指标节点既能按节点分组，又能提供全流程总量与缺失用量统计。</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F55" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G55" s="35" t="str">
         <x:v>验证检索评估节点启用 LLM 时记录评分与用量。</x:v>
@@ -2504,7 +2504,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F56" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G56" s="35" t="str">
         <x:v>验证答案生成节点记录实际生成结果和模型用量。</x:v>
@@ -2528,7 +2528,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F57" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G57" s="35" t="str">
         <x:v>验证关闭 LLM 评估时只使用规则评分且不创建虚假调用记录。</x:v>
@@ -2552,7 +2552,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F58" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G58" s="35" t="str">
         <x:v>验证 BM25 基线能把中文问题与英文术语、数字混合分词。</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F59" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G59" s="35" t="str">
         <x:v>验证 BM25 将包含查询词的文本块排在无关块之前，且重复运行排名与分数一致。</x:v>
@@ -2600,7 +2600,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F60" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G60" s="35" t="str">
         <x:v>验证 BM25 拒绝空语料和非正数返回条数。</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F61" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G61" s="35" t="str">
         <x:v>用手工可计算的排名验证本地 RAG Recall、MRR 与 nDCG 公式。</x:v>
@@ -2648,7 +2648,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F62" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G62" s="35" t="str">
         <x:v>验证同一相关 PDF 页返回多个 Chunk 时，page-level 指标只计算首次命中。</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F63" s="32" t="n">
-        <x:v>0.079</x:v>
+        <x:v>0.099</x:v>
       </x:c>
       <x:c r="G63" s="35" t="str">
         <x:v>验证代表论文来源清单生成 Manifest 时保留语料版本、论文身份和内容哈希。</x:v>
@@ -2696,7 +2696,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F64" s="32" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.043</x:v>
       </x:c>
       <x:c r="G64" s="35" t="str">
         <x:v>验证来源清单声明的 PDF 缺失时立即失败，而不是静默生成不完整语料。</x:v>
@@ -2720,7 +2720,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F65" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G65" s="35" t="str">
         <x:v>验证 Dense 检索显式归一化向量，并按余弦相似度将语义匹配块排在前面。</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F66" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G66" s="35" t="str">
         <x:v>验证 Dense 检索拒绝零向量和空语料。</x:v>
@@ -2768,7 +2768,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F67" s="32" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="G67" s="35" t="str">
         <x:v>验证 Dense 向量缓存可以无损加载，并在语料文本、模型或处理版本变化后使用不同指纹。</x:v>
@@ -2792,7 +2792,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F68" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G68" s="35" t="str">
         <x:v>验证缓存命中时 DenseRetriever 不会重新编码全部论文，只对查询生成向量。</x:v>
@@ -2816,7 +2816,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F69" s="32" t="n">
-        <x:v>0.028</x:v>
+        <x:v>0.071</x:v>
       </x:c>
       <x:c r="G69" s="35" t="str">
         <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
@@ -2840,7 +2840,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F70" s="32" t="n">
-        <x:v>62.614</x:v>
+        <x:v>32.041</x:v>
       </x:c>
       <x:c r="G70" s="35" t="str">
         <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
@@ -2864,7 +2864,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F71" s="32" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="G71" s="35" t="str">
         <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
@@ -2888,7 +2888,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F72" s="32" t="n">
-        <x:v>1.891</x:v>
+        <x:v>0.908</x:v>
       </x:c>
       <x:c r="G72" s="35" t="str">
         <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
@@ -2912,22 +2912,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F73" s="32" t="n">
-        <x:v>0.051</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="G73" s="35" t="str">
         <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
       </x:c>
       <x:c r="H73" s="35" t="str"/>
     </x:row>
-    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="74" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A74" s="26" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C74" s="35" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_stability_rejects_mixed_or_unexpected_models</x:v>
       </x:c>
       <x:c r="D74" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2936,22 +2936,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F74" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.026</x:v>
       </x:c>
       <x:c r="G74" s="35" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证稳定性评测拒绝混入其他 Embedding 模型或不符合预期模型身份的运行文件。</x:v>
       </x:c>
       <x:c r="H74" s="35" t="str"/>
     </x:row>
-    <x:row r="75" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="75" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A75" s="26" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability_compare.py</x:v>
       </x:c>
       <x:c r="C75" s="35" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_stability_comparison_preserves_failed_candidate_decision</x:v>
       </x:c>
       <x:c r="D75" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2960,14 +2960,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F75" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G75" s="35" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证 MiniLM/MPNet 稳定性并列比较保留 MPNet 的失败判定，不因平均质量收益或模型间比值覆盖原始闸门。</x:v>
       </x:c>
       <x:c r="H75" s="35" t="str"/>
     </x:row>
-    <x:row r="76" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="76" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A76" s="26" t="n">
         <x:v>72</x:v>
       </x:c>
@@ -2975,7 +2975,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C76" s="35" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D76" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2984,14 +2984,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F76" s="32" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G76" s="35" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="H76" s="35" t="str"/>
     </x:row>
-    <x:row r="77" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="77" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A77" s="26" t="n">
         <x:v>73</x:v>
       </x:c>
@@ -2999,7 +2999,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C77" s="35" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D77" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3008,10 +3008,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F77" s="32" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G77" s="35" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="H77" s="35" t="str"/>
     </x:row>
@@ -3020,10 +3020,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C78" s="35" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D78" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3032,22 +3032,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F78" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="G78" s="35" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="H78" s="35" t="str"/>
     </x:row>
-    <x:row r="79" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A79" s="26" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C79" s="35" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D79" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3056,22 +3056,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F79" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="G79" s="35" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="H79" s="35" t="str"/>
     </x:row>
-    <x:row r="80" ht="132" hidden="0" customHeight="1">
+    <x:row r="80" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A80" s="26" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="35" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C80" s="35" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D80" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3080,22 +3080,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F80" s="32" t="n">
-        <x:v>62.618</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G80" s="35" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="H80" s="35" t="str"/>
     </x:row>
-    <x:row r="81" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A81" s="26" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C81" s="35" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D81" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3104,22 +3104,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F81" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G81" s="35" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="H81" s="35" t="str"/>
     </x:row>
-    <x:row r="82" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="82" ht="132" hidden="0" customHeight="1">
       <x:c r="A82" s="26" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C82" s="35" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D82" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3128,10 +3128,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F82" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>30.915</x:v>
       </x:c>
       <x:c r="G82" s="35" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="H82" s="35" t="str"/>
     </x:row>
@@ -3143,7 +3143,7 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C83" s="35" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D83" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3152,22 +3152,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F83" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G83" s="35" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="H83" s="35" t="str"/>
     </x:row>
-    <x:row r="84" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="84" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A84" s="26" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C84" s="35" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D84" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3176,10 +3176,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F84" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G84" s="35" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="H84" s="35" t="str"/>
     </x:row>
@@ -3188,10 +3188,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C85" s="35" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D85" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3200,10 +3200,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F85" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G85" s="35" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="H85" s="35" t="str"/>
     </x:row>
@@ -3215,7 +3215,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="35" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D86" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3227,11 +3227,11 @@
         <x:v>0.004</x:v>
       </x:c>
       <x:c r="G86" s="35" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="H86" s="35" t="str"/>
     </x:row>
-    <x:row r="87" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="87" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A87" s="26" t="n">
         <x:v>83</x:v>
       </x:c>
@@ -3239,7 +3239,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="35" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D87" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3248,14 +3248,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F87" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G87" s="35" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="H87" s="35" t="str"/>
     </x:row>
-    <x:row r="88" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="88" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A88" s="26" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -3263,7 +3263,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="35" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D88" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3272,14 +3272,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F88" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G88" s="35" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="H88" s="35" t="str"/>
     </x:row>
-    <x:row r="89" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="89" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A89" s="26" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -3287,7 +3287,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C89" s="35" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D89" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3296,14 +3296,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F89" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G89" s="35" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="H89" s="35" t="str"/>
     </x:row>
-    <x:row r="90" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="90" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A90" s="26" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -3311,7 +3311,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C90" s="35" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D90" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3320,10 +3320,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F90" s="32" t="n">
-        <x:v>0.016</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G90" s="35" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="H90" s="35" t="str"/>
     </x:row>
@@ -3332,10 +3332,10 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C91" s="35" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D91" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3344,22 +3344,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F91" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G91" s="35" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="H91" s="35" t="str"/>
     </x:row>
-    <x:row r="92" ht="132" hidden="0" customHeight="1">
+    <x:row r="92" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A92" s="26" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C92" s="35" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D92" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3368,14 +3368,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F92" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G92" s="35" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="H92" s="35" t="str"/>
     </x:row>
-    <x:row r="93" ht="132" hidden="0" customHeight="1">
+    <x:row r="93" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A93" s="26" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -3383,7 +3383,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="35" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D93" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3392,14 +3392,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F93" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G93" s="35" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="H93" s="35" t="str"/>
     </x:row>
-    <x:row r="94" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="94" ht="132" hidden="0" customHeight="1">
       <x:c r="A94" s="26" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -3407,7 +3407,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="35" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D94" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3416,14 +3416,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F94" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G94" s="35" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="H94" s="35" t="str"/>
     </x:row>
-    <x:row r="95" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="95" ht="132" hidden="0" customHeight="1">
       <x:c r="A95" s="26" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -3431,7 +3431,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="35" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D95" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3440,14 +3440,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F95" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G95" s="35" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="H95" s="35" t="str"/>
     </x:row>
-    <x:row r="96" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="96" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A96" s="26" t="n">
         <x:v>92</x:v>
       </x:c>
@@ -3455,7 +3455,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C96" s="35" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D96" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3467,11 +3467,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G96" s="35" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="H96" s="35" t="str"/>
     </x:row>
-    <x:row r="97" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="97" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A97" s="26" t="n">
         <x:v>93</x:v>
       </x:c>
@@ -3479,7 +3479,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C97" s="35" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D97" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3491,7 +3491,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G97" s="35" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="H97" s="35" t="str"/>
     </x:row>
@@ -3500,10 +3500,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" s="35" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C98" s="35" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D98" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3512,22 +3512,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F98" s="32" t="n">
-        <x:v>2.352</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G98" s="35" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="H98" s="35" t="str"/>
     </x:row>
-    <x:row r="99" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="99" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A99" s="26" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B99" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C99" s="35" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D99" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3536,22 +3536,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F99" s="32" t="n">
-        <x:v>0.046</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G99" s="35" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="H99" s="35" t="str"/>
     </x:row>
-    <x:row r="100" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="100" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A100" s="26" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C100" s="35" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D100" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3560,14 +3560,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F100" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>2.357</x:v>
       </x:c>
       <x:c r="G100" s="35" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="H100" s="35" t="str"/>
     </x:row>
-    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="101" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A101" s="26" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -3575,7 +3575,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C101" s="35" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D101" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3584,14 +3584,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F101" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="G101" s="35" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="H101" s="35" t="str"/>
     </x:row>
-    <x:row r="102" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="102" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A102" s="26" t="n">
         <x:v>98</x:v>
       </x:c>
@@ -3599,7 +3599,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C102" s="35" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D102" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3608,22 +3608,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F102" s="32" t="n">
-        <x:v>1.166</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G102" s="35" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="H102" s="35" t="str"/>
     </x:row>
-    <x:row r="103" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="103" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A103" s="26" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C103" s="35" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D103" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3632,22 +3632,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F103" s="32" t="n">
-        <x:v>0.192</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G103" s="35" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="H103" s="35" t="str"/>
     </x:row>
-    <x:row r="104" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="104" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A104" s="26" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C104" s="35" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D104" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3656,10 +3656,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F104" s="32" t="n">
-        <x:v>0.085</x:v>
+        <x:v>1.156</x:v>
       </x:c>
       <x:c r="G104" s="35" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="H104" s="35" t="str"/>
     </x:row>
@@ -3671,7 +3671,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C105" s="35" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D105" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3680,14 +3680,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F105" s="32" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.189</x:v>
       </x:c>
       <x:c r="G105" s="35" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="H105" s="35" t="str"/>
     </x:row>
-    <x:row r="106" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="106" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A106" s="26" t="n">
         <x:v>102</x:v>
       </x:c>
@@ -3695,7 +3695,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C106" s="35" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D106" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3704,22 +3704,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F106" s="32" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="G106" s="35" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="H106" s="35" t="str"/>
     </x:row>
-    <x:row r="107" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="107" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A107" s="26" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="35" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C107" s="35" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D107" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3728,10 +3728,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F107" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="G107" s="35" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="H107" s="35" t="str"/>
     </x:row>
@@ -3740,10 +3740,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B108" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C108" s="35" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D108" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3752,10 +3752,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F108" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="G108" s="35" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="H108" s="35" t="str"/>
     </x:row>
@@ -3764,26 +3764,26 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C109" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D109" s="35" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E109" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F109" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G109" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="H109" s="35" t="str"/>
     </x:row>
-    <x:row r="110" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="110" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A110" s="26" t="n">
         <x:v>106</x:v>
       </x:c>
@@ -3791,19 +3791,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D110" s="35" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E110" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F110" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G110" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="H110" s="35" t="str"/>
     </x:row>
@@ -3815,16 +3815,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D111" s="35" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E111" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F111" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G111" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3839,16 +3839,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D112" s="35" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E112" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F112" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G112" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3863,23 +3863,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D113" s="35" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F113" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G113" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H113" s="35" t="str"/>
     </x:row>
-    <x:row r="114" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="114" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A114" s="26" t="n">
         <x:v>110</x:v>
       </x:c>
@@ -3887,10 +3887,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D114" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E114" s="26" t="str">
         <x:v>通过</x:v>
@@ -3899,11 +3899,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G114" s="35" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H114" s="35" t="str"/>
     </x:row>
-    <x:row r="115" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="115" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A115" s="26" t="n">
         <x:v>111</x:v>
       </x:c>
@@ -3911,19 +3911,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D115" s="35" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F115" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G115" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H115" s="35" t="str"/>
     </x:row>
@@ -3935,19 +3935,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D116" s="35" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E116" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F116" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G116" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="H116" s="35" t="str"/>
     </x:row>
@@ -3959,16 +3959,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D117" s="35" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F117" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G117" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -3983,16 +3983,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D118" s="35" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E118" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F118" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G118" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -4007,23 +4007,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D119" s="35" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E119" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F119" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G119" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H119" s="35" t="str"/>
     </x:row>
-    <x:row r="120" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="120" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A120" s="26" t="n">
         <x:v>116</x:v>
       </x:c>
@@ -4031,23 +4031,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D120" s="35" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E120" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F120" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G120" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H120" s="35" t="str"/>
     </x:row>
-    <x:row r="121" ht="66" hidden="0" customHeight="1">
+    <x:row r="121" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A121" s="26" t="n">
         <x:v>117</x:v>
       </x:c>
@@ -4055,23 +4055,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="35" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D121" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E121" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F121" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G121" s="35" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H121" s="35" t="str"/>
     </x:row>
-    <x:row r="122" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="122" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A122" s="26" t="n">
         <x:v>118</x:v>
       </x:c>
@@ -4079,10 +4079,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="35" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D122" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E122" s="26" t="str">
         <x:v>通过</x:v>
@@ -4091,19 +4091,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G122" s="35" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H122" s="35" t="str"/>
     </x:row>
-    <x:row r="123" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="123" ht="66" hidden="0" customHeight="1">
       <x:c r="A123" s="26" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B123" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C123" s="35" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D123" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4112,10 +4112,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F123" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G123" s="35" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="H123" s="35" t="str"/>
     </x:row>
@@ -4124,10 +4124,10 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C124" s="35" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D124" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4136,14 +4136,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F124" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G124" s="35" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="H124" s="35" t="str"/>
     </x:row>
-    <x:row r="125" ht="132" hidden="0" customHeight="1">
+    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A125" s="26" t="n">
         <x:v>121</x:v>
       </x:c>
@@ -4151,7 +4151,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C125" s="35" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D125" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4160,14 +4160,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F125" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G125" s="35" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="H125" s="35" t="str"/>
     </x:row>
-    <x:row r="126" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="126" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A126" s="26" t="n">
         <x:v>122</x:v>
       </x:c>
@@ -4175,7 +4175,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C126" s="35" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D126" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4184,10 +4184,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F126" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G126" s="35" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="H126" s="35" t="str"/>
     </x:row>
@@ -4196,10 +4196,10 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C127" s="35" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D127" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4208,10 +4208,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F127" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G127" s="35" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="H127" s="35" t="str"/>
     </x:row>
@@ -4220,10 +4220,10 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C128" s="35" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D128" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4232,14 +4232,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F128" s="32" t="n">
-        <x:v>32.145</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G128" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="H128" s="35" t="str"/>
     </x:row>
-    <x:row r="129" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="129" ht="132" hidden="0" customHeight="1">
       <x:c r="A129" s="26" t="n">
         <x:v>125</x:v>
       </x:c>
@@ -4247,7 +4247,7 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="35" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D129" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4256,22 +4256,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F129" s="32" t="n">
-        <x:v>31.502</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G129" s="35" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="H129" s="35" t="str"/>
     </x:row>
-    <x:row r="130" ht="132" hidden="0" customHeight="1">
+    <x:row r="130" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A130" s="26" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C130" s="35" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D130" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4280,22 +4280,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F130" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>14.665</x:v>
       </x:c>
       <x:c r="G130" s="35" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="H130" s="35" t="str"/>
     </x:row>
-    <x:row r="131" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="131" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A131" s="26" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C131" s="35" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D131" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4304,14 +4304,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F131" s="32" t="n">
-        <x:v>38.998</x:v>
+        <x:v>15.135</x:v>
       </x:c>
       <x:c r="G131" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="H131" s="35" t="str"/>
     </x:row>
-    <x:row r="132" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="132" ht="132" hidden="0" customHeight="1">
       <x:c r="A132" s="26" t="n">
         <x:v>128</x:v>
       </x:c>
@@ -4319,7 +4319,7 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C132" s="35" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D132" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4328,10 +4328,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F132" s="32" t="n">
-        <x:v>30.151</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G132" s="35" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="H132" s="35" t="str"/>
     </x:row>
@@ -4340,10 +4340,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C133" s="35" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D133" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4352,10 +4352,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F133" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>18.548</x:v>
       </x:c>
       <x:c r="G133" s="35" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="H133" s="35" t="str"/>
     </x:row>
@@ -4364,10 +4364,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B134" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C134" s="35" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D134" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4376,14 +4376,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F134" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>15.261</x:v>
       </x:c>
       <x:c r="G134" s="35" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="H134" s="35" t="str"/>
     </x:row>
-    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="135" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A135" s="26" t="n">
         <x:v>131</x:v>
       </x:c>
@@ -4391,7 +4391,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="35" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D135" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4400,10 +4400,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F135" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G135" s="35" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="H135" s="35" t="str"/>
     </x:row>
@@ -4415,7 +4415,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="35" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D136" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4427,11 +4427,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G136" s="35" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="H136" s="35" t="str"/>
     </x:row>
-    <x:row r="137" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="137" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A137" s="26" t="n">
         <x:v>133</x:v>
       </x:c>
@@ -4439,7 +4439,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="35" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D137" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4448,14 +4448,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F137" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G137" s="35" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="H137" s="35" t="str"/>
     </x:row>
-    <x:row r="138" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="138" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A138" s="26" t="n">
         <x:v>134</x:v>
       </x:c>
@@ -4463,7 +4463,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="35" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D138" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4472,10 +4472,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F138" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G138" s="35" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="H138" s="35" t="str"/>
     </x:row>
@@ -4487,7 +4487,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="35" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D139" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4496,10 +4496,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F139" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G139" s="35" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="H139" s="35" t="str"/>
     </x:row>
@@ -4511,7 +4511,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="35" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D140" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4520,14 +4520,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F140" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G140" s="35" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="H140" s="35" t="str"/>
     </x:row>
-    <x:row r="141" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="141" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A141" s="26" t="n">
         <x:v>137</x:v>
       </x:c>
@@ -4535,7 +4535,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D141" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4547,11 +4547,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G141" s="35" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="H141" s="35" t="str"/>
     </x:row>
-    <x:row r="142" ht="132" hidden="0" customHeight="1">
+    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A142" s="26" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -4559,7 +4559,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D142" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4568,10 +4568,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F142" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G142" s="35" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="H142" s="35" t="str"/>
     </x:row>
@@ -4583,7 +4583,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="35" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D143" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4592,14 +4592,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F143" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G143" s="35" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="H143" s="35" t="str"/>
     </x:row>
-    <x:row r="144" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="144" ht="132" hidden="0" customHeight="1">
       <x:c r="A144" s="26" t="n">
         <x:v>140</x:v>
       </x:c>
@@ -4607,7 +4607,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="35" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D144" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4616,14 +4616,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F144" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G144" s="35" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="H144" s="35" t="str"/>
     </x:row>
-    <x:row r="145" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="145" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A145" s="26" t="n">
         <x:v>141</x:v>
       </x:c>
@@ -4631,7 +4631,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="35" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D145" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4640,22 +4640,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F145" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G145" s="35" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="H145" s="35" t="str"/>
     </x:row>
-    <x:row r="146" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A146" s="26" t="n">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B146" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C146" s="35" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D146" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4664,10 +4664,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F146" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G146" s="35" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="H146" s="35" t="str"/>
     </x:row>
@@ -4676,10 +4676,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B147" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C147" s="35" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D147" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4691,11 +4691,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G147" s="35" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="H147" s="35" t="str"/>
     </x:row>
-    <x:row r="148" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="148" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A148" s="26" t="n">
         <x:v>144</x:v>
       </x:c>
@@ -4703,7 +4703,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D148" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4712,14 +4712,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F148" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G148" s="35" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="H148" s="35" t="str"/>
     </x:row>
-    <x:row r="149" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A149" s="26" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -4727,7 +4727,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D149" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4736,10 +4736,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F149" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G149" s="35" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="H149" s="35" t="str"/>
     </x:row>
@@ -4751,7 +4751,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D150" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4760,14 +4760,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F150" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G150" s="35" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="H150" s="35" t="str"/>
     </x:row>
-    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="151" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A151" s="26" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -4775,7 +4775,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="35" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D151" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4784,14 +4784,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F151" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G151" s="35" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="H151" s="35" t="str"/>
     </x:row>
-    <x:row r="152" ht="66" hidden="0" customHeight="1">
+    <x:row r="152" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A152" s="26" t="n">
         <x:v>148</x:v>
       </x:c>
@@ -4799,7 +4799,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C152" s="35" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D152" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4808,14 +4808,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F152" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G152" s="35" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="H152" s="35" t="str"/>
     </x:row>
-    <x:row r="153" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A153" s="26" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -4823,7 +4823,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="35" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D153" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4832,22 +4832,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F153" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G153" s="35" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="H153" s="35" t="str"/>
     </x:row>
-    <x:row r="154" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="154" ht="66" hidden="0" customHeight="1">
       <x:c r="A154" s="26" t="n">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B154" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C154" s="35" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D154" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4856,10 +4856,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F154" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G154" s="35" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="H154" s="35" t="str"/>
     </x:row>
@@ -4868,10 +4868,10 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B155" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C155" s="35" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D155" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4880,14 +4880,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F155" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G155" s="35" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="H155" s="35" t="str"/>
     </x:row>
-    <x:row r="156" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="156" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A156" s="26" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -4895,7 +4895,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="35" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D156" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4907,11 +4907,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G156" s="35" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="H156" s="35" t="str"/>
     </x:row>
-    <x:row r="157" ht="132" hidden="0" customHeight="1">
+    <x:row r="157" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A157" s="26" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -4919,7 +4919,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="35" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D157" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4928,14 +4928,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F157" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G157" s="35" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="H157" s="35" t="str"/>
     </x:row>
-    <x:row r="158" ht="132" hidden="0" customHeight="1">
+    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A158" s="26" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -4943,7 +4943,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="35" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D158" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4952,14 +4952,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F158" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G158" s="35" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="H158" s="35" t="str"/>
     </x:row>
-    <x:row r="159" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="159" ht="132" hidden="0" customHeight="1">
       <x:c r="A159" s="26" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -4967,7 +4967,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4979,11 +4979,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G159" s="35" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="H159" s="35" t="str"/>
     </x:row>
-    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="160" ht="132" hidden="0" customHeight="1">
       <x:c r="A160" s="26" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -4991,7 +4991,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5000,14 +5000,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F160" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G160" s="35" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="H160" s="35" t="str"/>
     </x:row>
-    <x:row r="161" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="161" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A161" s="26" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -5015,7 +5015,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5024,14 +5024,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F161" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G161" s="35" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="H161" s="35" t="str"/>
     </x:row>
-    <x:row r="162" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A162" s="26" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -5039,7 +5039,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5048,14 +5048,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F162" s="32" t="n">
-        <x:v>0.157</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G162" s="35" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H162" s="35" t="str"/>
     </x:row>
-    <x:row r="163" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="163" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A163" s="26" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -5063,7 +5063,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5072,14 +5072,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F163" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G163" s="35" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="H163" s="35" t="str"/>
     </x:row>
-    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="164" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A164" s="26" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -5087,7 +5087,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5096,14 +5096,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F164" s="32" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="G164" s="35" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="H164" s="35" t="str"/>
     </x:row>
-    <x:row r="165" ht="132" hidden="0" customHeight="1">
+    <x:row r="165" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A165" s="26" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -5111,7 +5111,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5120,14 +5120,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F165" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G165" s="35" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="H165" s="35" t="str"/>
     </x:row>
-    <x:row r="166" ht="132" hidden="0" customHeight="1">
+    <x:row r="166" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A166" s="26" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -5135,7 +5135,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5144,14 +5144,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F166" s="32" t="n">
-        <x:v>0.294</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G166" s="35" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="H166" s="35" t="str"/>
     </x:row>
-    <x:row r="167" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="167" ht="132" hidden="0" customHeight="1">
       <x:c r="A167" s="26" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -5159,7 +5159,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="35" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D167" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5168,14 +5168,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F167" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G167" s="35" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="H167" s="35" t="str"/>
     </x:row>
-    <x:row r="168" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="168" ht="132" hidden="0" customHeight="1">
       <x:c r="A168" s="26" t="n">
         <x:v>164</x:v>
       </x:c>
@@ -5183,7 +5183,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="35" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D168" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5192,14 +5192,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F168" s="32" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="G168" s="35" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="H168" s="35" t="str"/>
     </x:row>
-    <x:row r="169" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="169" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A169" s="26" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -5207,7 +5207,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="35" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D169" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5216,22 +5216,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F169" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G169" s="35" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="H169" s="35" t="str"/>
     </x:row>
-    <x:row r="170" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A170" s="26" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B170" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C170" s="35" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D170" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5240,22 +5240,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F170" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G170" s="35" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="H170" s="35" t="str"/>
     </x:row>
-    <x:row r="171" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="171" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A171" s="26" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B171" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="35" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D171" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5264,14 +5264,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F171" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G171" s="35" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="H171" s="35" t="str"/>
     </x:row>
-    <x:row r="172" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="172" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A172" s="26" t="n">
         <x:v>168</x:v>
       </x:c>
@@ -5279,7 +5279,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C172" s="35" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D172" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5288,14 +5288,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F172" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G172" s="35" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="H172" s="35" t="str"/>
     </x:row>
-    <x:row r="173" ht="66" hidden="0" customHeight="1">
+    <x:row r="173" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A173" s="26" t="n">
         <x:v>169</x:v>
       </x:c>
@@ -5303,7 +5303,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C173" s="35" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D173" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5312,22 +5312,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F173" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G173" s="35" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="H173" s="35" t="str"/>
     </x:row>
-    <x:row r="174" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="174" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A174" s="26" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="35" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C174" s="35" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D174" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5336,22 +5336,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F174" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G174" s="35" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="H174" s="35" t="str"/>
     </x:row>
-    <x:row r="175" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="175" ht="66" hidden="0" customHeight="1">
       <x:c r="A175" s="26" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C175" s="35" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D175" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5360,10 +5360,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F175" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G175" s="35" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="H175" s="35" t="str"/>
     </x:row>
@@ -5372,10 +5372,10 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C176" s="35" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D176" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5384,10 +5384,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F176" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G176" s="35" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="H176" s="35" t="str"/>
     </x:row>
@@ -5396,10 +5396,10 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B177" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C177" s="35" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D177" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5408,22 +5408,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F177" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G177" s="35" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="H177" s="35" t="str"/>
     </x:row>
-    <x:row r="178" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="178" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A178" s="26" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C178" s="35" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D178" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5432,14 +5432,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F178" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G178" s="35" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="H178" s="35" t="str"/>
     </x:row>
-    <x:row r="179" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="179" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A179" s="26" t="n">
         <x:v>175</x:v>
       </x:c>
@@ -5447,7 +5447,7 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5456,22 +5456,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F179" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G179" s="35" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="H179" s="35" t="str"/>
     </x:row>
-    <x:row r="180" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="180" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A180" s="26" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C180" s="35" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D180" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5483,7 +5483,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G180" s="35" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="H180" s="35" t="str"/>
     </x:row>
@@ -5492,10 +5492,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C181" s="35" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D181" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5504,14 +5504,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F181" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G181" s="35" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="H181" s="35" t="str"/>
     </x:row>
-    <x:row r="182" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="182" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A182" s="26" t="n">
         <x:v>178</x:v>
       </x:c>
@@ -5519,7 +5519,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5528,10 +5528,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F182" s="32" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G182" s="35" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="H182" s="35" t="str"/>
     </x:row>
@@ -5543,7 +5543,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5552,22 +5552,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F183" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G183" s="35" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="H183" s="35" t="str"/>
     </x:row>
-    <x:row r="184" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="184" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A184" s="26" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C184" s="35" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D184" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5576,22 +5576,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F184" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.041</x:v>
       </x:c>
       <x:c r="G184" s="35" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="H184" s="35" t="str"/>
     </x:row>
-    <x:row r="185" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="185" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A185" s="26" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C185" s="35" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D185" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5600,22 +5600,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F185" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G185" s="35" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="H185" s="35" t="str"/>
     </x:row>
-    <x:row r="186" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="186" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A186" s="26" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="35" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C186" s="35" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D186" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5624,10 +5624,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F186" s="32" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G186" s="35" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="H186" s="35" t="str"/>
     </x:row>
@@ -5636,10 +5636,10 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B187" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5648,22 +5648,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F187" s="32" t="n">
-        <x:v>0.022</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G187" s="35" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H187" s="35" t="str"/>
     </x:row>
-    <x:row r="188" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="188" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A188" s="26" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C188" s="35" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D188" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5672,10 +5672,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F188" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.063</x:v>
       </x:c>
       <x:c r="G188" s="35" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="H188" s="35" t="str"/>
     </x:row>
@@ -5684,10 +5684,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B189" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5696,22 +5696,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F189" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="G189" s="35" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="H189" s="35" t="str"/>
     </x:row>
-    <x:row r="190" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="190" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A190" s="26" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B190" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C190" s="35" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D190" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5723,11 +5723,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G190" s="35" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="H190" s="35" t="str"/>
     </x:row>
-    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="191" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A191" s="26" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -5735,7 +5735,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5744,14 +5744,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F191" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G191" s="35" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="H191" s="35" t="str"/>
     </x:row>
-    <x:row r="192" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="192" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A192" s="26" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -5759,7 +5759,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="35" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D192" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5768,14 +5768,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F192" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G192" s="35" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="H192" s="35" t="str"/>
     </x:row>
-    <x:row r="193" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A193" s="26" t="n">
         <x:v>189</x:v>
       </x:c>
@@ -5783,7 +5783,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="35" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D193" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5792,14 +5792,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F193" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G193" s="35" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="H193" s="35" t="str"/>
     </x:row>
-    <x:row r="194" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A194" s="26" t="n">
         <x:v>190</x:v>
       </x:c>
@@ -5807,7 +5807,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5816,10 +5816,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F194" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G194" s="35" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="H194" s="35" t="str"/>
     </x:row>
@@ -5831,7 +5831,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5840,14 +5840,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F195" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G195" s="35" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="H195" s="35" t="str"/>
     </x:row>
-    <x:row r="196" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="196" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A196" s="26" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -5855,7 +5855,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5864,14 +5864,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F196" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G196" s="35" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="H196" s="35" t="str"/>
     </x:row>
-    <x:row r="197" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="197" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A197" s="26" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -5879,7 +5879,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5888,14 +5888,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F197" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G197" s="35" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="H197" s="35" t="str"/>
     </x:row>
-    <x:row r="198" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="198" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A198" s="26" t="n">
         <x:v>194</x:v>
       </x:c>
@@ -5903,7 +5903,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5912,14 +5912,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F198" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G198" s="35" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="H198" s="35" t="str"/>
     </x:row>
-    <x:row r="199" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="199" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A199" s="26" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -5927,7 +5927,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5936,10 +5936,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F199" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.011</x:v>
       </x:c>
       <x:c r="G199" s="35" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="H199" s="35" t="str"/>
     </x:row>
@@ -5951,7 +5951,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D200" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5963,11 +5963,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G200" s="35" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="H200" s="35" t="str"/>
     </x:row>
-    <x:row r="201" ht="132" hidden="0" customHeight="1">
+    <x:row r="201" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A201" s="26" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -5975,7 +5975,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="35" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D201" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5984,14 +5984,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F201" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G201" s="35" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="H201" s="35" t="str"/>
     </x:row>
-    <x:row r="202" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="202" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A202" s="26" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -5999,7 +5999,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="35" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D202" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6008,14 +6008,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F202" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G202" s="35" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="H202" s="35" t="str"/>
     </x:row>
-    <x:row r="203" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="203" ht="132" hidden="0" customHeight="1">
       <x:c r="A203" s="26" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -6023,7 +6023,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="35" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D203" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6032,14 +6032,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F203" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G203" s="35" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="H203" s="35" t="str"/>
     </x:row>
-    <x:row r="204" ht="132" hidden="0" customHeight="1">
+    <x:row r="204" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A204" s="26" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -6047,7 +6047,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="35" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D204" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6056,14 +6056,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F204" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G204" s="35" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="H204" s="35" t="str"/>
     </x:row>
-    <x:row r="205" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="205" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A205" s="26" t="n">
         <x:v>201</x:v>
       </x:c>
@@ -6071,7 +6071,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C205" s="35" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D205" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6080,14 +6080,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F205" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G205" s="35" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="H205" s="35" t="str"/>
     </x:row>
-    <x:row r="206" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="206" ht="132" hidden="0" customHeight="1">
       <x:c r="A206" s="26" t="n">
         <x:v>202</x:v>
       </x:c>
@@ -6095,52 +6095,100 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C206" s="35" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D206" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E206" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F206" s="32" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="G206" s="35" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="H206" s="35" t="str"/>
+    </x:row>
+    <x:row r="207" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A207" s="26" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B207" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C207" s="35" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D207" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E207" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F207" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G207" s="35" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="H207" s="35" t="str"/>
+    </x:row>
+    <x:row r="208" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A208" s="26" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B208" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C208" s="35" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D206" s="35" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E206" s="26" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F206" s="32" t="n">
+      <x:c r="D208" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E208" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F208" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G208" s="35" t="str">
+        <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
+      </x:c>
+      <x:c r="H208" s="35" t="str"/>
+    </x:row>
+    <x:row r="209" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A209" s="27" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B209" s="36" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C209" s="36" t="str">
+        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
+      </x:c>
+      <x:c r="D209" s="36" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E209" s="27" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F209" s="33" t="n">
         <x:v>0.004</x:v>
       </x:c>
-      <x:c r="G206" s="35" t="str">
-        <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
-      </x:c>
-      <x:c r="H206" s="35" t="str"/>
-    </x:row>
-    <x:row r="207" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A207" s="27" t="n">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="B207" s="36" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
-      </x:c>
-      <x:c r="C207" s="36" t="str">
-        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
-      </x:c>
-      <x:c r="D207" s="36" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E207" s="27" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F207" s="33" t="n">
-        <x:v>0.009</x:v>
-      </x:c>
-      <x:c r="G207" s="36" t="str">
+      <x:c r="G209" s="36" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="H207" s="36" t="str"/>
+      <x:c r="H209" s="36" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E5:E207">
+  <x:conditionalFormatting sqref="E5:E209">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="错误"/>
@@ -6148,7 +6196,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R919e2d24181d4deb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R886a297fc97f42ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6255,7 +6303,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I5" s="54" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J5" s="57" t="str">
         <x:v>已登记</x:v>
@@ -6287,7 +6335,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I6" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J6" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6319,7 +6367,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I7" s="55" t="n">
-        <x:v>0.036</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J7" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6351,7 +6399,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I8" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J8" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6383,7 +6431,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I9" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J9" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6415,7 +6463,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I10" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J10" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6447,7 +6495,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I11" s="55" t="n">
-        <x:v>0.014</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J11" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6479,7 +6527,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I12" s="55" t="n">
-        <x:v>0.231</x:v>
+        <x:v>0.185</x:v>
       </x:c>
       <x:c r="J12" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6511,7 +6559,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I13" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J13" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6543,7 +6591,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I14" s="55" t="n">
-        <x:v>0.029</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="J14" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6575,7 +6623,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I15" s="55" t="n">
-        <x:v>0.032</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6607,7 +6655,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I16" s="55" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.031</x:v>
       </x:c>
       <x:c r="J16" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6639,7 +6687,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I17" s="55" t="n">
-        <x:v>0.042</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="J17" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6671,7 +6719,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I18" s="55" t="n">
-        <x:v>0.03</x:v>
+        <x:v>0.065</x:v>
       </x:c>
       <x:c r="J18" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6703,7 +6751,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I19" s="55" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="J19" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6735,7 +6783,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I20" s="55" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.037</x:v>
       </x:c>
       <x:c r="J20" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6767,7 +6815,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I21" s="55" t="n">
-        <x:v>0.057</x:v>
+        <x:v>0.124</x:v>
       </x:c>
       <x:c r="J21" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6831,7 +6879,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I23" s="55" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="J23" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6863,7 +6911,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I24" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J24" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6895,7 +6943,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I25" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J25" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6927,7 +6975,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I26" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J26" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6959,7 +7007,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I27" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J27" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6991,7 +7039,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I28" s="55" t="n">
-        <x:v>0.142</x:v>
+        <x:v>0.094</x:v>
       </x:c>
       <x:c r="J28" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7023,7 +7071,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I29" s="55" t="n">
-        <x:v>0.107</x:v>
+        <x:v>0.067</x:v>
       </x:c>
       <x:c r="J29" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7055,7 +7103,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I30" s="55" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.066</x:v>
       </x:c>
       <x:c r="J30" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7087,7 +7135,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I31" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J31" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7119,7 +7167,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I32" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J32" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7151,7 +7199,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I33" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J33" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7183,7 +7231,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I34" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J34" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7215,7 +7263,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I35" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J35" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7247,7 +7295,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I36" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J36" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7279,7 +7327,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I37" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J37" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7311,7 +7359,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I38" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J38" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7343,7 +7391,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I39" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J39" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7375,7 +7423,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I40" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J40" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7407,7 +7455,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I41" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J41" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7439,7 +7487,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I42" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J42" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7535,7 +7583,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I45" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J45" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7567,7 +7615,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I46" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J46" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7599,7 +7647,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I47" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J47" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7631,7 +7679,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I48" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J48" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7663,7 +7711,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I49" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J49" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7695,7 +7743,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I50" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J50" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7727,7 +7775,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I51" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J51" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7759,7 +7807,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I52" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J52" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7791,7 +7839,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I53" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J53" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7855,7 +7903,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I55" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J55" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7887,7 +7935,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I56" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J56" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7919,7 +7967,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I57" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J57" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7951,7 +7999,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I58" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J58" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7983,7 +8031,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I59" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J59" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8015,7 +8063,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I60" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J60" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8047,7 +8095,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I61" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J61" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8079,7 +8127,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I62" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J62" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8111,7 +8159,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I63" s="55" t="n">
-        <x:v>0.079</x:v>
+        <x:v>0.099</x:v>
       </x:c>
       <x:c r="J63" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8143,7 +8191,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I64" s="55" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.043</x:v>
       </x:c>
       <x:c r="J64" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8175,7 +8223,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I65" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J65" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8207,7 +8255,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I66" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J66" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8239,7 +8287,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I67" s="55" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="J67" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8271,7 +8319,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I68" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J68" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8303,7 +8351,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I69" s="55" t="n">
-        <x:v>0.028</x:v>
+        <x:v>0.071</x:v>
       </x:c>
       <x:c r="J69" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8335,7 +8383,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I70" s="55" t="n">
-        <x:v>62.614</x:v>
+        <x:v>32.041</x:v>
       </x:c>
       <x:c r="J70" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8367,7 +8415,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I71" s="55" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="J71" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8399,7 +8447,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I72" s="55" t="n">
-        <x:v>1.891</x:v>
+        <x:v>0.908</x:v>
       </x:c>
       <x:c r="J72" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8431,77 +8479,77 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I73" s="55" t="n">
-        <x:v>0.051</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="J73" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="74" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A74" s="42" t="n">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B74" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C74" s="49" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_dense_stability_rejects_mixed_or_unexpected_models</x:v>
       </x:c>
       <x:c r="D74" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E74" s="49" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证稳定性评测拒绝混入其他 Embedding 模型或不符合预期模型身份的运行文件。</x:v>
       </x:c>
       <x:c r="F74" s="49" t="str">
-        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
+        <x:v>只有全部运行来自同一指定模型时，稳定性才可能通过。</x:v>
       </x:c>
       <x:c r="G74" s="49" t="str">
-        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
+        <x:v>MiniLM 与 MPNet 结果误混可能制造虚假的稳定性结论或错误的耗时统计。</x:v>
       </x:c>
       <x:c r="H74" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I74" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.026</x:v>
       </x:c>
       <x:c r="J74" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="75" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A75" s="42" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability_compare.py</x:v>
       </x:c>
       <x:c r="C75" s="49" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_stability_comparison_preserves_failed_candidate_decision</x:v>
       </x:c>
       <x:c r="D75" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E75" s="49" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证 MiniLM/MPNet 稳定性并列比较保留 MPNet 的失败判定，不因平均质量收益或模型间比值覆盖原始闸门。</x:v>
       </x:c>
       <x:c r="F75" s="49" t="str">
-        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
+        <x:v>报告展示性能倍数，但 MPNet CV 超限时仍保持稳定性未通过和生产关闭。</x:v>
       </x:c>
       <x:c r="G75" s="49" t="str">
-        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
+        <x:v>跨模型汇总可能错误抹平单模型波动，使失败候选绕过稳定性门槛。</x:v>
       </x:c>
       <x:c r="H75" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I75" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J75" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="76" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A76" s="42" t="n">
         <x:v>72</x:v>
       </x:c>
@@ -8509,31 +8557,31 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C76" s="49" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D76" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E76" s="49" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="F76" s="49" t="str">
-        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
+        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
       </x:c>
       <x:c r="G76" s="49" t="str">
-        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
+        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
       </x:c>
       <x:c r="H76" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I76" s="55" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J76" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="77" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A77" s="42" t="n">
         <x:v>73</x:v>
       </x:c>
@@ -8541,25 +8589,25 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C77" s="49" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D77" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E77" s="49" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="F77" s="49" t="str">
-        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
+        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
       </x:c>
       <x:c r="G77" s="49" t="str">
-        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
+        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
       </x:c>
       <x:c r="H77" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I77" s="55" t="n">
-        <x:v>0.055</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J77" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8570,162 +8618,162 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B78" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C78" s="49" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D78" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E78" s="49" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="F78" s="49" t="str">
-        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
+        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
       </x:c>
       <x:c r="G78" s="49" t="str">
-        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
+        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
       </x:c>
       <x:c r="H78" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I78" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="J78" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A79" s="42" t="n">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B79" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C79" s="49" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D79" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E79" s="49" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="F79" s="49" t="str">
-        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
+        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
       </x:c>
       <x:c r="G79" s="49" t="str">
-        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
+        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
       </x:c>
       <x:c r="H79" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I79" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="J79" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="132" hidden="0" customHeight="1">
+    <x:row r="80" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A80" s="42" t="n">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="49" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C80" s="49" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D80" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E80" s="49" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="F80" s="49" t="str">
-        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
+        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
       </x:c>
       <x:c r="G80" s="49" t="str">
-        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
+        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
       </x:c>
       <x:c r="H80" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I80" s="55" t="n">
-        <x:v>62.618</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J80" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="132" hidden="0" customHeight="1">
+    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A81" s="42" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C81" s="49" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D81" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E81" s="49" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="F81" s="49" t="str">
-        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
+        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
       </x:c>
       <x:c r="G81" s="49" t="str">
-        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
+        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
       </x:c>
       <x:c r="H81" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I81" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J81" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="82" ht="132" hidden="0" customHeight="1">
       <x:c r="A82" s="42" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C82" s="49" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D82" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E82" s="49" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="F82" s="49" t="str">
-        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
+        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
       </x:c>
       <x:c r="G82" s="49" t="str">
-        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
+        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
       </x:c>
       <x:c r="H82" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I82" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>30.915</x:v>
       </x:c>
       <x:c r="J82" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="83" ht="132" hidden="0" customHeight="1">
       <x:c r="A83" s="42" t="n">
         <x:v>79</x:v>
       </x:c>
@@ -8733,57 +8781,57 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C83" s="49" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D83" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E83" s="49" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="F83" s="49" t="str">
-        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
+        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
       </x:c>
       <x:c r="G83" s="49" t="str">
-        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
+        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
       </x:c>
       <x:c r="H83" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I83" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J83" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="84" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A84" s="42" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C84" s="49" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D84" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E84" s="49" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="F84" s="49" t="str">
-        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
+        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
       </x:c>
       <x:c r="G84" s="49" t="str">
-        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
+        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
       </x:c>
       <x:c r="H84" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I84" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J84" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8794,28 +8842,28 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C85" s="49" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D85" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E85" s="49" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="F85" s="49" t="str">
-        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
+        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
       </x:c>
       <x:c r="G85" s="49" t="str">
-        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
+        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
       </x:c>
       <x:c r="H85" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I85" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J85" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8829,19 +8877,19 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C86" s="49" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D86" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E86" s="49" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="F86" s="49" t="str">
-        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
+        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
       </x:c>
       <x:c r="G86" s="49" t="str">
-        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
+        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
       </x:c>
       <x:c r="H86" s="52" t="str">
         <x:v>通过</x:v>
@@ -8853,7 +8901,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="87" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A87" s="42" t="n">
         <x:v>83</x:v>
       </x:c>
@@ -8861,31 +8909,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C87" s="49" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D87" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E87" s="49" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="F87" s="49" t="str">
-        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
+        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
       </x:c>
       <x:c r="G87" s="49" t="str">
-        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
+        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
       </x:c>
       <x:c r="H87" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I87" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J87" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="132" hidden="0" customHeight="1">
+    <x:row r="88" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A88" s="42" t="n">
         <x:v>84</x:v>
       </x:c>
@@ -8893,31 +8941,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="49" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D88" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E88" s="49" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="F88" s="49" t="str">
-        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
+        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
       </x:c>
       <x:c r="G88" s="49" t="str">
-        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
+        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
       </x:c>
       <x:c r="H88" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I88" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J88" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="89" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A89" s="42" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -8925,31 +8973,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C89" s="49" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D89" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E89" s="49" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="F89" s="49" t="str">
-        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
+        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
       </x:c>
       <x:c r="G89" s="49" t="str">
-        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
+        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
       </x:c>
       <x:c r="H89" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I89" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J89" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="90" ht="132" hidden="0" customHeight="1">
       <x:c r="A90" s="42" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -8957,95 +9005,95 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C90" s="49" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D90" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E90" s="49" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="F90" s="49" t="str">
-        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
+        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
       </x:c>
       <x:c r="G90" s="49" t="str">
-        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
+        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
       </x:c>
       <x:c r="H90" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I90" s="55" t="n">
-        <x:v>0.016</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J90" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="91" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A91" s="42" t="n">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B91" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C91" s="49" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D91" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E91" s="49" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="F91" s="49" t="str">
-        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
+        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
       </x:c>
       <x:c r="G91" s="49" t="str">
-        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
+        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
       </x:c>
       <x:c r="H91" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I91" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J91" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="132" hidden="0" customHeight="1">
+    <x:row r="92" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A92" s="42" t="n">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B92" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C92" s="49" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D92" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E92" s="49" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="F92" s="49" t="str">
-        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
+        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
       </x:c>
       <x:c r="G92" s="49" t="str">
-        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
+        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
       </x:c>
       <x:c r="H92" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I92" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J92" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="132" hidden="0" customHeight="1">
+    <x:row r="93" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A93" s="42" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -9053,31 +9101,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C93" s="49" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D93" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E93" s="49" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="F93" s="49" t="str">
-        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
+        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
       </x:c>
       <x:c r="G93" s="49" t="str">
-        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
+        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
       </x:c>
       <x:c r="H93" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I93" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J93" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="94" ht="132" hidden="0" customHeight="1">
       <x:c r="A94" s="42" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -9085,31 +9133,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C94" s="49" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D94" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E94" s="49" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="F94" s="49" t="str">
-        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
+        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
       </x:c>
       <x:c r="G94" s="49" t="str">
-        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
+        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
       </x:c>
       <x:c r="H94" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I94" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J94" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="95" ht="132" hidden="0" customHeight="1">
       <x:c r="A95" s="42" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -9117,25 +9165,25 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="49" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D95" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E95" s="49" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="F95" s="49" t="str">
-        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
+        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
       </x:c>
       <x:c r="G95" s="49" t="str">
-        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
+        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
       </x:c>
       <x:c r="H95" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I95" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J95" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9149,19 +9197,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C96" s="49" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D96" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E96" s="49" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="F96" s="49" t="str">
-        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
+        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
       </x:c>
       <x:c r="G96" s="49" t="str">
-        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
+        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
       </x:c>
       <x:c r="H96" s="52" t="str">
         <x:v>通过</x:v>
@@ -9181,19 +9229,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C97" s="49" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D97" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E97" s="49" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="F97" s="49" t="str">
-        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
+        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
       </x:c>
       <x:c r="G97" s="49" t="str">
-        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
+        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
       </x:c>
       <x:c r="H97" s="52" t="str">
         <x:v>通过</x:v>
@@ -9205,103 +9253,103 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="98" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A98" s="42" t="n">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B98" s="49" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C98" s="49" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D98" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E98" s="49" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="F98" s="49" t="str">
-        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
+        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
       </x:c>
       <x:c r="G98" s="49" t="str">
-        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
+        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
       </x:c>
       <x:c r="H98" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I98" s="55" t="n">
-        <x:v>2.352</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J98" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="99" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A99" s="42" t="n">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B99" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C99" s="49" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D99" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E99" s="49" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="F99" s="49" t="str">
-        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
+        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
       </x:c>
       <x:c r="G99" s="49" t="str">
-        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
+        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
       </x:c>
       <x:c r="H99" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I99" s="55" t="n">
-        <x:v>0.046</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J99" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="100" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A100" s="42" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C100" s="49" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D100" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E100" s="49" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="F100" s="49" t="str">
-        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
+        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
       </x:c>
       <x:c r="G100" s="49" t="str">
-        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
+        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
       </x:c>
       <x:c r="H100" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I100" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>2.357</x:v>
       </x:c>
       <x:c r="J100" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="101" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A101" s="42" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -9309,25 +9357,25 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C101" s="49" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D101" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E101" s="49" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="F101" s="49" t="str">
-        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
+        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
       </x:c>
       <x:c r="G101" s="49" t="str">
-        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
+        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
       </x:c>
       <x:c r="H101" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I101" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="J101" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9341,95 +9389,95 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C102" s="49" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D102" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E102" s="49" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="F102" s="49" t="str">
-        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
+        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
       </x:c>
       <x:c r="G102" s="49" t="str">
-        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
+        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
       </x:c>
       <x:c r="H102" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I102" s="55" t="n">
-        <x:v>1.166</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J102" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="103" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A103" s="42" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C103" s="49" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D103" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E103" s="49" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="F103" s="49" t="str">
-        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
+        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
       </x:c>
       <x:c r="G103" s="49" t="str">
-        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
+        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
       </x:c>
       <x:c r="H103" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I103" s="55" t="n">
-        <x:v>0.192</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J103" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="104" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A104" s="42" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C104" s="49" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D104" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E104" s="49" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="F104" s="49" t="str">
-        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
+        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
       </x:c>
       <x:c r="G104" s="49" t="str">
-        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
+        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
       </x:c>
       <x:c r="H104" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I104" s="55" t="n">
-        <x:v>0.085</x:v>
+        <x:v>1.156</x:v>
       </x:c>
       <x:c r="J104" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="105" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A105" s="42" t="n">
         <x:v>101</x:v>
       </x:c>
@@ -9437,25 +9485,25 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C105" s="49" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D105" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E105" s="49" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="F105" s="49" t="str">
-        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
+        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
       </x:c>
       <x:c r="G105" s="49" t="str">
-        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
+        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
       </x:c>
       <x:c r="H105" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I105" s="55" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.189</x:v>
       </x:c>
       <x:c r="J105" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9469,127 +9517,127 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C106" s="49" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D106" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E106" s="49" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="F106" s="49" t="str">
-        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
+        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
       </x:c>
       <x:c r="G106" s="49" t="str">
-        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
+        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
       </x:c>
       <x:c r="H106" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I106" s="55" t="n">
-        <x:v>0.1</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="J106" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="132" hidden="0" customHeight="1">
+    <x:row r="107" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A107" s="42" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="49" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C107" s="49" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D107" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E107" s="49" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="F107" s="49" t="str">
-        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
+        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
       </x:c>
       <x:c r="G107" s="49" t="str">
-        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
+        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
       </x:c>
       <x:c r="H107" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I107" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="J107" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="108" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A108" s="42" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B108" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C108" s="49" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D108" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E108" s="49" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="F108" s="49" t="str">
-        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
+        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
       </x:c>
       <x:c r="G108" s="49" t="str">
-        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
+        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
       </x:c>
       <x:c r="H108" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I108" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.097</x:v>
       </x:c>
       <x:c r="J108" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="109" ht="132" hidden="0" customHeight="1">
       <x:c r="A109" s="42" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C109" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D109" s="49" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E109" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="F109" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
       </x:c>
       <x:c r="G109" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
       </x:c>
       <x:c r="H109" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I109" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J109" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="110" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A110" s="42" t="n">
         <x:v>106</x:v>
       </x:c>
@@ -9597,25 +9645,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C110" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D110" s="49" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E110" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="F110" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
       </x:c>
       <x:c r="G110" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
       </x:c>
       <x:c r="H110" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I110" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J110" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9629,10 +9677,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C111" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D111" s="49" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E111" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9647,7 +9695,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I111" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J111" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9661,10 +9709,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D112" s="49" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E112" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9679,7 +9727,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I112" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J112" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9693,10 +9741,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D113" s="49" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E113" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9711,13 +9759,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I113" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J113" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="114" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A114" s="42" t="n">
         <x:v>110</x:v>
       </x:c>
@@ -9725,19 +9773,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D114" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E114" s="49" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F114" s="49" t="str">
-        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G114" s="49" t="str">
-        <x:v>查询改写异常可能导致完全不检索。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H114" s="52" t="str">
         <x:v>通过</x:v>
@@ -9757,31 +9805,31 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D115" s="49" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E115" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F115" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G115" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H115" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I115" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J115" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="116" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A116" s="42" t="n">
         <x:v>112</x:v>
       </x:c>
@@ -9789,25 +9837,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D116" s="49" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E116" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="F116" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
       </x:c>
       <x:c r="G116" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>查询改写异常可能导致完全不检索。</x:v>
       </x:c>
       <x:c r="H116" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I116" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J116" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9821,10 +9869,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D117" s="49" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E117" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9839,7 +9887,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I117" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J117" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9853,10 +9901,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D118" s="49" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E118" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9871,7 +9919,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I118" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J118" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9885,10 +9933,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D119" s="49" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E119" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9903,7 +9951,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I119" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J119" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9917,10 +9965,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D120" s="49" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E120" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9935,13 +9983,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I120" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J120" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="121" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A121" s="42" t="n">
         <x:v>117</x:v>
       </x:c>
@@ -9949,25 +9997,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="49" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D121" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E121" s="49" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F121" s="49" t="str">
-        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G121" s="49" t="str">
-        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H121" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I121" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J121" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9981,19 +10029,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="49" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D122" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E122" s="49" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F122" s="49" t="str">
-        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G122" s="49" t="str">
-        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H122" s="52" t="str">
         <x:v>通过</x:v>
@@ -10005,33 +10053,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="123" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A123" s="42" t="n">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B123" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C123" s="49" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D123" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E123" s="49" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="F123" s="49" t="str">
-        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
+        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
       </x:c>
       <x:c r="G123" s="49" t="str">
-        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
+        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
       </x:c>
       <x:c r="H123" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I123" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J123" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10042,34 +10090,34 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B124" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C124" s="49" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D124" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E124" s="49" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="F124" s="49" t="str">
-        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
+        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
       </x:c>
       <x:c r="G124" s="49" t="str">
-        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
+        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
       </x:c>
       <x:c r="H124" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I124" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J124" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="132" hidden="0" customHeight="1">
+    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A125" s="42" t="n">
         <x:v>121</x:v>
       </x:c>
@@ -10077,31 +10125,31 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C125" s="49" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D125" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E125" s="49" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="F125" s="49" t="str">
-        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
+        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
       </x:c>
       <x:c r="G125" s="49" t="str">
-        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
+        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
       </x:c>
       <x:c r="H125" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I125" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J125" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="126" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A126" s="42" t="n">
         <x:v>122</x:v>
       </x:c>
@@ -10109,25 +10157,25 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C126" s="49" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D126" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E126" s="49" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="F126" s="49" t="str">
-        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
+        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
       </x:c>
       <x:c r="G126" s="49" t="str">
-        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
+        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
       </x:c>
       <x:c r="H126" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I126" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J126" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10138,66 +10186,66 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C127" s="49" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D127" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E127" s="49" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="F127" s="49" t="str">
-        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
+        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
       </x:c>
       <x:c r="G127" s="49" t="str">
-        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
+        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
       </x:c>
       <x:c r="H127" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I127" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J127" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="128" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A128" s="42" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C128" s="49" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D128" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E128" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="F128" s="49" t="str">
-        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
+        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
       </x:c>
       <x:c r="G128" s="49" t="str">
-        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
+        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
       </x:c>
       <x:c r="H128" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I128" s="55" t="n">
-        <x:v>32.145</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J128" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="129" ht="132" hidden="0" customHeight="1">
       <x:c r="A129" s="42" t="n">
         <x:v>125</x:v>
       </x:c>
@@ -10205,95 +10253,95 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C129" s="49" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D129" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E129" s="49" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="F129" s="49" t="str">
-        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
+        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
       </x:c>
       <x:c r="G129" s="49" t="str">
-        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
+        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
       </x:c>
       <x:c r="H129" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I129" s="55" t="n">
-        <x:v>31.502</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J129" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="132" hidden="0" customHeight="1">
+    <x:row r="130" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A130" s="42" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C130" s="49" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D130" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E130" s="49" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="F130" s="49" t="str">
-        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
+        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
       </x:c>
       <x:c r="G130" s="49" t="str">
-        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
+        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
       </x:c>
       <x:c r="H130" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I130" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>14.665</x:v>
       </x:c>
       <x:c r="J130" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="131" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A131" s="42" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C131" s="49" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D131" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E131" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="F131" s="49" t="str">
-        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
+        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
       </x:c>
       <x:c r="G131" s="49" t="str">
-        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
+        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
       </x:c>
       <x:c r="H131" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I131" s="55" t="n">
-        <x:v>38.998</x:v>
+        <x:v>15.135</x:v>
       </x:c>
       <x:c r="J131" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="132" ht="132" hidden="0" customHeight="1">
       <x:c r="A132" s="42" t="n">
         <x:v>128</x:v>
       </x:c>
@@ -10301,57 +10349,57 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C132" s="49" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D132" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E132" s="49" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="F132" s="49" t="str">
-        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
+        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
       </x:c>
       <x:c r="G132" s="49" t="str">
-        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
+        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
       </x:c>
       <x:c r="H132" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I132" s="55" t="n">
-        <x:v>30.151</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J132" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="133" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A133" s="42" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C133" s="49" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D133" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E133" s="49" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="F133" s="49" t="str">
-        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
+        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
       </x:c>
       <x:c r="G133" s="49" t="str">
-        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
+        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
       </x:c>
       <x:c r="H133" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I133" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>18.548</x:v>
       </x:c>
       <x:c r="J133" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10362,34 +10410,34 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B134" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C134" s="49" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D134" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E134" s="49" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="F134" s="49" t="str">
-        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
+        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
       </x:c>
       <x:c r="G134" s="49" t="str">
-        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
+        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
       </x:c>
       <x:c r="H134" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I134" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>15.261</x:v>
       </x:c>
       <x:c r="J134" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="135" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A135" s="42" t="n">
         <x:v>131</x:v>
       </x:c>
@@ -10397,31 +10445,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C135" s="49" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D135" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E135" s="49" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="F135" s="49" t="str">
-        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
+        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
       </x:c>
       <x:c r="G135" s="49" t="str">
-        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
+        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
       </x:c>
       <x:c r="H135" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I135" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J135" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A136" s="42" t="n">
         <x:v>132</x:v>
       </x:c>
@@ -10429,19 +10477,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C136" s="49" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D136" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E136" s="49" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="F136" s="49" t="str">
-        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
+        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
       </x:c>
       <x:c r="G136" s="49" t="str">
-        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
+        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
       </x:c>
       <x:c r="H136" s="52" t="str">
         <x:v>通过</x:v>
@@ -10461,31 +10509,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="49" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D137" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E137" s="49" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="F137" s="49" t="str">
-        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
+        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
       </x:c>
       <x:c r="G137" s="49" t="str">
-        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
+        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
       </x:c>
       <x:c r="H137" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I137" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J137" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="138" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A138" s="42" t="n">
         <x:v>134</x:v>
       </x:c>
@@ -10493,31 +10541,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="49" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D138" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E138" s="49" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="F138" s="49" t="str">
-        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
+        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
       </x:c>
       <x:c r="G138" s="49" t="str">
-        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
+        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
       </x:c>
       <x:c r="H138" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I138" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J138" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A139" s="42" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -10525,31 +10573,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="49" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D139" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E139" s="49" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="F139" s="49" t="str">
-        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
+        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
       </x:c>
       <x:c r="G139" s="49" t="str">
-        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
+        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
       </x:c>
       <x:c r="H139" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I139" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J139" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="140" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A140" s="42" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -10557,31 +10605,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="49" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D140" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E140" s="49" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="F140" s="49" t="str">
-        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
+        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
       </x:c>
       <x:c r="G140" s="49" t="str">
-        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
+        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
       </x:c>
       <x:c r="H140" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I140" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J140" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="141" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A141" s="42" t="n">
         <x:v>137</x:v>
       </x:c>
@@ -10589,19 +10637,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D141" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E141" s="49" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="F141" s="49" t="str">
-        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
+        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
       </x:c>
       <x:c r="G141" s="49" t="str">
-        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
+        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
       </x:c>
       <x:c r="H141" s="52" t="str">
         <x:v>通过</x:v>
@@ -10613,7 +10661,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="132" hidden="0" customHeight="1">
+    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A142" s="42" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -10621,25 +10669,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D142" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E142" s="49" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="F142" s="49" t="str">
-        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
+        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
       </x:c>
       <x:c r="G142" s="49" t="str">
-        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
+        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
       </x:c>
       <x:c r="H142" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I142" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J142" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10653,31 +10701,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="49" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D143" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E143" s="49" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="F143" s="49" t="str">
-        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
+        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
       </x:c>
       <x:c r="G143" s="49" t="str">
-        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
+        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
       </x:c>
       <x:c r="H143" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I143" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J143" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="144" ht="132" hidden="0" customHeight="1">
       <x:c r="A144" s="42" t="n">
         <x:v>140</x:v>
       </x:c>
@@ -10685,31 +10733,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="49" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D144" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E144" s="49" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="F144" s="49" t="str">
-        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
+        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
       </x:c>
       <x:c r="G144" s="49" t="str">
-        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
+        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
       </x:c>
       <x:c r="H144" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I144" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J144" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="145" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A145" s="42" t="n">
         <x:v>141</x:v>
       </x:c>
@@ -10717,57 +10765,57 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="49" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D145" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E145" s="49" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="F145" s="49" t="str">
-        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
+        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
       </x:c>
       <x:c r="G145" s="49" t="str">
-        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
+        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
       </x:c>
       <x:c r="H145" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I145" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J145" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A146" s="42" t="n">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B146" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C146" s="49" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D146" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E146" s="49" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="F146" s="49" t="str">
-        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
+        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
       </x:c>
       <x:c r="G146" s="49" t="str">
-        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
+        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
       </x:c>
       <x:c r="H146" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I146" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J146" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10778,22 +10826,22 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B147" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C147" s="49" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D147" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E147" s="49" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="F147" s="49" t="str">
-        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
+        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
       </x:c>
       <x:c r="G147" s="49" t="str">
-        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
+        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
       </x:c>
       <x:c r="H147" s="52" t="str">
         <x:v>通过</x:v>
@@ -10813,31 +10861,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C148" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D148" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E148" s="49" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="F148" s="49" t="str">
-        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
+        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
       </x:c>
       <x:c r="G148" s="49" t="str">
-        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
+        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
       </x:c>
       <x:c r="H148" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I148" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J148" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A149" s="42" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -10845,25 +10893,25 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C149" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D149" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E149" s="49" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="F149" s="49" t="str">
-        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
+        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
       </x:c>
       <x:c r="G149" s="49" t="str">
-        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
+        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
       </x:c>
       <x:c r="H149" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I149" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J149" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10877,31 +10925,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D150" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E150" s="49" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="F150" s="49" t="str">
-        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
+        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
       </x:c>
       <x:c r="G150" s="49" t="str">
-        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
+        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
       </x:c>
       <x:c r="H150" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I150" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J150" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="151" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A151" s="42" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -10909,31 +10957,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="49" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D151" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E151" s="49" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="F151" s="49" t="str">
-        <x:v>两条无去重键文档均被保留。</x:v>
+        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
       </x:c>
       <x:c r="G151" s="49" t="str">
-        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
+        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
       </x:c>
       <x:c r="H151" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I151" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J151" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="152" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A152" s="42" t="n">
         <x:v>148</x:v>
       </x:c>
@@ -10941,31 +10989,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C152" s="49" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D152" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E152" s="49" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="F152" s="49" t="str">
-        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
+        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
       </x:c>
       <x:c r="G152" s="49" t="str">
-        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
+        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
       </x:c>
       <x:c r="H152" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I152" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J152" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A153" s="42" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -10973,57 +11021,57 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="49" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D153" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E153" s="49" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="F153" s="49" t="str">
-        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
+        <x:v>两条无去重键文档均被保留。</x:v>
       </x:c>
       <x:c r="G153" s="49" t="str">
-        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
+        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
       </x:c>
       <x:c r="H153" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I153" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J153" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="154" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A154" s="42" t="n">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B154" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C154" s="49" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D154" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E154" s="49" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="F154" s="49" t="str">
-        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
+        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
       </x:c>
       <x:c r="G154" s="49" t="str">
-        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
+        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
       </x:c>
       <x:c r="H154" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I154" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J154" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11034,34 +11082,34 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B155" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C155" s="49" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D155" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E155" s="49" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="F155" s="49" t="str">
-        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
+        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
       </x:c>
       <x:c r="G155" s="49" t="str">
-        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
+        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
       </x:c>
       <x:c r="H155" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I155" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J155" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="156" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A156" s="42" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -11069,19 +11117,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C156" s="49" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D156" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E156" s="49" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="F156" s="49" t="str">
-        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
+        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
       </x:c>
       <x:c r="G156" s="49" t="str">
-        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
+        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
       </x:c>
       <x:c r="H156" s="52" t="str">
         <x:v>通过</x:v>
@@ -11093,7 +11141,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="132" hidden="0" customHeight="1">
+    <x:row r="157" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A157" s="42" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -11101,31 +11149,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C157" s="49" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D157" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E157" s="49" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="F157" s="49" t="str">
-        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
+        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
       </x:c>
       <x:c r="G157" s="49" t="str">
-        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
+        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
       </x:c>
       <x:c r="H157" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I157" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J157" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="132" hidden="0" customHeight="1">
+    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A158" s="42" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -11133,31 +11181,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="49" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D158" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E158" s="49" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="F158" s="49" t="str">
-        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
+        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
       </x:c>
       <x:c r="G158" s="49" t="str">
-        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
+        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
       </x:c>
       <x:c r="H158" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I158" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J158" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="159" ht="132" hidden="0" customHeight="1">
       <x:c r="A159" s="42" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -11165,19 +11213,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="49" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D159" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E159" s="49" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="F159" s="49" t="str">
-        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
+        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
       </x:c>
       <x:c r="G159" s="49" t="str">
-        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
+        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
       </x:c>
       <x:c r="H159" s="52" t="str">
         <x:v>通过</x:v>
@@ -11189,7 +11237,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="160" ht="132" hidden="0" customHeight="1">
       <x:c r="A160" s="42" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -11197,31 +11245,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="49" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D160" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E160" s="49" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="F160" s="49" t="str">
-        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
+        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
       </x:c>
       <x:c r="G160" s="49" t="str">
-        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
+        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
       </x:c>
       <x:c r="H160" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I160" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J160" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="161" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A161" s="42" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -11229,31 +11277,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="49" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D161" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E161" s="49" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="F161" s="49" t="str">
-        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
+        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
       </x:c>
       <x:c r="G161" s="49" t="str">
-        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
+        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
       </x:c>
       <x:c r="H161" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I161" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J161" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A162" s="42" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -11261,25 +11309,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="49" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D162" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E162" s="49" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F162" s="49" t="str">
-        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
+        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
       </x:c>
       <x:c r="G162" s="49" t="str">
-        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
+        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
       </x:c>
       <x:c r="H162" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I162" s="55" t="n">
-        <x:v>0.157</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J162" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11293,31 +11341,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="49" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D163" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E163" s="49" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="F163" s="49" t="str">
-        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
+        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
       </x:c>
       <x:c r="G163" s="49" t="str">
-        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
+        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
       </x:c>
       <x:c r="H163" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I163" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J163" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="164" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A164" s="42" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -11325,31 +11373,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="49" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D164" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E164" s="49" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="F164" s="49" t="str">
-        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
+        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
       </x:c>
       <x:c r="G164" s="49" t="str">
-        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
+        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
       </x:c>
       <x:c r="H164" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I164" s="55" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.085</x:v>
       </x:c>
       <x:c r="J164" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A165" s="42" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -11357,31 +11405,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="49" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D165" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E165" s="49" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="F165" s="49" t="str">
-        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
+        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
       </x:c>
       <x:c r="G165" s="49" t="str">
-        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
+        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
       </x:c>
       <x:c r="H165" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I165" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J165" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="132" hidden="0" customHeight="1">
+    <x:row r="166" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A166" s="42" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -11389,31 +11437,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="49" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D166" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E166" s="49" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="F166" s="49" t="str">
-        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
+        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
       </x:c>
       <x:c r="G166" s="49" t="str">
-        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
+        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
       </x:c>
       <x:c r="H166" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I166" s="55" t="n">
-        <x:v>0.294</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J166" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="167" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A167" s="42" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -11421,31 +11469,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="49" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D167" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E167" s="49" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="F167" s="49" t="str">
-        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
+        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
       </x:c>
       <x:c r="G167" s="49" t="str">
-        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
+        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
       </x:c>
       <x:c r="H167" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I167" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J167" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="168" ht="132" hidden="0" customHeight="1">
       <x:c r="A168" s="42" t="n">
         <x:v>164</x:v>
       </x:c>
@@ -11453,25 +11501,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="49" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D168" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E168" s="49" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="F168" s="49" t="str">
-        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
+        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
       </x:c>
       <x:c r="G168" s="49" t="str">
-        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
+        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
       </x:c>
       <x:c r="H168" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I168" s="55" t="n">
-        <x:v>0.023</x:v>
+        <x:v>0.15</x:v>
       </x:c>
       <x:c r="J168" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11485,95 +11533,95 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="49" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D169" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E169" s="49" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="F169" s="49" t="str">
-        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
+        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
       </x:c>
       <x:c r="G169" s="49" t="str">
-        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
+        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
       </x:c>
       <x:c r="H169" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I169" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J169" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A170" s="42" t="n">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B170" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C170" s="49" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D170" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E170" s="49" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="F170" s="49" t="str">
-        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
+        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
       </x:c>
       <x:c r="G170" s="49" t="str">
-        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
+        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
       </x:c>
       <x:c r="H170" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I170" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J170" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="171" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A171" s="42" t="n">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B171" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="49" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D171" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E171" s="49" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="F171" s="49" t="str">
-        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
+        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
       </x:c>
       <x:c r="G171" s="49" t="str">
-        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
+        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
       </x:c>
       <x:c r="H171" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I171" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J171" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="172" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A172" s="42" t="n">
         <x:v>168</x:v>
       </x:c>
@@ -11581,25 +11629,25 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C172" s="49" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D172" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E172" s="49" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="F172" s="49" t="str">
-        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
+        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
       </x:c>
       <x:c r="G172" s="49" t="str">
-        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
+        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
       </x:c>
       <x:c r="H172" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I172" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J172" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11613,121 +11661,121 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C173" s="49" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D173" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E173" s="49" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="F173" s="49" t="str">
-        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
+        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
       </x:c>
       <x:c r="G173" s="49" t="str">
-        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
+        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
       </x:c>
       <x:c r="H173" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I173" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J173" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="174" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A174" s="42" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="49" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C174" s="49" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D174" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E174" s="49" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="F174" s="49" t="str">
-        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
+        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
       </x:c>
       <x:c r="G174" s="49" t="str">
-        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
+        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
       </x:c>
       <x:c r="H174" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I174" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J174" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="175" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A175" s="42" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C175" s="49" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D175" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E175" s="49" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="F175" s="49" t="str">
-        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
+        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
       </x:c>
       <x:c r="G175" s="49" t="str">
-        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
+        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
       </x:c>
       <x:c r="H175" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I175" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J175" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="176" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A176" s="42" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C176" s="49" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D176" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E176" s="49" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="F176" s="49" t="str">
-        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
+        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
       </x:c>
       <x:c r="G176" s="49" t="str">
-        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
+        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
       </x:c>
       <x:c r="H176" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I176" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J176" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11738,28 +11786,28 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B177" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C177" s="49" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D177" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E177" s="49" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="F177" s="49" t="str">
-        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
+        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
       </x:c>
       <x:c r="G177" s="49" t="str">
-        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
+        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
       </x:c>
       <x:c r="H177" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I177" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J177" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11770,34 +11818,34 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C178" s="49" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D178" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E178" s="49" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="F178" s="49" t="str">
-        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
+        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
       </x:c>
       <x:c r="G178" s="49" t="str">
-        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
+        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
       </x:c>
       <x:c r="H178" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I178" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J178" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="179" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="179" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A179" s="42" t="n">
         <x:v>175</x:v>
       </x:c>
@@ -11805,25 +11853,25 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C179" s="49" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D179" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E179" s="49" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="F179" s="49" t="str">
-        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
+        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
       </x:c>
       <x:c r="G179" s="49" t="str">
-        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
+        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
       </x:c>
       <x:c r="H179" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I179" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J179" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11834,22 +11882,22 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C180" s="49" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D180" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E180" s="49" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="F180" s="49" t="str">
-        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
+        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
       </x:c>
       <x:c r="G180" s="49" t="str">
-        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
+        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
       </x:c>
       <x:c r="H180" s="52" t="str">
         <x:v>通过</x:v>
@@ -11866,34 +11914,34 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C181" s="49" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D181" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E181" s="49" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="F181" s="49" t="str">
-        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
+        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
       </x:c>
       <x:c r="G181" s="49" t="str">
-        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
+        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
       </x:c>
       <x:c r="H181" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I181" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J181" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="182" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A182" s="42" t="n">
         <x:v>178</x:v>
       </x:c>
@@ -11901,31 +11949,31 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C182" s="49" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D182" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E182" s="49" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="F182" s="49" t="str">
-        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
+        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
       </x:c>
       <x:c r="G182" s="49" t="str">
-        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
+        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
       </x:c>
       <x:c r="H182" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I182" s="55" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J182" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A183" s="42" t="n">
         <x:v>179</x:v>
       </x:c>
@@ -11933,121 +11981,121 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C183" s="49" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D183" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E183" s="49" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="F183" s="49" t="str">
-        <x:v>单子查询继续走直接调用路径。</x:v>
+        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
       </x:c>
       <x:c r="G183" s="49" t="str">
-        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
+        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
       </x:c>
       <x:c r="H183" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I183" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J183" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A184" s="42" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C184" s="49" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D184" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E184" s="49" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="F184" s="49" t="str">
-        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
+        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
       </x:c>
       <x:c r="G184" s="49" t="str">
-        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
+        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
       </x:c>
       <x:c r="H184" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I184" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.041</x:v>
       </x:c>
       <x:c r="J184" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="185" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A185" s="42" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C185" s="49" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D185" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E185" s="49" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="F185" s="49" t="str">
-        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
+        <x:v>单子查询继续走直接调用路径。</x:v>
       </x:c>
       <x:c r="G185" s="49" t="str">
-        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
+        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
       </x:c>
       <x:c r="H185" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I185" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J185" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="186" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A186" s="42" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="49" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C186" s="49" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D186" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E186" s="49" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="F186" s="49" t="str">
-        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
+        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
       </x:c>
       <x:c r="G186" s="49" t="str">
-        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
+        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
       </x:c>
       <x:c r="H186" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I186" s="55" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J186" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12058,118 +12106,118 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B187" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C187" s="49" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D187" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E187" s="49" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F187" s="49" t="str">
-        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
+        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
       </x:c>
       <x:c r="G187" s="49" t="str">
-        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
+        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
       </x:c>
       <x:c r="H187" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I187" s="55" t="n">
-        <x:v>0.022</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J187" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="132" hidden="0" customHeight="1">
+    <x:row r="188" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A188" s="42" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C188" s="49" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D188" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E188" s="49" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="F188" s="49" t="str">
-        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
+        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
       </x:c>
       <x:c r="G188" s="49" t="str">
-        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
+        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
       </x:c>
       <x:c r="H188" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I188" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.063</x:v>
       </x:c>
       <x:c r="J188" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" ht="132" hidden="0" customHeight="1">
+    <x:row r="189" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A189" s="42" t="n">
         <x:v>185</x:v>
       </x:c>
       <x:c r="B189" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C189" s="49" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D189" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E189" s="49" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="F189" s="49" t="str">
-        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
+        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
       </x:c>
       <x:c r="G189" s="49" t="str">
-        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
+        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
       </x:c>
       <x:c r="H189" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I189" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="J189" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="190" ht="132" hidden="0" customHeight="1">
       <x:c r="A190" s="42" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B190" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C190" s="49" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D190" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E190" s="49" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="F190" s="49" t="str">
-        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
+        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
       </x:c>
       <x:c r="G190" s="49" t="str">
-        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
+        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
       </x:c>
       <x:c r="H190" s="52" t="str">
         <x:v>通过</x:v>
@@ -12181,7 +12229,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="191" ht="132" hidden="0" customHeight="1">
       <x:c r="A191" s="42" t="n">
         <x:v>187</x:v>
       </x:c>
@@ -12189,31 +12237,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C191" s="49" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D191" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E191" s="49" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="F191" s="49" t="str">
-        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
+        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
       </x:c>
       <x:c r="G191" s="49" t="str">
-        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
+        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
       </x:c>
       <x:c r="H191" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I191" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J191" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="192" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A192" s="42" t="n">
         <x:v>188</x:v>
       </x:c>
@@ -12221,31 +12269,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C192" s="49" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D192" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E192" s="49" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="F192" s="49" t="str">
-        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
+        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
       </x:c>
       <x:c r="G192" s="49" t="str">
-        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
+        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
       </x:c>
       <x:c r="H192" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I192" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J192" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A193" s="42" t="n">
         <x:v>189</x:v>
       </x:c>
@@ -12253,25 +12301,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="49" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D193" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E193" s="49" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="F193" s="49" t="str">
-        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
+        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
       </x:c>
       <x:c r="G193" s="49" t="str">
-        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
+        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
       </x:c>
       <x:c r="H193" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I193" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J193" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12285,31 +12333,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="49" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D194" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E194" s="49" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="F194" s="49" t="str">
-        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
+        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
       </x:c>
       <x:c r="G194" s="49" t="str">
-        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
+        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
       </x:c>
       <x:c r="H194" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I194" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J194" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="195" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A195" s="42" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -12317,25 +12365,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="49" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D195" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E195" s="49" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="F195" s="49" t="str">
-        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
+        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
       </x:c>
       <x:c r="G195" s="49" t="str">
-        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
+        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
       </x:c>
       <x:c r="H195" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I195" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J195" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12349,31 +12397,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="49" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D196" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E196" s="49" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="F196" s="49" t="str">
-        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
+        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
       </x:c>
       <x:c r="G196" s="49" t="str">
-        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
+        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
       </x:c>
       <x:c r="H196" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I196" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J196" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="197" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A197" s="42" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -12381,31 +12429,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="49" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D197" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E197" s="49" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="F197" s="49" t="str">
-        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
+        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
       </x:c>
       <x:c r="G197" s="49" t="str">
-        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
+        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
       </x:c>
       <x:c r="H197" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I197" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J197" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="198" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A198" s="42" t="n">
         <x:v>194</x:v>
       </x:c>
@@ -12413,25 +12461,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="49" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D198" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E198" s="49" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="F198" s="49" t="str">
-        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
+        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
       </x:c>
       <x:c r="G198" s="49" t="str">
-        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
+        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
       </x:c>
       <x:c r="H198" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I198" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J198" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12445,31 +12493,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="49" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D199" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E199" s="49" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="F199" s="49" t="str">
-        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
+        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
       </x:c>
       <x:c r="G199" s="49" t="str">
-        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
+        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
       </x:c>
       <x:c r="H199" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I199" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.011</x:v>
       </x:c>
       <x:c r="J199" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="200" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A200" s="42" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -12477,19 +12525,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="49" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D200" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E200" s="49" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="F200" s="49" t="str">
-        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
+        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
       </x:c>
       <x:c r="G200" s="49" t="str">
-        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
+        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
       </x:c>
       <x:c r="H200" s="52" t="str">
         <x:v>通过</x:v>
@@ -12501,7 +12549,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="132" hidden="0" customHeight="1">
+    <x:row r="201" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A201" s="42" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -12509,31 +12557,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="49" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D201" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E201" s="49" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="F201" s="49" t="str">
-        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
+        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
       </x:c>
       <x:c r="G201" s="49" t="str">
-        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
+        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
       </x:c>
       <x:c r="H201" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I201" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J201" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="202" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A202" s="42" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -12541,31 +12589,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="49" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D202" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E202" s="49" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="F202" s="49" t="str">
-        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
+        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
       </x:c>
       <x:c r="G202" s="49" t="str">
-        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
+        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
       </x:c>
       <x:c r="H202" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I202" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J202" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="203" ht="132" hidden="0" customHeight="1">
       <x:c r="A203" s="42" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -12573,31 +12621,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="49" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D203" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E203" s="49" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="F203" s="49" t="str">
-        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
       </x:c>
       <x:c r="G203" s="49" t="str">
-        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
       </x:c>
       <x:c r="H203" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I203" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J203" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="132" hidden="0" customHeight="1">
+    <x:row r="204" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A204" s="42" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -12605,31 +12653,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="49" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D204" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E204" s="49" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="F204" s="49" t="str">
-        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G204" s="49" t="str">
-        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
       </x:c>
       <x:c r="H204" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I204" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J204" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="205" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A205" s="42" t="n">
         <x:v>201</x:v>
       </x:c>
@@ -12637,31 +12685,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C205" s="49" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D205" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E205" s="49" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="F205" s="49" t="str">
-        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
       </x:c>
       <x:c r="G205" s="49" t="str">
-        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
       </x:c>
       <x:c r="H205" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I205" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J205" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="206" ht="132" hidden="0" customHeight="1">
       <x:c r="A206" s="42" t="n">
         <x:v>202</x:v>
       </x:c>
@@ -12669,59 +12717,123 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C206" s="49" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D206" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E206" s="49" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="F206" s="49" t="str">
+        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+      </x:c>
+      <x:c r="G206" s="49" t="str">
+        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+      </x:c>
+      <x:c r="H206" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I206" s="55" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="J206" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A207" s="42" t="n">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B207" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C207" s="49" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D207" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E207" s="49" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="F207" s="49" t="str">
+        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+      </x:c>
+      <x:c r="G207" s="49" t="str">
+        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+      </x:c>
+      <x:c r="H207" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I207" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J207" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A208" s="42" t="n">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B208" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C208" s="49" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D206" s="49" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E206" s="49" t="str">
+      <x:c r="D208" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E208" s="49" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="F206" s="49" t="str">
+      <x:c r="F208" s="49" t="str">
         <x:v>限流进入可重试失败类别，不被误记为论文查无。</x:v>
       </x:c>
-      <x:c r="G206" s="49" t="str">
+      <x:c r="G208" s="49" t="str">
         <x:v>匿名访问限流可能污染覆盖率并错误触发论文隔离。</x:v>
       </x:c>
-      <x:c r="H206" s="52" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I206" s="55" t="n">
+      <x:c r="H208" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I208" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J208" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" ht="132" hidden="0" customHeight="1">
+      <x:c r="A209" s="45" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B209" s="50" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C209" s="50" t="str">
+        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
+      </x:c>
+      <x:c r="D209" s="50" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E209" s="50" t="str">
+        <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
+      </x:c>
+      <x:c r="F209" s="50" t="str">
+        <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
+      </x:c>
+      <x:c r="G209" s="50" t="str">
+        <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
+      </x:c>
+      <x:c r="H209" s="53" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I209" s="56" t="n">
         <x:v>0.004</x:v>
       </x:c>
-      <x:c r="J206" s="58" t="str">
-        <x:v>已登记</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" ht="132" hidden="0" customHeight="1">
-      <x:c r="A207" s="45" t="n">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="B207" s="50" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
-      </x:c>
-      <x:c r="C207" s="50" t="str">
-        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
-      </x:c>
-      <x:c r="D207" s="50" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E207" s="50" t="str">
-        <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
-      </x:c>
-      <x:c r="F207" s="50" t="str">
-        <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
-      </x:c>
-      <x:c r="G207" s="50" t="str">
-        <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
-      </x:c>
-      <x:c r="H207" s="53" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I207" s="56" t="n">
-        <x:v>0.009</x:v>
-      </x:c>
-      <x:c r="J207" s="59" t="str">
+      <x:c r="J209" s="59" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
@@ -12730,18 +12842,18 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H207">
+  <x:conditionalFormatting sqref="H5:H209">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="错误"/>
     <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="跳过"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J207">
+  <x:conditionalFormatting sqref="J5:J209">
     <x:cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="未登记"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R167d9a8028744dfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R506bed307c8749e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14126,34 +14238,66 @@
       </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="128" t="n">
+      <x:c r="A43" s="127" t="n">
         <x:v>46247.44788194445</x:v>
       </x:c>
-      <x:c r="B43" s="24" t="str">
+      <x:c r="B43" s="23" t="str">
         <x:v>fa64c7c71283</x:v>
       </x:c>
-      <x:c r="C43" s="24" t="n">
+      <x:c r="C43" s="23" t="n">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="D43" s="24" t="n">
+      <x:c r="D43" s="23" t="n">
         <x:v>203</x:v>
       </x:c>
-      <x:c r="E43" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F43" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G43" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H43" s="131" t="n">
+      <x:c r="E43" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F43" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G43" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H43" s="130" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I43" s="30" t="n">
+      <x:c r="I43" s="29" t="n">
         <x:v>266.505</x:v>
       </x:c>
-      <x:c r="J43" s="24" t="n">
+      <x:c r="J43" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="128" t="n">
+        <x:v>46247.46724537037</x:v>
+      </x:c>
+      <x:c r="B44" s="24" t="str">
+        <x:v>39a19fca1f84</x:v>
+      </x:c>
+      <x:c r="C44" s="24" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D44" s="24" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="E44" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F44" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G44" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I44" s="30" t="n">
+        <x:v>133.422</x:v>
+      </x:c>
+      <x:c r="J44" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -14163,7 +14307,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92c795e84cb5497d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R581d0fc40e8740fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/latest_test_report.xlsx
+++ b/reports/latest_test_report.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R18e549adb67b44cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R32182924db02494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R9136c57f12034b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="R47726ba19d1b4a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="R53a14c2706714391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R087a5f18c200467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="Rca93a6ff5dc44bb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R7514022f6aff4ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Rae9f99fccf904a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Ra88ea3c36ae34545"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H209" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J209" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J44" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="运行时间"/>
     <x:tableColumn id="2" name="Git Commit"/>
@@ -977,7 +977,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T11:12:50+08:00  |  Git：39a19fca1f844df50e7f0bf2f4be816c7b3c4672</x:v>
+        <x:v>运行时间：2026-08-13T11:34:17+08:00  |  Git：4a50f5528c4fb4e494b3893aa8bd43826ac629f1</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1007,22 +1007,22 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="74" t="n">
-        <x:f>COUNTA('测试明细'!$A$5:$A$209)</x:f>
-        <x:v>205</x:v>
+        <x:f>COUNTA('测试明细'!$A$5:$A$211)</x:f>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B5" s="75"/>
       <x:c r="C5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$209,"通过")</x:f>
-        <x:v>205</x:v>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$211,"通过")</x:f>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D5" s="75"/>
       <x:c r="E5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$209,"失败")+COUNTIF('测试明细'!$E$5:$E$209,"错误")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$211,"失败")+COUNTIF('测试明细'!$E$5:$E$211,"错误")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="75"/>
       <x:c r="G5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$209,"跳过")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$211,"跳过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="76"/>
@@ -1062,8 +1062,8 @@
       </x:c>
       <x:c r="B9" s="108"/>
       <x:c r="C9" s="109" t="n">
-        <x:f>SUM('测试明细'!$F$5:$F$209)</x:f>
-        <x:v>133.42200000000025</x:v>
+        <x:f>SUM('测试明细'!$F$5:$F$211)</x:f>
+        <x:v>142.61500000000032</x:v>
       </x:c>
       <x:c r="D9" s="109"/>
       <x:c r="E9" s="110" t="n">
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="F9" s="110"/>
       <x:c r="G9" s="110" t="n">
-        <x:f>COUNTIF('用例说明'!$J$5:$J$209,"未登记")</x:f>
+        <x:f>COUNTIF('用例说明'!$J$5:$J$211,"未登记")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="111"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T11:12:50+08:00  |  Git：39a19fca1f844df50e7f0bf2f4be816c7b3c4672</x:v>
+        <x:v>运行时间：2026-08-13T11:34:17+08:00  |  Git：4a50f5528c4fb4e494b3893aa8bd43826ac629f1</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1280,7 +1280,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
         <x:v>确认旧基线与当前候选实现使用完全相同的能力模块，保证能力对比口径一致。</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F6" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
         <x:v>确认当前实现相对旧基线确实提升关键确定性能力的准确率。</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>验证动态查询规划不会为简单问题创建多余检索词，同时保持规划准确。</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F8" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>验证基准报告能同时给出基线值、候选值和差值。</x:v>
@@ -1376,7 +1376,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F9" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
         <x:v>验证离线基准能准确统计成功/失败调用以及输入、输出和总 Token。</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F10" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
         <x:v>验证离线基准能够量化统一 Tool 层的协议、错误和恢复能力。</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F11" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
         <x:v>验证离线 Benchmark 对比单源基线与多源候选的覆盖、去重和故障恢复。</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F12" s="32" t="n">
-        <x:v>0.185</x:v>
+        <x:v>0.141</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
         <x:v>验证完整能力基准报告可以用 UTF-8 JSON 保存并重新读取。</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F13" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G13" s="35" t="str">
         <x:v>验证基准工具拒绝不存在的运行配置名称。</x:v>
@@ -1496,7 +1496,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F14" s="32" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str">
         <x:v>验证候选评测能从 OpenAlex 等二级来源的 DOI 中提取待验证 arXiv 身份。</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G15" s="35" t="str">
         <x:v>验证联合重放只把普通 DOI 交给 Crossref，排除 arXiv DOI。</x:v>
@@ -1544,7 +1544,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F16" s="32" t="n">
-        <x:v>0.031</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="G16" s="35" t="str">
         <x:v>验证成功取得的规范元数据会缓存，快照重放不会重复消耗网络请求。</x:v>
@@ -1568,7 +1568,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G17" s="35" t="str">
         <x:v>验证 SSL、超时等临时失败不会被当成永久缓存结果。</x:v>
@@ -1592,7 +1592,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>0.065</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="G18" s="35" t="str">
         <x:v>验证 Crossref 成功记录和明确查无均可重复使用。</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G19" s="35" t="str">
         <x:v>验证 DOI authority 网络失败不会写入成功缓存。</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="G20" s="35" t="str">
         <x:v>验证本轮候选实验只查询 v2 实际隔离过的身份，控制外部请求成本。</x:v>
@@ -1664,7 +1664,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
-        <x:v>0.124</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="G21" s="35" t="str">
         <x:v>验证规范元数据候选只有在三份完整独立快照、权威覆盖完整且逐题无回归时才通过晋升门槛。</x:v>
@@ -1688,7 +1688,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F22" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G22" s="35" t="str">
         <x:v>验证 Crossref 相对仅 arXiv canonical 没有指标变化时不得宣称质量提升。</x:v>
@@ -1712,7 +1712,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F23" s="32" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G23" s="35" t="str">
         <x:v>验证普通 DOI 候选评测只使用所有独立快照都出现的非 arXiv DOI。</x:v>
@@ -1760,7 +1760,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F25" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G25" s="35" t="str">
         <x:v>验证普通 DOI 样本按注册前缀轮转抽取，避免单一高频前缀垄断评测集。</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F27" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G27" s="35" t="str">
         <x:v>验证 DOI 校验在固定污染、缺失、近似、查无和失败场景中达到阶段止损条件。</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F28" s="32" t="n">
-        <x:v>0.094</x:v>
+        <x:v>0.074</x:v>
       </x:c>
       <x:c r="G28" s="35" t="str">
         <x:v>验证普通研究问题按完整 Agentic RAG 节点顺序执行。</x:v>
@@ -1856,7 +1856,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F29" s="32" t="n">
-        <x:v>0.067</x:v>
+        <x:v>0.087</x:v>
       </x:c>
       <x:c r="G29" s="35" t="str">
         <x:v>验证已有 PDF 的请求不会重复进行外部查询规划和检索。</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F30" s="32" t="n">
-        <x:v>0.066</x:v>
+        <x:v>0.091</x:v>
       </x:c>
       <x:c r="G30" s="35" t="str">
         <x:v>验证问候类输入在进入 RAG 与 LLM 节点前本地结束。</x:v>
@@ -1976,7 +1976,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F34" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G34" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -2000,7 +2000,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F35" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G35" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2048,7 +2048,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F37" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G37" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2120,7 +2120,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F40" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G40" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F41" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G41" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2216,7 +2216,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F44" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G44" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2264,7 +2264,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F46" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G46" s="35" t="str">
         <x:v>验证本地闲聊响应不会破坏已有状态和请求元数据。</x:v>
@@ -2288,7 +2288,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F47" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G47" s="35" t="str">
         <x:v>验证能读取 LangChain 标准 usage_metadata Token 字段。</x:v>
@@ -2384,7 +2384,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F51" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G51" s="35" t="str">
         <x:v>验证 LLM 调用失败时仍保留失败类型和耗时记录。</x:v>
@@ -2408,7 +2408,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F52" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G52" s="35" t="str">
         <x:v>验证多个节点的 LLM 用量可以累加且不会重复计数。</x:v>
@@ -2432,7 +2432,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F53" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G53" s="35" t="str">
         <x:v>验证指标节点既能按节点分组，又能提供全流程总量与缺失用量统计。</x:v>
@@ -2504,7 +2504,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F56" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G56" s="35" t="str">
         <x:v>验证答案生成节点记录实际生成结果和模型用量。</x:v>
@@ -2528,7 +2528,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F57" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G57" s="35" t="str">
         <x:v>验证关闭 LLM 评估时只使用规则评分且不创建虚假调用记录。</x:v>
@@ -2552,7 +2552,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F58" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G58" s="35" t="str">
         <x:v>验证 BM25 基线能把中文问题与英文术语、数字混合分词。</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F59" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G59" s="35" t="str">
         <x:v>验证 BM25 将包含查询词的文本块排在无关块之前，且重复运行排名与分数一致。</x:v>
@@ -2600,7 +2600,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F60" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G60" s="35" t="str">
         <x:v>验证 BM25 拒绝空语料和非正数返回条数。</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F61" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G61" s="35" t="str">
         <x:v>用手工可计算的排名验证本地 RAG Recall、MRR 与 nDCG 公式。</x:v>
@@ -2648,7 +2648,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F62" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G62" s="35" t="str">
         <x:v>验证同一相关 PDF 页返回多个 Chunk 时，page-level 指标只计算首次命中。</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F63" s="32" t="n">
-        <x:v>0.099</x:v>
+        <x:v>0.074</x:v>
       </x:c>
       <x:c r="G63" s="35" t="str">
         <x:v>验证代表论文来源清单生成 Manifest 时保留语料版本、论文身份和内容哈希。</x:v>
@@ -2696,7 +2696,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F64" s="32" t="n">
-        <x:v>0.043</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G64" s="35" t="str">
         <x:v>验证来源清单声明的 PDF 缺失时立即失败，而不是静默生成不完整语料。</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F66" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G66" s="35" t="str">
         <x:v>验证 Dense 检索拒绝零向量和空语料。</x:v>
@@ -2768,7 +2768,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F67" s="32" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.031</x:v>
       </x:c>
       <x:c r="G67" s="35" t="str">
         <x:v>验证 Dense 向量缓存可以无损加载，并在语料文本、模型或处理版本变化后使用不同指纹。</x:v>
@@ -2792,22 +2792,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F68" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G68" s="35" t="str">
         <x:v>验证缓存命中时 DenseRetriever 不会重新编码全部论文，只对查询生成向量。</x:v>
       </x:c>
       <x:c r="H68" s="35" t="str"/>
     </x:row>
-    <x:row r="69" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="69" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A69" s="26" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_cache_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense.py</x:v>
       </x:c>
       <x:c r="C69" s="35" t="str">
-        <x:v>test_dense_cache_comparison_requires_same_quality_and_faster_warm_build</x:v>
+        <x:v>test_dense_warmup_is_fixed_and_excluded_from_formal_timing</x:v>
       </x:c>
       <x:c r="D69" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2816,22 +2816,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F69" s="32" t="n">
-        <x:v>0.071</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G69" s="35" t="str">
-        <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
+        <x:v>验证 Dense 正式评测前执行固定次数的查询预热，并将预热延迟与正式查询指标明确隔离。</x:v>
       </x:c>
       <x:c r="H69" s="35" t="str"/>
     </x:row>
-    <x:row r="70" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="70" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A70" s="26" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense_cache_compare.py</x:v>
       </x:c>
       <x:c r="C70" s="35" t="str">
-        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
+        <x:v>test_dense_cache_comparison_requires_same_quality_and_faster_warm_build</x:v>
       </x:c>
       <x:c r="D70" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2840,22 +2840,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F70" s="32" t="n">
-        <x:v>32.041</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="G70" s="35" t="str">
-        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
+        <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
       </x:c>
       <x:c r="H70" s="35" t="str"/>
     </x:row>
-    <x:row r="71" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="71" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A71" s="26" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_model_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense_compare.py</x:v>
       </x:c>
       <x:c r="C71" s="35" t="str">
-        <x:v>test_dense_model_comparison_prefers_quality_gain_without_excess_regression</x:v>
+        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
       </x:c>
       <x:c r="D71" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2864,22 +2864,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F71" s="32" t="n">
-        <x:v>0.039</x:v>
+        <x:v>31.084</x:v>
       </x:c>
       <x:c r="G71" s="35" t="str">
-        <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
+        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
       </x:c>
       <x:c r="H71" s="35" t="str"/>
     </x:row>
-    <x:row r="72" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="72" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A72" s="26" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_models.py</x:v>
+        <x:v>tests/test_local_rag_dense_model_compare.py</x:v>
       </x:c>
       <x:c r="C72" s="35" t="str">
-        <x:v>test_dense_model_matrix_changes_only_declared_embedding_properties</x:v>
+        <x:v>test_dense_model_comparison_prefers_quality_gain_without_excess_regression</x:v>
       </x:c>
       <x:c r="D72" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2888,22 +2888,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F72" s="32" t="n">
-        <x:v>0.908</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="G72" s="35" t="str">
-        <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
+        <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
       </x:c>
       <x:c r="H72" s="35" t="str"/>
     </x:row>
-    <x:row r="73" ht="198" hidden="0" customHeight="1">
+    <x:row r="73" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A73" s="26" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_stability.py</x:v>
+        <x:v>tests/test_local_rag_dense_models.py</x:v>
       </x:c>
       <x:c r="C73" s="35" t="str">
-        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
+        <x:v>test_dense_model_matrix_changes_only_declared_embedding_properties</x:v>
       </x:c>
       <x:c r="D73" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2912,14 +2912,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F73" s="32" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.774</x:v>
       </x:c>
       <x:c r="G73" s="35" t="str">
-        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
+        <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
       </x:c>
       <x:c r="H73" s="35" t="str"/>
     </x:row>
-    <x:row r="74" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="74" ht="198" hidden="0" customHeight="1">
       <x:c r="A74" s="26" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -2927,7 +2927,7 @@
         <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C74" s="35" t="str">
-        <x:v>test_dense_stability_rejects_mixed_or_unexpected_models</x:v>
+        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
       </x:c>
       <x:c r="D74" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2936,22 +2936,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F74" s="32" t="n">
-        <x:v>0.026</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="G74" s="35" t="str">
-        <x:v>验证稳定性评测拒绝混入其他 Embedding 模型或不符合预期模型身份的运行文件。</x:v>
+        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
       </x:c>
       <x:c r="H74" s="35" t="str"/>
     </x:row>
-    <x:row r="75" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="75" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A75" s="26" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="35" t="str">
-        <x:v>tests/test_local_rag_dense_stability_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C75" s="35" t="str">
-        <x:v>test_stability_comparison_preserves_failed_candidate_decision</x:v>
+        <x:v>test_dense_stability_rejects_mixed_or_unexpected_models</x:v>
       </x:c>
       <x:c r="D75" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2960,22 +2960,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F75" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="G75" s="35" t="str">
-        <x:v>验证 MiniLM/MPNet 稳定性并列比较保留 MPNet 的失败判定，不因平均质量收益或模型间比值覆盖原始闸门。</x:v>
+        <x:v>验证稳定性评测拒绝混入其他 Embedding 模型或不符合预期模型身份的运行文件。</x:v>
       </x:c>
       <x:c r="H75" s="35" t="str"/>
     </x:row>
-    <x:row r="76" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="76" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A76" s="26" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability_compare.py</x:v>
       </x:c>
       <x:c r="C76" s="35" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_stability_comparison_preserves_failed_candidate_decision</x:v>
       </x:c>
       <x:c r="D76" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -2984,22 +2984,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F76" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="G76" s="35" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证 MiniLM/MPNet 稳定性并列比较保留 MPNet 的失败判定，不因平均质量收益或模型间比值覆盖原始闸门。</x:v>
       </x:c>
       <x:c r="H76" s="35" t="str"/>
     </x:row>
-    <x:row r="77" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="77" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A77" s="26" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="35" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_warmup_compare.py</x:v>
       </x:c>
       <x:c r="C77" s="35" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_warmup_comparison_requires_failed_before_and_passed_after</x:v>
       </x:c>
       <x:c r="D77" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3008,14 +3008,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F77" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G77" s="35" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证预热对照只在同一模型由预热前失败转为预热后通过时，才判断首次初始化解释了稳定性问题。</x:v>
       </x:c>
       <x:c r="H77" s="35" t="str"/>
     </x:row>
-    <x:row r="78" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="78" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A78" s="26" t="n">
         <x:v>74</x:v>
       </x:c>
@@ -3023,7 +3023,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C78" s="35" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D78" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3032,14 +3032,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F78" s="32" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G78" s="35" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="H78" s="35" t="str"/>
     </x:row>
-    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="79" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A79" s="26" t="n">
         <x:v>75</x:v>
       </x:c>
@@ -3047,7 +3047,7 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C79" s="35" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D79" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3056,10 +3056,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F79" s="32" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G79" s="35" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="H79" s="35" t="str"/>
     </x:row>
@@ -3068,10 +3068,10 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C80" s="35" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D80" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3080,22 +3080,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F80" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="G80" s="35" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="H80" s="35" t="str"/>
     </x:row>
-    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="81" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A81" s="26" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C81" s="35" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D81" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3104,22 +3104,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F81" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.035</x:v>
       </x:c>
       <x:c r="G81" s="35" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="H81" s="35" t="str"/>
     </x:row>
-    <x:row r="82" ht="132" hidden="0" customHeight="1">
+    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A82" s="26" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="35" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C82" s="35" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D82" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3128,22 +3128,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F82" s="32" t="n">
-        <x:v>30.915</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G82" s="35" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="H82" s="35" t="str"/>
     </x:row>
-    <x:row r="83" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="83" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A83" s="26" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C83" s="35" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D83" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3152,22 +3152,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F83" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G83" s="35" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="H83" s="35" t="str"/>
     </x:row>
-    <x:row r="84" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="84" ht="132" hidden="0" customHeight="1">
       <x:c r="A84" s="26" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C84" s="35" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D84" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3176,10 +3176,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F84" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>30.792</x:v>
       </x:c>
       <x:c r="G84" s="35" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="H84" s="35" t="str"/>
     </x:row>
@@ -3191,7 +3191,7 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C85" s="35" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D85" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3200,22 +3200,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F85" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G85" s="35" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="H85" s="35" t="str"/>
     </x:row>
-    <x:row r="86" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="86" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A86" s="26" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C86" s="35" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D86" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3224,10 +3224,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F86" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G86" s="35" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="H86" s="35" t="str"/>
     </x:row>
@@ -3236,10 +3236,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C87" s="35" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D87" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3248,10 +3248,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F87" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G87" s="35" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="H87" s="35" t="str"/>
     </x:row>
@@ -3263,7 +3263,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="35" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D88" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3272,14 +3272,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F88" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G88" s="35" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="H88" s="35" t="str"/>
     </x:row>
-    <x:row r="89" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="89" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A89" s="26" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -3287,7 +3287,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C89" s="35" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D89" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3296,14 +3296,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F89" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G89" s="35" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="H89" s="35" t="str"/>
     </x:row>
-    <x:row r="90" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="90" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A90" s="26" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -3311,7 +3311,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C90" s="35" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D90" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3320,14 +3320,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F90" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G90" s="35" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="H90" s="35" t="str"/>
     </x:row>
-    <x:row r="91" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="91" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A91" s="26" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -3335,7 +3335,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C91" s="35" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D91" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3344,14 +3344,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F91" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G91" s="35" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="H91" s="35" t="str"/>
     </x:row>
-    <x:row r="92" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="92" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A92" s="26" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -3359,7 +3359,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C92" s="35" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D92" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3368,10 +3368,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F92" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G92" s="35" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="H92" s="35" t="str"/>
     </x:row>
@@ -3380,10 +3380,10 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B93" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C93" s="35" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D93" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3392,22 +3392,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F93" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G93" s="35" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="H93" s="35" t="str"/>
     </x:row>
-    <x:row r="94" ht="132" hidden="0" customHeight="1">
+    <x:row r="94" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A94" s="26" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B94" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C94" s="35" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D94" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3416,14 +3416,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F94" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G94" s="35" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="H94" s="35" t="str"/>
     </x:row>
-    <x:row r="95" ht="132" hidden="0" customHeight="1">
+    <x:row r="95" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A95" s="26" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -3431,7 +3431,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="35" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D95" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3440,14 +3440,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F95" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G95" s="35" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="H95" s="35" t="str"/>
     </x:row>
-    <x:row r="96" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="96" ht="132" hidden="0" customHeight="1">
       <x:c r="A96" s="26" t="n">
         <x:v>92</x:v>
       </x:c>
@@ -3455,7 +3455,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C96" s="35" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D96" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3464,14 +3464,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F96" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G96" s="35" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="H96" s="35" t="str"/>
     </x:row>
-    <x:row r="97" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="97" ht="132" hidden="0" customHeight="1">
       <x:c r="A97" s="26" t="n">
         <x:v>93</x:v>
       </x:c>
@@ -3479,7 +3479,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C97" s="35" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D97" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3491,11 +3491,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G97" s="35" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="H97" s="35" t="str"/>
     </x:row>
-    <x:row r="98" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="98" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A98" s="26" t="n">
         <x:v>94</x:v>
       </x:c>
@@ -3503,7 +3503,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C98" s="35" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D98" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3512,14 +3512,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F98" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G98" s="35" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="H98" s="35" t="str"/>
     </x:row>
-    <x:row r="99" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="99" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A99" s="26" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -3527,7 +3527,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C99" s="35" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D99" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3539,7 +3539,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G99" s="35" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="H99" s="35" t="str"/>
     </x:row>
@@ -3548,10 +3548,10 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="35" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C100" s="35" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D100" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3560,22 +3560,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F100" s="32" t="n">
-        <x:v>2.357</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G100" s="35" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="H100" s="35" t="str"/>
     </x:row>
-    <x:row r="101" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A101" s="26" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C101" s="35" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D101" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3584,22 +3584,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F101" s="32" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G101" s="35" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="H101" s="35" t="str"/>
     </x:row>
-    <x:row r="102" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="102" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A102" s="26" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C102" s="35" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D102" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3608,14 +3608,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F102" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="G102" s="35" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="H102" s="35" t="str"/>
     </x:row>
-    <x:row r="103" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="103" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A103" s="26" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -3623,7 +3623,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C103" s="35" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D103" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3632,14 +3632,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F103" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="G103" s="35" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="H103" s="35" t="str"/>
     </x:row>
-    <x:row r="104" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="104" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A104" s="26" t="n">
         <x:v>100</x:v>
       </x:c>
@@ -3647,7 +3647,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C104" s="35" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D104" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3656,22 +3656,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F104" s="32" t="n">
-        <x:v>1.156</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G104" s="35" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="H104" s="35" t="str"/>
     </x:row>
-    <x:row r="105" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="105" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A105" s="26" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C105" s="35" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D105" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3680,22 +3680,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F105" s="32" t="n">
-        <x:v>0.189</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G105" s="35" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="H105" s="35" t="str"/>
     </x:row>
-    <x:row r="106" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="106" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A106" s="26" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C106" s="35" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D106" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3704,10 +3704,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F106" s="32" t="n">
-        <x:v>0.085</x:v>
+        <x:v>1.131</x:v>
       </x:c>
       <x:c r="G106" s="35" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="H106" s="35" t="str"/>
     </x:row>
@@ -3719,7 +3719,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C107" s="35" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D107" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3728,14 +3728,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F107" s="32" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.171</x:v>
       </x:c>
       <x:c r="G107" s="35" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="H107" s="35" t="str"/>
     </x:row>
-    <x:row r="108" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="108" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A108" s="26" t="n">
         <x:v>104</x:v>
       </x:c>
@@ -3743,7 +3743,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C108" s="35" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D108" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3752,22 +3752,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F108" s="32" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.092</x:v>
       </x:c>
       <x:c r="G108" s="35" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="H108" s="35" t="str"/>
     </x:row>
-    <x:row r="109" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="109" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A109" s="26" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="35" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C109" s="35" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D109" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3776,10 +3776,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F109" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.047</x:v>
       </x:c>
       <x:c r="G109" s="35" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="H109" s="35" t="str"/>
     </x:row>
@@ -3788,10 +3788,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B110" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C110" s="35" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D110" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3800,10 +3800,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F110" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.076</x:v>
       </x:c>
       <x:c r="G110" s="35" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="H110" s="35" t="str"/>
     </x:row>
@@ -3812,13 +3812,13 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B111" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C111" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D111" s="35" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E111" s="26" t="str">
         <x:v>通过</x:v>
@@ -3827,11 +3827,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G111" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="H111" s="35" t="str"/>
     </x:row>
-    <x:row r="112" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="112" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A112" s="26" t="n">
         <x:v>108</x:v>
       </x:c>
@@ -3839,19 +3839,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D112" s="35" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E112" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F112" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G112" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="H112" s="35" t="str"/>
     </x:row>
@@ -3863,10 +3863,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D113" s="35" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
         <x:v>通过</x:v>
@@ -3887,16 +3887,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D114" s="35" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E114" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F114" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G114" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3911,23 +3911,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D115" s="35" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F115" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G115" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H115" s="35" t="str"/>
     </x:row>
-    <x:row r="116" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="116" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A116" s="26" t="n">
         <x:v>112</x:v>
       </x:c>
@@ -3935,23 +3935,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D116" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E116" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F116" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G116" s="35" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H116" s="35" t="str"/>
     </x:row>
-    <x:row r="117" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="117" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A117" s="26" t="n">
         <x:v>113</x:v>
       </x:c>
@@ -3959,19 +3959,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D117" s="35" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F117" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G117" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H117" s="35" t="str"/>
     </x:row>
@@ -3983,10 +3983,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D118" s="35" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E118" s="26" t="str">
         <x:v>通过</x:v>
@@ -3995,7 +3995,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G118" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="H118" s="35" t="str"/>
     </x:row>
@@ -4007,16 +4007,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D119" s="35" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E119" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F119" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G119" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -4031,16 +4031,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D120" s="35" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E120" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F120" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G120" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -4055,10 +4055,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D121" s="35" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E121" s="26" t="str">
         <x:v>通过</x:v>
@@ -4071,7 +4071,7 @@
       </x:c>
       <x:c r="H121" s="35" t="str"/>
     </x:row>
-    <x:row r="122" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="122" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A122" s="26" t="n">
         <x:v>118</x:v>
       </x:c>
@@ -4079,23 +4079,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D122" s="35" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E122" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F122" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G122" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H122" s="35" t="str"/>
     </x:row>
-    <x:row r="123" ht="66" hidden="0" customHeight="1">
+    <x:row r="123" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A123" s="26" t="n">
         <x:v>119</x:v>
       </x:c>
@@ -4103,23 +4103,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C123" s="35" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D123" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E123" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F123" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G123" s="35" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H123" s="35" t="str"/>
     </x:row>
-    <x:row r="124" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="124" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A124" s="26" t="n">
         <x:v>120</x:v>
       </x:c>
@@ -4127,10 +4127,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C124" s="35" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D124" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E124" s="26" t="str">
         <x:v>通过</x:v>
@@ -4139,19 +4139,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G124" s="35" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H124" s="35" t="str"/>
     </x:row>
-    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="125" ht="66" hidden="0" customHeight="1">
       <x:c r="A125" s="26" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C125" s="35" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D125" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4160,10 +4160,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F125" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G125" s="35" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="H125" s="35" t="str"/>
     </x:row>
@@ -4172,10 +4172,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C126" s="35" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D126" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4184,14 +4184,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F126" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G126" s="35" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="H126" s="35" t="str"/>
     </x:row>
-    <x:row r="127" ht="132" hidden="0" customHeight="1">
+    <x:row r="127" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A127" s="26" t="n">
         <x:v>123</x:v>
       </x:c>
@@ -4199,7 +4199,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C127" s="35" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D127" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4211,11 +4211,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G127" s="35" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="H127" s="35" t="str"/>
     </x:row>
-    <x:row r="128" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="128" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A128" s="26" t="n">
         <x:v>124</x:v>
       </x:c>
@@ -4223,7 +4223,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C128" s="35" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D128" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4232,10 +4232,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F128" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G128" s="35" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="H128" s="35" t="str"/>
     </x:row>
@@ -4244,10 +4244,10 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C129" s="35" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D129" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4256,10 +4256,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F129" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G129" s="35" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="H129" s="35" t="str"/>
     </x:row>
@@ -4268,10 +4268,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C130" s="35" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D130" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4280,14 +4280,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F130" s="32" t="n">
-        <x:v>14.665</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G130" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="H130" s="35" t="str"/>
     </x:row>
-    <x:row r="131" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="131" ht="132" hidden="0" customHeight="1">
       <x:c r="A131" s="26" t="n">
         <x:v>127</x:v>
       </x:c>
@@ -4295,7 +4295,7 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C131" s="35" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D131" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4304,22 +4304,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F131" s="32" t="n">
-        <x:v>15.135</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G131" s="35" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="H131" s="35" t="str"/>
     </x:row>
-    <x:row r="132" ht="132" hidden="0" customHeight="1">
+    <x:row r="132" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A132" s="26" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C132" s="35" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D132" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4328,22 +4328,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F132" s="32" t="n">
-        <x:v>0.005</x:v>
+        <x:v>14.691</x:v>
       </x:c>
       <x:c r="G132" s="35" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="H132" s="35" t="str"/>
     </x:row>
-    <x:row r="133" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="133" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A133" s="26" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C133" s="35" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D133" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4352,14 +4352,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F133" s="32" t="n">
-        <x:v>18.548</x:v>
+        <x:v>26.027</x:v>
       </x:c>
       <x:c r="G133" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="H133" s="35" t="str"/>
     </x:row>
-    <x:row r="134" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="134" ht="132" hidden="0" customHeight="1">
       <x:c r="A134" s="26" t="n">
         <x:v>130</x:v>
       </x:c>
@@ -4367,7 +4367,7 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C134" s="35" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D134" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4376,10 +4376,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F134" s="32" t="n">
-        <x:v>15.261</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G134" s="35" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="H134" s="35" t="str"/>
     </x:row>
@@ -4388,10 +4388,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B135" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C135" s="35" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D135" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4400,10 +4400,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F135" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>18.907</x:v>
       </x:c>
       <x:c r="G135" s="35" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="H135" s="35" t="str"/>
     </x:row>
@@ -4412,10 +4412,10 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B136" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C136" s="35" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D136" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4424,14 +4424,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F136" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>14.794</x:v>
       </x:c>
       <x:c r="G136" s="35" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="H136" s="35" t="str"/>
     </x:row>
-    <x:row r="137" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="137" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A137" s="26" t="n">
         <x:v>133</x:v>
       </x:c>
@@ -4439,7 +4439,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="35" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D137" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4448,10 +4448,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F137" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G137" s="35" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="H137" s="35" t="str"/>
     </x:row>
@@ -4463,7 +4463,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="35" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D138" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4475,11 +4475,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G138" s="35" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="H138" s="35" t="str"/>
     </x:row>
-    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A139" s="26" t="n">
         <x:v>135</x:v>
       </x:c>
@@ -4487,7 +4487,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="35" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D139" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4499,11 +4499,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G139" s="35" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="H139" s="35" t="str"/>
     </x:row>
-    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="140" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A140" s="26" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -4511,7 +4511,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="35" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D140" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4523,7 +4523,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G140" s="35" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="H140" s="35" t="str"/>
     </x:row>
@@ -4535,7 +4535,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="35" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D141" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4547,7 +4547,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G141" s="35" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="H141" s="35" t="str"/>
     </x:row>
@@ -4559,7 +4559,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="35" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D142" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4571,11 +4571,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G142" s="35" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="H142" s="35" t="str"/>
     </x:row>
-    <x:row r="143" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A143" s="26" t="n">
         <x:v>139</x:v>
       </x:c>
@@ -4583,7 +4583,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D143" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4595,11 +4595,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G143" s="35" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="H143" s="35" t="str"/>
     </x:row>
-    <x:row r="144" ht="132" hidden="0" customHeight="1">
+    <x:row r="144" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A144" s="26" t="n">
         <x:v>140</x:v>
       </x:c>
@@ -4607,7 +4607,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D144" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4619,7 +4619,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G144" s="35" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="H144" s="35" t="str"/>
     </x:row>
@@ -4631,7 +4631,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="35" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D145" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4643,11 +4643,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G145" s="35" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="H145" s="35" t="str"/>
     </x:row>
-    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="146" ht="132" hidden="0" customHeight="1">
       <x:c r="A146" s="26" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -4655,7 +4655,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C146" s="35" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D146" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4667,11 +4667,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G146" s="35" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="H146" s="35" t="str"/>
     </x:row>
-    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="147" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A147" s="26" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -4679,7 +4679,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C147" s="35" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D147" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4688,22 +4688,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F147" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G147" s="35" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="H147" s="35" t="str"/>
     </x:row>
-    <x:row r="148" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="148" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A148" s="26" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B148" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C148" s="35" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D148" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4715,7 +4715,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G148" s="35" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="H148" s="35" t="str"/>
     </x:row>
@@ -4724,10 +4724,10 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B149" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C149" s="35" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D149" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4739,11 +4739,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G149" s="35" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="H149" s="35" t="str"/>
     </x:row>
-    <x:row r="150" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="150" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A150" s="26" t="n">
         <x:v>146</x:v>
       </x:c>
@@ -4751,7 +4751,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D150" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4763,11 +4763,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G150" s="35" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="H150" s="35" t="str"/>
     </x:row>
-    <x:row r="151" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A151" s="26" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -4775,7 +4775,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D151" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4787,7 +4787,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G151" s="35" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="H151" s="35" t="str"/>
     </x:row>
@@ -4799,7 +4799,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C152" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D152" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4811,11 +4811,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G152" s="35" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="H152" s="35" t="str"/>
     </x:row>
-    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="153" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A153" s="26" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -4823,7 +4823,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="35" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D153" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4832,14 +4832,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F153" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G153" s="35" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="H153" s="35" t="str"/>
     </x:row>
-    <x:row r="154" ht="66" hidden="0" customHeight="1">
+    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A154" s="26" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -4847,7 +4847,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C154" s="35" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D154" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4856,14 +4856,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F154" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G154" s="35" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="H154" s="35" t="str"/>
     </x:row>
-    <x:row r="155" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="155" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A155" s="26" t="n">
         <x:v>151</x:v>
       </x:c>
@@ -4871,7 +4871,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C155" s="35" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D155" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4883,19 +4883,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G155" s="35" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="H155" s="35" t="str"/>
     </x:row>
-    <x:row r="156" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="156" ht="66" hidden="0" customHeight="1">
       <x:c r="A156" s="26" t="n">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B156" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C156" s="35" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D156" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4904,10 +4904,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F156" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G156" s="35" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="H156" s="35" t="str"/>
     </x:row>
@@ -4916,10 +4916,10 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B157" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C157" s="35" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D157" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4928,14 +4928,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F157" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G157" s="35" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="H157" s="35" t="str"/>
     </x:row>
-    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="158" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A158" s="26" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -4943,7 +4943,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="35" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D158" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4952,14 +4952,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F158" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G158" s="35" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="H158" s="35" t="str"/>
     </x:row>
-    <x:row r="159" ht="132" hidden="0" customHeight="1">
+    <x:row r="159" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A159" s="26" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -4967,7 +4967,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4979,11 +4979,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G159" s="35" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="H159" s="35" t="str"/>
     </x:row>
-    <x:row r="160" ht="132" hidden="0" customHeight="1">
+    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A160" s="26" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -4991,7 +4991,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5000,14 +5000,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F160" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G160" s="35" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="H160" s="35" t="str"/>
     </x:row>
-    <x:row r="161" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="161" ht="132" hidden="0" customHeight="1">
       <x:c r="A161" s="26" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -5015,7 +5015,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5027,11 +5027,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G161" s="35" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="H161" s="35" t="str"/>
     </x:row>
-    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="162" ht="132" hidden="0" customHeight="1">
       <x:c r="A162" s="26" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -5039,7 +5039,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5048,14 +5048,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F162" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G162" s="35" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="H162" s="35" t="str"/>
     </x:row>
-    <x:row r="163" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="163" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A163" s="26" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -5063,7 +5063,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5072,14 +5072,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F163" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G163" s="35" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="H163" s="35" t="str"/>
     </x:row>
-    <x:row r="164" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A164" s="26" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -5087,7 +5087,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5096,14 +5096,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F164" s="32" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G164" s="35" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H164" s="35" t="str"/>
     </x:row>
-    <x:row r="165" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A165" s="26" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -5111,7 +5111,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5123,11 +5123,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G165" s="35" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="H165" s="35" t="str"/>
     </x:row>
-    <x:row r="166" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="166" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A166" s="26" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -5135,7 +5135,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5144,14 +5144,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F166" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.084</x:v>
       </x:c>
       <x:c r="G166" s="35" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="H166" s="35" t="str"/>
     </x:row>
-    <x:row r="167" ht="132" hidden="0" customHeight="1">
+    <x:row r="167" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A167" s="26" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -5159,7 +5159,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="35" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D167" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5171,11 +5171,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G167" s="35" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="H167" s="35" t="str"/>
     </x:row>
-    <x:row r="168" ht="132" hidden="0" customHeight="1">
+    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A168" s="26" t="n">
         <x:v>164</x:v>
       </x:c>
@@ -5183,7 +5183,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="35" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D168" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5192,14 +5192,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F168" s="32" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G168" s="35" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="H168" s="35" t="str"/>
     </x:row>
-    <x:row r="169" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="169" ht="132" hidden="0" customHeight="1">
       <x:c r="A169" s="26" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -5207,7 +5207,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="35" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D169" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5216,14 +5216,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F169" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G169" s="35" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="H169" s="35" t="str"/>
     </x:row>
-    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="170" ht="132" hidden="0" customHeight="1">
       <x:c r="A170" s="26" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -5231,7 +5231,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C170" s="35" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D170" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5240,14 +5240,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F170" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.178</x:v>
       </x:c>
       <x:c r="G170" s="35" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="H170" s="35" t="str"/>
     </x:row>
-    <x:row r="171" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="171" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A171" s="26" t="n">
         <x:v>167</x:v>
       </x:c>
@@ -5255,7 +5255,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="35" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D171" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5264,22 +5264,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F171" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G171" s="35" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="H171" s="35" t="str"/>
     </x:row>
-    <x:row r="172" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A172" s="26" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C172" s="35" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D172" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5288,22 +5288,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F172" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G172" s="35" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="H172" s="35" t="str"/>
     </x:row>
-    <x:row r="173" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="173" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A173" s="26" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B173" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C173" s="35" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D173" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5315,11 +5315,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G173" s="35" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="H173" s="35" t="str"/>
     </x:row>
-    <x:row r="174" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="174" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A174" s="26" t="n">
         <x:v>170</x:v>
       </x:c>
@@ -5327,7 +5327,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C174" s="35" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D174" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5339,11 +5339,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G174" s="35" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="H174" s="35" t="str"/>
     </x:row>
-    <x:row r="175" ht="66" hidden="0" customHeight="1">
+    <x:row r="175" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A175" s="26" t="n">
         <x:v>171</x:v>
       </x:c>
@@ -5351,7 +5351,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C175" s="35" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D175" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5360,22 +5360,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F175" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G175" s="35" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="H175" s="35" t="str"/>
     </x:row>
-    <x:row r="176" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="176" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A176" s="26" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="35" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C176" s="35" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D176" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5387,19 +5387,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G176" s="35" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="H176" s="35" t="str"/>
     </x:row>
-    <x:row r="177" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="177" ht="66" hidden="0" customHeight="1">
       <x:c r="A177" s="26" t="n">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B177" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C177" s="35" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D177" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5408,10 +5408,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F177" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G177" s="35" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="H177" s="35" t="str"/>
     </x:row>
@@ -5420,10 +5420,10 @@
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C178" s="35" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D178" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5432,10 +5432,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F178" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G178" s="35" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="H178" s="35" t="str"/>
     </x:row>
@@ -5444,10 +5444,10 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5459,19 +5459,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G179" s="35" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="H179" s="35" t="str"/>
     </x:row>
-    <x:row r="180" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A180" s="26" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C180" s="35" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D180" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5480,14 +5480,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F180" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G180" s="35" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="H180" s="35" t="str"/>
     </x:row>
-    <x:row r="181" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="181" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A181" s="26" t="n">
         <x:v>177</x:v>
       </x:c>
@@ -5495,7 +5495,7 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C181" s="35" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D181" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5504,22 +5504,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F181" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G181" s="35" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="H181" s="35" t="str"/>
     </x:row>
-    <x:row r="182" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="182" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A182" s="26" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5531,7 +5531,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G182" s="35" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="H182" s="35" t="str"/>
     </x:row>
@@ -5540,10 +5540,10 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5552,14 +5552,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F183" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G183" s="35" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="H183" s="35" t="str"/>
     </x:row>
-    <x:row r="184" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="184" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A184" s="26" t="n">
         <x:v>180</x:v>
       </x:c>
@@ -5567,7 +5567,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C184" s="35" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D184" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5576,10 +5576,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F184" s="32" t="n">
-        <x:v>0.041</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G184" s="35" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="H184" s="35" t="str"/>
     </x:row>
@@ -5591,7 +5591,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C185" s="35" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D185" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5603,19 +5603,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G185" s="35" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="H185" s="35" t="str"/>
     </x:row>
-    <x:row r="186" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="186" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A186" s="26" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C186" s="35" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D186" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5624,22 +5624,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F186" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="G186" s="35" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="H186" s="35" t="str"/>
     </x:row>
-    <x:row r="187" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="187" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A187" s="26" t="n">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B187" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5651,19 +5651,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G187" s="35" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="H187" s="35" t="str"/>
     </x:row>
-    <x:row r="188" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="188" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A188" s="26" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="35" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C188" s="35" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D188" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5672,10 +5672,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F188" s="32" t="n">
-        <x:v>0.063</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G188" s="35" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="H188" s="35" t="str"/>
     </x:row>
@@ -5684,10 +5684,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B189" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5696,22 +5696,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F189" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G189" s="35" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H189" s="35" t="str"/>
     </x:row>
-    <x:row r="190" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="190" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A190" s="26" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B190" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C190" s="35" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D190" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5720,10 +5720,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F190" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.063</x:v>
       </x:c>
       <x:c r="G190" s="35" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="H190" s="35" t="str"/>
     </x:row>
@@ -5732,10 +5732,10 @@
         <x:v>187</x:v>
       </x:c>
       <x:c r="B191" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5744,22 +5744,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F191" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.035</x:v>
       </x:c>
       <x:c r="G191" s="35" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="H191" s="35" t="str"/>
     </x:row>
-    <x:row r="192" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="192" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A192" s="26" t="n">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B192" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C192" s="35" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D192" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5771,11 +5771,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G192" s="35" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="H192" s="35" t="str"/>
     </x:row>
-    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="193" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A193" s="26" t="n">
         <x:v>189</x:v>
       </x:c>
@@ -5783,7 +5783,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="35" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D193" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5792,14 +5792,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F193" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G193" s="35" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="H193" s="35" t="str"/>
     </x:row>
-    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="194" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A194" s="26" t="n">
         <x:v>190</x:v>
       </x:c>
@@ -5807,7 +5807,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5819,11 +5819,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G194" s="35" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="H194" s="35" t="str"/>
     </x:row>
-    <x:row r="195" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="195" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A195" s="26" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -5831,7 +5831,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5843,11 +5843,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G195" s="35" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="H195" s="35" t="str"/>
     </x:row>
-    <x:row r="196" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="196" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A196" s="26" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -5855,7 +5855,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5864,10 +5864,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F196" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G196" s="35" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="H196" s="35" t="str"/>
     </x:row>
@@ -5879,7 +5879,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5888,14 +5888,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F197" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G197" s="35" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="H197" s="35" t="str"/>
     </x:row>
-    <x:row r="198" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="198" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A198" s="26" t="n">
         <x:v>194</x:v>
       </x:c>
@@ -5903,7 +5903,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5915,11 +5915,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G198" s="35" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="H198" s="35" t="str"/>
     </x:row>
-    <x:row r="199" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="199" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A199" s="26" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -5927,7 +5927,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5936,14 +5936,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F199" s="32" t="n">
-        <x:v>0.011</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G199" s="35" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="H199" s="35" t="str"/>
     </x:row>
-    <x:row r="200" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="200" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A200" s="26" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -5951,7 +5951,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D200" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5960,14 +5960,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F200" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G200" s="35" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="H200" s="35" t="str"/>
     </x:row>
-    <x:row r="201" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="201" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A201" s="26" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -5975,7 +5975,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="35" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D201" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5984,10 +5984,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F201" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="G201" s="35" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="H201" s="35" t="str"/>
     </x:row>
@@ -5999,7 +5999,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="35" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D202" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6008,14 +6008,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F202" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G202" s="35" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="H202" s="35" t="str"/>
     </x:row>
-    <x:row r="203" ht="132" hidden="0" customHeight="1">
+    <x:row r="203" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A203" s="26" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -6023,7 +6023,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="35" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D203" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6032,14 +6032,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F203" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G203" s="35" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="H203" s="35" t="str"/>
     </x:row>
-    <x:row r="204" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="204" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A204" s="26" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -6047,7 +6047,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="35" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D204" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6059,11 +6059,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G204" s="35" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="H204" s="35" t="str"/>
     </x:row>
-    <x:row r="205" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="205" ht="132" hidden="0" customHeight="1">
       <x:c r="A205" s="26" t="n">
         <x:v>201</x:v>
       </x:c>
@@ -6071,7 +6071,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C205" s="35" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D205" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6080,14 +6080,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F205" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G205" s="35" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="H205" s="35" t="str"/>
     </x:row>
-    <x:row r="206" ht="132" hidden="0" customHeight="1">
+    <x:row r="206" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A206" s="26" t="n">
         <x:v>202</x:v>
       </x:c>
@@ -6095,7 +6095,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C206" s="35" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D206" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6107,11 +6107,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G206" s="35" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="H206" s="35" t="str"/>
     </x:row>
-    <x:row r="207" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="207" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A207" s="26" t="n">
         <x:v>203</x:v>
       </x:c>
@@ -6119,7 +6119,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C207" s="35" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D207" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6128,14 +6128,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F207" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G207" s="35" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="H207" s="35" t="str"/>
     </x:row>
-    <x:row r="208" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="208" ht="132" hidden="0" customHeight="1">
       <x:c r="A208" s="26" t="n">
         <x:v>204</x:v>
       </x:c>
@@ -6143,7 +6143,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C208" s="35" t="str">
-        <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D208" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6155,40 +6155,88 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G208" s="35" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="H208" s="35" t="str"/>
+    </x:row>
+    <x:row r="209" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A209" s="26" t="n">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B209" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C209" s="35" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D209" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E209" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F209" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G209" s="35" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="H209" s="35" t="str"/>
+    </x:row>
+    <x:row r="210" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A210" s="26" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B210" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C210" s="35" t="str">
+        <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
+      </x:c>
+      <x:c r="D210" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E210" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F210" s="32" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="G210" s="35" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="H208" s="35" t="str"/>
-    </x:row>
-    <x:row r="209" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A209" s="27" t="n">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="B209" s="36" t="str">
+      <x:c r="H210" s="35" t="str"/>
+    </x:row>
+    <x:row r="211" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A211" s="27" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B211" s="36" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C209" s="36" t="str">
+      <x:c r="C211" s="36" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D209" s="36" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E209" s="27" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F209" s="33" t="n">
-        <x:v>0.004</x:v>
-      </x:c>
-      <x:c r="G209" s="36" t="str">
+      <x:c r="D211" s="36" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E211" s="27" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F211" s="33" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="G211" s="36" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="H209" s="36" t="str"/>
+      <x:c r="H211" s="36" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E5:E209">
+  <x:conditionalFormatting sqref="E5:E211">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="错误"/>
@@ -6196,7 +6244,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R886a297fc97f42ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6b8e2df80094ecd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6303,7 +6351,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I5" s="54" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J5" s="57" t="str">
         <x:v>已登记</x:v>
@@ -6335,7 +6383,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I6" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J6" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6367,7 +6415,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I7" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J7" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6399,7 +6447,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I8" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J8" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6431,7 +6479,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I9" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J9" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6463,7 +6511,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I10" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="J10" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6495,7 +6543,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I11" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J11" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6527,7 +6575,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I12" s="55" t="n">
-        <x:v>0.185</x:v>
+        <x:v>0.141</x:v>
       </x:c>
       <x:c r="J12" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6559,7 +6607,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I13" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J13" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6591,7 +6639,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I14" s="55" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J14" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6623,7 +6671,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I15" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6655,7 +6703,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I16" s="55" t="n">
-        <x:v>0.031</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="J16" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6687,7 +6735,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I17" s="55" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J17" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6719,7 +6767,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I18" s="55" t="n">
-        <x:v>0.065</x:v>
+        <x:v>0.02</x:v>
       </x:c>
       <x:c r="J18" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6751,7 +6799,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I19" s="55" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J19" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6783,7 +6831,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I20" s="55" t="n">
-        <x:v>0.037</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="J20" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6815,7 +6863,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I21" s="55" t="n">
-        <x:v>0.124</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="J21" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6847,7 +6895,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I22" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J22" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6879,7 +6927,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I23" s="55" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J23" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6943,7 +6991,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I25" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J25" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7007,7 +7055,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I27" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J27" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7039,7 +7087,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I28" s="55" t="n">
-        <x:v>0.094</x:v>
+        <x:v>0.074</x:v>
       </x:c>
       <x:c r="J28" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7071,7 +7119,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I29" s="55" t="n">
-        <x:v>0.067</x:v>
+        <x:v>0.087</x:v>
       </x:c>
       <x:c r="J29" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7103,7 +7151,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I30" s="55" t="n">
-        <x:v>0.066</x:v>
+        <x:v>0.091</x:v>
       </x:c>
       <x:c r="J30" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7231,7 +7279,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I34" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J34" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7263,7 +7311,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I35" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J35" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7327,7 +7375,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I37" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J37" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7423,7 +7471,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I40" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J40" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7455,7 +7503,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I41" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J41" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7551,7 +7599,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I44" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J44" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7615,7 +7663,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I46" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J46" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7647,7 +7695,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I47" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J47" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7775,7 +7823,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I51" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J51" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7807,7 +7855,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I52" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J52" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7839,7 +7887,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I53" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J53" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7935,7 +7983,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I56" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J56" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7967,7 +8015,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I57" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J57" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7999,7 +8047,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I58" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J58" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8031,7 +8079,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I59" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J59" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8063,7 +8111,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I60" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J60" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8095,7 +8143,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I61" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J61" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8127,7 +8175,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I62" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J62" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8159,7 +8207,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I63" s="55" t="n">
-        <x:v>0.099</x:v>
+        <x:v>0.074</x:v>
       </x:c>
       <x:c r="J63" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8191,7 +8239,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I64" s="55" t="n">
-        <x:v>0.043</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J64" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8255,7 +8303,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I66" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J66" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8287,7 +8335,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I67" s="55" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.031</x:v>
       </x:c>
       <x:c r="J67" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8319,173 +8367,173 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I68" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J68" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="69" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A69" s="42" t="n">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B69" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_cache_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense.py</x:v>
       </x:c>
       <x:c r="C69" s="49" t="str">
-        <x:v>test_dense_cache_comparison_requires_same_quality_and_faster_warm_build</x:v>
+        <x:v>test_dense_warmup_is_fixed_and_excluded_from_formal_timing</x:v>
       </x:c>
       <x:c r="D69" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E69" s="49" t="str">
-        <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
+        <x:v>验证 Dense 正式评测前执行固定次数的查询预热，并将预热延迟与正式查询指标明确隔离。</x:v>
       </x:c>
       <x:c r="F69" s="49" t="str">
-        <x:v>缓存被确认只改变启动成本，不改变 Recall、MRR、nDCG 或生产开关。</x:v>
+        <x:v>预热执行两次、逐次记录耗时，且报告明确标记不计入正式计时。</x:v>
       </x:c>
       <x:c r="G69" s="49" t="str">
-        <x:v>缓存可能悄悄改变排序结果，或速度收益不足却被错误判定为可用。</x:v>
+        <x:v>ONNX 首次推理初始化可能混入测试集延迟，制造虚假的性能波动。</x:v>
       </x:c>
       <x:c r="H69" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I69" s="55" t="n">
-        <x:v>0.071</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J69" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="211.1999969482422" hidden="0" customHeight="1">
+    <x:row r="70" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A70" s="42" t="n">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B70" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense_cache_compare.py</x:v>
       </x:c>
       <x:c r="C70" s="49" t="str">
-        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
+        <x:v>test_dense_cache_comparison_requires_same_quality_and_faster_warm_build</x:v>
       </x:c>
       <x:c r="D70" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E70" s="49" t="str">
-        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
+        <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
       </x:c>
       <x:c r="F70" s="49" t="str">
-        <x:v>保留集 Recall@5 提升 20 个百分点且 nDCG 为正，但存在 3 个逐题回归，超过最多 2 个的门槛，因此候选晋升和生产默认均保持关闭。</x:v>
+        <x:v>缓存被确认只改变启动成本，不改变 Recall、MRR、nDCG 或生产开关。</x:v>
       </x:c>
       <x:c r="G70" s="49" t="str">
-        <x:v>系统可能再次依据开发集拟合晋升，或未经重复验证就直接改动生产检索路径。</x:v>
+        <x:v>缓存可能悄悄改变排序结果，或速度收益不足却被错误判定为可用。</x:v>
       </x:c>
       <x:c r="H70" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I70" s="55" t="n">
-        <x:v>32.041</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="J70" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="71" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A71" s="42" t="n">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B71" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_model_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense_compare.py</x:v>
       </x:c>
       <x:c r="C71" s="49" t="str">
-        <x:v>test_dense_model_comparison_prefers_quality_gain_without_excess_regression</x:v>
+        <x:v>test_dense_comparison_uses_holdout_quality_and_keeps_production_off</x:v>
       </x:c>
       <x:c r="D71" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E71" s="49" t="str">
-        <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
+        <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
       </x:c>
       <x:c r="F71" s="49" t="str">
-        <x:v>模型候选可以晋升，但生产默认开关仍独立保持关闭。</x:v>
+        <x:v>保留集 Recall@5 提升 20 个百分点且 nDCG 为正，但存在 3 个逐题回归，超过最多 2 个的门槛，因此候选晋升和生产默认均保持关闭。</x:v>
       </x:c>
       <x:c r="G71" s="49" t="str">
-        <x:v>只看平均指标或速度可能掩盖逐题回归，或者把模型候选误当成生产上线。</x:v>
+        <x:v>系统可能再次依据开发集拟合晋升，或未经重复验证就直接改动生产检索路径。</x:v>
       </x:c>
       <x:c r="H71" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I71" s="55" t="n">
-        <x:v>0.039</x:v>
+        <x:v>31.084</x:v>
       </x:c>
       <x:c r="J71" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="72" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A72" s="42" t="n">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B72" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_models.py</x:v>
+        <x:v>tests/test_local_rag_dense_model_compare.py</x:v>
       </x:c>
       <x:c r="C72" s="49" t="str">
-        <x:v>test_dense_model_matrix_changes_only_declared_embedding_properties</x:v>
+        <x:v>test_dense_model_comparison_prefers_quality_gain_without_excess_regression</x:v>
       </x:c>
       <x:c r="D72" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E72" s="49" t="str">
-        <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
+        <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
       </x:c>
       <x:c r="F72" s="49" t="str">
-        <x:v>MiniLM 与 MPNet 共用语料、Chunker、相似度、缓存和指标逻辑，未知模型被拒绝。</x:v>
+        <x:v>模型候选可以晋升，但生产默认开关仍独立保持关闭。</x:v>
       </x:c>
       <x:c r="G72" s="49" t="str">
-        <x:v>复制评测代码或接受任意模型可能引入口径漂移，使模型质量对比失去单变量意义。</x:v>
+        <x:v>只看平均指标或速度可能掩盖逐题回归，或者把模型候选误当成生产上线。</x:v>
       </x:c>
       <x:c r="H72" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I72" s="55" t="n">
-        <x:v>0.908</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="J72" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="198" hidden="0" customHeight="1">
+    <x:row r="73" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A73" s="42" t="n">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B73" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_stability.py</x:v>
+        <x:v>tests/test_local_rag_dense_models.py</x:v>
       </x:c>
       <x:c r="C73" s="49" t="str">
-        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
+        <x:v>test_dense_model_matrix_changes_only_declared_embedding_properties</x:v>
       </x:c>
       <x:c r="D73" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E73" s="49" t="str">
-        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
+        <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
       </x:c>
       <x:c r="F73" s="49" t="str">
-        <x:v>三个运行的检索结果完全一致，查询延迟变异系数不超过 50%，但生产开关仍保持关闭。</x:v>
+        <x:v>MiniLM 与 MPNet 共用语料、Chunker、相似度、缓存和指标逻辑，未知模型被拒绝。</x:v>
       </x:c>
       <x:c r="G73" s="49" t="str">
-        <x:v>单次偶然结果或不稳定排名可能被错误当成可复现能力，导致后续模型对照失去公平基线。</x:v>
+        <x:v>复制评测代码或接受任意模型可能引入口径漂移，使模型质量对比失去单变量意义。</x:v>
       </x:c>
       <x:c r="H73" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I73" s="55" t="n">
-        <x:v>0.048</x:v>
+        <x:v>0.774</x:v>
       </x:c>
       <x:c r="J73" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="74" ht="198" hidden="0" customHeight="1">
       <x:c r="A74" s="42" t="n">
         <x:v>70</x:v>
       </x:c>
@@ -8493,127 +8541,127 @@
         <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C74" s="49" t="str">
-        <x:v>test_dense_stability_rejects_mixed_or_unexpected_models</x:v>
+        <x:v>test_dense_stability_requires_three_deterministic_warm_processes</x:v>
       </x:c>
       <x:c r="D74" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E74" s="49" t="str">
-        <x:v>验证稳定性评测拒绝混入其他 Embedding 模型或不符合预期模型身份的运行文件。</x:v>
+        <x:v>验证 Dense 稳定性晋升至少需要三个独立热启动进程，并同时满足缓存命中、质量一致、Top-5 与分数确定性和延迟波动门槛。</x:v>
       </x:c>
       <x:c r="F74" s="49" t="str">
-        <x:v>只有全部运行来自同一指定模型时，稳定性才可能通过。</x:v>
+        <x:v>三个运行的检索结果完全一致，查询延迟变异系数不超过 50%，但生产开关仍保持关闭。</x:v>
       </x:c>
       <x:c r="G74" s="49" t="str">
-        <x:v>MiniLM 与 MPNet 结果误混可能制造虚假的稳定性结论或错误的耗时统计。</x:v>
+        <x:v>单次偶然结果或不稳定排名可能被错误当成可复现能力，导致后续模型对照失去公平基线。</x:v>
       </x:c>
       <x:c r="H74" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I74" s="55" t="n">
-        <x:v>0.026</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="J74" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="171.60000610351562" hidden="0" customHeight="1">
+    <x:row r="75" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A75" s="42" t="n">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B75" s="49" t="str">
-        <x:v>tests/test_local_rag_dense_stability_compare.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability.py</x:v>
       </x:c>
       <x:c r="C75" s="49" t="str">
-        <x:v>test_stability_comparison_preserves_failed_candidate_decision</x:v>
+        <x:v>test_dense_stability_rejects_mixed_or_unexpected_models</x:v>
       </x:c>
       <x:c r="D75" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E75" s="49" t="str">
-        <x:v>验证 MiniLM/MPNet 稳定性并列比较保留 MPNet 的失败判定，不因平均质量收益或模型间比值覆盖原始闸门。</x:v>
+        <x:v>验证稳定性评测拒绝混入其他 Embedding 模型或不符合预期模型身份的运行文件。</x:v>
       </x:c>
       <x:c r="F75" s="49" t="str">
-        <x:v>报告展示性能倍数，但 MPNet CV 超限时仍保持稳定性未通过和生产关闭。</x:v>
+        <x:v>只有全部运行来自同一指定模型时，稳定性才可能通过。</x:v>
       </x:c>
       <x:c r="G75" s="49" t="str">
-        <x:v>跨模型汇总可能错误抹平单模型波动，使失败候选绕过稳定性门槛。</x:v>
+        <x:v>MiniLM 与 MPNet 结果误混可能制造虚假的稳定性结论或错误的耗时统计。</x:v>
       </x:c>
       <x:c r="H75" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I75" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="J75" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="76" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A76" s="42" t="n">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B76" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_stability_compare.py</x:v>
       </x:c>
       <x:c r="C76" s="49" t="str">
-        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
+        <x:v>test_stability_comparison_preserves_failed_candidate_decision</x:v>
       </x:c>
       <x:c r="D76" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E76" s="49" t="str">
-        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
+        <x:v>验证 MiniLM/MPNet 稳定性并列比较保留 MPNet 的失败判定，不因平均质量收益或模型间比值覆盖原始闸门。</x:v>
       </x:c>
       <x:c r="F76" s="49" t="str">
-        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
+        <x:v>报告展示性能倍数，但 MPNet CV 超限时仍保持稳定性未通过和生产关闭。</x:v>
       </x:c>
       <x:c r="G76" s="49" t="str">
-        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
+        <x:v>跨模型汇总可能错误抹平单模型波动，使失败候选绕过稳定性门槛。</x:v>
       </x:c>
       <x:c r="H76" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I76" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="J76" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="77" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A77" s="42" t="n">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B77" s="49" t="str">
-        <x:v>tests/test_local_rag_foundation.py</x:v>
+        <x:v>tests/test_local_rag_dense_warmup_compare.py</x:v>
       </x:c>
       <x:c r="C77" s="49" t="str">
-        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
+        <x:v>test_warmup_comparison_requires_failed_before_and_passed_after</x:v>
       </x:c>
       <x:c r="D77" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E77" s="49" t="str">
-        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
+        <x:v>验证预热对照只在同一模型由预热前失败转为预热后通过时，才判断首次初始化解释了稳定性问题。</x:v>
       </x:c>
       <x:c r="F77" s="49" t="str">
-        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
+        <x:v>报告正确计算均值和 CV 变化，并将下一步推进到 Hybrid 互补实验。</x:v>
       </x:c>
       <x:c r="G77" s="49" t="str">
-        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
+        <x:v>仅凭一次更快结果可能错误归因预热效果，或绕过稳定性门槛。</x:v>
       </x:c>
       <x:c r="H77" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I77" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J77" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="78" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A78" s="42" t="n">
         <x:v>74</x:v>
       </x:c>
@@ -8621,31 +8669,31 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C78" s="49" t="str">
-        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
+        <x:v>test_fixed_window_chunker_preserves_page_and_overlap</x:v>
       </x:c>
       <x:c r="D78" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E78" s="49" t="str">
-        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
+        <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
       </x:c>
       <x:c r="F78" s="49" t="str">
-        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
+        <x:v>分块文本和 char_start 正确，所有片段仍定位到原 PDF 页。</x:v>
       </x:c>
       <x:c r="G78" s="49" t="str">
-        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
+        <x:v>全文检索结果可能无法回溯页码，或分块边界丢失上下文。</x:v>
       </x:c>
       <x:c r="H78" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I78" s="55" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J78" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="79" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A79" s="42" t="n">
         <x:v>75</x:v>
       </x:c>
@@ -8653,25 +8701,25 @@
         <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C79" s="49" t="str">
-        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
+        <x:v>test_fixed_window_chunker_rejects_invalid_parameters</x:v>
       </x:c>
       <x:c r="D79" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E79" s="49" t="str">
-        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
+        <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
       </x:c>
       <x:c r="F79" s="49" t="str">
-        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
+        <x:v>非法参数触发 ValueError，避免零步长或无限循环。</x:v>
       </x:c>
       <x:c r="G79" s="49" t="str">
-        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
+        <x:v>错误 Chunk 配置可能造成挂起、重复片段或不可控索引体积。</x:v>
       </x:c>
       <x:c r="H79" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I79" s="55" t="n">
-        <x:v>0.034</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J79" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8682,162 +8730,162 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B80" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C80" s="49" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_manifest_rebuilds_only_for_content_or_processing_version_change</x:v>
       </x:c>
       <x:c r="D80" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E80" s="49" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
       </x:c>
       <x:c r="F80" s="49" t="str">
-        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
+        <x:v>相同哈希与版本跳过，内容或处理版本变化触发 rebuild。</x:v>
       </x:c>
       <x:c r="G80" s="49" t="str">
-        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
+        <x:v>每次更新可能全库重建，或变化论文没有刷新造成旧证据。</x:v>
       </x:c>
       <x:c r="H80" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I80" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.019</x:v>
       </x:c>
       <x:c r="J80" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="81" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A81" s="42" t="n">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B81" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_foundation.py</x:v>
       </x:c>
       <x:c r="C81" s="49" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_manifest_writer_keeps_corpus_version_and_status</x:v>
       </x:c>
       <x:c r="D81" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E81" s="49" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="F81" s="49" t="str">
-        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
+        <x:v>JSON 清单可读，版本和 pending 状态完整保存。</x:v>
       </x:c>
       <x:c r="G81" s="49" t="str">
-        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
+        <x:v>知识库更新可能失去语料版本与处理进度，无法复现实验。</x:v>
       </x:c>
       <x:c r="H81" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I81" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.035</x:v>
       </x:c>
       <x:c r="J81" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="132" hidden="0" customHeight="1">
+    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A82" s="42" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="49" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C82" s="49" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D82" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E82" s="49" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="F82" s="49" t="str">
-        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
+        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
       </x:c>
       <x:c r="G82" s="49" t="str">
-        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
+        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
       </x:c>
       <x:c r="H82" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I82" s="55" t="n">
-        <x:v>30.915</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J82" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="132" hidden="0" customHeight="1">
+    <x:row r="83" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A83" s="42" t="n">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C83" s="49" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D83" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E83" s="49" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="F83" s="49" t="str">
-        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
+        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
       </x:c>
       <x:c r="G83" s="49" t="str">
-        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
+        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
       </x:c>
       <x:c r="H83" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I83" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J83" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="84" ht="132" hidden="0" customHeight="1">
       <x:c r="A84" s="42" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C84" s="49" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D84" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E84" s="49" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="F84" s="49" t="str">
-        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
+        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
       </x:c>
       <x:c r="G84" s="49" t="str">
-        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
+        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
       </x:c>
       <x:c r="H84" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I84" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>30.792</x:v>
       </x:c>
       <x:c r="J84" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="85" ht="132" hidden="0" customHeight="1">
       <x:c r="A85" s="42" t="n">
         <x:v>81</x:v>
       </x:c>
@@ -8845,57 +8893,57 @@
         <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C85" s="49" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D85" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E85" s="49" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="F85" s="49" t="str">
-        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
+        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
       </x:c>
       <x:c r="G85" s="49" t="str">
-        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
+        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
       </x:c>
       <x:c r="H85" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I85" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J85" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="86" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A86" s="42" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C86" s="49" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D86" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E86" s="49" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="F86" s="49" t="str">
-        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
+        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
       </x:c>
       <x:c r="G86" s="49" t="str">
-        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
+        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
       </x:c>
       <x:c r="H86" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I86" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J86" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8906,28 +8954,28 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C87" s="49" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D87" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E87" s="49" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="F87" s="49" t="str">
-        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
+        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
       </x:c>
       <x:c r="G87" s="49" t="str">
-        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
+        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
       </x:c>
       <x:c r="H87" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I87" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J87" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8941,31 +8989,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C88" s="49" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D88" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E88" s="49" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="F88" s="49" t="str">
-        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
+        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
       </x:c>
       <x:c r="G88" s="49" t="str">
-        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
+        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
       </x:c>
       <x:c r="H88" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I88" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J88" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="89" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A89" s="42" t="n">
         <x:v>85</x:v>
       </x:c>
@@ -8973,31 +9021,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C89" s="49" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D89" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E89" s="49" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="F89" s="49" t="str">
-        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
+        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
       </x:c>
       <x:c r="G89" s="49" t="str">
-        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
+        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
       </x:c>
       <x:c r="H89" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I89" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J89" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" ht="132" hidden="0" customHeight="1">
+    <x:row r="90" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A90" s="42" t="n">
         <x:v>86</x:v>
       </x:c>
@@ -9005,31 +9053,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C90" s="49" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D90" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E90" s="49" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="F90" s="49" t="str">
-        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
+        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
       </x:c>
       <x:c r="G90" s="49" t="str">
-        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
+        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
       </x:c>
       <x:c r="H90" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I90" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J90" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="91" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A91" s="42" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -9037,31 +9085,31 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C91" s="49" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D91" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E91" s="49" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="F91" s="49" t="str">
-        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
+        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
       </x:c>
       <x:c r="G91" s="49" t="str">
-        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
+        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
       </x:c>
       <x:c r="H91" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I91" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J91" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="92" ht="132" hidden="0" customHeight="1">
       <x:c r="A92" s="42" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -9069,95 +9117,95 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C92" s="49" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D92" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E92" s="49" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="F92" s="49" t="str">
-        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
+        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
       </x:c>
       <x:c r="G92" s="49" t="str">
-        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
+        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
       </x:c>
       <x:c r="H92" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I92" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J92" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="93" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A93" s="42" t="n">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B93" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C93" s="49" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D93" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E93" s="49" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="F93" s="49" t="str">
-        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
+        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
       </x:c>
       <x:c r="G93" s="49" t="str">
-        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
+        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
       </x:c>
       <x:c r="H93" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I93" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J93" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="132" hidden="0" customHeight="1">
+    <x:row r="94" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A94" s="42" t="n">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B94" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C94" s="49" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D94" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E94" s="49" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="F94" s="49" t="str">
-        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
+        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
       </x:c>
       <x:c r="G94" s="49" t="str">
-        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
+        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
       </x:c>
       <x:c r="H94" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I94" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J94" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="132" hidden="0" customHeight="1">
+    <x:row r="95" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A95" s="42" t="n">
         <x:v>91</x:v>
       </x:c>
@@ -9165,31 +9213,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C95" s="49" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D95" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E95" s="49" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="F95" s="49" t="str">
-        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
+        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
       </x:c>
       <x:c r="G95" s="49" t="str">
-        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
+        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
       </x:c>
       <x:c r="H95" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I95" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J95" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="96" ht="132" hidden="0" customHeight="1">
       <x:c r="A96" s="42" t="n">
         <x:v>92</x:v>
       </x:c>
@@ -9197,31 +9245,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C96" s="49" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D96" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E96" s="49" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="F96" s="49" t="str">
-        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
+        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
       </x:c>
       <x:c r="G96" s="49" t="str">
-        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
+        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
       </x:c>
       <x:c r="H96" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I96" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J96" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="97" ht="132" hidden="0" customHeight="1">
       <x:c r="A97" s="42" t="n">
         <x:v>93</x:v>
       </x:c>
@@ -9229,19 +9277,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C97" s="49" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D97" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E97" s="49" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="F97" s="49" t="str">
-        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
+        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
       </x:c>
       <x:c r="G97" s="49" t="str">
-        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
+        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
       </x:c>
       <x:c r="H97" s="52" t="str">
         <x:v>通过</x:v>
@@ -9261,25 +9309,25 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C98" s="49" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D98" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E98" s="49" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="F98" s="49" t="str">
-        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
+        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
       </x:c>
       <x:c r="G98" s="49" t="str">
-        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
+        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
       </x:c>
       <x:c r="H98" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I98" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J98" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9293,19 +9341,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C99" s="49" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D99" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E99" s="49" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="F99" s="49" t="str">
-        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
+        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
       </x:c>
       <x:c r="G99" s="49" t="str">
-        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
+        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
       </x:c>
       <x:c r="H99" s="52" t="str">
         <x:v>通过</x:v>
@@ -9317,103 +9365,103 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="100" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A100" s="42" t="n">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="49" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C100" s="49" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D100" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E100" s="49" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="F100" s="49" t="str">
-        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
+        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
       </x:c>
       <x:c r="G100" s="49" t="str">
-        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
+        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
       </x:c>
       <x:c r="H100" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I100" s="55" t="n">
-        <x:v>2.357</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J100" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="101" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A101" s="42" t="n">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C101" s="49" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D101" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E101" s="49" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="F101" s="49" t="str">
-        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
+        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
       </x:c>
       <x:c r="G101" s="49" t="str">
-        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
+        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
       </x:c>
       <x:c r="H101" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I101" s="55" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J101" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="102" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A102" s="42" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C102" s="49" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D102" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E102" s="49" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="F102" s="49" t="str">
-        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
+        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
       </x:c>
       <x:c r="G102" s="49" t="str">
-        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
+        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
       </x:c>
       <x:c r="H102" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I102" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>2.35</x:v>
       </x:c>
       <x:c r="J102" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="103" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A103" s="42" t="n">
         <x:v>99</x:v>
       </x:c>
@@ -9421,25 +9469,25 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C103" s="49" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D103" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E103" s="49" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="F103" s="49" t="str">
-        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
+        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
       </x:c>
       <x:c r="G103" s="49" t="str">
-        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
+        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
       </x:c>
       <x:c r="H103" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I103" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.039</x:v>
       </x:c>
       <x:c r="J103" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9453,95 +9501,95 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C104" s="49" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D104" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E104" s="49" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="F104" s="49" t="str">
-        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
+        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
       </x:c>
       <x:c r="G104" s="49" t="str">
-        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
+        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
       </x:c>
       <x:c r="H104" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I104" s="55" t="n">
-        <x:v>1.156</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J104" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="105" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A105" s="42" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C105" s="49" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D105" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E105" s="49" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="F105" s="49" t="str">
-        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
+        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
       </x:c>
       <x:c r="G105" s="49" t="str">
-        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
+        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
       </x:c>
       <x:c r="H105" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I105" s="55" t="n">
-        <x:v>0.189</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J105" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="106" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A106" s="42" t="n">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B106" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C106" s="49" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D106" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E106" s="49" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="F106" s="49" t="str">
-        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
+        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
       </x:c>
       <x:c r="G106" s="49" t="str">
-        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
+        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
       </x:c>
       <x:c r="H106" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I106" s="55" t="n">
-        <x:v>0.085</x:v>
+        <x:v>1.131</x:v>
       </x:c>
       <x:c r="J106" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="107" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A107" s="42" t="n">
         <x:v>103</x:v>
       </x:c>
@@ -9549,25 +9597,25 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C107" s="49" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D107" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E107" s="49" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="F107" s="49" t="str">
-        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
+        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
       </x:c>
       <x:c r="G107" s="49" t="str">
-        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
+        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
       </x:c>
       <x:c r="H107" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I107" s="55" t="n">
-        <x:v>0.04</x:v>
+        <x:v>0.171</x:v>
       </x:c>
       <x:c r="J107" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9581,115 +9629,115 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C108" s="49" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D108" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E108" s="49" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="F108" s="49" t="str">
-        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
+        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
       </x:c>
       <x:c r="G108" s="49" t="str">
-        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
+        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
       </x:c>
       <x:c r="H108" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I108" s="55" t="n">
-        <x:v>0.097</x:v>
+        <x:v>0.092</x:v>
       </x:c>
       <x:c r="J108" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="132" hidden="0" customHeight="1">
+    <x:row r="109" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A109" s="42" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="49" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C109" s="49" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D109" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E109" s="49" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="F109" s="49" t="str">
-        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
+        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
       </x:c>
       <x:c r="G109" s="49" t="str">
-        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
+        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
       </x:c>
       <x:c r="H109" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I109" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.047</x:v>
       </x:c>
       <x:c r="J109" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="110" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A110" s="42" t="n">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B110" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C110" s="49" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D110" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E110" s="49" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="F110" s="49" t="str">
-        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
+        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
       </x:c>
       <x:c r="G110" s="49" t="str">
-        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
+        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
       </x:c>
       <x:c r="H110" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I110" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.076</x:v>
       </x:c>
       <x:c r="J110" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="111" ht="132" hidden="0" customHeight="1">
       <x:c r="A111" s="42" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B111" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C111" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D111" s="49" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E111" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="F111" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
       </x:c>
       <x:c r="G111" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
       </x:c>
       <x:c r="H111" s="52" t="str">
         <x:v>通过</x:v>
@@ -9701,7 +9749,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="112" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A112" s="42" t="n">
         <x:v>108</x:v>
       </x:c>
@@ -9709,25 +9757,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C112" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D112" s="49" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E112" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="F112" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
       </x:c>
       <x:c r="G112" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
       </x:c>
       <x:c r="H112" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I112" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J112" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9741,10 +9789,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C113" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D113" s="49" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E113" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9773,10 +9821,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C114" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D114" s="49" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E114" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9791,7 +9839,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I114" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J114" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9805,10 +9853,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D115" s="49" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E115" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9823,13 +9871,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I115" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J115" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="116" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A116" s="42" t="n">
         <x:v>112</x:v>
       </x:c>
@@ -9837,25 +9885,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D116" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E116" s="49" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F116" s="49" t="str">
-        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G116" s="49" t="str">
-        <x:v>查询改写异常可能导致完全不检索。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H116" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I116" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J116" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9869,31 +9917,31 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D117" s="49" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E117" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F117" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G117" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H117" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I117" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J117" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="118" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A118" s="42" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -9901,19 +9949,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D118" s="49" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E118" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="F118" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
       </x:c>
       <x:c r="G118" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>查询改写异常可能导致完全不检索。</x:v>
       </x:c>
       <x:c r="H118" s="52" t="str">
         <x:v>通过</x:v>
@@ -9933,10 +9981,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D119" s="49" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E119" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9951,7 +9999,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I119" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J119" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9965,10 +10013,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D120" s="49" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E120" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -9983,7 +10031,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I120" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J120" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9997,10 +10045,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D121" s="49" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E121" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -10029,10 +10077,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D122" s="49" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E122" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -10047,13 +10095,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I122" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J122" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="123" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A123" s="42" t="n">
         <x:v>119</x:v>
       </x:c>
@@ -10061,25 +10109,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C123" s="49" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D123" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E123" s="49" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F123" s="49" t="str">
-        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G123" s="49" t="str">
-        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H123" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I123" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J123" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10093,19 +10141,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C124" s="49" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D124" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E124" s="49" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F124" s="49" t="str">
-        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G124" s="49" t="str">
-        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H124" s="52" t="str">
         <x:v>通过</x:v>
@@ -10117,33 +10165,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="125" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A125" s="42" t="n">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B125" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C125" s="49" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D125" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E125" s="49" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="F125" s="49" t="str">
-        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
+        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
       </x:c>
       <x:c r="G125" s="49" t="str">
-        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
+        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
       </x:c>
       <x:c r="H125" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I125" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J125" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10154,34 +10202,34 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B126" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C126" s="49" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D126" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E126" s="49" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="F126" s="49" t="str">
-        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
+        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
       </x:c>
       <x:c r="G126" s="49" t="str">
-        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
+        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
       </x:c>
       <x:c r="H126" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I126" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J126" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="132" hidden="0" customHeight="1">
+    <x:row r="127" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A127" s="42" t="n">
         <x:v>123</x:v>
       </x:c>
@@ -10189,19 +10237,19 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C127" s="49" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D127" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E127" s="49" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="F127" s="49" t="str">
-        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
+        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
       </x:c>
       <x:c r="G127" s="49" t="str">
-        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
+        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
       </x:c>
       <x:c r="H127" s="52" t="str">
         <x:v>通过</x:v>
@@ -10213,7 +10261,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="128" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A128" s="42" t="n">
         <x:v>124</x:v>
       </x:c>
@@ -10221,25 +10269,25 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C128" s="49" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D128" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E128" s="49" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="F128" s="49" t="str">
-        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
+        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
       </x:c>
       <x:c r="G128" s="49" t="str">
-        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
+        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
       </x:c>
       <x:c r="H128" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I128" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J128" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10250,66 +10298,66 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C129" s="49" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D129" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E129" s="49" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="F129" s="49" t="str">
-        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
+        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
       </x:c>
       <x:c r="G129" s="49" t="str">
-        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
+        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
       </x:c>
       <x:c r="H129" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I129" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J129" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="130" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A130" s="42" t="n">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B130" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C130" s="49" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D130" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E130" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="F130" s="49" t="str">
-        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
+        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
       </x:c>
       <x:c r="G130" s="49" t="str">
-        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
+        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
       </x:c>
       <x:c r="H130" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I130" s="55" t="n">
-        <x:v>14.665</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J130" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="131" ht="132" hidden="0" customHeight="1">
       <x:c r="A131" s="42" t="n">
         <x:v>127</x:v>
       </x:c>
@@ -10317,95 +10365,95 @@
         <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C131" s="49" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D131" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E131" s="49" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="F131" s="49" t="str">
-        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
+        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
       </x:c>
       <x:c r="G131" s="49" t="str">
-        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
+        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
       </x:c>
       <x:c r="H131" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I131" s="55" t="n">
-        <x:v>15.135</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J131" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="132" hidden="0" customHeight="1">
+    <x:row r="132" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A132" s="42" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C132" s="49" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D132" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E132" s="49" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="F132" s="49" t="str">
-        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
+        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
       </x:c>
       <x:c r="G132" s="49" t="str">
-        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
+        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
       </x:c>
       <x:c r="H132" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I132" s="55" t="n">
-        <x:v>0.005</x:v>
+        <x:v>14.691</x:v>
       </x:c>
       <x:c r="J132" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="133" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A133" s="42" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C133" s="49" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D133" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E133" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="F133" s="49" t="str">
-        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
+        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
       </x:c>
       <x:c r="G133" s="49" t="str">
-        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
+        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
       </x:c>
       <x:c r="H133" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I133" s="55" t="n">
-        <x:v>18.548</x:v>
+        <x:v>26.027</x:v>
       </x:c>
       <x:c r="J133" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="134" ht="132" hidden="0" customHeight="1">
       <x:c r="A134" s="42" t="n">
         <x:v>130</x:v>
       </x:c>
@@ -10413,57 +10461,57 @@
         <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C134" s="49" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D134" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E134" s="49" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="F134" s="49" t="str">
-        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
+        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
       </x:c>
       <x:c r="G134" s="49" t="str">
-        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
+        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
       </x:c>
       <x:c r="H134" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I134" s="55" t="n">
-        <x:v>15.261</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J134" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="135" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A135" s="42" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B135" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C135" s="49" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D135" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E135" s="49" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="F135" s="49" t="str">
-        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
+        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
       </x:c>
       <x:c r="G135" s="49" t="str">
-        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
+        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
       </x:c>
       <x:c r="H135" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I135" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>18.907</x:v>
       </x:c>
       <x:c r="J135" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10474,34 +10522,34 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B136" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C136" s="49" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D136" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E136" s="49" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="F136" s="49" t="str">
-        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
+        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
       </x:c>
       <x:c r="G136" s="49" t="str">
-        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
+        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
       </x:c>
       <x:c r="H136" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I136" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>14.794</x:v>
       </x:c>
       <x:c r="J136" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="137" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A137" s="42" t="n">
         <x:v>133</x:v>
       </x:c>
@@ -10509,31 +10557,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C137" s="49" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D137" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E137" s="49" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="F137" s="49" t="str">
-        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
+        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
       </x:c>
       <x:c r="G137" s="49" t="str">
-        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
+        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
       </x:c>
       <x:c r="H137" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I137" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J137" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="138" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A138" s="42" t="n">
         <x:v>134</x:v>
       </x:c>
@@ -10541,19 +10589,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C138" s="49" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D138" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E138" s="49" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="F138" s="49" t="str">
-        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
+        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
       </x:c>
       <x:c r="G138" s="49" t="str">
-        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
+        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
       </x:c>
       <x:c r="H138" s="52" t="str">
         <x:v>通过</x:v>
@@ -10573,19 +10621,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C139" s="49" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D139" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E139" s="49" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="F139" s="49" t="str">
-        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
+        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
       </x:c>
       <x:c r="G139" s="49" t="str">
-        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
+        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
       </x:c>
       <x:c r="H139" s="52" t="str">
         <x:v>通过</x:v>
@@ -10597,7 +10645,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A140" s="42" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -10605,19 +10653,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="49" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D140" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E140" s="49" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="F140" s="49" t="str">
-        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
+        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
       </x:c>
       <x:c r="G140" s="49" t="str">
-        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
+        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
       </x:c>
       <x:c r="H140" s="52" t="str">
         <x:v>通过</x:v>
@@ -10629,7 +10677,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="141" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A141" s="42" t="n">
         <x:v>137</x:v>
       </x:c>
@@ -10637,19 +10685,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="49" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D141" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E141" s="49" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="F141" s="49" t="str">
-        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
+        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
       </x:c>
       <x:c r="G141" s="49" t="str">
-        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
+        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
       </x:c>
       <x:c r="H141" s="52" t="str">
         <x:v>通过</x:v>
@@ -10661,7 +10709,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="142" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A142" s="42" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -10669,19 +10717,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="49" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D142" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E142" s="49" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="F142" s="49" t="str">
-        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
+        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
       </x:c>
       <x:c r="G142" s="49" t="str">
-        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
+        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
       </x:c>
       <x:c r="H142" s="52" t="str">
         <x:v>通过</x:v>
@@ -10693,7 +10741,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A143" s="42" t="n">
         <x:v>139</x:v>
       </x:c>
@@ -10701,19 +10749,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D143" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E143" s="49" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="F143" s="49" t="str">
-        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
+        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
       </x:c>
       <x:c r="G143" s="49" t="str">
-        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
+        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
       </x:c>
       <x:c r="H143" s="52" t="str">
         <x:v>通过</x:v>
@@ -10725,7 +10773,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" ht="132" hidden="0" customHeight="1">
+    <x:row r="144" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A144" s="42" t="n">
         <x:v>140</x:v>
       </x:c>
@@ -10733,19 +10781,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D144" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E144" s="49" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="F144" s="49" t="str">
-        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
+        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
       </x:c>
       <x:c r="G144" s="49" t="str">
-        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
+        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
       </x:c>
       <x:c r="H144" s="52" t="str">
         <x:v>通过</x:v>
@@ -10765,19 +10813,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="49" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D145" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E145" s="49" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="F145" s="49" t="str">
-        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
+        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
       </x:c>
       <x:c r="G145" s="49" t="str">
-        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
+        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
       </x:c>
       <x:c r="H145" s="52" t="str">
         <x:v>通过</x:v>
@@ -10789,7 +10837,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="146" ht="132" hidden="0" customHeight="1">
       <x:c r="A146" s="42" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -10797,19 +10845,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C146" s="49" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D146" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E146" s="49" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="F146" s="49" t="str">
-        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
+        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
       </x:c>
       <x:c r="G146" s="49" t="str">
-        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
+        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
       </x:c>
       <x:c r="H146" s="52" t="str">
         <x:v>通过</x:v>
@@ -10821,7 +10869,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="147" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A147" s="42" t="n">
         <x:v>143</x:v>
       </x:c>
@@ -10829,51 +10877,51 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C147" s="49" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D147" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E147" s="49" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="F147" s="49" t="str">
-        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
+        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
       </x:c>
       <x:c r="G147" s="49" t="str">
-        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
+        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
       </x:c>
       <x:c r="H147" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I147" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J147" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="148" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A148" s="42" t="n">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B148" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C148" s="49" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D148" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E148" s="49" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="F148" s="49" t="str">
-        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
+        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
       </x:c>
       <x:c r="G148" s="49" t="str">
-        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
+        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
       </x:c>
       <x:c r="H148" s="52" t="str">
         <x:v>通过</x:v>
@@ -10890,22 +10938,22 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B149" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C149" s="49" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D149" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E149" s="49" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="F149" s="49" t="str">
-        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
+        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
       </x:c>
       <x:c r="G149" s="49" t="str">
-        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
+        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
       </x:c>
       <x:c r="H149" s="52" t="str">
         <x:v>通过</x:v>
@@ -10925,19 +10973,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C150" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D150" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E150" s="49" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="F150" s="49" t="str">
-        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
+        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
       </x:c>
       <x:c r="G150" s="49" t="str">
-        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
+        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
       </x:c>
       <x:c r="H150" s="52" t="str">
         <x:v>通过</x:v>
@@ -10949,7 +10997,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A151" s="42" t="n">
         <x:v>147</x:v>
       </x:c>
@@ -10957,19 +11005,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C151" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D151" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E151" s="49" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="F151" s="49" t="str">
-        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
+        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
       </x:c>
       <x:c r="G151" s="49" t="str">
-        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
+        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
       </x:c>
       <x:c r="H151" s="52" t="str">
         <x:v>通过</x:v>
@@ -10989,19 +11037,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C152" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D152" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E152" s="49" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="F152" s="49" t="str">
-        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
+        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
       </x:c>
       <x:c r="G152" s="49" t="str">
-        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
+        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
       </x:c>
       <x:c r="H152" s="52" t="str">
         <x:v>通过</x:v>
@@ -11013,7 +11061,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="153" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A153" s="42" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -11021,31 +11069,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="49" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D153" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E153" s="49" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="F153" s="49" t="str">
-        <x:v>两条无去重键文档均被保留。</x:v>
+        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
       </x:c>
       <x:c r="G153" s="49" t="str">
-        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
+        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
       </x:c>
       <x:c r="H153" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I153" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J153" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="154" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A154" s="42" t="n">
         <x:v>150</x:v>
       </x:c>
@@ -11053,31 +11101,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C154" s="49" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D154" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E154" s="49" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="F154" s="49" t="str">
-        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
+        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
       </x:c>
       <x:c r="G154" s="49" t="str">
-        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
+        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
       </x:c>
       <x:c r="H154" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I154" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J154" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="155" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A155" s="42" t="n">
         <x:v>151</x:v>
       </x:c>
@@ -11085,19 +11133,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C155" s="49" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D155" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E155" s="49" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="F155" s="49" t="str">
-        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
+        <x:v>两条无去重键文档均被保留。</x:v>
       </x:c>
       <x:c r="G155" s="49" t="str">
-        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
+        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
       </x:c>
       <x:c r="H155" s="52" t="str">
         <x:v>通过</x:v>
@@ -11109,33 +11157,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="156" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A156" s="42" t="n">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B156" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C156" s="49" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D156" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E156" s="49" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="F156" s="49" t="str">
-        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
+        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
       </x:c>
       <x:c r="G156" s="49" t="str">
-        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
+        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
       </x:c>
       <x:c r="H156" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I156" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J156" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11146,34 +11194,34 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B157" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C157" s="49" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D157" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E157" s="49" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="F157" s="49" t="str">
-        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
+        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
       </x:c>
       <x:c r="G157" s="49" t="str">
-        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
+        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
       </x:c>
       <x:c r="H157" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I157" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J157" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="158" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A158" s="42" t="n">
         <x:v>154</x:v>
       </x:c>
@@ -11181,31 +11229,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C158" s="49" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D158" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E158" s="49" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="F158" s="49" t="str">
-        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
+        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
       </x:c>
       <x:c r="G158" s="49" t="str">
-        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
+        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
       </x:c>
       <x:c r="H158" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I158" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J158" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" ht="132" hidden="0" customHeight="1">
+    <x:row r="159" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A159" s="42" t="n">
         <x:v>155</x:v>
       </x:c>
@@ -11213,19 +11261,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C159" s="49" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D159" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E159" s="49" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="F159" s="49" t="str">
-        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
+        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
       </x:c>
       <x:c r="G159" s="49" t="str">
-        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
+        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
       </x:c>
       <x:c r="H159" s="52" t="str">
         <x:v>通过</x:v>
@@ -11237,7 +11285,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="132" hidden="0" customHeight="1">
+    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A160" s="42" t="n">
         <x:v>156</x:v>
       </x:c>
@@ -11245,31 +11293,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C160" s="49" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D160" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E160" s="49" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="F160" s="49" t="str">
-        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
+        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
       </x:c>
       <x:c r="G160" s="49" t="str">
-        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
+        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
       </x:c>
       <x:c r="H160" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I160" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J160" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="161" ht="132" hidden="0" customHeight="1">
       <x:c r="A161" s="42" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -11277,19 +11325,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="49" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D161" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E161" s="49" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="F161" s="49" t="str">
-        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
+        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
       </x:c>
       <x:c r="G161" s="49" t="str">
-        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
+        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
       </x:c>
       <x:c r="H161" s="52" t="str">
         <x:v>通过</x:v>
@@ -11301,7 +11349,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="162" ht="132" hidden="0" customHeight="1">
       <x:c r="A162" s="42" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -11309,31 +11357,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="49" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D162" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E162" s="49" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="F162" s="49" t="str">
-        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
+        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
       </x:c>
       <x:c r="G162" s="49" t="str">
-        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
+        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
       </x:c>
       <x:c r="H162" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I162" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J162" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="163" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A163" s="42" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -11341,31 +11389,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="49" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D163" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E163" s="49" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="F163" s="49" t="str">
-        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
+        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
       </x:c>
       <x:c r="G163" s="49" t="str">
-        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
+        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
       </x:c>
       <x:c r="H163" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I163" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J163" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A164" s="42" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -11373,25 +11421,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="49" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D164" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E164" s="49" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F164" s="49" t="str">
-        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
+        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
       </x:c>
       <x:c r="G164" s="49" t="str">
-        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
+        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
       </x:c>
       <x:c r="H164" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I164" s="55" t="n">
-        <x:v>0.085</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J164" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11405,19 +11453,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="49" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D165" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E165" s="49" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="F165" s="49" t="str">
-        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
+        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
       </x:c>
       <x:c r="G165" s="49" t="str">
-        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
+        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
       </x:c>
       <x:c r="H165" s="52" t="str">
         <x:v>通过</x:v>
@@ -11429,7 +11477,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="166" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A166" s="42" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -11437,31 +11485,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="49" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D166" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E166" s="49" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="F166" s="49" t="str">
-        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
+        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
       </x:c>
       <x:c r="G166" s="49" t="str">
-        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
+        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
       </x:c>
       <x:c r="H166" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I166" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.084</x:v>
       </x:c>
       <x:c r="J166" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="167" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A167" s="42" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -11469,19 +11517,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="49" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D167" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E167" s="49" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="F167" s="49" t="str">
-        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
+        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
       </x:c>
       <x:c r="G167" s="49" t="str">
-        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
+        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
       </x:c>
       <x:c r="H167" s="52" t="str">
         <x:v>通过</x:v>
@@ -11493,7 +11541,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="132" hidden="0" customHeight="1">
+    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A168" s="42" t="n">
         <x:v>164</x:v>
       </x:c>
@@ -11501,31 +11549,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="49" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D168" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E168" s="49" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="F168" s="49" t="str">
-        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
+        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
       </x:c>
       <x:c r="G168" s="49" t="str">
-        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
+        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
       </x:c>
       <x:c r="H168" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I168" s="55" t="n">
-        <x:v>0.15</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J168" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="169" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A169" s="42" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -11533,31 +11581,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="49" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D169" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E169" s="49" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="F169" s="49" t="str">
-        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
+        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
       </x:c>
       <x:c r="G169" s="49" t="str">
-        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
+        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
       </x:c>
       <x:c r="H169" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I169" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J169" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="170" ht="132" hidden="0" customHeight="1">
       <x:c r="A170" s="42" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -11565,25 +11613,25 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C170" s="49" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D170" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E170" s="49" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="F170" s="49" t="str">
-        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
+        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
       </x:c>
       <x:c r="G170" s="49" t="str">
-        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
+        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
       </x:c>
       <x:c r="H170" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I170" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.178</x:v>
       </x:c>
       <x:c r="J170" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11597,83 +11645,83 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="49" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D171" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E171" s="49" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="F171" s="49" t="str">
-        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
+        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
       </x:c>
       <x:c r="G171" s="49" t="str">
-        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
+        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
       </x:c>
       <x:c r="H171" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I171" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J171" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A172" s="42" t="n">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B172" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C172" s="49" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D172" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E172" s="49" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="F172" s="49" t="str">
-        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
+        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
       </x:c>
       <x:c r="G172" s="49" t="str">
-        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
+        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
       </x:c>
       <x:c r="H172" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I172" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="J172" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="173" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A173" s="42" t="n">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B173" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C173" s="49" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D173" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E173" s="49" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="F173" s="49" t="str">
-        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
+        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
       </x:c>
       <x:c r="G173" s="49" t="str">
-        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
+        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
       </x:c>
       <x:c r="H173" s="52" t="str">
         <x:v>通过</x:v>
@@ -11685,7 +11733,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="174" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A174" s="42" t="n">
         <x:v>170</x:v>
       </x:c>
@@ -11693,19 +11741,19 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C174" s="49" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D174" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E174" s="49" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="F174" s="49" t="str">
-        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
+        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
       </x:c>
       <x:c r="G174" s="49" t="str">
-        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
+        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
       </x:c>
       <x:c r="H174" s="52" t="str">
         <x:v>通过</x:v>
@@ -11725,51 +11773,51 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C175" s="49" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D175" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E175" s="49" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="F175" s="49" t="str">
-        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
+        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
       </x:c>
       <x:c r="G175" s="49" t="str">
-        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
+        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
       </x:c>
       <x:c r="H175" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I175" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J175" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="176" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A176" s="42" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="49" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C176" s="49" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D176" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E176" s="49" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="F176" s="49" t="str">
-        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
+        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
       </x:c>
       <x:c r="G176" s="49" t="str">
-        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
+        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
       </x:c>
       <x:c r="H176" s="52" t="str">
         <x:v>通过</x:v>
@@ -11781,65 +11829,65 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="177" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A177" s="42" t="n">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B177" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C177" s="49" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D177" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E177" s="49" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="F177" s="49" t="str">
-        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
+        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
       </x:c>
       <x:c r="G177" s="49" t="str">
-        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
+        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
       </x:c>
       <x:c r="H177" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I177" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J177" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="178" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A178" s="42" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C178" s="49" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D178" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E178" s="49" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="F178" s="49" t="str">
-        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
+        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
       </x:c>
       <x:c r="G178" s="49" t="str">
-        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
+        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
       </x:c>
       <x:c r="H178" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I178" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J178" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11850,22 +11898,22 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C179" s="49" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D179" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E179" s="49" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="F179" s="49" t="str">
-        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
+        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
       </x:c>
       <x:c r="G179" s="49" t="str">
-        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
+        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
       </x:c>
       <x:c r="H179" s="52" t="str">
         <x:v>通过</x:v>
@@ -11882,34 +11930,34 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C180" s="49" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D180" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E180" s="49" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="F180" s="49" t="str">
-        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
+        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
       </x:c>
       <x:c r="G180" s="49" t="str">
-        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
+        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
       </x:c>
       <x:c r="H180" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I180" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J180" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="181" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A181" s="42" t="n">
         <x:v>177</x:v>
       </x:c>
@@ -11917,25 +11965,25 @@
         <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C181" s="49" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D181" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E181" s="49" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="F181" s="49" t="str">
-        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
+        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
       </x:c>
       <x:c r="G181" s="49" t="str">
-        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
+        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
       </x:c>
       <x:c r="H181" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I181" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J181" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11946,22 +11994,22 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C182" s="49" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D182" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E182" s="49" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="F182" s="49" t="str">
-        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
+        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
       </x:c>
       <x:c r="G182" s="49" t="str">
-        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
+        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
       </x:c>
       <x:c r="H182" s="52" t="str">
         <x:v>通过</x:v>
@@ -11978,34 +12026,34 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C183" s="49" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D183" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E183" s="49" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="F183" s="49" t="str">
-        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
+        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
       </x:c>
       <x:c r="G183" s="49" t="str">
-        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
+        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
       </x:c>
       <x:c r="H183" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I183" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J183" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="184" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A184" s="42" t="n">
         <x:v>180</x:v>
       </x:c>
@@ -12013,31 +12061,31 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C184" s="49" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D184" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E184" s="49" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="F184" s="49" t="str">
-        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
+        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
       </x:c>
       <x:c r="G184" s="49" t="str">
-        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
+        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
       </x:c>
       <x:c r="H184" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I184" s="55" t="n">
-        <x:v>0.041</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J184" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="185" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A185" s="42" t="n">
         <x:v>181</x:v>
       </x:c>
@@ -12045,19 +12093,19 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C185" s="49" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D185" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E185" s="49" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="F185" s="49" t="str">
-        <x:v>单子查询继续走直接调用路径。</x:v>
+        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
       </x:c>
       <x:c r="G185" s="49" t="str">
-        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
+        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
       </x:c>
       <x:c r="H185" s="52" t="str">
         <x:v>通过</x:v>
@@ -12069,59 +12117,59 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="186" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A186" s="42" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C186" s="49" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D186" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E186" s="49" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="F186" s="49" t="str">
-        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
+        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
       </x:c>
       <x:c r="G186" s="49" t="str">
-        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
+        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
       </x:c>
       <x:c r="H186" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I186" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="J186" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="187" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A187" s="42" t="n">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B187" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C187" s="49" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D187" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E187" s="49" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="F187" s="49" t="str">
-        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
+        <x:v>单子查询继续走直接调用路径。</x:v>
       </x:c>
       <x:c r="G187" s="49" t="str">
-        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
+        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
       </x:c>
       <x:c r="H187" s="52" t="str">
         <x:v>通过</x:v>
@@ -12133,33 +12181,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="188" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A188" s="42" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="49" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C188" s="49" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D188" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E188" s="49" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="F188" s="49" t="str">
-        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
+        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
       </x:c>
       <x:c r="G188" s="49" t="str">
-        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
+        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
       </x:c>
       <x:c r="H188" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I188" s="55" t="n">
-        <x:v>0.063</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J188" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12170,118 +12218,118 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B189" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C189" s="49" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D189" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E189" s="49" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F189" s="49" t="str">
-        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
+        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
       </x:c>
       <x:c r="G189" s="49" t="str">
-        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
+        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
       </x:c>
       <x:c r="H189" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I189" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J189" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="132" hidden="0" customHeight="1">
+    <x:row r="190" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A190" s="42" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B190" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C190" s="49" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D190" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E190" s="49" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="F190" s="49" t="str">
-        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
+        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
       </x:c>
       <x:c r="G190" s="49" t="str">
-        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
+        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
       </x:c>
       <x:c r="H190" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I190" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.063</x:v>
       </x:c>
       <x:c r="J190" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="132" hidden="0" customHeight="1">
+    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A191" s="42" t="n">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B191" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C191" s="49" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D191" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E191" s="49" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="F191" s="49" t="str">
-        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
+        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
       </x:c>
       <x:c r="G191" s="49" t="str">
-        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
+        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
       </x:c>
       <x:c r="H191" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I191" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.035</x:v>
       </x:c>
       <x:c r="J191" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="192" ht="132" hidden="0" customHeight="1">
       <x:c r="A192" s="42" t="n">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B192" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C192" s="49" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D192" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E192" s="49" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="F192" s="49" t="str">
-        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
+        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
       </x:c>
       <x:c r="G192" s="49" t="str">
-        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
+        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
       </x:c>
       <x:c r="H192" s="52" t="str">
         <x:v>通过</x:v>
@@ -12293,7 +12341,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="193" ht="132" hidden="0" customHeight="1">
       <x:c r="A193" s="42" t="n">
         <x:v>189</x:v>
       </x:c>
@@ -12301,31 +12349,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C193" s="49" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D193" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E193" s="49" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="F193" s="49" t="str">
-        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
+        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
       </x:c>
       <x:c r="G193" s="49" t="str">
-        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
+        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
       </x:c>
       <x:c r="H193" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I193" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J193" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A194" s="42" t="n">
         <x:v>190</x:v>
       </x:c>
@@ -12333,19 +12381,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C194" s="49" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D194" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E194" s="49" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="F194" s="49" t="str">
-        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
+        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
       </x:c>
       <x:c r="G194" s="49" t="str">
-        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
+        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
       </x:c>
       <x:c r="H194" s="52" t="str">
         <x:v>通过</x:v>
@@ -12357,7 +12405,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="195" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A195" s="42" t="n">
         <x:v>191</x:v>
       </x:c>
@@ -12365,19 +12413,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C195" s="49" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D195" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E195" s="49" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="F195" s="49" t="str">
-        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
+        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
       </x:c>
       <x:c r="G195" s="49" t="str">
-        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
+        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
       </x:c>
       <x:c r="H195" s="52" t="str">
         <x:v>通过</x:v>
@@ -12397,31 +12445,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="49" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D196" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E196" s="49" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="F196" s="49" t="str">
-        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
+        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
       </x:c>
       <x:c r="G196" s="49" t="str">
-        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
+        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
       </x:c>
       <x:c r="H196" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I196" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J196" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="197" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A197" s="42" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -12429,25 +12477,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="49" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D197" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E197" s="49" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="F197" s="49" t="str">
-        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
+        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
       </x:c>
       <x:c r="G197" s="49" t="str">
-        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
+        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
       </x:c>
       <x:c r="H197" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I197" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J197" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12461,19 +12509,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="49" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D198" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E198" s="49" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="F198" s="49" t="str">
-        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
+        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
       </x:c>
       <x:c r="G198" s="49" t="str">
-        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
+        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
       </x:c>
       <x:c r="H198" s="52" t="str">
         <x:v>通过</x:v>
@@ -12485,7 +12533,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="199" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A199" s="42" t="n">
         <x:v>195</x:v>
       </x:c>
@@ -12493,31 +12541,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="49" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D199" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E199" s="49" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="F199" s="49" t="str">
-        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
+        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
       </x:c>
       <x:c r="G199" s="49" t="str">
-        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
+        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
       </x:c>
       <x:c r="H199" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I199" s="55" t="n">
-        <x:v>0.011</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J199" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="200" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A200" s="42" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -12525,25 +12573,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="49" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D200" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E200" s="49" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="F200" s="49" t="str">
-        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
+        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
       </x:c>
       <x:c r="G200" s="49" t="str">
-        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
+        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
       </x:c>
       <x:c r="H200" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I200" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J200" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12557,31 +12605,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="49" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D201" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E201" s="49" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="F201" s="49" t="str">
-        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
+        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
       </x:c>
       <x:c r="G201" s="49" t="str">
-        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
+        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
       </x:c>
       <x:c r="H201" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I201" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.021</x:v>
       </x:c>
       <x:c r="J201" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="202" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A202" s="42" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -12589,31 +12637,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="49" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D202" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E202" s="49" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="F202" s="49" t="str">
-        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
+        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
       </x:c>
       <x:c r="G202" s="49" t="str">
-        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
+        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
       </x:c>
       <x:c r="H202" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I202" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J202" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="132" hidden="0" customHeight="1">
+    <x:row r="203" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A203" s="42" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -12621,31 +12669,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="49" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D203" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E203" s="49" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="F203" s="49" t="str">
-        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
+        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
       </x:c>
       <x:c r="G203" s="49" t="str">
-        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
+        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
       </x:c>
       <x:c r="H203" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I203" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J203" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="204" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A204" s="42" t="n">
         <x:v>200</x:v>
       </x:c>
@@ -12653,19 +12701,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="49" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D204" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E204" s="49" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="F204" s="49" t="str">
-        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
+        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
       </x:c>
       <x:c r="G204" s="49" t="str">
-        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
+        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
       </x:c>
       <x:c r="H204" s="52" t="str">
         <x:v>通过</x:v>
@@ -12677,7 +12725,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="205" ht="132" hidden="0" customHeight="1">
       <x:c r="A205" s="42" t="n">
         <x:v>201</x:v>
       </x:c>
@@ -12685,31 +12733,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C205" s="49" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D205" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E205" s="49" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="F205" s="49" t="str">
-        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
       </x:c>
       <x:c r="G205" s="49" t="str">
-        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
       </x:c>
       <x:c r="H205" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I205" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J205" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" ht="132" hidden="0" customHeight="1">
+    <x:row r="206" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A206" s="42" t="n">
         <x:v>202</x:v>
       </x:c>
@@ -12717,19 +12765,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C206" s="49" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D206" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E206" s="49" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="F206" s="49" t="str">
-        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G206" s="49" t="str">
-        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
       </x:c>
       <x:c r="H206" s="52" t="str">
         <x:v>通过</x:v>
@@ -12741,7 +12789,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="207" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A207" s="42" t="n">
         <x:v>203</x:v>
       </x:c>
@@ -12749,31 +12797,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C207" s="49" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
       </x:c>
       <x:c r="D207" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E207" s="49" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
       </x:c>
       <x:c r="F207" s="49" t="str">
-        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
       </x:c>
       <x:c r="G207" s="49" t="str">
-        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
       </x:c>
       <x:c r="H207" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I207" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J207" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="208" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="208" ht="132" hidden="0" customHeight="1">
       <x:c r="A208" s="42" t="n">
         <x:v>204</x:v>
       </x:c>
@@ -12781,19 +12829,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C208" s="49" t="str">
-        <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D208" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E208" s="49" t="str">
-        <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
       </x:c>
       <x:c r="F208" s="49" t="str">
-        <x:v>限流进入可重试失败类别，不被误记为论文查无。</x:v>
+        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G208" s="49" t="str">
-        <x:v>匿名访问限流可能污染覆盖率并错误触发论文隔离。</x:v>
+        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
       </x:c>
       <x:c r="H208" s="52" t="str">
         <x:v>通过</x:v>
@@ -12805,35 +12853,99 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" ht="132" hidden="0" customHeight="1">
-      <x:c r="A209" s="45" t="n">
+    <x:row r="209" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A209" s="42" t="n">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="B209" s="50" t="str">
+      <x:c r="B209" s="49" t="str">
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
-      <x:c r="C209" s="50" t="str">
+      <x:c r="C209" s="49" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D209" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E209" s="49" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="F209" s="49" t="str">
+        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+      </x:c>
+      <x:c r="G209" s="49" t="str">
+        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+      </x:c>
+      <x:c r="H209" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I209" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J209" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A210" s="42" t="n">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B210" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C210" s="49" t="str">
+        <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
+      </x:c>
+      <x:c r="D210" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E210" s="49" t="str">
+        <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
+      </x:c>
+      <x:c r="F210" s="49" t="str">
+        <x:v>限流进入可重试失败类别，不被误记为论文查无。</x:v>
+      </x:c>
+      <x:c r="G210" s="49" t="str">
+        <x:v>匿名访问限流可能污染覆盖率并错误触发论文隔离。</x:v>
+      </x:c>
+      <x:c r="H210" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I210" s="55" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="J210" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="132" hidden="0" customHeight="1">
+      <x:c r="A211" s="45" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B211" s="50" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C211" s="50" t="str">
         <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
       </x:c>
-      <x:c r="D209" s="50" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E209" s="50" t="str">
+      <x:c r="D211" s="50" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E211" s="50" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="F209" s="50" t="str">
+      <x:c r="F211" s="50" t="str">
         <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
       </x:c>
-      <x:c r="G209" s="50" t="str">
+      <x:c r="G211" s="50" t="str">
         <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
       </x:c>
-      <x:c r="H209" s="53" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I209" s="56" t="n">
-        <x:v>0.004</x:v>
-      </x:c>
-      <x:c r="J209" s="59" t="str">
+      <x:c r="H211" s="53" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I211" s="56" t="n">
+        <x:v>0.003</x:v>
+      </x:c>
+      <x:c r="J211" s="59" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
@@ -12842,18 +12954,18 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H209">
+  <x:conditionalFormatting sqref="H5:H211">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="错误"/>
     <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="跳过"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J209">
+  <x:conditionalFormatting sqref="J5:J211">
     <x:cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="未登记"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R506bed307c8749e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R474013acfb17436f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14270,34 +14382,66 @@
       </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="128" t="n">
+      <x:c r="A44" s="127" t="n">
         <x:v>46247.46724537037</x:v>
       </x:c>
-      <x:c r="B44" s="24" t="str">
+      <x:c r="B44" s="23" t="str">
         <x:v>39a19fca1f84</x:v>
       </x:c>
-      <x:c r="C44" s="24" t="n">
+      <x:c r="C44" s="23" t="n">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="D44" s="24" t="n">
+      <x:c r="D44" s="23" t="n">
         <x:v>205</x:v>
       </x:c>
-      <x:c r="E44" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F44" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G44" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H44" s="131" t="n">
+      <x:c r="E44" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F44" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G44" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" s="130" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I44" s="30" t="n">
+      <x:c r="I44" s="29" t="n">
         <x:v>133.422</x:v>
       </x:c>
-      <x:c r="J44" s="24" t="n">
+      <x:c r="J44" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="128" t="n">
+        <x:v>46247.482141203705</x:v>
+      </x:c>
+      <x:c r="B45" s="24" t="str">
+        <x:v>4a50f5528c4f</x:v>
+      </x:c>
+      <x:c r="C45" s="24" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D45" s="24" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="E45" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F45" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G45" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I45" s="30" t="n">
+        <x:v>142.615</x:v>
+      </x:c>
+      <x:c r="J45" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -14307,7 +14451,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R581d0fc40e8740fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56d0c7ba455547db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/latest_test_report.xlsx
+++ b/reports/latest_test_report.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R087a5f18c200467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="Rca93a6ff5dc44bb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R7514022f6aff4ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Rae9f99fccf904a17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Ra88ea3c36ae34545"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R840acf28d9844883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="Rcf9c72b0f8cb4e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R5040751c96d54361"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="R5c445ab6bdd44f43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Reb02fb5ea0f047b2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J211" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J45" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="运行时间"/>
     <x:tableColumn id="2" name="Git Commit"/>
@@ -977,7 +977,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T11:34:17+08:00  |  Git：4a50f5528c4fb4e494b3893aa8bd43826ac629f1</x:v>
+        <x:v>运行时间：2026-08-13T11:50:34+08:00  |  Git：0fbbcbb04859d5a43e681259eadaab9e08057c5e</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1007,22 +1007,22 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="74" t="n">
-        <x:f>COUNTA('测试明细'!$A$5:$A$211)</x:f>
-        <x:v>207</x:v>
+        <x:f>COUNTA('测试明细'!$A$5:$A$214)</x:f>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B5" s="75"/>
       <x:c r="C5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$211,"通过")</x:f>
-        <x:v>207</x:v>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$214,"通过")</x:f>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D5" s="75"/>
       <x:c r="E5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$211,"失败")+COUNTIF('测试明细'!$E$5:$E$211,"错误")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$214,"失败")+COUNTIF('测试明细'!$E$5:$E$214,"错误")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="75"/>
       <x:c r="G5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$211,"跳过")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$214,"跳过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="76"/>
@@ -1062,8 +1062,8 @@
       </x:c>
       <x:c r="B9" s="108"/>
       <x:c r="C9" s="109" t="n">
-        <x:f>SUM('测试明细'!$F$5:$F$211)</x:f>
-        <x:v>142.61500000000032</x:v>
+        <x:f>SUM('测试明细'!$F$5:$F$214)</x:f>
+        <x:v>181.57700000000014</x:v>
       </x:c>
       <x:c r="D9" s="109"/>
       <x:c r="E9" s="110" t="n">
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="F9" s="110"/>
       <x:c r="G9" s="110" t="n">
-        <x:f>COUNTIF('用例说明'!$J$5:$J$211,"未登记")</x:f>
+        <x:f>COUNTIF('用例说明'!$J$5:$J$214,"未登记")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="111"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T11:34:17+08:00  |  Git：4a50f5528c4fb4e494b3893aa8bd43826ac629f1</x:v>
+        <x:v>运行时间：2026-08-13T11:50:34+08:00  |  Git：0fbbcbb04859d5a43e681259eadaab9e08057c5e</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1280,7 +1280,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
         <x:v>确认旧基线与当前候选实现使用完全相同的能力模块，保证能力对比口径一致。</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F6" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
         <x:v>确认当前实现相对旧基线确实提升关键确定性能力的准确率。</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="32" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>验证动态查询规划不会为简单问题创建多余检索词，同时保持规划准确。</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F8" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>验证基准报告能同时给出基线值、候选值和差值。</x:v>
@@ -1376,7 +1376,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F9" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
         <x:v>验证离线基准能准确统计成功/失败调用以及输入、输出和总 Token。</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F10" s="32" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
         <x:v>验证离线基准能够量化统一 Tool 层的协议、错误和恢复能力。</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F11" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.011</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
         <x:v>验证离线 Benchmark 对比单源基线与多源候选的覆盖、去重和故障恢复。</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F12" s="32" t="n">
-        <x:v>0.141</x:v>
+        <x:v>0.166</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
         <x:v>验证完整能力基准报告可以用 UTF-8 JSON 保存并重新读取。</x:v>
@@ -1496,7 +1496,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F14" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="G14" s="35" t="str">
         <x:v>验证候选评测能从 OpenAlex 等二级来源的 DOI 中提取待验证 arXiv 身份。</x:v>
@@ -1520,7 +1520,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.031</x:v>
       </x:c>
       <x:c r="G15" s="35" t="str">
         <x:v>验证联合重放只把普通 DOI 交给 Crossref，排除 arXiv DOI。</x:v>
@@ -1544,7 +1544,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F16" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="G16" s="35" t="str">
         <x:v>验证成功取得的规范元数据会缓存，快照重放不会重复消耗网络请求。</x:v>
@@ -1568,7 +1568,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G17" s="35" t="str">
         <x:v>验证 SSL、超时等临时失败不会被当成永久缓存结果。</x:v>
@@ -1592,7 +1592,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="G18" s="35" t="str">
         <x:v>验证 Crossref 成功记录和明确查无均可重复使用。</x:v>
@@ -1616,7 +1616,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.016</x:v>
       </x:c>
       <x:c r="G19" s="35" t="str">
         <x:v>验证 DOI authority 网络失败不会写入成功缓存。</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="G20" s="35" t="str">
         <x:v>验证本轮候选实验只查询 v2 实际隔离过的身份，控制外部请求成本。</x:v>
@@ -1664,7 +1664,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="G21" s="35" t="str">
         <x:v>验证规范元数据候选只有在三份完整独立快照、权威覆盖完整且逐题无回归时才通过晋升门槛。</x:v>
@@ -1688,7 +1688,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F22" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G22" s="35" t="str">
         <x:v>验证 Crossref 相对仅 arXiv canonical 没有指标变化时不得宣称质量提升。</x:v>
@@ -1712,7 +1712,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F23" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.026</x:v>
       </x:c>
       <x:c r="G23" s="35" t="str">
         <x:v>验证普通 DOI 候选评测只使用所有独立快照都出现的非 arXiv DOI。</x:v>
@@ -1736,7 +1736,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F24" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G24" s="35" t="str">
         <x:v>验证 Crossref 评测严格区分标题匹配、标题冲突、规范查无和网络失败。</x:v>
@@ -1760,7 +1760,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F25" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G25" s="35" t="str">
         <x:v>验证普通 DOI 样本按注册前缀轮转抽取，避免单一高频前缀垄断评测集。</x:v>
@@ -1784,7 +1784,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F26" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G26" s="35" t="str">
         <x:v>验证 provider 一致率只使用双方均成功返回标题的 DOI。</x:v>
@@ -1808,7 +1808,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F27" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G27" s="35" t="str">
         <x:v>验证 DOI 校验在固定污染、缺失、近似、查无和失败场景中达到阶段止损条件。</x:v>
@@ -1832,7 +1832,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F28" s="32" t="n">
-        <x:v>0.074</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="G28" s="35" t="str">
         <x:v>验证普通研究问题按完整 Agentic RAG 节点顺序执行。</x:v>
@@ -1856,7 +1856,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F29" s="32" t="n">
-        <x:v>0.087</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="G29" s="35" t="str">
         <x:v>验证已有 PDF 的请求不会重复进行外部查询规划和检索。</x:v>
@@ -1880,7 +1880,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F30" s="32" t="n">
-        <x:v>0.091</x:v>
+        <x:v>0.068</x:v>
       </x:c>
       <x:c r="G30" s="35" t="str">
         <x:v>验证问候类输入在进入 RAG 与 LLM 节点前本地结束。</x:v>
@@ -1952,7 +1952,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F33" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G33" s="35" t="str">
         <x:v>验证不同语言和格式的纯问候可由本地规则识别。</x:v>
@@ -2024,7 +2024,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F36" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G36" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2072,7 +2072,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F38" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G38" s="35" t="str">
         <x:v>验证中英文感谢表达可由本地规则识别。</x:v>
@@ -2096,7 +2096,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F39" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G39" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2144,7 +2144,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F41" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G41" s="35" t="str">
         <x:v>验证“你是谁/能做什么”等身份能力问题可本地识别。</x:v>
@@ -2168,7 +2168,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F42" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G42" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2192,7 +2192,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F43" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G43" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2216,7 +2216,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F44" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G44" s="35" t="str">
         <x:v>防止含问候词的真实研究请求或 PDF 请求被错误当成闲聊短路。</x:v>
@@ -2240,7 +2240,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F45" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G45" s="35" t="str">
         <x:v>验证意图匹配前只清理空格、大小写和末尾标点等表面差异。</x:v>
@@ -2288,7 +2288,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F47" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G47" s="35" t="str">
         <x:v>验证能读取 LangChain 标准 usage_metadata Token 字段。</x:v>
@@ -2336,7 +2336,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F49" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G49" s="35" t="str">
         <x:v>验证模型未返回 Token 数据时系统明确标记缺失而不伪造估算值。</x:v>
@@ -2480,7 +2480,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F55" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G55" s="35" t="str">
         <x:v>验证检索评估节点启用 LLM 时记录评分与用量。</x:v>
@@ -2504,7 +2504,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F56" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G56" s="35" t="str">
         <x:v>验证答案生成节点记录实际生成结果和模型用量。</x:v>
@@ -2576,7 +2576,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F59" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G59" s="35" t="str">
         <x:v>验证 BM25 将包含查询词的文本块排在无关块之前，且重复运行排名与分数一致。</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F61" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G61" s="35" t="str">
         <x:v>用手工可计算的排名验证本地 RAG Recall、MRR 与 nDCG 公式。</x:v>
@@ -2672,7 +2672,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F63" s="32" t="n">
-        <x:v>0.074</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="G63" s="35" t="str">
         <x:v>验证代表论文来源清单生成 Manifest 时保留语料版本、论文身份和内容哈希。</x:v>
@@ -2696,7 +2696,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F64" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G64" s="35" t="str">
         <x:v>验证来源清单声明的 PDF 缺失时立即失败，而不是静默生成不完整语料。</x:v>
@@ -2720,7 +2720,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F65" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G65" s="35" t="str">
         <x:v>验证 Dense 检索显式归一化向量，并按余弦相似度将语义匹配块排在前面。</x:v>
@@ -2744,7 +2744,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F66" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G66" s="35" t="str">
         <x:v>验证 Dense 检索拒绝零向量和空语料。</x:v>
@@ -2768,7 +2768,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F67" s="32" t="n">
-        <x:v>0.031</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="G67" s="35" t="str">
         <x:v>验证 Dense 向量缓存可以无损加载，并在语料文本、模型或处理版本变化后使用不同指纹。</x:v>
@@ -2792,7 +2792,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F68" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G68" s="35" t="str">
         <x:v>验证缓存命中时 DenseRetriever 不会重新编码全部论文，只对查询生成向量。</x:v>
@@ -2816,7 +2816,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F69" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G69" s="35" t="str">
         <x:v>验证 Dense 正式评测前执行固定次数的查询预热，并将预热延迟与正式查询指标明确隔离。</x:v>
@@ -2840,7 +2840,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F70" s="32" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.027</x:v>
       </x:c>
       <x:c r="G70" s="35" t="str">
         <x:v>验证 Dense 缓存只有在冷启动未命中、热启动命中、质量完全一致且建库耗时下降超过 99% 时才通过。</x:v>
@@ -2864,7 +2864,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F71" s="32" t="n">
-        <x:v>31.084</x:v>
+        <x:v>36.665</x:v>
       </x:c>
       <x:c r="G71" s="35" t="str">
         <x:v>验证 Dense 晋升判断以独立保留集质量为依据，并与生产默认开关分离。</x:v>
@@ -2888,7 +2888,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F72" s="32" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="G72" s="35" t="str">
         <x:v>验证第二 Dense 模型只有在保留集 nDCG 提升、Recall 不下降且逐题回归不超过 2 个时才成为首选候选。</x:v>
@@ -2912,7 +2912,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F73" s="32" t="n">
-        <x:v>0.774</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G73" s="35" t="str">
         <x:v>验证第二 Dense 模型通过同一评测入口配置，只声明模型自身的维度、输入长度、池化和配置身份差异。</x:v>
@@ -2960,7 +2960,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F75" s="32" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="G75" s="35" t="str">
         <x:v>验证稳定性评测拒绝混入其他 Embedding 模型或不符合预期模型身份的运行文件。</x:v>
@@ -2984,7 +2984,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F76" s="32" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G76" s="35" t="str">
         <x:v>验证 MiniLM/MPNet 稳定性并列比较保留 MPNet 的失败判定，不因平均质量收益或模型间比值覆盖原始闸门。</x:v>
@@ -3008,7 +3008,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F77" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="G77" s="35" t="str">
         <x:v>验证预热对照只在同一模型由预热前失败转为预热后通过时，才判断首次初始化解释了稳定性问题。</x:v>
@@ -3032,7 +3032,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F78" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G78" s="35" t="str">
         <x:v>验证固定窗口分块保留页码、字符位置和配置的重叠区间。</x:v>
@@ -3056,7 +3056,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F79" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G79" s="35" t="str">
         <x:v>验证重叠长度不能等于或超过分块长度。</x:v>
@@ -3080,7 +3080,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F80" s="32" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="G80" s="35" t="str">
         <x:v>验证知识库只在 PDF 内容、Parser 或 Chunker 版本变化时局部重建。</x:v>
@@ -3104,22 +3104,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F81" s="32" t="n">
-        <x:v>0.035</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="G81" s="35" t="str">
         <x:v>验证语料清单记录 corpus_version 和每篇论文的处理状态。</x:v>
       </x:c>
       <x:c r="H81" s="35" t="str"/>
     </x:row>
-    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="82" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A82" s="26" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_hybrid.py</x:v>
       </x:c>
       <x:c r="C82" s="35" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_rrf_rewards_cross_retriever_agreement_without_mixing_raw_scores</x:v>
       </x:c>
       <x:c r="D82" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3131,7 +3131,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G82" s="35" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证 Hybrid 使用倒数排名融合奖励 BM25 与 Dense 共同命中的证据，而不直接相加尺度不同的原始分数。</x:v>
       </x:c>
       <x:c r="H82" s="35" t="str"/>
     </x:row>
@@ -3140,10 +3140,10 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="35" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_hybrid.py</x:v>
       </x:c>
       <x:c r="C83" s="35" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_rrf_is_deterministic_and_rejects_invalid_configuration</x:v>
       </x:c>
       <x:c r="D83" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3155,19 +3155,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G83" s="35" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证 RRF 参数必须为正，并在融合分数相同时按确定性身份规则打破平局。</x:v>
       </x:c>
       <x:c r="H83" s="35" t="str"/>
     </x:row>
-    <x:row r="84" ht="132" hidden="0" customHeight="1">
+    <x:row r="84" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A84" s="26" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="35" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_hybrid_eval.py</x:v>
       </x:c>
       <x:c r="C84" s="35" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_hybrid_parameter_selection_uses_frozen_quality_first_order</x:v>
       </x:c>
       <x:c r="D84" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3176,22 +3176,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F84" s="32" t="n">
-        <x:v>30.792</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G84" s="35" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证 Hybrid 参数只按预先冻结的开发集规则选择：Recall@5、nDCG@5、回归数、延迟、较小 RRF k。</x:v>
       </x:c>
       <x:c r="H84" s="35" t="str"/>
     </x:row>
-    <x:row r="85" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="85" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A85" s="26" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C85" s="35" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D85" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3200,22 +3200,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F85" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G85" s="35" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="H85" s="35" t="str"/>
     </x:row>
-    <x:row r="86" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="86" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A86" s="26" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C86" s="35" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D86" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3227,19 +3227,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G86" s="35" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="H86" s="35" t="str"/>
     </x:row>
-    <x:row r="87" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="87" ht="132" hidden="0" customHeight="1">
       <x:c r="A87" s="26" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" s="35" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C87" s="35" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D87" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3248,22 +3248,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F87" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>44.64</x:v>
       </x:c>
       <x:c r="G87" s="35" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="H87" s="35" t="str"/>
     </x:row>
-    <x:row r="88" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="88" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A88" s="26" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C88" s="35" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D88" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3275,19 +3275,19 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G88" s="35" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="H88" s="35" t="str"/>
     </x:row>
-    <x:row r="89" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="89" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A89" s="26" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C89" s="35" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D89" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3296,22 +3296,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F89" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G89" s="35" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="H89" s="35" t="str"/>
     </x:row>
-    <x:row r="90" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="90" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A90" s="26" t="n">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" s="35" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C90" s="35" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D90" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3320,14 +3320,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F90" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G90" s="35" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="H90" s="35" t="str"/>
     </x:row>
-    <x:row r="91" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="91" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A91" s="26" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -3335,7 +3335,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C91" s="35" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D91" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3347,11 +3347,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G91" s="35" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="H91" s="35" t="str"/>
     </x:row>
-    <x:row r="92" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="92" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A92" s="26" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -3359,7 +3359,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C92" s="35" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D92" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3371,11 +3371,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G92" s="35" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="H92" s="35" t="str"/>
     </x:row>
-    <x:row r="93" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="93" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A93" s="26" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -3383,7 +3383,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C93" s="35" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D93" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3395,11 +3395,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G93" s="35" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="H93" s="35" t="str"/>
     </x:row>
-    <x:row r="94" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="94" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A94" s="26" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -3407,7 +3407,7 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C94" s="35" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D94" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3416,22 +3416,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F94" s="32" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G94" s="35" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="H94" s="35" t="str"/>
     </x:row>
-    <x:row r="95" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="95" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A95" s="26" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C95" s="35" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D95" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3443,19 +3443,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G95" s="35" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="H95" s="35" t="str"/>
     </x:row>
-    <x:row r="96" ht="132" hidden="0" customHeight="1">
+    <x:row r="96" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A96" s="26" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C96" s="35" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D96" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3464,22 +3464,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F96" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G96" s="35" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="H96" s="35" t="str"/>
     </x:row>
-    <x:row r="97" ht="132" hidden="0" customHeight="1">
+    <x:row r="97" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A97" s="26" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" s="35" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C97" s="35" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D97" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3488,10 +3488,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F97" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.011</x:v>
       </x:c>
       <x:c r="G97" s="35" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="H97" s="35" t="str"/>
     </x:row>
@@ -3503,7 +3503,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C98" s="35" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D98" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3515,11 +3515,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G98" s="35" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="H98" s="35" t="str"/>
     </x:row>
-    <x:row r="99" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="99" ht="132" hidden="0" customHeight="1">
       <x:c r="A99" s="26" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -3527,7 +3527,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C99" s="35" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D99" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3539,11 +3539,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G99" s="35" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="H99" s="35" t="str"/>
     </x:row>
-    <x:row r="100" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="100" ht="132" hidden="0" customHeight="1">
       <x:c r="A100" s="26" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -3551,7 +3551,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C100" s="35" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D100" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3560,14 +3560,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F100" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G100" s="35" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="H100" s="35" t="str"/>
     </x:row>
-    <x:row r="101" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="101" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A101" s="26" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -3575,7 +3575,7 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C101" s="35" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D101" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3587,7 +3587,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G101" s="35" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="H101" s="35" t="str"/>
     </x:row>
@@ -3596,10 +3596,10 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="35" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C102" s="35" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D102" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3608,22 +3608,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F102" s="32" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G102" s="35" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="H102" s="35" t="str"/>
     </x:row>
-    <x:row r="103" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="103" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A103" s="26" t="n">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C103" s="35" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D103" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3632,22 +3632,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F103" s="32" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G103" s="35" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="H103" s="35" t="str"/>
     </x:row>
-    <x:row r="104" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="104" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A104" s="26" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C104" s="35" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D104" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3656,22 +3656,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F104" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G104" s="35" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="H104" s="35" t="str"/>
     </x:row>
-    <x:row r="105" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="105" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A105" s="26" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C105" s="35" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D105" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3680,14 +3680,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F105" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>2.378</x:v>
       </x:c>
       <x:c r="G105" s="35" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="H105" s="35" t="str"/>
     </x:row>
-    <x:row r="106" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="106" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A106" s="26" t="n">
         <x:v>102</x:v>
       </x:c>
@@ -3695,7 +3695,7 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C106" s="35" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D106" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3704,22 +3704,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F106" s="32" t="n">
-        <x:v>1.131</x:v>
+        <x:v>0.043</x:v>
       </x:c>
       <x:c r="G106" s="35" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="H106" s="35" t="str"/>
     </x:row>
-    <x:row r="107" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="107" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A107" s="26" t="n">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C107" s="35" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D107" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3728,10 +3728,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F107" s="32" t="n">
-        <x:v>0.171</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G107" s="35" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="H107" s="35" t="str"/>
     </x:row>
@@ -3740,10 +3740,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B108" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C108" s="35" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D108" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3752,22 +3752,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F108" s="32" t="n">
-        <x:v>0.092</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="G108" s="35" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="H108" s="35" t="str"/>
     </x:row>
-    <x:row r="109" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="109" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A109" s="26" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="35" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C109" s="35" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D109" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3776,14 +3776,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F109" s="32" t="n">
-        <x:v>0.047</x:v>
+        <x:v>1.158</x:v>
       </x:c>
       <x:c r="G109" s="35" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="H109" s="35" t="str"/>
     </x:row>
-    <x:row r="110" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="110" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A110" s="26" t="n">
         <x:v>106</x:v>
       </x:c>
@@ -3791,7 +3791,7 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C110" s="35" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D110" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3800,22 +3800,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F110" s="32" t="n">
-        <x:v>0.076</x:v>
+        <x:v>0.178</x:v>
       </x:c>
       <x:c r="G110" s="35" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="H110" s="35" t="str"/>
     </x:row>
-    <x:row r="111" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="111" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A111" s="26" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B111" s="35" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C111" s="35" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D111" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3824,22 +3824,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F111" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.091</x:v>
       </x:c>
       <x:c r="G111" s="35" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="H111" s="35" t="str"/>
     </x:row>
-    <x:row r="112" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="112" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A112" s="26" t="n">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B112" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C112" s="35" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D112" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -3848,34 +3848,34 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F112" s="32" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.047</x:v>
       </x:c>
       <x:c r="G112" s="35" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="H112" s="35" t="str"/>
     </x:row>
-    <x:row r="113" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="113" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A113" s="26" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B113" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C113" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D113" s="35" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E113" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F113" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.089</x:v>
       </x:c>
       <x:c r="G113" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="H113" s="35" t="str"/>
     </x:row>
@@ -3884,13 +3884,13 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B114" s="35" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C114" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D114" s="35" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E114" s="26" t="str">
         <x:v>通过</x:v>
@@ -3899,11 +3899,11 @@
         <x:v>0.004</x:v>
       </x:c>
       <x:c r="G114" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="H114" s="35" t="str"/>
     </x:row>
-    <x:row r="115" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="115" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A115" s="26" t="n">
         <x:v>111</x:v>
       </x:c>
@@ -3911,19 +3911,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D115" s="35" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E115" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F115" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G115" s="35" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="H115" s="35" t="str"/>
     </x:row>
@@ -3935,16 +3935,16 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D116" s="35" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E116" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F116" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G116" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -3959,23 +3959,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D117" s="35" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E117" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F117" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G117" s="35" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H117" s="35" t="str"/>
     </x:row>
-    <x:row r="118" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="118" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A118" s="26" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -3983,23 +3983,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="35" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D118" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E118" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F118" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G118" s="35" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H118" s="35" t="str"/>
     </x:row>
-    <x:row r="119" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="119" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A119" s="26" t="n">
         <x:v>115</x:v>
       </x:c>
@@ -4007,10 +4007,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D119" s="35" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E119" s="26" t="str">
         <x:v>通过</x:v>
@@ -4019,11 +4019,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G119" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H119" s="35" t="str"/>
     </x:row>
-    <x:row r="120" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="120" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A120" s="26" t="n">
         <x:v>116</x:v>
       </x:c>
@@ -4031,19 +4031,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D120" s="35" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E120" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F120" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G120" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="H120" s="35" t="str"/>
     </x:row>
@@ -4055,19 +4055,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D121" s="35" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E121" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F121" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G121" s="35" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="H121" s="35" t="str"/>
     </x:row>
@@ -4079,10 +4079,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D122" s="35" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E122" s="26" t="str">
         <x:v>通过</x:v>
@@ -4103,23 +4103,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C123" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D123" s="35" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E123" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F123" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G123" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H123" s="35" t="str"/>
     </x:row>
-    <x:row r="124" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="124" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A124" s="26" t="n">
         <x:v>120</x:v>
       </x:c>
@@ -4127,23 +4127,23 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C124" s="35" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D124" s="35" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E124" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F124" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G124" s="35" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H124" s="35" t="str"/>
     </x:row>
-    <x:row r="125" ht="66" hidden="0" customHeight="1">
+    <x:row r="125" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A125" s="26" t="n">
         <x:v>121</x:v>
       </x:c>
@@ -4151,10 +4151,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C125" s="35" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D125" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E125" s="26" t="str">
         <x:v>通过</x:v>
@@ -4163,7 +4163,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G125" s="35" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H125" s="35" t="str"/>
     </x:row>
@@ -4175,55 +4175,55 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C126" s="35" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D126" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E126" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F126" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G126" s="35" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H126" s="35" t="str"/>
     </x:row>
-    <x:row r="127" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="127" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A127" s="26" t="n">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C127" s="35" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D127" s="35" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E127" s="26" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F127" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G127" s="35" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="H127" s="35" t="str"/>
     </x:row>
-    <x:row r="128" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="128" ht="66" hidden="0" customHeight="1">
       <x:c r="A128" s="26" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C128" s="35" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D128" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4232,22 +4232,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F128" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G128" s="35" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="H128" s="35" t="str"/>
     </x:row>
-    <x:row r="129" ht="132" hidden="0" customHeight="1">
+    <x:row r="129" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A129" s="26" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="35" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C129" s="35" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D129" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4256,10 +4256,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F129" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G129" s="35" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="H129" s="35" t="str"/>
     </x:row>
@@ -4271,7 +4271,7 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C130" s="35" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D130" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4280,22 +4280,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F130" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G130" s="35" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="H130" s="35" t="str"/>
     </x:row>
-    <x:row r="131" ht="132" hidden="0" customHeight="1">
+    <x:row r="131" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A131" s="26" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C131" s="35" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D131" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4304,22 +4304,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F131" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G131" s="35" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="H131" s="35" t="str"/>
     </x:row>
-    <x:row r="132" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="132" ht="132" hidden="0" customHeight="1">
       <x:c r="A132" s="26" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C132" s="35" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D132" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4328,10 +4328,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F132" s="32" t="n">
-        <x:v>14.691</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G132" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="H132" s="35" t="str"/>
     </x:row>
@@ -4340,10 +4340,10 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="35" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C133" s="35" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D133" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4352,10 +4352,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F133" s="32" t="n">
-        <x:v>26.027</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G133" s="35" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="H133" s="35" t="str"/>
     </x:row>
@@ -4364,10 +4364,10 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B134" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C134" s="35" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D134" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4379,19 +4379,19 @@
         <x:v>0.005</x:v>
       </x:c>
       <x:c r="G134" s="35" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="H134" s="35" t="str"/>
     </x:row>
-    <x:row r="135" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A135" s="26" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B135" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C135" s="35" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D135" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4400,22 +4400,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F135" s="32" t="n">
-        <x:v>18.907</x:v>
+        <x:v>30.032</x:v>
       </x:c>
       <x:c r="G135" s="35" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="H135" s="35" t="str"/>
     </x:row>
-    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="136" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A136" s="26" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B136" s="35" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C136" s="35" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D136" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4424,22 +4424,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F136" s="32" t="n">
-        <x:v>14.794</x:v>
+        <x:v>28.684</x:v>
       </x:c>
       <x:c r="G136" s="35" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="H136" s="35" t="str"/>
     </x:row>
-    <x:row r="137" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="137" ht="132" hidden="0" customHeight="1">
       <x:c r="A137" s="26" t="n">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B137" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C137" s="35" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D137" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4448,22 +4448,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F137" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="G137" s="35" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="H137" s="35" t="str"/>
     </x:row>
-    <x:row r="138" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="138" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A138" s="26" t="n">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B138" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C138" s="35" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D138" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4472,22 +4472,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F138" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>19.055</x:v>
       </x:c>
       <x:c r="G138" s="35" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="H138" s="35" t="str"/>
     </x:row>
-    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A139" s="26" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B139" s="35" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C139" s="35" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D139" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4496,14 +4496,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F139" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>16.691</x:v>
       </x:c>
       <x:c r="G139" s="35" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="H139" s="35" t="str"/>
     </x:row>
-    <x:row r="140" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="140" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A140" s="26" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -4511,7 +4511,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="35" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D140" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4520,10 +4520,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F140" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G140" s="35" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="H140" s="35" t="str"/>
     </x:row>
@@ -4535,7 +4535,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="35" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D141" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4544,10 +4544,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F141" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G141" s="35" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="H141" s="35" t="str"/>
     </x:row>
@@ -4559,7 +4559,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="35" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D142" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4568,10 +4568,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F142" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G142" s="35" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="H142" s="35" t="str"/>
     </x:row>
@@ -4583,7 +4583,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="35" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D143" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4592,14 +4592,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F143" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G143" s="35" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="H143" s="35" t="str"/>
     </x:row>
-    <x:row r="144" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="144" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A144" s="26" t="n">
         <x:v>140</x:v>
       </x:c>
@@ -4607,7 +4607,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="35" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D144" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4619,7 +4619,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G144" s="35" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="H144" s="35" t="str"/>
     </x:row>
@@ -4631,7 +4631,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D145" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4640,14 +4640,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F145" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G145" s="35" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="H145" s="35" t="str"/>
     </x:row>
-    <x:row r="146" ht="132" hidden="0" customHeight="1">
+    <x:row r="146" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A146" s="26" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -4655,7 +4655,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C146" s="35" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D146" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4664,10 +4664,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F146" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G146" s="35" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="H146" s="35" t="str"/>
     </x:row>
@@ -4679,7 +4679,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C147" s="35" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D147" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4688,10 +4688,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F147" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G147" s="35" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="H147" s="35" t="str"/>
     </x:row>
@@ -4703,7 +4703,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C148" s="35" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D148" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4712,14 +4712,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F148" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G148" s="35" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="H148" s="35" t="str"/>
     </x:row>
-    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="149" ht="132" hidden="0" customHeight="1">
       <x:c r="A149" s="26" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -4727,7 +4727,7 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C149" s="35" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D149" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4736,22 +4736,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F149" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G149" s="35" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="H149" s="35" t="str"/>
     </x:row>
-    <x:row r="150" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="150" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A150" s="26" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B150" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C150" s="35" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D150" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4760,22 +4760,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F150" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G150" s="35" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="H150" s="35" t="str"/>
     </x:row>
-    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="151" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A151" s="26" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B151" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C151" s="35" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D151" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4784,10 +4784,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F151" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G151" s="35" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="H151" s="35" t="str"/>
     </x:row>
@@ -4796,10 +4796,10 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B152" s="35" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C152" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D152" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4811,11 +4811,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G152" s="35" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="H152" s="35" t="str"/>
     </x:row>
-    <x:row r="153" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="153" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A153" s="26" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -4823,7 +4823,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D153" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4835,7 +4835,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G153" s="35" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="H153" s="35" t="str"/>
     </x:row>
@@ -4847,7 +4847,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C154" s="35" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D154" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4856,10 +4856,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F154" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G154" s="35" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="H154" s="35" t="str"/>
     </x:row>
@@ -4871,7 +4871,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C155" s="35" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D155" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4883,11 +4883,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G155" s="35" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="H155" s="35" t="str"/>
     </x:row>
-    <x:row r="156" ht="66" hidden="0" customHeight="1">
+    <x:row r="156" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A156" s="26" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -4895,7 +4895,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C156" s="35" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D156" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4904,14 +4904,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F156" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G156" s="35" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="H156" s="35" t="str"/>
     </x:row>
-    <x:row r="157" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="157" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A157" s="26" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -4919,7 +4919,7 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C157" s="35" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D157" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4931,19 +4931,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G157" s="35" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="H157" s="35" t="str"/>
     </x:row>
-    <x:row r="158" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A158" s="26" t="n">
         <x:v>154</x:v>
       </x:c>
       <x:c r="B158" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C158" s="35" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D158" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4952,22 +4952,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F158" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G158" s="35" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="H158" s="35" t="str"/>
     </x:row>
-    <x:row r="159" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="159" ht="66" hidden="0" customHeight="1">
       <x:c r="A159" s="26" t="n">
         <x:v>155</x:v>
       </x:c>
       <x:c r="B159" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C159" s="35" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D159" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -4976,22 +4976,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F159" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G159" s="35" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="H159" s="35" t="str"/>
     </x:row>
-    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="160" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A160" s="26" t="n">
         <x:v>156</x:v>
       </x:c>
       <x:c r="B160" s="35" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C160" s="35" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D160" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5003,11 +5003,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G160" s="35" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="H160" s="35" t="str"/>
     </x:row>
-    <x:row r="161" ht="132" hidden="0" customHeight="1">
+    <x:row r="161" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A161" s="26" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -5015,7 +5015,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="35" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D161" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5024,14 +5024,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F161" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G161" s="35" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="H161" s="35" t="str"/>
     </x:row>
-    <x:row r="162" ht="132" hidden="0" customHeight="1">
+    <x:row r="162" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A162" s="26" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -5039,7 +5039,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="35" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D162" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5048,14 +5048,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F162" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G162" s="35" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="H162" s="35" t="str"/>
     </x:row>
-    <x:row r="163" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="163" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A163" s="26" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -5063,7 +5063,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="35" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D163" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5072,14 +5072,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F163" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G163" s="35" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="H163" s="35" t="str"/>
     </x:row>
-    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="164" ht="132" hidden="0" customHeight="1">
       <x:c r="A164" s="26" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -5087,7 +5087,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="35" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D164" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5099,11 +5099,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G164" s="35" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="H164" s="35" t="str"/>
     </x:row>
-    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="165" ht="132" hidden="0" customHeight="1">
       <x:c r="A165" s="26" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -5111,7 +5111,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="35" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D165" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5123,11 +5123,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G165" s="35" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="H165" s="35" t="str"/>
     </x:row>
-    <x:row r="166" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="166" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A166" s="26" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -5135,7 +5135,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="35" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D166" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5144,14 +5144,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F166" s="32" t="n">
-        <x:v>0.084</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G166" s="35" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="H166" s="35" t="str"/>
     </x:row>
-    <x:row r="167" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="167" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A167" s="26" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -5159,7 +5159,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="35" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D167" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5171,11 +5171,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G167" s="35" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H167" s="35" t="str"/>
     </x:row>
-    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="168" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A168" s="26" t="n">
         <x:v>164</x:v>
       </x:c>
@@ -5183,7 +5183,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="35" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D168" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5192,14 +5192,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F168" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G168" s="35" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="H168" s="35" t="str"/>
     </x:row>
-    <x:row r="169" ht="132" hidden="0" customHeight="1">
+    <x:row r="169" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A169" s="26" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -5207,7 +5207,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="35" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D169" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5216,14 +5216,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F169" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.091</x:v>
       </x:c>
       <x:c r="G169" s="35" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="H169" s="35" t="str"/>
     </x:row>
-    <x:row r="170" ht="132" hidden="0" customHeight="1">
+    <x:row r="170" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A170" s="26" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -5231,7 +5231,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C170" s="35" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D170" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5240,10 +5240,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F170" s="32" t="n">
-        <x:v>0.178</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G170" s="35" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="H170" s="35" t="str"/>
     </x:row>
@@ -5255,7 +5255,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="35" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D171" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5264,14 +5264,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F171" s="32" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G171" s="35" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="H171" s="35" t="str"/>
     </x:row>
-    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="172" ht="132" hidden="0" customHeight="1">
       <x:c r="A172" s="26" t="n">
         <x:v>168</x:v>
       </x:c>
@@ -5279,7 +5279,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C172" s="35" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D172" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5288,14 +5288,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F172" s="32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G172" s="35" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="H172" s="35" t="str"/>
     </x:row>
-    <x:row r="173" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="173" ht="132" hidden="0" customHeight="1">
       <x:c r="A173" s="26" t="n">
         <x:v>169</x:v>
       </x:c>
@@ -5303,7 +5303,7 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C173" s="35" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D173" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5312,22 +5312,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F173" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.181</x:v>
       </x:c>
       <x:c r="G173" s="35" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="H173" s="35" t="str"/>
     </x:row>
-    <x:row r="174" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="174" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A174" s="26" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C174" s="35" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D174" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5336,22 +5336,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F174" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G174" s="35" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="H174" s="35" t="str"/>
     </x:row>
-    <x:row r="175" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="175" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A175" s="26" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C175" s="35" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D175" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5360,22 +5360,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F175" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G175" s="35" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="H175" s="35" t="str"/>
     </x:row>
-    <x:row r="176" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="176" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A176" s="26" t="n">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="35" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C176" s="35" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D176" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5384,14 +5384,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F176" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G176" s="35" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="H176" s="35" t="str"/>
     </x:row>
-    <x:row r="177" ht="66" hidden="0" customHeight="1">
+    <x:row r="177" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A177" s="26" t="n">
         <x:v>173</x:v>
       </x:c>
@@ -5399,7 +5399,7 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C177" s="35" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D177" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5408,22 +5408,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F177" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G177" s="35" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="H177" s="35" t="str"/>
     </x:row>
-    <x:row r="178" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="178" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A178" s="26" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="35" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C178" s="35" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D178" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5435,19 +5435,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G178" s="35" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="H178" s="35" t="str"/>
     </x:row>
-    <x:row r="179" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="179" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A179" s="26" t="n">
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C179" s="35" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D179" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5456,22 +5456,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F179" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G179" s="35" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="H179" s="35" t="str"/>
     </x:row>
-    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="180" ht="66" hidden="0" customHeight="1">
       <x:c r="A180" s="26" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="35" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C180" s="35" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D180" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5483,7 +5483,7 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G180" s="35" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="H180" s="35" t="str"/>
     </x:row>
@@ -5492,10 +5492,10 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C181" s="35" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D181" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5504,22 +5504,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F181" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G181" s="35" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="H181" s="35" t="str"/>
     </x:row>
-    <x:row r="182" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="182" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A182" s="26" t="n">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C182" s="35" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D182" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5531,19 +5531,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G182" s="35" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="H182" s="35" t="str"/>
     </x:row>
-    <x:row r="183" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A183" s="26" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="35" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C183" s="35" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D183" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5555,19 +5555,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G183" s="35" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="H183" s="35" t="str"/>
     </x:row>
-    <x:row r="184" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="184" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A184" s="26" t="n">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C184" s="35" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D184" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5576,22 +5576,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F184" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G184" s="35" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="H184" s="35" t="str"/>
     </x:row>
-    <x:row r="185" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="185" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A185" s="26" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C185" s="35" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D185" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5603,19 +5603,19 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G185" s="35" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="H185" s="35" t="str"/>
     </x:row>
-    <x:row r="186" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="186" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A186" s="26" t="n">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="35" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C186" s="35" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D186" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5624,10 +5624,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F186" s="32" t="n">
-        <x:v>0.038</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G186" s="35" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="H186" s="35" t="str"/>
     </x:row>
@@ -5639,7 +5639,7 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C187" s="35" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D187" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5651,19 +5651,19 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G187" s="35" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="H187" s="35" t="str"/>
     </x:row>
-    <x:row r="188" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="188" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A188" s="26" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C188" s="35" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D188" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5672,10 +5672,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F188" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G188" s="35" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="H188" s="35" t="str"/>
     </x:row>
@@ -5684,10 +5684,10 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B189" s="35" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C189" s="35" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D189" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5696,22 +5696,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F189" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="G189" s="35" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="H189" s="35" t="str"/>
     </x:row>
-    <x:row r="190" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="190" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A190" s="26" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B190" s="35" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C190" s="35" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D190" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5720,22 +5720,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F190" s="32" t="n">
-        <x:v>0.063</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G190" s="35" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="H190" s="35" t="str"/>
     </x:row>
-    <x:row r="191" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="191" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A191" s="26" t="n">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B191" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C191" s="35" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D191" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5744,10 +5744,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F191" s="32" t="n">
-        <x:v>0.035</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="G191" s="35" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="H191" s="35" t="str"/>
     </x:row>
@@ -5756,10 +5756,10 @@
         <x:v>188</x:v>
       </x:c>
       <x:c r="B192" s="35" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C192" s="35" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D192" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5768,22 +5768,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F192" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G192" s="35" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="H192" s="35" t="str"/>
     </x:row>
-    <x:row r="193" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A193" s="26" t="n">
         <x:v>189</x:v>
       </x:c>
       <x:c r="B193" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C193" s="35" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D193" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5792,22 +5792,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F193" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.061</x:v>
       </x:c>
       <x:c r="G193" s="35" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="H193" s="35" t="str"/>
     </x:row>
-    <x:row r="194" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A194" s="26" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="B194" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C194" s="35" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D194" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5816,22 +5816,22 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F194" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="G194" s="35" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="H194" s="35" t="str"/>
     </x:row>
-    <x:row r="195" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="195" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A195" s="26" t="n">
         <x:v>191</x:v>
       </x:c>
       <x:c r="B195" s="35" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C195" s="35" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D195" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5840,10 +5840,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F195" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G195" s="35" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="H195" s="35" t="str"/>
     </x:row>
@@ -5855,7 +5855,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="35" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D196" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5867,11 +5867,11 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G196" s="35" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="H196" s="35" t="str"/>
     </x:row>
-    <x:row r="197" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="197" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A197" s="26" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -5879,7 +5879,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="35" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D197" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5888,10 +5888,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F197" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G197" s="35" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="H197" s="35" t="str"/>
     </x:row>
@@ -5903,7 +5903,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="35" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D198" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5915,7 +5915,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G198" s="35" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="H198" s="35" t="str"/>
     </x:row>
@@ -5927,7 +5927,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="35" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D199" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5936,10 +5936,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F199" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G199" s="35" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="H199" s="35" t="str"/>
     </x:row>
@@ -5951,7 +5951,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="35" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D200" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5960,14 +5960,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F200" s="32" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G200" s="35" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="H200" s="35" t="str"/>
     </x:row>
-    <x:row r="201" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="201" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A201" s="26" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -5975,7 +5975,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="35" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D201" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -5984,14 +5984,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F201" s="32" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G201" s="35" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="H201" s="35" t="str"/>
     </x:row>
-    <x:row r="202" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="202" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A202" s="26" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -5999,7 +5999,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="35" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D202" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6011,7 +6011,7 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G202" s="35" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="H202" s="35" t="str"/>
     </x:row>
@@ -6023,7 +6023,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="35" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D203" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6035,7 +6035,7 @@
         <x:v>0.002</x:v>
       </x:c>
       <x:c r="G203" s="35" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="H203" s="35" t="str"/>
     </x:row>
@@ -6047,7 +6047,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="35" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D204" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6056,14 +6056,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F204" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G204" s="35" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="H204" s="35" t="str"/>
     </x:row>
-    <x:row r="205" ht="132" hidden="0" customHeight="1">
+    <x:row r="205" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A205" s="26" t="n">
         <x:v>201</x:v>
       </x:c>
@@ -6071,7 +6071,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C205" s="35" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D205" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6083,11 +6083,11 @@
         <x:v>0.003</x:v>
       </x:c>
       <x:c r="G205" s="35" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="H205" s="35" t="str"/>
     </x:row>
-    <x:row r="206" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="206" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A206" s="26" t="n">
         <x:v>202</x:v>
       </x:c>
@@ -6095,7 +6095,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C206" s="35" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D206" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6104,14 +6104,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F206" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="G206" s="35" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="H206" s="35" t="str"/>
     </x:row>
-    <x:row r="207" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="207" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A207" s="26" t="n">
         <x:v>203</x:v>
       </x:c>
@@ -6119,7 +6119,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C207" s="35" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D207" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6128,10 +6128,10 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F207" s="32" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="G207" s="35" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="H207" s="35" t="str"/>
     </x:row>
@@ -6143,7 +6143,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C208" s="35" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D208" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6155,11 +6155,11 @@
         <x:v>0.001</x:v>
       </x:c>
       <x:c r="G208" s="35" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="H208" s="35" t="str"/>
     </x:row>
-    <x:row r="209" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="209" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A209" s="26" t="n">
         <x:v>205</x:v>
       </x:c>
@@ -6167,7 +6167,7 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C209" s="35" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D209" s="35" t="str">
         <x:v>默认场景</x:v>
@@ -6176,14 +6176,14 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F209" s="32" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="G209" s="35" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="H209" s="35" t="str"/>
     </x:row>
-    <x:row r="210" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="210" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A210" s="26" t="n">
         <x:v>206</x:v>
       </x:c>
@@ -6191,52 +6191,124 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C210" s="35" t="str">
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D210" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E210" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F210" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G210" s="35" t="str">
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+      </x:c>
+      <x:c r="H210" s="35" t="str"/>
+    </x:row>
+    <x:row r="211" ht="132" hidden="0" customHeight="1">
+      <x:c r="A211" s="26" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B211" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C211" s="35" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D211" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E211" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F211" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G211" s="35" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="H211" s="35" t="str"/>
+    </x:row>
+    <x:row r="212" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A212" s="26" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B212" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C212" s="35" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D212" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E212" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F212" s="32" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="G212" s="35" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="H212" s="35" t="str"/>
+    </x:row>
+    <x:row r="213" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A213" s="26" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B213" s="35" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C213" s="35" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D210" s="35" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E210" s="26" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F210" s="32" t="n">
+      <x:c r="D213" s="35" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E213" s="26" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F213" s="32" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="G213" s="35" t="str">
+        <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
+      </x:c>
+      <x:c r="H213" s="35" t="str"/>
+    </x:row>
+    <x:row r="214" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A214" s="27" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B214" s="36" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C214" s="36" t="str">
+        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
+      </x:c>
+      <x:c r="D214" s="36" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E214" s="27" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="F214" s="33" t="n">
         <x:v>0.003</x:v>
       </x:c>
-      <x:c r="G210" s="35" t="str">
-        <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
-      </x:c>
-      <x:c r="H210" s="35" t="str"/>
-    </x:row>
-    <x:row r="211" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A211" s="27" t="n">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B211" s="36" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
-      </x:c>
-      <x:c r="C211" s="36" t="str">
-        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
-      </x:c>
-      <x:c r="D211" s="36" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E211" s="27" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="F211" s="33" t="n">
-        <x:v>0.003</x:v>
-      </x:c>
-      <x:c r="G211" s="36" t="str">
+      <x:c r="G214" s="36" t="str">
         <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
       </x:c>
-      <x:c r="H211" s="36" t="str"/>
+      <x:c r="H214" s="36" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="E5:E211">
+  <x:conditionalFormatting sqref="E5:E214">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="错误"/>
@@ -6244,7 +6316,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6b8e2df80094ecd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9336592b1364790"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6351,7 +6423,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I5" s="54" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.013</x:v>
       </x:c>
       <x:c r="J5" s="57" t="str">
         <x:v>已登记</x:v>
@@ -6383,7 +6455,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I6" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="J6" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6415,7 +6487,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I7" s="55" t="n">
-        <x:v>0.006</x:v>
+        <x:v>0.014</x:v>
       </x:c>
       <x:c r="J7" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6447,7 +6519,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I8" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="J8" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6479,7 +6551,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I9" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J9" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6511,7 +6583,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I10" s="55" t="n">
-        <x:v>0.008</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J10" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6543,7 +6615,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I11" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.011</x:v>
       </x:c>
       <x:c r="J11" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6575,7 +6647,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I12" s="55" t="n">
-        <x:v>0.141</x:v>
+        <x:v>0.166</x:v>
       </x:c>
       <x:c r="J12" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6639,7 +6711,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I14" s="55" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.03</x:v>
       </x:c>
       <x:c r="J14" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6671,7 +6743,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I15" s="55" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.031</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6703,7 +6775,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I16" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.022</x:v>
       </x:c>
       <x:c r="J16" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6735,7 +6807,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I17" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J17" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6767,7 +6839,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I18" s="55" t="n">
-        <x:v>0.02</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="J18" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6799,7 +6871,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I19" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.016</x:v>
       </x:c>
       <x:c r="J19" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6831,7 +6903,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I20" s="55" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.023</x:v>
       </x:c>
       <x:c r="J20" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6863,7 +6935,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I21" s="55" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="J21" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6895,7 +6967,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I22" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J22" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6927,7 +6999,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I23" s="55" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.026</x:v>
       </x:c>
       <x:c r="J23" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6959,7 +7031,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I24" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J24" s="58" t="str">
         <x:v>已登记</x:v>
@@ -6991,7 +7063,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I25" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J25" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7023,7 +7095,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I26" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J26" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7055,7 +7127,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I27" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J27" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7087,7 +7159,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I28" s="55" t="n">
-        <x:v>0.074</x:v>
+        <x:v>0.11</x:v>
       </x:c>
       <x:c r="J28" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7119,7 +7191,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I29" s="55" t="n">
-        <x:v>0.087</x:v>
+        <x:v>0.08</x:v>
       </x:c>
       <x:c r="J29" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7151,7 +7223,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I30" s="55" t="n">
-        <x:v>0.091</x:v>
+        <x:v>0.068</x:v>
       </x:c>
       <x:c r="J30" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7247,7 +7319,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I33" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J33" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7343,7 +7415,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I36" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J36" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7407,7 +7479,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I38" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J38" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7439,7 +7511,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I39" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J39" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7503,7 +7575,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I41" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J41" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7535,7 +7607,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I42" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J42" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7567,7 +7639,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I43" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J43" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7599,7 +7671,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I44" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J44" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7631,7 +7703,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I45" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J45" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7695,7 +7767,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I47" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J47" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7759,7 +7831,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I49" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J49" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7951,7 +8023,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I55" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J55" s="58" t="str">
         <x:v>已登记</x:v>
@@ -7983,7 +8055,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I56" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J56" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8079,7 +8151,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I59" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J59" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8143,7 +8215,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I61" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J61" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8207,7 +8279,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I63" s="55" t="n">
-        <x:v>0.074</x:v>
+        <x:v>0.048</x:v>
       </x:c>
       <x:c r="J63" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8239,7 +8311,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I64" s="55" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J64" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8271,7 +8343,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I65" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J65" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8303,7 +8375,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I66" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J66" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8335,7 +8407,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I67" s="55" t="n">
-        <x:v>0.031</x:v>
+        <x:v>0.028</x:v>
       </x:c>
       <x:c r="J67" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8367,7 +8439,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I68" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J68" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8399,7 +8471,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I69" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J69" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8431,7 +8503,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I70" s="55" t="n">
-        <x:v>0.024</x:v>
+        <x:v>0.027</x:v>
       </x:c>
       <x:c r="J70" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8463,7 +8535,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I71" s="55" t="n">
-        <x:v>31.084</x:v>
+        <x:v>36.665</x:v>
       </x:c>
       <x:c r="J71" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8495,7 +8567,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I72" s="55" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.024</x:v>
       </x:c>
       <x:c r="J72" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8527,7 +8599,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I73" s="55" t="n">
-        <x:v>0.774</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J73" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8591,7 +8663,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I75" s="55" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.018</x:v>
       </x:c>
       <x:c r="J75" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8623,7 +8695,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I76" s="55" t="n">
-        <x:v>0.018</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J76" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8655,7 +8727,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I77" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.015</x:v>
       </x:c>
       <x:c r="J77" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8687,7 +8759,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I78" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J78" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8719,7 +8791,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I79" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J79" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8751,7 +8823,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I80" s="55" t="n">
-        <x:v>0.019</x:v>
+        <x:v>0.017</x:v>
       </x:c>
       <x:c r="J80" s="58" t="str">
         <x:v>已登记</x:v>
@@ -8783,33 +8855,33 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I81" s="55" t="n">
-        <x:v>0.035</x:v>
+        <x:v>0.038</x:v>
       </x:c>
       <x:c r="J81" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="82" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A82" s="42" t="n">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B82" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_hybrid.py</x:v>
       </x:c>
       <x:c r="C82" s="49" t="str">
-        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
+        <x:v>test_rrf_rewards_cross_retriever_agreement_without_mixing_raw_scores</x:v>
       </x:c>
       <x:c r="D82" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E82" s="49" t="str">
-        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
+        <x:v>验证 Hybrid 使用倒数排名融合奖励 BM25 与 Dense 共同命中的证据，而不直接相加尺度不同的原始分数。</x:v>
       </x:c>
       <x:c r="F82" s="49" t="str">
-        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
+        <x:v>两个检索器都返回的 Chunk 通过名次贡献叠加排到首位，分数符合 RRF 公式。</x:v>
       </x:c>
       <x:c r="G82" s="49" t="str">
-        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
+        <x:v>直接混合 BM25 与余弦分数会被某一分值尺度主导，导致融合不可解释。</x:v>
       </x:c>
       <x:c r="H82" s="52" t="str">
         <x:v>通过</x:v>
@@ -8826,22 +8898,22 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B83" s="49" t="str">
-        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
+        <x:v>tests/test_local_rag_hybrid.py</x:v>
       </x:c>
       <x:c r="C83" s="49" t="str">
-        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
+        <x:v>test_rrf_is_deterministic_and_rejects_invalid_configuration</x:v>
       </x:c>
       <x:c r="D83" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E83" s="49" t="str">
-        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
+        <x:v>验证 RRF 参数必须为正，并在融合分数相同时按确定性身份规则打破平局。</x:v>
       </x:c>
       <x:c r="F83" s="49" t="str">
-        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
+        <x:v>非法配置被拒绝，相同输入始终产生相同排序。</x:v>
       </x:c>
       <x:c r="G83" s="49" t="str">
-        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
+        <x:v>不稳定平局或无效参数会使重复评测和缓存结果不可比较。</x:v>
       </x:c>
       <x:c r="H83" s="52" t="str">
         <x:v>通过</x:v>
@@ -8853,91 +8925,91 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="132" hidden="0" customHeight="1">
+    <x:row r="84" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A84" s="42" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B84" s="49" t="str">
-        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
+        <x:v>tests/test_local_rag_hybrid_eval.py</x:v>
       </x:c>
       <x:c r="C84" s="49" t="str">
-        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
+        <x:v>test_hybrid_parameter_selection_uses_frozen_quality_first_order</x:v>
       </x:c>
       <x:c r="D84" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E84" s="49" t="str">
-        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
+        <x:v>验证 Hybrid 参数只按预先冻结的开发集规则选择：Recall@5、nDCG@5、回归数、延迟、较小 RRF k。</x:v>
       </x:c>
       <x:c r="F84" s="49" t="str">
-        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
+        <x:v>质量指标优先于速度，候选并列时按固定顺序确定唯一参数。</x:v>
       </x:c>
       <x:c r="G84" s="49" t="str">
-        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
+        <x:v>事后改变选参顺序或使用保留集调参会造成测试集泄漏和虚假提升。</x:v>
       </x:c>
       <x:c r="H84" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I84" s="55" t="n">
-        <x:v>30.792</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J84" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="132" hidden="0" customHeight="1">
+    <x:row r="85" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A85" s="42" t="n">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B85" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C85" s="49" t="str">
-        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
+        <x:v>test_query_expansion_preserves_original_and_adds_auditable_terms</x:v>
       </x:c>
       <x:c r="D85" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E85" s="49" t="str">
-        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
+        <x:v>验证规则查询扩展保留原问题，并把命中的中文科研术语追加为可审计英文术语。</x:v>
       </x:c>
       <x:c r="F85" s="49" t="str">
-        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
+        <x:v>短期记忆和长期记忆分别扩展为对应英文表达，且返回明确的来源到目标映射。</x:v>
       </x:c>
       <x:c r="G85" s="49" t="str">
-        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
+        <x:v>查询可能丢失用户原意、产生不可追踪改写，或无法跨越中英文词汇鸿沟。</x:v>
       </x:c>
       <x:c r="H85" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I85" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J85" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="86" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A86" s="42" t="n">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_query_rewrite.py</x:v>
       </x:c>
       <x:c r="C86" s="49" t="str">
-        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
+        <x:v>test_query_expansion_is_deterministic_and_leaves_unknown_query_unchanged</x:v>
       </x:c>
       <x:c r="D86" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E86" s="49" t="str">
-        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
+        <x:v>验证未登记术语不被猜测改写，并且相同输入的扩展结果完全一致。</x:v>
       </x:c>
       <x:c r="F86" s="49" t="str">
-        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
+        <x:v>未知问题原样返回，已知术语重复运行得到相同查询和匹配记录。</x:v>
       </x:c>
       <x:c r="G86" s="49" t="str">
-        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
+        <x:v>规则可能过度改写未知问题或产生不稳定结果，使 A/B 对照不可复现。</x:v>
       </x:c>
       <x:c r="H86" s="52" t="str">
         <x:v>通过</x:v>
@@ -8949,59 +9021,59 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="87" ht="132" hidden="0" customHeight="1">
       <x:c r="A87" s="42" t="n">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B87" s="49" t="str">
-        <x:v>tests/test_low_quality_generation.py</x:v>
+        <x:v>tests/test_local_rag_rewrite_ab.py</x:v>
       </x:c>
       <x:c r="C87" s="49" t="str">
-        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
+        <x:v>test_holdout_ab_detects_rank_regression_when_recall_at_five_is_unchanged</x:v>
       </x:c>
       <x:c r="D87" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E87" s="49" t="str">
-        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
+        <x:v>验证查询扩展即使保持 Recall@5，也会因相关证据排名下降而被标记为逐题回归。</x:v>
       </x:c>
       <x:c r="F87" s="49" t="str">
-        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
+        <x:v>保留集 Recall@5 差值为 0、nDCG@5 差值为负，且至少记录一个 regressed 用例。</x:v>
       </x:c>
       <x:c r="G87" s="49" t="str">
-        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
+        <x:v>逐题结论可能只看是否进入 Top5，掩盖证据从前排下滑的真实排序损失。</x:v>
       </x:c>
       <x:c r="H87" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I87" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>44.64</x:v>
       </x:c>
       <x:c r="J87" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="88" ht="132" hidden="0" customHeight="1">
       <x:c r="A88" s="42" t="n">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B88" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C88" s="49" t="str">
-        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
+        <x:v>test_low_quality_stop_returns_evidence_safe_answer_without_llm</x:v>
       </x:c>
       <x:c r="D88" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E88" s="49" t="str">
-        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
+        <x:v>验证第二轮仍低质量时跳过大模型并返回证据安全的降级答复。</x:v>
       </x:c>
       <x:c r="F88" s="49" t="str">
-        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
+        <x:v>回答明确标记证据不足、列出待核验候选，generation_skipped 为真且无 LLM 调用。</x:v>
       </x:c>
       <x:c r="G88" s="49" t="str">
-        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
+        <x:v>系统可能把低质量证据包装成确定结论，并继续浪费生成 Token。</x:v>
       </x:c>
       <x:c r="H88" s="52" t="str">
         <x:v>通过</x:v>
@@ -9013,33 +9085,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="89" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A89" s="42" t="n">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B89" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C89" s="49" t="str">
-        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
+        <x:v>test_accepted_retrieval_keeps_normal_generation_path</x:v>
       </x:c>
       <x:c r="D89" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E89" s="49" t="str">
-        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
+        <x:v>验证质量通过的检索仍走原有 Skill/生成路径。</x:v>
       </x:c>
       <x:c r="F89" s="49" t="str">
-        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
+        <x:v>accepted 状态正常执行技能并返回原回答。</x:v>
       </x:c>
       <x:c r="G89" s="49" t="str">
-        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
+        <x:v>质量闸门可能误拦截正常任务，造成不必要降级。</x:v>
       </x:c>
       <x:c r="H89" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I89" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J89" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9050,34 +9122,34 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B90" s="49" t="str">
-        <x:v>tests/test_multi_source_retrieval.py</x:v>
+        <x:v>tests/test_low_quality_generation.py</x:v>
       </x:c>
       <x:c r="C90" s="49" t="str">
-        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
+        <x:v>test_metrics_records_recovery_budget_and_generation_mode</x:v>
       </x:c>
       <x:c r="D90" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E90" s="49" t="str">
-        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
+        <x:v>验证指标记录检索恢复、预算耗尽、回答模式和生成跳过状态。</x:v>
       </x:c>
       <x:c r="F90" s="49" t="str">
-        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
+        <x:v>预算耗尽为真、恢复为假，answer_mode 与 generation_skipped 正确写入。</x:v>
       </x:c>
       <x:c r="G90" s="49" t="str">
-        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
+        <x:v>降级行为可能无法审计，后续无法比较 Replan、Reflection 与普通重试。</x:v>
       </x:c>
       <x:c r="H90" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I90" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J90" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="91" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A91" s="42" t="n">
         <x:v>87</x:v>
       </x:c>
@@ -9085,19 +9157,19 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C91" s="49" t="str">
-        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
+        <x:v>test_multi_source_retrieval_calls_both_tools_and_deduplicates_by_doi</x:v>
       </x:c>
       <x:c r="D91" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E91" s="49" t="str">
-        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
+        <x:v>验证 multi 模式调用 arXiv 与 OpenAlex，并按 DOI 合并重复论文。</x:v>
       </x:c>
       <x:c r="F91" s="49" t="str">
-        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
+        <x:v>两个 Tool 都执行，三条原始记录合并为两篇并记录一次去重。</x:v>
       </x:c>
       <x:c r="G91" s="49" t="str">
-        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
+        <x:v>多源模式可能只调用一个来源、保留重复论文或统计不一致。</x:v>
       </x:c>
       <x:c r="H91" s="52" t="str">
         <x:v>通过</x:v>
@@ -9109,7 +9181,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="132" hidden="0" customHeight="1">
+    <x:row r="92" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A92" s="42" t="n">
         <x:v>88</x:v>
       </x:c>
@@ -9117,19 +9189,19 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C92" s="49" t="str">
-        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
+        <x:v>test_multi_source_retrieval_keeps_success_when_one_provider_fails</x:v>
       </x:c>
       <x:c r="D92" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E92" s="49" t="str">
-        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
+        <x:v>验证一个论文来源超时时，多源检索仍使用另一个成功来源。</x:v>
       </x:c>
       <x:c r="F92" s="49" t="str">
-        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
+        <x:v>保留 OpenAlex 论文和 arXiv TIMEOUT 明细，不错误触发静态兜底。</x:v>
       </x:c>
       <x:c r="G92" s="49" t="str">
-        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
+        <x:v>局部数据源故障可能拖垮整个检索，或掩盖成功结果与失败原因。</x:v>
       </x:c>
       <x:c r="H92" s="52" t="str">
         <x:v>通过</x:v>
@@ -9141,7 +9213,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="93" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A93" s="42" t="n">
         <x:v>89</x:v>
       </x:c>
@@ -9149,19 +9221,19 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C93" s="49" t="str">
-        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
+        <x:v>test_multi_source_retrieval_uses_reranker_only_when_feature_flag_is_enabled</x:v>
       </x:c>
       <x:c r="D93" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E93" s="49" t="str">
-        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
+        <x:v>验证跨来源重排只有在功能开关开启时接入真实 multi 检索流程。</x:v>
       </x:c>
       <x:c r="F93" s="49" t="str">
-        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
+        <x:v>OpenAlex 高相关候选升到首位，并记录确定性重排策略和完整候选数。</x:v>
       </x:c>
       <x:c r="G93" s="49" t="str">
-        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
+        <x:v>重排器可能没有进入运行时，或无法通过开关安全回滚到原有合并策略。</x:v>
       </x:c>
       <x:c r="H93" s="52" t="str">
         <x:v>通过</x:v>
@@ -9173,7 +9245,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="94" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A94" s="42" t="n">
         <x:v>90</x:v>
       </x:c>
@@ -9181,51 +9253,51 @@
         <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C94" s="49" t="str">
-        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
+        <x:v>test_multi_source_metadata_verification_can_quarantine_unsafe_record</x:v>
       </x:c>
       <x:c r="D94" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E94" s="49" t="str">
-        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
+        <x:v>验证权威元数据校验开关接入真实多来源检索并隔离低可信身份记录。</x:v>
       </x:c>
       <x:c r="F94" s="49" t="str">
-        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
+        <x:v>不相关标题与未经原生来源确认的 arXiv DOI 被移出候选，同时输出 v2 策略和隔离计数。</x:v>
       </x:c>
       <x:c r="G94" s="49" t="str">
-        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
+        <x:v>校验器可能只在评测中生效而没有保护正式 LangGraph 检索流程，或关闭后无法回滚。</x:v>
       </x:c>
       <x:c r="H94" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I94" s="55" t="n">
-        <x:v>0.009</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J94" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="95" ht="132" hidden="0" customHeight="1">
       <x:c r="A95" s="42" t="n">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C95" s="49" t="str">
-        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
+        <x:v>test_arxiv_authority_switch_is_independent_from_legacy_metadata_gate</x:v>
       </x:c>
       <x:c r="D95" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E95" s="49" t="str">
-        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
+        <x:v>验证 arXiv 原生身份验证可独立于旧版词法元数据开关受控启用。</x:v>
       </x:c>
       <x:c r="F95" s="49" t="str">
-        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
+        <x:v>旧 v2 开关关闭时，独立开关仍能注入原生证据、修复标题并记录 lookup 工具。</x:v>
       </x:c>
       <x:c r="G95" s="49" t="str">
-        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
+        <x:v>已通过三快照门槛的 v3 可能被旧综合开关绑定，无法安全灰度或单独回滚。</x:v>
       </x:c>
       <x:c r="H95" s="52" t="str">
         <x:v>通过</x:v>
@@ -9237,71 +9309,71 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="132" hidden="0" customHeight="1">
+    <x:row r="96" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A96" s="42" t="n">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C96" s="49" t="str">
-        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
+        <x:v>test_doi_authority_switch_loads_crossref_without_legacy_gate</x:v>
       </x:c>
       <x:c r="D96" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E96" s="49" t="str">
-        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
+        <x:v>验证 DOI authority 可通过独立开关接入生产多源重排。</x:v>
       </x:c>
       <x:c r="F96" s="49" t="str">
-        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
+        <x:v>旧元数据开关关闭时仍可加载 Crossref 证据并修复污染标题。</x:v>
       </x:c>
       <x:c r="G96" s="49" t="str">
-        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
+        <x:v>普通 DOI 校验可能与旧综合开关耦合，无法单独灰度或回滚。</x:v>
       </x:c>
       <x:c r="H96" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I96" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J96" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="132" hidden="0" customHeight="1">
+    <x:row r="97" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A97" s="42" t="n">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B97" s="49" t="str">
-        <x:v>tests/test_openalex_tool.py</x:v>
+        <x:v>tests/test_multi_source_retrieval.py</x:v>
       </x:c>
       <x:c r="C97" s="49" t="str">
-        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
+        <x:v>test_failed_crossref_lookup_is_not_cached_or_negative_evidence</x:v>
       </x:c>
       <x:c r="D97" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E97" s="49" t="str">
-        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
+        <x:v>验证 Crossref 超时不会缓存或形成 DOI 负证据。</x:v>
       </x:c>
       <x:c r="F97" s="49" t="str">
-        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
+        <x:v>失败被记录到工具执行明细，authority 索引和缓存保持为空。</x:v>
       </x:c>
       <x:c r="G97" s="49" t="str">
-        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
+        <x:v>临时网络失败可能永久污染身份结论并误伤论文。</x:v>
       </x:c>
       <x:c r="H97" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I97" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.011</x:v>
       </x:c>
       <x:c r="J97" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="98" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A98" s="42" t="n">
         <x:v>94</x:v>
       </x:c>
@@ -9309,19 +9381,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C98" s="49" t="str">
-        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
+        <x:v>test_reconstruct_abstract_orders_openalex_inverted_positions</x:v>
       </x:c>
       <x:c r="D98" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E98" s="49" t="str">
-        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
+        <x:v>验证 OpenAlex 倒排摘要能够按照词位还原为可读文本。</x:v>
       </x:c>
       <x:c r="F98" s="49" t="str">
-        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
+        <x:v>乱序词典被恢复为正确句子，缺失摘要安全返回空串。</x:v>
       </x:c>
       <x:c r="G98" s="49" t="str">
-        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
+        <x:v>论文摘要可能词序错乱，污染相关性评分和最终答案。</x:v>
       </x:c>
       <x:c r="H98" s="52" t="str">
         <x:v>通过</x:v>
@@ -9333,7 +9405,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="99" ht="132" hidden="0" customHeight="1">
       <x:c r="A99" s="42" t="n">
         <x:v>95</x:v>
       </x:c>
@@ -9341,19 +9413,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C99" s="49" t="str">
-        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
+        <x:v>test_normalize_openalex_work_maps_stable_paper_fields</x:v>
       </x:c>
       <x:c r="D99" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E99" s="49" t="str">
-        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
+        <x:v>验证 OpenAlex Work 的作者、摘要、链接、DOI 和引用数映射到统一论文结构。</x:v>
       </x:c>
       <x:c r="F99" s="49" t="str">
-        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
+        <x:v>嵌套 API 字段被完整转换，来源明确标记为 openalex。</x:v>
       </x:c>
       <x:c r="G99" s="49" t="str">
-        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
+        <x:v>多数据源字段可能丢失或以不一致结构进入 LangGraph。</x:v>
       </x:c>
       <x:c r="H99" s="52" t="str">
         <x:v>通过</x:v>
@@ -9365,7 +9437,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="100" ht="132" hidden="0" customHeight="1">
       <x:c r="A100" s="42" t="n">
         <x:v>96</x:v>
       </x:c>
@@ -9373,31 +9445,31 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C100" s="49" t="str">
-        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
+        <x:v>test_openalex_client_sends_search_limits_identity_and_optional_key</x:v>
       </x:c>
       <x:c r="D100" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E100" s="49" t="str">
-        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
+        <x:v>验证 OpenAlex Client 使用官方 search 参数、数量限制、身份头和可选凭据。</x:v>
       </x:c>
       <x:c r="F100" s="49" t="str">
-        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
+        <x:v>请求 URL、per-page、API key、mailto、超时和 User-Agent 均符合配置。</x:v>
       </x:c>
       <x:c r="G100" s="49" t="str">
-        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
+        <x:v>请求可能使用过期参数、泄漏配置或绕过调用预算和超时。</x:v>
       </x:c>
       <x:c r="H100" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I100" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J100" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="101" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A101" s="42" t="n">
         <x:v>97</x:v>
       </x:c>
@@ -9405,19 +9477,19 @@
         <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C101" s="49" t="str">
-        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
+        <x:v>test_openalex_client_maps_rate_limit_for_executor_recovery</x:v>
       </x:c>
       <x:c r="D101" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E101" s="49" t="str">
-        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
+        <x:v>验证限流等 HTTP 错误不会被伪装成正常空结果。</x:v>
       </x:c>
       <x:c r="F101" s="49" t="str">
-        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
+        <x:v>429 被转换成 ToolRateLimitError，交给 Tool Executor 统一重试和记录。</x:v>
       </x:c>
       <x:c r="G101" s="49" t="str">
-        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
+        <x:v>网络失败可能被误判为无论文，导致无法观测、重试或定位问题。</x:v>
       </x:c>
       <x:c r="H101" s="52" t="str">
         <x:v>通过</x:v>
@@ -9429,33 +9501,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="102" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A102" s="42" t="n">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B102" s="49" t="str">
-        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C102" s="49" t="str">
-        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
+        <x:v>test_openalex_adapter_delegates_to_injected_client</x:v>
       </x:c>
       <x:c r="D102" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E102" s="49" t="str">
-        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
+        <x:v>验证 OpenAlex Adapter 保持统一 Tool 输入并调用可替换 Client。</x:v>
       </x:c>
       <x:c r="F102" s="49" t="str">
-        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
+        <x:v>查询词和最大数量不变，输出满足统一论文来源约定。</x:v>
       </x:c>
       <x:c r="G102" s="49" t="str">
-        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
+        <x:v>Adapter 可能篡改参数、耦合网络实现或返回非标准结构。</x:v>
       </x:c>
       <x:c r="H102" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I102" s="55" t="n">
-        <x:v>2.35</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J102" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9466,92 +9538,92 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B103" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C103" s="49" t="str">
-        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
+        <x:v>test_default_runtime_registers_and_routes_openalex_tool</x:v>
       </x:c>
       <x:c r="D103" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E103" s="49" t="str">
-        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
+        <x:v>验证默认 Tool Runtime 同时注册并可路由 OpenAlex 原生工具。</x:v>
       </x:c>
       <x:c r="F103" s="49" t="str">
-        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
+        <x:v>paper.search/openalex 稳定解析到 paper.search.openalex。</x:v>
       </x:c>
       <x:c r="G103" s="49" t="str">
-        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
+        <x:v>代码虽有 Adapter，但实际 LangGraph 运行时可能无法发现或调用。</x:v>
       </x:c>
       <x:c r="H103" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I103" s="55" t="n">
-        <x:v>0.039</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J103" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="104" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A104" s="42" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B104" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_openalex_tool.py</x:v>
       </x:c>
       <x:c r="C104" s="49" t="str">
-        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
+        <x:v>test_cache_keys_are_isolated_by_paper_source</x:v>
       </x:c>
       <x:c r="D104" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E104" s="49" t="str">
-        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
+        <x:v>验证同一查询在 arXiv 与 OpenAlex 使用独立缓存键。</x:v>
       </x:c>
       <x:c r="F104" s="49" t="str">
-        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
+        <x:v>来源不同得到不同键，同来源大小写和空格归一化后键保持一致。</x:v>
       </x:c>
       <x:c r="G104" s="49" t="str">
-        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
+        <x:v>不同数据源的论文可能互相污染缓存并产生虚假命中。</x:v>
       </x:c>
       <x:c r="H104" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I104" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J104" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="105" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A105" s="42" t="n">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B105" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval.py</x:v>
+        <x:v>tests/test_parallel_multi_query_eval.py</x:v>
       </x:c>
       <x:c r="C105" s="49" t="str">
-        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
+        <x:v>test_multi_query_parallel_benchmark_reports_gate_and_equivalence</x:v>
       </x:c>
       <x:c r="D105" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E105" s="49" t="str">
-        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
+        <x:v>验证子查询并行基准正确计算性能门槛，并保持结果与规划顺序一致。</x:v>
       </x:c>
       <x:c r="F105" s="49" t="str">
-        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
+        <x:v>结果与规划顺序一致率为 100%，acceptance_passed 与报告中的速度门槛计算一致。</x:v>
       </x:c>
       <x:c r="G105" s="49" t="str">
-        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
+        <x:v>基准可能错误计算晋升结论，或并发改变子查询合并语义；墙钟速度由独立 Benchmark 判定。</x:v>
       </x:c>
       <x:c r="H105" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I105" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>2.378</x:v>
       </x:c>
       <x:c r="J105" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9565,25 +9637,25 @@
         <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C106" s="49" t="str">
-        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
+        <x:v>test_parallel_retrieval_preserves_configured_source_order</x:v>
       </x:c>
       <x:c r="D106" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E106" s="49" t="str">
-        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
+        <x:v>验证来源完成顺序不同也不会改变配置顺序和合并结果顺序。</x:v>
       </x:c>
       <x:c r="F106" s="49" t="str">
-        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
+        <x:v>慢 arXiv 与快 OpenAlex 并发完成后仍按 arXiv、OpenAlex 顺序处理。</x:v>
       </x:c>
       <x:c r="G106" s="49" t="str">
-        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
+        <x:v>线程完成竞态可能导致结果排序和去重行为不可复现。</x:v>
       </x:c>
       <x:c r="H106" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I106" s="55" t="n">
-        <x:v>1.131</x:v>
+        <x:v>0.043</x:v>
       </x:c>
       <x:c r="J106" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9594,98 +9666,98 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B107" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C107" s="49" t="str">
-        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
+        <x:v>test_parallel_retrieval_keeps_partial_success</x:v>
       </x:c>
       <x:c r="D107" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E107" s="49" t="str">
-        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
+        <x:v>验证并行模式下单一来源空结果不影响另一来源成功返回。</x:v>
       </x:c>
       <x:c r="F107" s="49" t="str">
-        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
+        <x:v>OpenAlex 论文仍进入 multi_source 结果，不错误触发全局兜底。</x:v>
       </x:c>
       <x:c r="G107" s="49" t="str">
-        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
+        <x:v>一个来源异常可能取消其他来源结果，破坏原有失败恢复语义。</x:v>
       </x:c>
       <x:c r="H107" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I107" s="55" t="n">
-        <x:v>0.171</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J107" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="108" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A108" s="42" t="n">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B108" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C108" s="49" t="str">
-        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
+        <x:v>test_single_source_does_not_create_parallel_pool</x:v>
       </x:c>
       <x:c r="D108" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E108" s="49" t="str">
-        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
+        <x:v>验证单来源检索即使并行开关开启也不创建线程池。</x:v>
       </x:c>
       <x:c r="F108" s="49" t="str">
-        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
+        <x:v>arXiv 单来源继续走原有直接调用路径。</x:v>
       </x:c>
       <x:c r="G108" s="49" t="str">
-        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
+        <x:v>简单请求可能承担不必要的线程调度成本。</x:v>
       </x:c>
       <x:c r="H108" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I108" s="55" t="n">
-        <x:v>0.092</x:v>
+        <x:v>0.006</x:v>
       </x:c>
       <x:c r="J108" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="109" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A109" s="42" t="n">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B109" s="49" t="str">
-        <x:v>tests/test_parallel_retrieval_online.py</x:v>
+        <x:v>tests/test_parallel_retrieval.py</x:v>
       </x:c>
       <x:c r="C109" s="49" t="str">
-        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
+        <x:v>test_parallel_benchmark_reports_repeatable_speedup_and_equivalence</x:v>
       </x:c>
       <x:c r="D109" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E109" s="49" t="str">
-        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
+        <x:v>验证来源级并行在重复离线 I/O 实验中稳定降低延迟且保持结果一致。</x:v>
       </x:c>
       <x:c r="F109" s="49" t="str">
-        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
+        <x:v>至少获得 1.5 倍加速、30% 延迟下降和 100% 结果一致率。</x:v>
       </x:c>
       <x:c r="G109" s="49" t="str">
-        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
+        <x:v>单次偶然计时可能被误认为稳定性能提升，或并行改变业务结果。</x:v>
       </x:c>
       <x:c r="H109" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I109" s="55" t="n">
-        <x:v>0.047</x:v>
+        <x:v>1.158</x:v>
       </x:c>
       <x:c r="J109" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="110" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A110" s="42" t="n">
         <x:v>106</x:v>
       </x:c>
@@ -9693,57 +9765,57 @@
         <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C110" s="49" t="str">
-        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
+        <x:v>test_online_parallel_ab_reports_latency_equivalence_and_gate</x:v>
       </x:c>
       <x:c r="D110" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E110" s="49" t="str">
-        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
+        <x:v>验证在线串行/并行 A/B 同时记录延迟、结果重合率与晋升门槛。</x:v>
       </x:c>
       <x:c r="F110" s="49" t="str">
-        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
+        <x:v>请求数、P95、结果重合率和 acceptance_passed 均按成对实验正确计算。</x:v>
       </x:c>
       <x:c r="G110" s="49" t="str">
-        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
+        <x:v>在线性能结论可能缺少结果等价约束，导致以质量回归换取速度。</x:v>
       </x:c>
       <x:c r="H110" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I110" s="55" t="n">
-        <x:v>0.076</x:v>
+        <x:v>0.178</x:v>
       </x:c>
       <x:c r="J110" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="132" hidden="0" customHeight="1">
+    <x:row r="111" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A111" s="42" t="n">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B111" s="49" t="str">
-        <x:v>tests/test_quality_gate_eval.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C111" s="49" t="str">
-        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
+        <x:v>test_online_parallel_ab_counts_rate_limit_and_blocks_gate</x:v>
       </x:c>
       <x:c r="D111" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E111" s="49" t="str">
-        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
+        <x:v>验证外部来源限流会被单独统计并阻止并行开关晋升。</x:v>
       </x:c>
       <x:c r="F111" s="49" t="str">
-        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
+        <x:v>RATE_LIMITED 计数完整，acceptance_passed 为 false。</x:v>
       </x:c>
       <x:c r="G111" s="49" t="str">
-        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
+        <x:v>并行放大的限流风险可能被速度指标掩盖。</x:v>
       </x:c>
       <x:c r="H111" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I111" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.091</x:v>
       </x:c>
       <x:c r="J111" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9754,86 +9826,86 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B112" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C112" s="49" t="str">
-        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
+        <x:v>test_online_parallel_ab_blocks_equal_fallback_results_after_network_failure</x:v>
       </x:c>
       <x:c r="D112" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E112" s="49" t="str">
-        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
+        <x:v>验证网络全失败时，即使兜底结果完全相同也不能形成假阳性。</x:v>
       </x:c>
       <x:c r="F112" s="49" t="str">
-        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
+        <x:v>结果重合率可为 100%，但失败计数会阻止晋升。</x:v>
       </x:c>
       <x:c r="G112" s="49" t="str">
-        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
+        <x:v>相同兜底结果可能被误认成真实检索结果等价。</x:v>
       </x:c>
       <x:c r="H112" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I112" s="55" t="n">
-        <x:v>0.004</x:v>
+        <x:v>0.047</x:v>
       </x:c>
       <x:c r="J112" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="113" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A113" s="42" t="n">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B113" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_parallel_retrieval_online.py</x:v>
       </x:c>
       <x:c r="C113" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
+        <x:v>test_online_parallel_ab_rejects_invalid_budget_and_writes_report</x:v>
       </x:c>
       <x:c r="D113" s="49" t="str">
-        <x:v>qa-expected_suffixes0</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E113" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证在线评测拒绝空查询或非法预算，并能写出可审计 JSON。</x:v>
       </x:c>
       <x:c r="F113" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>非法输入抛出异常，合法报告可读且查询数正确。</x:v>
       </x:c>
       <x:c r="G113" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>评测可能无意产生零样本结论或无法留档。</x:v>
       </x:c>
       <x:c r="H113" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I113" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.089</x:v>
       </x:c>
       <x:c r="J113" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="114" ht="132" hidden="0" customHeight="1">
       <x:c r="A114" s="42" t="n">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B114" s="49" t="str">
-        <x:v>tests/test_query_plan.py</x:v>
+        <x:v>tests/test_quality_gate_eval.py</x:v>
       </x:c>
       <x:c r="C114" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
+        <x:v>test_quality_gate_blocks_low_quality_without_false_blocks_or_llm_cost</x:v>
       </x:c>
       <x:c r="D114" s="49" t="str">
-        <x:v>compare-expected_suffixes1</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E114" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证质量闸门能阻断低质量生成，同时不误拦截正常任务并减少模拟 LLM 成本。</x:v>
       </x:c>
       <x:c r="F114" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>阻断准确率和格式合规率 100%，误阻断率 0%，避免 4 次调用和 480 Token。</x:v>
       </x:c>
       <x:c r="G114" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>闸门可能漏放低质量证据、误阻断正常回答，或没有产生实际成本收益。</x:v>
       </x:c>
       <x:c r="H114" s="52" t="str">
         <x:v>通过</x:v>
@@ -9845,7 +9917,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="115" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A115" s="42" t="n">
         <x:v>111</x:v>
       </x:c>
@@ -9853,25 +9925,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C115" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
+        <x:v>test_deduplicate_queries_preserves_order_and_ignores_case</x:v>
       </x:c>
       <x:c r="D115" s="49" t="str">
-        <x:v>summarize-expected_suffixes2</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E115" s="49" t="str">
-        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
+        <x:v>验证查询去重忽略大小写和首尾空格，同时保留首次出现顺序。</x:v>
       </x:c>
       <x:c r="F115" s="49" t="str">
-        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
+        <x:v>重复 Graph RAG/Methods 被合并，输出顺序保持稳定。</x:v>
       </x:c>
       <x:c r="G115" s="49" t="str">
-        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
+        <x:v>可能产生重复检索、顺序变化或错误删除有效查询。</x:v>
       </x:c>
       <x:c r="H115" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I115" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J115" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9885,10 +9957,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C116" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[qa-expected_suffixes0]</x:v>
       </x:c>
       <x:c r="D116" s="49" t="str">
-        <x:v>recommend-expected_suffixes3</x:v>
+        <x:v>qa-expected_suffixes0</x:v>
       </x:c>
       <x:c r="E116" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9903,7 +9975,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I116" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J116" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9917,10 +9989,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C117" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[compare-expected_suffixes1]</x:v>
       </x:c>
       <x:c r="D117" s="49" t="str">
-        <x:v>citation-expected_suffixes4</x:v>
+        <x:v>compare-expected_suffixes1</x:v>
       </x:c>
       <x:c r="E117" s="49" t="str">
         <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
@@ -9935,13 +10007,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I117" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J117" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="118" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A118" s="42" t="n">
         <x:v>114</x:v>
       </x:c>
@@ -9949,25 +10021,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C118" s="49" t="str">
-        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[summarize-expected_suffixes2]</x:v>
       </x:c>
       <x:c r="D118" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>summarize-expected_suffixes2</x:v>
       </x:c>
       <x:c r="E118" s="49" t="str">
-        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F118" s="49" t="str">
-        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G118" s="49" t="str">
-        <x:v>查询改写异常可能导致完全不检索。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H118" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I118" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J118" s="58" t="str">
         <x:v>已登记</x:v>
@@ -9981,19 +10053,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C119" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[recommend-expected_suffixes3]</x:v>
       </x:c>
       <x:c r="D119" s="49" t="str">
-        <x:v>state0-simple</x:v>
+        <x:v>recommend-expected_suffixes3</x:v>
       </x:c>
       <x:c r="E119" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F119" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G119" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H119" s="52" t="str">
         <x:v>通过</x:v>
@@ -10013,31 +10085,31 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C120" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
+        <x:v>test_build_rule_based_sub_queries_for_each_task_type[citation-expected_suffixes4]</x:v>
       </x:c>
       <x:c r="D120" s="49" t="str">
-        <x:v>state1-simple</x:v>
+        <x:v>citation-expected_suffixes4</x:v>
       </x:c>
       <x:c r="E120" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证不同任务类型生成对应的规则子查询集合。</x:v>
       </x:c>
       <x:c r="F120" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>当前任务场景保留原查询，并追加预期的比较、总结、推荐或引用检索后缀。</x:v>
       </x:c>
       <x:c r="G120" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>任务类型与检索策略不匹配，可能漏找关键论文维度或增加无效查询。</x:v>
       </x:c>
       <x:c r="H120" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I120" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J120" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="121" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A121" s="42" t="n">
         <x:v>117</x:v>
       </x:c>
@@ -10045,25 +10117,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C121" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
+        <x:v>test_build_rule_based_sub_queries_falls_back_to_original_query</x:v>
       </x:c>
       <x:c r="D121" s="49" t="str">
-        <x:v>state2-complex</x:v>
+        <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E121" s="49" t="str">
-        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
+        <x:v>验证改写查询为空时使用原始用户问题兜底。</x:v>
       </x:c>
       <x:c r="F121" s="49" t="str">
-        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
+        <x:v>仍能得到 agentic rag 单查询，不会返回空规划。</x:v>
       </x:c>
       <x:c r="G121" s="49" t="str">
-        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
+        <x:v>查询改写异常可能导致完全不检索。</x:v>
       </x:c>
       <x:c r="H121" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I121" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J121" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10077,10 +10149,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C122" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state0-simple]</x:v>
       </x:c>
       <x:c r="D122" s="49" t="str">
-        <x:v>state3-complex</x:v>
+        <x:v>state0-simple</x:v>
       </x:c>
       <x:c r="E122" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -10109,10 +10181,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C123" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state1-simple]</x:v>
       </x:c>
       <x:c r="D123" s="49" t="str">
-        <x:v>state4-complex</x:v>
+        <x:v>state1-simple</x:v>
       </x:c>
       <x:c r="E123" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -10127,7 +10199,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I123" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J123" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10141,10 +10213,10 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C124" s="49" t="str">
-        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state2-complex]</x:v>
       </x:c>
       <x:c r="D124" s="49" t="str">
-        <x:v>state5-not_applicable</x:v>
+        <x:v>state2-complex</x:v>
       </x:c>
       <x:c r="E124" s="49" t="str">
         <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
@@ -10159,13 +10231,13 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I124" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J124" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="125" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A125" s="42" t="n">
         <x:v>121</x:v>
       </x:c>
@@ -10173,19 +10245,19 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C125" s="49" t="str">
-        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state3-complex]</x:v>
       </x:c>
       <x:c r="D125" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state3-complex</x:v>
       </x:c>
       <x:c r="E125" s="49" t="str">
-        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F125" s="49" t="str">
-        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G125" s="49" t="str">
-        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H125" s="52" t="str">
         <x:v>通过</x:v>
@@ -10205,25 +10277,25 @@
         <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C126" s="49" t="str">
-        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state4-complex]</x:v>
       </x:c>
       <x:c r="D126" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state4-complex</x:v>
       </x:c>
       <x:c r="E126" s="49" t="str">
-        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F126" s="49" t="str">
-        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G126" s="49" t="str">
-        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H126" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I126" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J126" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10234,98 +10306,98 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B127" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C127" s="49" t="str">
-        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
+        <x:v>test_classify_query_complexity_without_an_llm[state5-not_applicable]</x:v>
       </x:c>
       <x:c r="D127" s="49" t="str">
-        <x:v>默认场景</x:v>
+        <x:v>state5-not_applicable</x:v>
       </x:c>
       <x:c r="E127" s="49" t="str">
-        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
+        <x:v>验证本地复杂度规则可区分简单、复杂和不适用任务。</x:v>
       </x:c>
       <x:c r="F127" s="49" t="str">
-        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
+        <x:v>当前参数场景得到预期复杂度，并提供非空判断原因。</x:v>
       </x:c>
       <x:c r="G127" s="49" t="str">
-        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
+        <x:v>简单问题可能多检索浪费资源，复杂问题可能检索不足，或 PDF 被误规划。</x:v>
       </x:c>
       <x:c r="H127" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I127" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J127" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="128" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A128" s="42" t="n">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B128" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C128" s="49" t="str">
-        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
+        <x:v>test_query_plan_node_skips_pdf_reading_tasks</x:v>
       </x:c>
       <x:c r="D128" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E128" s="49" t="str">
-        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
+        <x:v>验证 PDF 阅读任务完全跳过外部检索规划。</x:v>
       </x:c>
       <x:c r="F128" s="49" t="str">
-        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
+        <x:v>子查询为空、规划关闭，复杂度和原因字段明确标记不适用。</x:v>
       </x:c>
       <x:c r="G128" s="49" t="str">
-        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
+        <x:v>PDF 分析可能错误触发搜索，增加延迟并混入外部内容。</x:v>
       </x:c>
       <x:c r="H128" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I128" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J128" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="132" hidden="0" customHeight="1">
+    <x:row r="129" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A129" s="42" t="n">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B129" s="49" t="str">
-        <x:v>tests/test_rag_eval_models.py</x:v>
+        <x:v>tests/test_query_plan.py</x:v>
       </x:c>
       <x:c r="C129" s="49" t="str">
-        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
+        <x:v>test_query_plan_node_preserves_and_extends_paper_metadata</x:v>
       </x:c>
       <x:c r="D129" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E129" s="49" t="str">
-        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
+        <x:v>验证查询规划在扩展论文元数据时保留已有请求信息。</x:v>
       </x:c>
       <x:c r="F129" s="49" t="str">
-        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
+        <x:v>request_id 保留，并新增一致的子查询、数量、复杂度和启用原因。</x:v>
       </x:c>
       <x:c r="G129" s="49" t="str">
-        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
+        <x:v>规划节点可能丢失追踪信息或写入相互矛盾的状态。</x:v>
       </x:c>
       <x:c r="H129" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I129" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J129" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="130" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A130" s="42" t="n">
         <x:v>126</x:v>
       </x:c>
@@ -10333,121 +10405,121 @@
         <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C130" s="49" t="str">
-        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
+        <x:v>test_rag_dataset_accepts_versioned_grounded_case</x:v>
       </x:c>
       <x:c r="D130" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E130" s="49" t="str">
-        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
+        <x:v>验证本地 RAG 评测数据能记录版本化问题、答案、证据片段、页码和来源。</x:v>
       </x:c>
       <x:c r="F130" s="49" t="str">
-        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
+        <x:v>合法数据通过校验，语料版本与证据页码可审计。</x:v>
       </x:c>
       <x:c r="G130" s="49" t="str">
-        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
+        <x:v>RAG 实验可能缺少可复现语料版本或人工证据依据。</x:v>
       </x:c>
       <x:c r="H130" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I130" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J130" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="132" hidden="0" customHeight="1">
+    <x:row r="131" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A131" s="42" t="n">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B131" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C131" s="49" t="str">
-        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
+        <x:v>test_rag_dataset_rejects_invalid_pages_and_duplicate_evidence</x:v>
       </x:c>
       <x:c r="D131" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E131" s="49" t="str">
-        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
+        <x:v>验证错误页码和重复证据身份会被评测契约拒绝。</x:v>
       </x:c>
       <x:c r="F131" s="49" t="str">
-        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
+        <x:v>页码倒置或跨案例重复 document/chunk 身份均触发 ValidationError。</x:v>
       </x:c>
       <x:c r="G131" s="49" t="str">
-        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
+        <x:v>脏标注可能污染 Recall、引用定位和技术选型结论。</x:v>
       </x:c>
       <x:c r="H131" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I131" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J131" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="132" ht="132" hidden="0" customHeight="1">
       <x:c r="A132" s="42" t="n">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B132" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C132" s="49" t="str">
-        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_dataset_allows_different_questions_to_share_evidence_chunk</x:v>
       </x:c>
       <x:c r="D132" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E132" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
+        <x:v>验证不同问题可以引用同一个真实证据块，同时仍禁止单个问题内部重复登记证据。</x:v>
       </x:c>
       <x:c r="F132" s="49" t="str">
-        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
+        <x:v>两个独立问题共享同一 document_id/chunk_id 时数据集通过校验。</x:v>
       </x:c>
       <x:c r="G132" s="49" t="str">
-        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
+        <x:v>契约会迫使标注者制造虚假 chunk ID，或无法表达一段原文支持多个问题的真实情况。</x:v>
       </x:c>
       <x:c r="H132" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I132" s="55" t="n">
-        <x:v>14.691</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J132" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="133" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A133" s="42" t="n">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B133" s="49" t="str">
-        <x:v>tests/test_rag_gold_dataset.py</x:v>
+        <x:v>tests/test_rag_eval_models.py</x:v>
       </x:c>
       <x:c r="C133" s="49" t="str">
-        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
+        <x:v>test_rag_experiment_config_keeps_technology_choices_replaceable</x:v>
       </x:c>
       <x:c r="D133" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E133" s="49" t="str">
-        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
+        <x:v>验证 Dense 与 Graph 等 RAG 技术通过统一配置字段替换，而非写死实现。</x:v>
       </x:c>
       <x:c r="F133" s="49" t="str">
-        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
+        <x:v>不同 retriever family、Embedding、Store 和 Graph Retriever 可使用独立 config_id。</x:v>
       </x:c>
       <x:c r="G133" s="49" t="str">
-        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
+        <x:v>项目可能在评测前绑定单一产品，无法进行公平单变量对照。</x:v>
       </x:c>
       <x:c r="H133" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I133" s="55" t="n">
-        <x:v>26.027</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J133" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10458,22 +10530,22 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B134" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C134" s="49" t="str">
-        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
+        <x:v>test_rag_gold_v1_has_balanced_corpus_and_question_coverage</x:v>
       </x:c>
       <x:c r="D134" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E134" s="49" t="str">
-        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
+        <x:v>验证首版人工金标准包含 16 题、覆盖全部 8 篇论文，并具有多种题型和两档难度。</x:v>
       </x:c>
       <x:c r="F134" s="49" t="str">
-        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
+        <x:v>语料、题型与难度覆盖满足首版设计矩阵，避免评测只偏向单篇或单类问题。</x:v>
       </x:c>
       <x:c r="G134" s="49" t="str">
-        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
+        <x:v>金标准可能遗漏论文或题型过于单一，使后续 BM25、Dense 与图检索对比失真。</x:v>
       </x:c>
       <x:c r="H134" s="52" t="str">
         <x:v>通过</x:v>
@@ -10485,97 +10557,97 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="135" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A135" s="42" t="n">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B135" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C135" s="49" t="str">
-        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
+        <x:v>test_rag_gold_v1_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D135" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E135" s="49" t="str">
-        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证人工证据原文确实存在于声明的 PDF 页序号。</x:v>
       </x:c>
       <x:c r="F135" s="49" t="str">
-        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
+        <x:v>16 题的证据片段与页码全部可回溯到本地原始论文。</x:v>
       </x:c>
       <x:c r="G135" s="49" t="str">
-        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
+        <x:v>参考答案可能引用错误页、错误论文或经过改写而无法核验的伪证据。</x:v>
       </x:c>
       <x:c r="H135" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I135" s="55" t="n">
-        <x:v>18.907</x:v>
+        <x:v>30.032</x:v>
       </x:c>
       <x:c r="J135" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="136" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A136" s="42" t="n">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B136" s="49" t="str">
-        <x:v>tests/test_rag_holdout_dataset.py</x:v>
+        <x:v>tests/test_rag_gold_dataset.py</x:v>
       </x:c>
       <x:c r="C136" s="49" t="str">
-        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
+        <x:v>test_rag_gold_builder_reproduces_committed_dataset</x:v>
       </x:c>
       <x:c r="D136" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E136" s="49" t="str">
-        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
+        <x:v>验证人工规格、PDF、Parser 与 Chunker 可确定性重建已提交的金标准 JSON。</x:v>
       </x:c>
       <x:c r="F136" s="49" t="str">
-        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
+        <x:v>重建结果逐字段等于版本控制中的数据集，包括真实 chunk ID 与证据片段。</x:v>
       </x:c>
       <x:c r="G136" s="49" t="str">
-        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
+        <x:v>标注产物可能不可复现，或处理组件变化后证据坐标已悄悄失效。</x:v>
       </x:c>
       <x:c r="H136" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I136" s="55" t="n">
-        <x:v>14.794</x:v>
+        <x:v>28.684</x:v>
       </x:c>
       <x:c r="J136" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="137" ht="132" hidden="0" customHeight="1">
       <x:c r="A137" s="42" t="n">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B137" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C137" s="49" t="str">
-        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
+        <x:v>test_holdout_has_ten_cases_and_no_development_evidence_pages</x:v>
       </x:c>
       <x:c r="D137" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E137" s="49" t="str">
-        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
+        <x:v>验证独立保留集包含 10 题、覆盖全部 8 篇论文，并且证据页不与开发集重叠。</x:v>
       </x:c>
       <x:c r="F137" s="49" t="str">
-        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
+        <x:v>保留集与开发集页面集合完全不相交，可用于检查冻结术语表的初步泛化。</x:v>
       </x:c>
       <x:c r="G137" s="49" t="str">
-        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
+        <x:v>保留题可能复用术语表设计时已见证据，导致把开发集拟合误判为泛化收益。</x:v>
       </x:c>
       <x:c r="H137" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I137" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.005</x:v>
       </x:c>
       <x:c r="J137" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10586,66 +10658,66 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B138" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C138" s="49" t="str">
-        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
+        <x:v>test_holdout_evidence_is_present_on_declared_pdf_page</x:v>
       </x:c>
       <x:c r="D138" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E138" s="49" t="str">
-        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
+        <x:v>逐题重新解析真实 PDF，验证保留集证据原文存在于声明页面。</x:v>
       </x:c>
       <x:c r="F138" s="49" t="str">
-        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
+        <x:v>10 个保留问题的原文片段和页码均可回溯到本地论文。</x:v>
       </x:c>
       <x:c r="G138" s="49" t="str">
-        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
+        <x:v>保留集可能含错误页码或不可核验的证据，使泛化评测失去可信基础。</x:v>
       </x:c>
       <x:c r="H138" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I138" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>19.055</x:v>
       </x:c>
       <x:c r="J138" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="139" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A139" s="42" t="n">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B139" s="49" t="str">
-        <x:v>tests/test_reranker.py</x:v>
+        <x:v>tests/test_rag_holdout_dataset.py</x:v>
       </x:c>
       <x:c r="C139" s="49" t="str">
-        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
+        <x:v>test_holdout_builder_reproduces_frozen_json</x:v>
       </x:c>
       <x:c r="D139" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E139" s="49" t="str">
-        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
+        <x:v>验证保留集可由冻结人工规格、PDF 和固定 Chunker 确定性重建。</x:v>
       </x:c>
       <x:c r="F139" s="49" t="str">
-        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
+        <x:v>重建 JSON 与已提交保留集逐字段一致。</x:v>
       </x:c>
       <x:c r="G139" s="49" t="str">
-        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
+        <x:v>评测输入可能漂移，无法确认不同检索方案是否使用同一保留集。</x:v>
       </x:c>
       <x:c r="H139" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I139" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>16.691</x:v>
       </x:c>
       <x:c r="J139" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="140" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A140" s="42" t="n">
         <x:v>136</x:v>
       </x:c>
@@ -10653,31 +10725,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C140" s="49" t="str">
-        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
+        <x:v>test_tokenize_handles_english_stopwords_and_chinese_characters</x:v>
       </x:c>
       <x:c r="D140" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E140" s="49" t="str">
-        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
+        <x:v>验证零 Token 重排器能稳定处理英文停用词和中文字符。</x:v>
       </x:c>
       <x:c r="F140" s="49" t="str">
-        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
+        <x:v>英文实词与中文字符被保留，常见英文停用词被删除。</x:v>
       </x:c>
       <x:c r="G140" s="49" t="str">
-        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
+        <x:v>中英文查询可能无法形成稳定特征，导致相关性评分失真。</x:v>
       </x:c>
       <x:c r="H140" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I140" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J140" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="141" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A141" s="42" t="n">
         <x:v>137</x:v>
       </x:c>
@@ -10685,31 +10757,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C141" s="49" t="str">
-        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
+        <x:v>test_metadata_verifier_detects_conflicting_arxiv_ids_and_missing_abstract</x:v>
       </x:c>
       <x:c r="D141" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E141" s="49" t="str">
-        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
+        <x:v>验证元数据校验器识别同一记录中的 arXiv ID 冲突和摘要缺失。</x:v>
       </x:c>
       <x:c r="F141" s="49" t="str">
-        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
+        <x:v>两个风险产生明确错误码并降低元数据质量分。</x:v>
       </x:c>
       <x:c r="G141" s="49" t="str">
-        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
+        <x:v>身份冲突或不完整论文可能以高可信度进入最终候选。</x:v>
       </x:c>
       <x:c r="H141" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I141" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J141" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="142" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A142" s="42" t="n">
         <x:v>138</x:v>
       </x:c>
@@ -10717,31 +10789,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C142" s="49" t="str">
-        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_reranker_promotes_query_relevant_openalex_candidate_into_top_k</x:v>
       </x:c>
       <x:c r="D142" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E142" s="49" t="str">
-        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
+        <x:v>验证统一重排能让被 arXiv 前五条遮挡的 OpenAlex 高相关论文进入 Top K。</x:v>
       </x:c>
       <x:c r="F142" s="49" t="str">
-        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
+        <x:v>Reflexion 论文从第二来源候选升至第一，并保留截断前候选数量。</x:v>
       </x:c>
       <x:c r="G142" s="49" t="str">
-        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
+        <x:v>multi 仍可能只保留第一来源结果，无法获得多来源互补收益。</x:v>
       </x:c>
       <x:c r="H142" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I142" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J142" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="143" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A143" s="42" t="n">
         <x:v>139</x:v>
       </x:c>
@@ -10749,25 +10821,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C143" s="49" t="str">
-        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
+        <x:v>test_reranker_interleaves_equal_relevance_candidates_by_source_rank</x:v>
       </x:c>
       <x:c r="D143" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E143" s="49" t="str">
-        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
+        <x:v>验证文本相关性相同时按各来源原始排名公平交错候选。</x:v>
       </x:c>
       <x:c r="F143" s="49" t="str">
-        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
+        <x:v>两个来源按照 A1/O1/A2/O2 排列，不再由来源列表顺序垄断 Top K。</x:v>
       </x:c>
       <x:c r="G143" s="49" t="str">
-        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
+        <x:v>弱文本信号场景仍可能被首个来源完全占据。</x:v>
       </x:c>
       <x:c r="H143" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I143" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J143" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10781,19 +10853,19 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C144" s="49" t="str">
-        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
+        <x:v>test_cross_source_title_conflict_is_visible_and_penalized</x:v>
       </x:c>
       <x:c r="D144" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E144" s="49" t="str">
-        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
+        <x:v>验证相同 DOI 的跨来源标题严重冲突会被合并、标记并降权。</x:v>
       </x:c>
       <x:c r="F144" s="49" t="str">
-        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
+        <x:v>重复论文只保留一条，记录两个来源及 CROSS_SOURCE_TITLE_CONFLICT。</x:v>
       </x:c>
       <x:c r="G144" s="49" t="str">
-        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
+        <x:v>OpenAlex 等来源的异常标题可能被当成可靠元数据进入高排名。</x:v>
       </x:c>
       <x:c r="H144" s="52" t="str">
         <x:v>通过</x:v>
@@ -10805,7 +10877,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="145" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A145" s="42" t="n">
         <x:v>141</x:v>
       </x:c>
@@ -10813,31 +10885,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C145" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
+        <x:v>test_authoritative_arxiv_record_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D145" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E145" s="49" t="str">
-        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
+        <x:v>验证相同 arXiv 身份存在原生 arXiv 证据时使用权威字段修复二级来源冲突。</x:v>
       </x:c>
       <x:c r="F145" s="49" t="str">
-        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
+        <x:v>即使 OpenAlex 记录先出现，最终标题也恢复为 arXiv 标题，并记录修复状态、动作和计数。</x:v>
       </x:c>
       <x:c r="G145" s="49" t="str">
-        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
+        <x:v>合并顺序可能错误决定规范标题，让污染或过期的二级来源覆盖原生元数据。</x:v>
       </x:c>
       <x:c r="H145" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I145" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J145" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" ht="132" hidden="0" customHeight="1">
+    <x:row r="146" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A146" s="42" t="n">
         <x:v>142</x:v>
       </x:c>
@@ -10845,25 +10917,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C146" s="49" t="str">
-        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
+        <x:v>test_unverified_arxiv_identity_with_unrelated_title_is_quarantined</x:v>
       </x:c>
       <x:c r="D146" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E146" s="49" t="str">
-        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
+        <x:v>验证只有二级来源声称 arXiv DOI 且标题与查询无关时执行隔离。</x:v>
       </x:c>
       <x:c r="F146" s="49" t="str">
-        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
+        <x:v>可疑记录不会进入排序结果，隔离明细保留身份、警告和动作以供审计。</x:v>
       </x:c>
       <x:c r="G146" s="49" t="str">
-        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
+        <x:v>伪造或错误关联的稳定 ID 可能借助身份信号进入高排名并污染答案。</x:v>
       </x:c>
       <x:c r="H146" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I146" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J146" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10877,25 +10949,25 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C147" s="49" t="str">
-        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
+        <x:v>test_unverified_but_query_supported_arxiv_identity_remains_available</x:v>
       </x:c>
       <x:c r="D147" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E147" s="49" t="str">
-        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
+        <x:v>验证尚无原生来源确认但标题与查询高度一致的二级来源记录不会被过度隔离。</x:v>
       </x:c>
       <x:c r="F147" s="49" t="str">
-        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
+        <x:v>记录保留在候选中并标为 SECONDARY_ACCEPTED，同时提示身份仍待确认。</x:v>
       </x:c>
       <x:c r="G147" s="49" t="str">
-        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
+        <x:v>元数据门槛可能过严而误删有价值论文，造成 Recall 回归。</x:v>
       </x:c>
       <x:c r="H147" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I147" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J147" s="58" t="str">
         <x:v>已登记</x:v>
@@ -10909,31 +10981,31 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C148" s="49" t="str">
-        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_secondary_claim_without_query_gate</x:v>
       </x:c>
       <x:c r="D148" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E148" s="49" t="str">
-        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
+        <x:v>验证取得原生 arXiv 证据后，身份判断不再依赖标题与用户查询的词法重合度。</x:v>
       </x:c>
       <x:c r="F148" s="49" t="str">
-        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
+        <x:v>即使查询故意无关，身份真实的二级记录仍被规范证据确认并保留。</x:v>
       </x:c>
       <x:c r="G148" s="49" t="str">
-        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
+        <x:v>相关性低可能继续被误判为身份造假，造成有价值论文被隔离。</x:v>
       </x:c>
       <x:c r="H148" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I148" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J148" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="149" ht="132" hidden="0" customHeight="1">
       <x:c r="A149" s="42" t="n">
         <x:v>145</x:v>
       </x:c>
@@ -10941,89 +11013,89 @@
         <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C149" s="49" t="str">
-        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
+        <x:v>test_canonical_arxiv_evidence_repairs_wrong_secondary_title</x:v>
       </x:c>
       <x:c r="D149" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E149" s="49" t="str">
-        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
+        <x:v>验证二级来源标题错误时使用同一 ID 的原生 arXiv 标题修复，而不是直接丢弃论文。</x:v>
       </x:c>
       <x:c r="F149" s="49" t="str">
-        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
+        <x:v>标题和摘要恢复为规范字段，记录修复动作且论文继续参与排序。</x:v>
       </x:c>
       <x:c r="G149" s="49" t="str">
-        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
+        <x:v>可修复的来源污染可能被保留为错误标题，或被过度隔离造成召回下降。</x:v>
       </x:c>
       <x:c r="H149" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I149" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J149" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="150" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A150" s="42" t="n">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B150" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C150" s="49" t="str">
-        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
+        <x:v>test_canonical_arxiv_not_found_is_explicit_negative_evidence</x:v>
       </x:c>
       <x:c r="D150" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E150" s="49" t="str">
-        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
+        <x:v>验证原生 arXiv 按 ID 明确查无记录时，将其作为身份声明无效的负证据。</x:v>
       </x:c>
       <x:c r="F150" s="49" t="str">
-        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
+        <x:v>记录以 AUTHORITATIVE_NOT_FOUND 状态隔离，并保留专用警告供审计。</x:v>
       </x:c>
       <x:c r="G150" s="49" t="str">
-        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
+        <x:v>不存在的 arXiv 身份可能因标题碰巧相关而绕过校验进入答案。</x:v>
       </x:c>
       <x:c r="H150" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I150" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J150" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="151" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A151" s="42" t="n">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B151" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C151" s="49" t="str">
-        <x:v>test_build_document_key_uses_stable_priority</x:v>
+        <x:v>test_crossref_doi_evidence_repairs_conflicting_secondary_title</x:v>
       </x:c>
       <x:c r="D151" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E151" s="49" t="str">
-        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
+        <x:v>验证同一普通 DOI 的 Crossref 规范标题可修复明显冲突的二级来源标题。</x:v>
       </x:c>
       <x:c r="F151" s="49" t="str">
-        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
+        <x:v>低相似度污染标题被替换，并记录 REPAIRED_TITLE_FROM_CROSSREF。</x:v>
       </x:c>
       <x:c r="G151" s="49" t="str">
-        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
+        <x:v>普通 DOI 证据可能只被记录却无法修复实际元数据污染。</x:v>
       </x:c>
       <x:c r="H151" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I151" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J151" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11034,22 +11106,22 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B152" s="49" t="str">
-        <x:v>tests/test_result_merger.py</x:v>
+        <x:v>tests/test_reranker.py</x:v>
       </x:c>
       <x:c r="C152" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
+        <x:v>test_crossref_doi_not_found_is_visible_but_does_not_quarantine</x:v>
       </x:c>
       <x:c r="D152" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E152" s="49" t="str">
-        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
+        <x:v>验证 Crossref 明确查无只形成可审计警告，不自动隔离普通 DOI。</x:v>
       </x:c>
       <x:c r="F152" s="49" t="str">
-        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
+        <x:v>记录 DOI_AUTHORITY_NOT_FOUND，论文仍保留在候选排序中。</x:v>
       </x:c>
       <x:c r="G152" s="49" t="str">
-        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
+        <x:v>单一规范源覆盖缺口可能被误当成虚假论文证据，造成召回损失。</x:v>
       </x:c>
       <x:c r="H152" s="52" t="str">
         <x:v>通过</x:v>
@@ -11061,7 +11133,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="153" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A153" s="42" t="n">
         <x:v>149</x:v>
       </x:c>
@@ -11069,19 +11141,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C153" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
+        <x:v>test_normalize_text_handles_none_whitespace_and_case</x:v>
       </x:c>
       <x:c r="D153" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E153" s="49" t="str">
-        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
+        <x:v>验证文档去重使用的文本归一化能处理空值、空格和大小写。</x:v>
       </x:c>
       <x:c r="F153" s="49" t="str">
-        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
+        <x:v>None 变为空串，Graph RAG 被稳定归一化为 graph rag。</x:v>
       </x:c>
       <x:c r="G153" s="49" t="str">
-        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
+        <x:v>同一文档可能因格式差异无法去重，或空值引发异常。</x:v>
       </x:c>
       <x:c r="H153" s="52" t="str">
         <x:v>通过</x:v>
@@ -11101,25 +11173,25 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C154" s="49" t="str">
-        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
+        <x:v>test_build_document_key_uses_stable_priority</x:v>
       </x:c>
       <x:c r="D154" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E154" s="49" t="str">
-        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
+        <x:v>验证文档唯一键按 DOI、entry_id、PDF URL、标题的稳定优先级选择。</x:v>
       </x:c>
       <x:c r="F154" s="49" t="str">
-        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
+        <x:v>跨源 DOI 优先，每种后备标识生成预期键，无标识文档返回空键。</x:v>
       </x:c>
       <x:c r="G154" s="49" t="str">
-        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
+        <x:v>同一论文可能生成不稳定键，导致重复或误合并。</x:v>
       </x:c>
       <x:c r="H154" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I154" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J154" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11133,19 +11205,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C155" s="49" t="str">
-        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
+        <x:v>test_merge_documents_deduplicates_across_groups_and_preserves_priority</x:v>
       </x:c>
       <x:c r="D155" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E155" s="49" t="str">
-        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
+        <x:v>验证多查询结果跨组去重，并保留首次出现的高优先级版本。</x:v>
       </x:c>
       <x:c r="F155" s="49" t="str">
-        <x:v>两条无去重键文档均被保留。</x:v>
+        <x:v>重复 entry_id 只保留 first，第二篇独立论文仍保留。</x:v>
       </x:c>
       <x:c r="G155" s="49" t="str">
-        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
+        <x:v>合并结果可能含重复论文或被后到的低优先级数据覆盖。</x:v>
       </x:c>
       <x:c r="H155" s="52" t="str">
         <x:v>通过</x:v>
@@ -11157,7 +11229,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="156" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A156" s="42" t="n">
         <x:v>152</x:v>
       </x:c>
@@ -11165,31 +11237,31 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C156" s="49" t="str">
-        <x:v>test_merge_documents_honors_max_documents</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_records_by_doi</x:v>
       </x:c>
       <x:c r="D156" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E156" s="49" t="str">
-        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
+        <x:v>验证 arXiv 与 OpenAlex 使用不同平台 ID 时仍能通过 DOI 识别同一论文。</x:v>
       </x:c>
       <x:c r="F156" s="49" t="str">
-        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
+        <x:v>大小写和 DOI URL 表示不同的两条记录只保留优先来源版本。</x:v>
       </x:c>
       <x:c r="G156" s="49" t="str">
-        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
+        <x:v>多源检索可能重复展示同一论文并浪费上下文 Token。</x:v>
       </x:c>
       <x:c r="H156" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I156" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J156" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="157" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A157" s="42" t="n">
         <x:v>153</x:v>
       </x:c>
@@ -11197,19 +11269,19 @@
         <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C157" s="49" t="str">
-        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
+        <x:v>test_merge_documents_deduplicates_cross_source_title_when_doi_is_missing</x:v>
       </x:c>
       <x:c r="D157" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E157" s="49" t="str">
-        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
+        <x:v>验证没有 DOI 的同一预印本可通过归一化标题跨来源去重。</x:v>
       </x:c>
       <x:c r="F157" s="49" t="str">
-        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
+        <x:v>不同平台 ID、标题大小写和空格不同的记录只保留 arXiv 优先版本。</x:v>
       </x:c>
       <x:c r="G157" s="49" t="str">
-        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
+        <x:v>无 DOI 预印本可能因平台 ID 不同而在多源结果中重复出现。</x:v>
       </x:c>
       <x:c r="H157" s="52" t="str">
         <x:v>通过</x:v>
@@ -11221,33 +11293,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="158" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A158" s="42" t="n">
         <x:v>154</x:v>
       </x:c>
       <x:c r="B158" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C158" s="49" t="str">
-        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
+        <x:v>test_merge_documents_keeps_documents_without_a_deduplication_key</x:v>
       </x:c>
       <x:c r="D158" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E158" s="49" t="str">
-        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
+        <x:v>验证缺少稳定标识的匿名结果不会被错误互相合并。</x:v>
       </x:c>
       <x:c r="F158" s="49" t="str">
-        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
+        <x:v>两条无去重键文档均被保留。</x:v>
       </x:c>
       <x:c r="G158" s="49" t="str">
-        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
+        <x:v>不同匿名内容可能被误删，造成检索信息丢失。</x:v>
       </x:c>
       <x:c r="H158" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I158" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J158" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11258,54 +11330,54 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B159" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C159" s="49" t="str">
-        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
+        <x:v>test_merge_documents_honors_max_documents</x:v>
       </x:c>
       <x:c r="D159" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E159" s="49" t="str">
-        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
+        <x:v>验证合并结果遵守最大文档数量限制。</x:v>
       </x:c>
       <x:c r="F159" s="49" t="str">
-        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
+        <x:v>五篇输入在上限为三时只返回前三篇。</x:v>
       </x:c>
       <x:c r="G159" s="49" t="str">
-        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
+        <x:v>上下文可能超过设定限制，增加 Token、延迟或截断风险。</x:v>
       </x:c>
       <x:c r="H159" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I159" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J159" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="160" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A160" s="42" t="n">
         <x:v>156</x:v>
       </x:c>
       <x:c r="B160" s="49" t="str">
-        <x:v>tests/test_retrieval_online_eval.py</x:v>
+        <x:v>tests/test_result_merger.py</x:v>
       </x:c>
       <x:c r="C160" s="49" t="str">
-        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
+        <x:v>test_merge_documents_with_stats_reports_counts</x:v>
       </x:c>
       <x:c r="D160" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E160" s="49" t="str">
-        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
+        <x:v>验证带统计的合并能准确报告原始数、合并数和去重数。</x:v>
       </x:c>
       <x:c r="F160" s="49" t="str">
-        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
+        <x:v>四条原始结果合并为三篇，准确报告去除一条重复。</x:v>
       </x:c>
       <x:c r="G160" s="49" t="str">
-        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
+        <x:v>去重效果指标可能与实际文档列表不一致。</x:v>
       </x:c>
       <x:c r="H160" s="52" t="str">
         <x:v>通过</x:v>
@@ -11317,7 +11389,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" ht="132" hidden="0" customHeight="1">
+    <x:row r="161" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A161" s="42" t="n">
         <x:v>157</x:v>
       </x:c>
@@ -11325,31 +11397,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C161" s="49" t="str">
-        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
+        <x:v>test_retrieval_dataset_loads_versioned_twenty_case_gold_standard</x:v>
       </x:c>
       <x:c r="D161" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E161" s="49" t="str">
-        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
+        <x:v>验证在线检索评测集具有固定版本、20 个唯一问题、统一 K 值和非空金标准论文。</x:v>
       </x:c>
       <x:c r="F161" s="49" t="str">
-        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
+        <x:v>评测输入可追溯且结构完整，不会因重复问题或缺少相关论文而污染指标。</x:v>
       </x:c>
       <x:c r="G161" s="49" t="str">
-        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
+        <x:v>评测集版本、规模或标注结构发生意外变化，历史结果将失去可比性。</x:v>
       </x:c>
       <x:c r="H161" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I161" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J161" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" ht="132" hidden="0" customHeight="1">
+    <x:row r="162" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A162" s="42" t="n">
         <x:v>158</x:v>
       </x:c>
@@ -11357,31 +11429,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C162" s="49" t="str">
-        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
+        <x:v>test_retrieval_dataset_rejects_duplicate_case_ids</x:v>
       </x:c>
       <x:c r="D162" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E162" s="49" t="str">
-        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
+        <x:v>验证评测集拒绝重复 case id，避免同一问题被重复计分。</x:v>
       </x:c>
       <x:c r="F162" s="49" t="str">
-        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
+        <x:v>重复标识会在加载阶段被明确拒绝。</x:v>
       </x:c>
       <x:c r="G162" s="49" t="str">
-        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
+        <x:v>重复问题可能被静默纳入平均值，造成检索质量指标偏差。</x:v>
       </x:c>
       <x:c r="H162" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I162" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J162" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="163" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A163" s="42" t="n">
         <x:v>159</x:v>
       </x:c>
@@ -11389,31 +11461,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C163" s="49" t="str">
-        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
+        <x:v>test_paper_identity_normalizes_doi_arxiv_id_and_title</x:v>
       </x:c>
       <x:c r="D163" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E163" s="49" t="str">
-        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
+        <x:v>验证 DOI、arXiv ID 和标题能被归一化为稳定的论文身份键。</x:v>
       </x:c>
       <x:c r="F163" s="49" t="str">
-        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
+        <x:v>不同 URL、大小写和标点形式仍能识别为同一论文。</x:v>
       </x:c>
       <x:c r="G163" s="49" t="str">
-        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
+        <x:v>同一论文可能无法匹配金标准或无法跨来源去重。</x:v>
       </x:c>
       <x:c r="H163" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I163" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J163" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="164" ht="132" hidden="0" customHeight="1">
       <x:c r="A164" s="42" t="n">
         <x:v>160</x:v>
       </x:c>
@@ -11421,19 +11493,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C164" s="49" t="str">
-        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
+        <x:v>test_gold_match_rejects_stable_identity_with_contradictory_title</x:v>
       </x:c>
       <x:c r="D164" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E164" s="49" t="str">
-        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
+        <x:v>验证 DOI/arXiv ID 相同但标题严重冲突的来源记录不会被金标准误判为相关论文。</x:v>
       </x:c>
       <x:c r="F164" s="49" t="str">
-        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
+        <x:v>异常 OpenAlex 标题即使复用了金标准 DOI，也不会虚增 Recall、MRR 或 nDCG。</x:v>
       </x:c>
       <x:c r="G164" s="49" t="str">
-        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
+        <x:v>来源元数据污染可能制造虚假能力提升，使重排技术选型结论失真。</x:v>
       </x:c>
       <x:c r="H164" s="52" t="str">
         <x:v>通过</x:v>
@@ -11445,7 +11517,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="165" ht="132" hidden="0" customHeight="1">
       <x:c r="A165" s="42" t="n">
         <x:v>161</x:v>
       </x:c>
@@ -11453,19 +11525,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C165" s="49" t="str">
-        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
+        <x:v>test_ranking_metrics_calculate_recall_precision_mrr_ndcg_and_dimensions</x:v>
       </x:c>
       <x:c r="D165" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E165" s="49" t="str">
-        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
+        <x:v>用手工可验证的排名检查 Recall、Precision、MRR、nDCG 和维度覆盖率公式。</x:v>
       </x:c>
       <x:c r="F165" s="49" t="str">
-        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
+        <x:v>相关论文位于第 2 名时，各项指标与预先计算值完全一致。</x:v>
       </x:c>
       <x:c r="G165" s="49" t="str">
-        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
+        <x:v>至少一个核心检索指标计算错误，在线来源对比结论不可信。</x:v>
       </x:c>
       <x:c r="H165" s="52" t="str">
         <x:v>通过</x:v>
@@ -11477,7 +11549,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="166" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A166" s="42" t="n">
         <x:v>162</x:v>
       </x:c>
@@ -11485,31 +11557,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C166" s="49" t="str">
-        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
+        <x:v>test_duplicate_rate_handles_zero_and_merged_counts</x:v>
       </x:c>
       <x:c r="D166" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E166" s="49" t="str">
-        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
+        <x:v>验证空结果和存在重复结果时的重复率计算边界。</x:v>
       </x:c>
       <x:c r="F166" s="49" t="str">
-        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
+        <x:v>空结果返回 0%，4 条合并为 3 条时返回 25%。</x:v>
       </x:c>
       <x:c r="G166" s="49" t="str">
-        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
+        <x:v>重复率可能除零或错误反映多来源结果冗余。</x:v>
       </x:c>
       <x:c r="H166" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I166" s="55" t="n">
-        <x:v>0.084</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J166" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="167" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A167" s="42" t="n">
         <x:v>163</x:v>
       </x:c>
@@ -11517,19 +11589,19 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C167" s="49" t="str">
-        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
+        <x:v>test_multi_profile_deduplicates_and_records_partial_provider_failure</x:v>
       </x:c>
       <x:c r="D167" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E167" s="49" t="str">
-        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
+        <x:v>验证多来源评测在一个来源失败时仍合并成功来源，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F167" s="49" t="str">
-        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
+        <x:v>结果标记为部分成功，相关论文仍被命中，TIMEOUT 明细可追踪。</x:v>
       </x:c>
       <x:c r="G167" s="49" t="str">
-        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
+        <x:v>单来源故障可能拖垮整个评测，或错误被隐藏为正常空结果。</x:v>
       </x:c>
       <x:c r="H167" s="52" t="str">
         <x:v>通过</x:v>
@@ -11541,7 +11613,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="168" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A168" s="42" t="n">
         <x:v>164</x:v>
       </x:c>
@@ -11549,31 +11621,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C168" s="49" t="str">
-        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
+        <x:v>test_successful_zero_result_is_empty_instead_of_failed</x:v>
       </x:c>
       <x:c r="D168" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E168" s="49" t="str">
-        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
+        <x:v>验证来源正常响应但没有论文时标记为 empty，而不是网络或执行失败。</x:v>
       </x:c>
       <x:c r="F168" s="49" t="str">
-        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
+        <x:v>空结果与工具故障采用不同状态，且不会产生虚假的来源错误。</x:v>
       </x:c>
       <x:c r="G168" s="49" t="str">
-        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
+        <x:v>失败率会混入正常零结果，导致可靠性与检索覆盖问题无法区分。</x:v>
       </x:c>
       <x:c r="H168" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I168" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J168" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" ht="158.39999389648438" hidden="0" customHeight="1">
+    <x:row r="169" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A169" s="42" t="n">
         <x:v>165</x:v>
       </x:c>
@@ -11581,31 +11653,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C169" s="49" t="str">
-        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
+        <x:v>test_online_benchmark_reuses_provider_results_across_profiles</x:v>
       </x:c>
       <x:c r="D169" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E169" s="49" t="str">
-        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
+        <x:v>验证同一问题的原始来源响应会在 arXiv、OpenAlex 和 multi 配置间复用。</x:v>
       </x:c>
       <x:c r="F169" s="49" t="str">
-        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
+        <x:v>每个来源只调用一次，三种配置基于相同快照比较，避免浪费 API 配额。</x:v>
       </x:c>
       <x:c r="G169" s="49" t="str">
-        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
+        <x:v>同一轮对比可能重复联网，增加耗时、限流风险并破坏公平性。</x:v>
       </x:c>
       <x:c r="H169" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I169" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.091</x:v>
       </x:c>
       <x:c r="J169" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" ht="132" hidden="0" customHeight="1">
+    <x:row r="170" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A170" s="42" t="n">
         <x:v>166</x:v>
       </x:c>
@@ -11613,31 +11685,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C170" s="49" t="str">
-        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
+        <x:v>test_verified_rerank_reports_quarantined_secondary_identity</x:v>
       </x:c>
       <x:c r="D170" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E170" s="49" t="str">
-        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
+        <x:v>验证在线评测为元数据校验策略单独记录隔离数量和规范身份。</x:v>
       </x:c>
       <x:c r="F170" s="49" t="str">
-        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
+        <x:v>被隔离论文不计入返回结果，报告仍保存 arXiv 规范身份供异常追踪。</x:v>
       </x:c>
       <x:c r="G170" s="49" t="str">
-        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
+        <x:v>评测可能遗漏校验器的实际动作，导致质量不变时无法证明异常记录已被清除。</x:v>
       </x:c>
       <x:c r="H170" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I170" s="55" t="n">
-        <x:v>0.178</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J170" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="171" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A171" s="42" t="n">
         <x:v>167</x:v>
       </x:c>
@@ -11645,31 +11717,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C171" s="49" t="str">
-        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
+        <x:v>test_missing_openalex_key_is_explicitly_skipped_without_network</x:v>
       </x:c>
       <x:c r="D171" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E171" s="49" t="str">
-        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
+        <x:v>验证缺少 OpenAlex API Key 时明确跳过该来源且不发起网络请求。</x:v>
       </x:c>
       <x:c r="F171" s="49" t="str">
-        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
+        <x:v>报告记录 MISSING_API_KEY，实际 API 调用数保持为零。</x:v>
       </x:c>
       <x:c r="G171" s="49" t="str">
-        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
+        <x:v>无凭据运行可能消耗匿名额度，或把配置缺失误报为检索质量差。</x:v>
       </x:c>
       <x:c r="H171" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I171" s="55" t="n">
-        <x:v>0.007</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J171" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="172" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A172" s="42" t="n">
         <x:v>168</x:v>
       </x:c>
@@ -11677,31 +11749,31 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C172" s="49" t="str">
-        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
+        <x:v>test_arxiv_pacing_waits_only_for_remaining_interval</x:v>
       </x:c>
       <x:c r="D172" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E172" s="49" t="str">
-        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
+        <x:v>验证在线评测在连续 arXiv 请求之间只等待尚未满足的全局间隔，并能识别 HTTP 429。</x:v>
       </x:c>
       <x:c r="F172" s="49" t="str">
-        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
+        <x:v>已过去 2.5 秒时只等待剩余 3.5 秒，OpenAlex 不受该节流影响，429 可触发恢复。</x:v>
       </x:c>
       <x:c r="G172" s="49" t="str">
-        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
+        <x:v>评测可能请求过快触发限流，或不必要地拖慢其他论文来源。</x:v>
       </x:c>
       <x:c r="H172" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I172" s="55" t="n">
-        <x:v>0.012</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J172" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="173" ht="132" hidden="0" customHeight="1">
       <x:c r="A173" s="42" t="n">
         <x:v>169</x:v>
       </x:c>
@@ -11709,89 +11781,89 @@
         <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C173" s="49" t="str">
-        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
+        <x:v>test_online_report_writes_json_summary_case_and_paper_tables</x:v>
       </x:c>
       <x:c r="D173" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E173" s="49" t="str">
-        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
+        <x:v>验证在线评测可同时输出机器可读 JSON、快照清单及总览、逐题、论文明细 CSV。</x:v>
       </x:c>
       <x:c r="F173" s="49" t="str">
-        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
+        <x:v>报告文件和快照清单均成功生成，且清单保存稳定的快照身份。</x:v>
       </x:c>
       <x:c r="G173" s="49" t="str">
-        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
+        <x:v>评测结果无法沉淀为可审计数据，Excel 和历史对比也无法稳定生成。</x:v>
       </x:c>
       <x:c r="H173" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I173" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.181</x:v>
       </x:c>
       <x:c r="J173" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="174" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A174" s="42" t="n">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B174" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C174" s="49" t="str">
-        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
+        <x:v>test_snapshot_id_is_path_safe_and_uses_isolated_directory</x:v>
       </x:c>
       <x:c r="D174" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E174" s="49" t="str">
-        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
+        <x:v>验证在线评测快照 ID 只能使用安全字符，并映射到独立快照目录。</x:v>
       </x:c>
       <x:c r="F174" s="49" t="str">
-        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
+        <x:v>合法 ID 获得独立目录，路径穿越、嵌套路径、空值和非约定字符均被拒绝。</x:v>
       </x:c>
       <x:c r="G174" s="49" t="str">
-        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
+        <x:v>快照名称可能逃逸评测目录、覆盖其他文件，或让两次来源响应混入同一实验。</x:v>
       </x:c>
       <x:c r="H174" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I174" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="J174" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="175" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A175" s="42" t="n">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B175" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C175" s="49" t="str">
-        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
+        <x:v>test_existing_snapshot_requires_explicit_resume</x:v>
       </x:c>
       <x:c r="D175" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E175" s="49" t="str">
-        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
+        <x:v>验证已有在线评测快照默认不可覆盖，只有显式续跑才能复用其成功响应。</x:v>
       </x:c>
       <x:c r="F175" s="49" t="str">
-        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
+        <x:v>普通运行遇到已有快照立即失败，resume 模式准确返回原快照目录。</x:v>
       </x:c>
       <x:c r="G175" s="49" t="str">
-        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
+        <x:v>第二次实验可能静默覆盖第一份证据，导致跨快照结论无法审计和复现。</x:v>
       </x:c>
       <x:c r="H175" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I175" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J175" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11802,34 +11874,34 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B176" s="49" t="str">
-        <x:v>tests/test_retrieval_replan.py</x:v>
+        <x:v>tests/test_retrieval_online_eval.py</x:v>
       </x:c>
       <x:c r="C176" s="49" t="str">
-        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
+        <x:v>test_arxiv_network_failure_propagates_to_tool_executor</x:v>
       </x:c>
       <x:c r="D176" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E176" s="49" t="str">
-        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
+        <x:v>验证 arXiv 网络异常会传递给 Tool Executor，而不是被伪装成零篇论文。</x:v>
       </x:c>
       <x:c r="F176" s="49" t="str">
-        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
+        <x:v>连接失败保留异常语义，可由统一执行层记录、重试或降级。</x:v>
       </x:c>
       <x:c r="G176" s="49" t="str">
-        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
+        <x:v>真实故障可能被误判为正常无结果，导致失败率和恢复指标失真。</x:v>
       </x:c>
       <x:c r="H176" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I176" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J176" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="177" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A177" s="42" t="n">
         <x:v>173</x:v>
       </x:c>
@@ -11837,51 +11909,51 @@
         <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C177" s="49" t="str">
-        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
+        <x:v>test_replan_retries_same_query_for_transient_tool_failure</x:v>
       </x:c>
       <x:c r="D177" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E177" s="49" t="str">
-        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
+        <x:v>验证超时等暂时工具错误不会被误判为查询质量问题。</x:v>
       </x:c>
       <x:c r="F177" s="49" t="str">
-        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
+        <x:v>保持原查询重试一次，并记录失败类型、错误码和重试次数。</x:v>
       </x:c>
       <x:c r="G177" s="49" t="str">
-        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
+        <x:v>网络故障可能触发无意义查询改写，降低恢复概率。</x:v>
       </x:c>
       <x:c r="H177" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I177" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J177" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="178" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A178" s="42" t="n">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B178" s="49" t="str">
-        <x:v>tests/test_retrieval_replan_eval.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C178" s="49" t="str">
-        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
+        <x:v>test_replan_broadens_empty_query_without_llm</x:v>
       </x:c>
       <x:c r="D178" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E178" s="49" t="str">
-        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
+        <x:v>验证零结果场景使用确定性规则放宽过窄查询。</x:v>
       </x:c>
       <x:c r="F178" s="49" t="str">
-        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
+        <x:v>去除引号和括号并追加 research survey，不产生 LLM 调用。</x:v>
       </x:c>
       <x:c r="G178" s="49" t="str">
-        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
+        <x:v>空结果可能原样重试，重复消耗工具预算。</x:v>
       </x:c>
       <x:c r="H178" s="52" t="str">
         <x:v>通过</x:v>
@@ -11898,54 +11970,54 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B179" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C179" s="49" t="str">
-        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
+        <x:v>test_replan_expands_low_relevance_query_and_records_reason</x:v>
       </x:c>
       <x:c r="D179" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E179" s="49" t="str">
-        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
+        <x:v>验证有结果但相关性低时扩展综述上下文并记录评分原因。</x:v>
       </x:c>
       <x:c r="F179" s="49" t="str">
-        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
+        <x:v>追加 survey review，审计记录包含 low_relevance 与原评分。</x:v>
       </x:c>
       <x:c r="G179" s="49" t="str">
-        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
+        <x:v>低相关结果可能只通过扩大数量重试而不改变检索意图。</x:v>
       </x:c>
       <x:c r="H179" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I179" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J179" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="180" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A180" s="42" t="n">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B180" s="49" t="str">
-        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
+        <x:v>tests/test_retrieval_replan.py</x:v>
       </x:c>
       <x:c r="C180" s="49" t="str">
-        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
+        <x:v>test_retry_query_overrides_old_multi_query_plan</x:v>
       </x:c>
       <x:c r="D180" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E180" s="49" t="str">
-        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
+        <x:v>验证重规划查询优先于旧的多子查询计划。</x:v>
       </x:c>
       <x:c r="F180" s="49" t="str">
-        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
+        <x:v>第二轮只执行 retry_query，不重复运行已经失败的旧计划。</x:v>
       </x:c>
       <x:c r="G180" s="49" t="str">
-        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
+        <x:v>重规划动作可能被旧 sub_queries 遮蔽，形成伪 Replan。</x:v>
       </x:c>
       <x:c r="H180" s="52" t="str">
         <x:v>通过</x:v>
@@ -11957,33 +12029,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="181" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A181" s="42" t="n">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B181" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_replan_eval.py</x:v>
       </x:c>
       <x:c r="C181" s="49" t="str">
-        <x:v>test_first_low_score_requests_replan</x:v>
+        <x:v>test_replan_outperforms_plain_retry_and_meets_acceptance_gate</x:v>
       </x:c>
       <x:c r="D181" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E181" s="49" t="str">
-        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
+        <x:v>验证固定故障集中 Replan 相对原样重试提升恢复率并减少无效重试。</x:v>
       </x:c>
       <x:c r="F181" s="49" t="str">
-        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
+        <x:v>分类准确率 100%，候选恢复率达到门槛、语义失败无效重试率为 0，且不调用 LLM。</x:v>
       </x:c>
       <x:c r="G181" s="49" t="str">
-        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
+        <x:v>Replan 可能只改变查询形式却没有改善受控恢复结果，或引入额外 Token 成本。</x:v>
       </x:c>
       <x:c r="H181" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I181" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J181" s="58" t="str">
         <x:v>已登记</x:v>
@@ -11994,22 +12066,22 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B182" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C182" s="49" t="str">
-        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
+        <x:v>test_snapshot_comparison_passes_stable_complete_non_regressing_candidate</x:v>
       </x:c>
       <x:c r="D182" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E182" s="49" t="str">
-        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
+        <x:v>验证两份完整快照在质量不回归且隔离集合稳定时可以通过晋升门槛。</x:v>
       </x:c>
       <x:c r="F182" s="49" t="str">
-        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
+        <x:v>质量提升、逐题无回归、隔离集合完全一致，比较器明确返回 promotion_ready。</x:v>
       </x:c>
       <x:c r="G182" s="49" t="str">
-        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
+        <x:v>稳定候选可能因比较口径错误被拒绝，阻碍经过复现验证的能力晋升。</x:v>
       </x:c>
       <x:c r="H182" s="52" t="str">
         <x:v>通过</x:v>
@@ -12021,27 +12093,27 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="183" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A183" s="42" t="n">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B183" s="49" t="str">
-        <x:v>tests/test_retrieval_stop_decision.py</x:v>
+        <x:v>tests/test_retrieval_snapshot_compare.py</x:v>
       </x:c>
       <x:c r="C183" s="49" t="str">
-        <x:v>test_second_high_score_records_recovery</x:v>
+        <x:v>test_snapshot_comparison_blocks_quality_or_quarantine_instability</x:v>
       </x:c>
       <x:c r="D183" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E183" s="49" t="str">
-        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
+        <x:v>验证跨快照出现逐题质量下降或隔离集合漂移时阻止默认启用候选策略。</x:v>
       </x:c>
       <x:c r="F183" s="49" t="str">
-        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
+        <x:v>比较器同时报告质量回归与隔离不稳定，并输出需要人工复核的新增和移除记录。</x:v>
       </x:c>
       <x:c r="G183" s="49" t="str">
-        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
+        <x:v>只看平均指标可能掩盖逐题退化或误伤漂移，让不稳定元数据策略进入默认流程。</x:v>
       </x:c>
       <x:c r="H183" s="52" t="str">
         <x:v>通过</x:v>
@@ -12058,54 +12130,54 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B184" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C184" s="49" t="str">
-        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
+        <x:v>test_first_low_score_requests_replan</x:v>
       </x:c>
       <x:c r="D184" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E184" s="49" t="str">
-        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
+        <x:v>验证首次检索低于质量门槛时输出明确的 Replan 请求状态。</x:v>
       </x:c>
       <x:c r="F184" s="49" t="str">
-        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
+        <x:v>outcome 为 replan_required，停止原因为 quality_below_threshold。</x:v>
       </x:c>
       <x:c r="G184" s="49" t="str">
-        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
+        <x:v>低质量首次结果可能缺少后续动作信号而直接生成答案。</x:v>
       </x:c>
       <x:c r="H184" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I184" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J184" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="185" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A185" s="42" t="n">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B185" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C185" s="49" t="str">
-        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
+        <x:v>test_second_low_score_stops_when_retry_budget_is_exhausted</x:v>
       </x:c>
       <x:c r="D185" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E185" s="49" t="str">
-        <x:v>验证多个规划查询时启用多查询检索。</x:v>
+        <x:v>验证第二轮仍低质量时停止并记录重试预算耗尽。</x:v>
       </x:c>
       <x:c r="F185" s="49" t="str">
-        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
+        <x:v>outcome 为 stopped_low_quality，原因是 retry_budget_exhausted。</x:v>
       </x:c>
       <x:c r="G185" s="49" t="str">
-        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
+        <x:v>第二轮失败可能无审计地继续循环或被误记为成功。</x:v>
       </x:c>
       <x:c r="H185" s="52" t="str">
         <x:v>通过</x:v>
@@ -12122,34 +12194,34 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B186" s="49" t="str">
-        <x:v>tests/test_retrieve_planning.py</x:v>
+        <x:v>tests/test_retrieval_stop_decision.py</x:v>
       </x:c>
       <x:c r="C186" s="49" t="str">
-        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
+        <x:v>test_second_high_score_records_recovery</x:v>
       </x:c>
       <x:c r="D186" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E186" s="49" t="str">
-        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
+        <x:v>验证 Replan 后质量达到门槛时记录恢复成功。</x:v>
       </x:c>
       <x:c r="F186" s="49" t="str">
-        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
+        <x:v>outcome 为 recovered，停止原因为 quality_threshold_met。</x:v>
       </x:c>
       <x:c r="G186" s="49" t="str">
-        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
+        <x:v>成功恢复可能无法与首轮直接通过区分，影响后续能力评测。</x:v>
       </x:c>
       <x:c r="H186" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I186" s="55" t="n">
-        <x:v>0.038</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J186" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" ht="79.19999694824219" hidden="0" customHeight="1">
+    <x:row r="187" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A187" s="42" t="n">
         <x:v>183</x:v>
       </x:c>
@@ -12157,19 +12229,19 @@
         <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C187" s="49" t="str">
-        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
+        <x:v>test_single_planned_query_uses_single_query_retrieval</x:v>
       </x:c>
       <x:c r="D187" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E187" s="49" t="str">
-        <x:v>验证只有一个子查询时不创建线程池。</x:v>
+        <x:v>验证只有一个规划查询时走低成本单查询检索路径。</x:v>
       </x:c>
       <x:c r="F187" s="49" t="str">
-        <x:v>单子查询继续走直接调用路径。</x:v>
+        <x:v>只调用 single retrieval，agentic_rag_enabled 为 false，并保留缓存来源。</x:v>
       </x:c>
       <x:c r="G187" s="49" t="str">
-        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
+        <x:v>简单问题可能误用多查询检索，造成额外请求与 Token 消耗。</x:v>
       </x:c>
       <x:c r="H187" s="52" t="str">
         <x:v>通过</x:v>
@@ -12181,33 +12253,33 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="188" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A188" s="42" t="n">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B188" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C188" s="49" t="str">
-        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
+        <x:v>test_multiple_planned_queries_use_multi_query_retrieval</x:v>
       </x:c>
       <x:c r="D188" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E188" s="49" t="str">
-        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
+        <x:v>验证多个规划查询时启用多查询检索。</x:v>
       </x:c>
       <x:c r="F188" s="49" t="str">
-        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
+        <x:v>完整查询列表传入 multi retrieval，并标记 Agentic RAG 已启用。</x:v>
       </x:c>
       <x:c r="G188" s="49" t="str">
-        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
+        <x:v>复杂问题可能只检索一个角度，降低论文覆盖度。</x:v>
       </x:c>
       <x:c r="H188" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I188" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J188" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12218,226 +12290,226 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B189" s="49" t="str">
-        <x:v>tests/test_retrieve_tool_integration.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C189" s="49" t="str">
-        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
+        <x:v>test_multi_query_parallel_preserves_planned_order</x:v>
       </x:c>
       <x:c r="D189" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E189" s="49" t="str">
-        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
+        <x:v>验证子查询完成顺序不同也不会改变规划顺序与合并结果顺序。</x:v>
       </x:c>
       <x:c r="F189" s="49" t="str">
-        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
+        <x:v>慢查询和快查询并发完成后仍按 first、second 顺序收集。</x:v>
       </x:c>
       <x:c r="G189" s="49" t="str">
-        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
+        <x:v>并发竞态可能使复杂任务结果不可复现。</x:v>
       </x:c>
       <x:c r="H189" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I189" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.034</x:v>
       </x:c>
       <x:c r="J189" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="190" ht="79.19999694824219" hidden="0" customHeight="1">
       <x:c r="A190" s="42" t="n">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B190" s="49" t="str">
-        <x:v>tests/test_test_catalog.py</x:v>
+        <x:v>tests/test_retrieve_planning.py</x:v>
       </x:c>
       <x:c r="C190" s="49" t="str">
-        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
+        <x:v>test_multi_query_single_query_does_not_create_pool</x:v>
       </x:c>
       <x:c r="D190" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E190" s="49" t="str">
-        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
+        <x:v>验证只有一个子查询时不创建线程池。</x:v>
       </x:c>
       <x:c r="F190" s="49" t="str">
-        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
+        <x:v>单子查询继续走直接调用路径。</x:v>
       </x:c>
       <x:c r="G190" s="49" t="str">
-        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
+        <x:v>简单任务可能承担不必要的并发调度成本。</x:v>
       </x:c>
       <x:c r="H190" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I190" s="55" t="n">
-        <x:v>0.063</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J190" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="191" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A191" s="42" t="n">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B191" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C191" s="49" t="str">
-        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
+        <x:v>test_cache_miss_uses_tool_runtime_and_records_execution</x:v>
       </x:c>
       <x:c r="D191" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E191" s="49" t="str">
-        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
+        <x:v>验证缓存未命中时 Retrieve Node 通过 Router 和 Executor 调用 arXiv。</x:v>
       </x:c>
       <x:c r="F191" s="49" t="str">
-        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
+        <x:v>统一工具名称、查询参数、论文结果、缓存写入和执行指标全部正确。</x:v>
       </x:c>
       <x:c r="G191" s="49" t="str">
-        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
+        <x:v>检索节点可能仍直接依赖 arXiv，或工具结果无法进入现有缓存和文档流程。</x:v>
       </x:c>
       <x:c r="H191" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I191" s="55" t="n">
-        <x:v>0.035</x:v>
+        <x:v>0.003</x:v>
       </x:c>
       <x:c r="J191" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" ht="132" hidden="0" customHeight="1">
+    <x:row r="192" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A192" s="42" t="n">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B192" s="49" t="str">
-        <x:v>tests/test_test_report.py</x:v>
+        <x:v>tests/test_retrieve_tool_integration.py</x:v>
       </x:c>
       <x:c r="C192" s="49" t="str">
-        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
+        <x:v>test_tool_failure_uses_existing_fallback_and_keeps_error_metadata</x:v>
       </x:c>
       <x:c r="D192" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E192" s="49" t="str">
-        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
+        <x:v>验证统一工具执行失败后沿用现有 fallback，并保留失败原因。</x:v>
       </x:c>
       <x:c r="F192" s="49" t="str">
-        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
+        <x:v>超时不会使图崩溃，静态兜底文档可用且 TIMEOUT 元数据未丢失。</x:v>
       </x:c>
       <x:c r="G192" s="49" t="str">
-        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
+        <x:v>外部工具失败可能中断流程，或降级后无法定位原始错误。</x:v>
       </x:c>
       <x:c r="H192" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I192" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J192" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" ht="132" hidden="0" customHeight="1">
+    <x:row r="193" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A193" s="42" t="n">
         <x:v>189</x:v>
       </x:c>
       <x:c r="B193" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_catalog.py</x:v>
       </x:c>
       <x:c r="C193" s="49" t="str">
-        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
+        <x:v>test_catalog_exactly_covers_all_test_functions</x:v>
       </x:c>
       <x:c r="D193" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E193" s="49" t="str">
-        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
+        <x:v>强制每个测试函数都登记作用、通过含义和失败含义，并清理失效记录。</x:v>
       </x:c>
       <x:c r="F193" s="49" t="str">
-        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
+        <x:v>测试源码中的函数集合与说明目录完全一致，且三个说明字段均非空。</x:v>
       </x:c>
       <x:c r="G193" s="49" t="str">
-        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
+        <x:v>存在未说明的新测试、已删除测试的遗留记录，或说明字段不完整。</x:v>
       </x:c>
       <x:c r="H193" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I193" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.061</x:v>
       </x:c>
       <x:c r="J193" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="194" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A194" s="42" t="n">
         <x:v>190</x:v>
       </x:c>
       <x:c r="B194" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C194" s="49" t="str">
-        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
+        <x:v>test_parse_junit_xml_normalizes_status_duration_and_message</x:v>
       </x:c>
       <x:c r="D194" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E194" s="49" t="str">
-        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
+        <x:v>验证测试报告采集器能把 JUnit XML 转成统一明细记录。</x:v>
       </x:c>
       <x:c r="F194" s="49" t="str">
-        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
+        <x:v>通过、失败、错误、跳过状态及文件、耗时、消息和详情均正确解析。</x:v>
       </x:c>
       <x:c r="G194" s="49" t="str">
-        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
+        <x:v>Excel/CSV 报告可能漏掉测试、错误状态或失败原因。</x:v>
       </x:c>
       <x:c r="H194" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I194" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.01</x:v>
       </x:c>
       <x:c r="J194" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="195" ht="132" hidden="0" customHeight="1">
       <x:c r="A195" s="42" t="n">
         <x:v>191</x:v>
       </x:c>
       <x:c r="B195" s="49" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
+        <x:v>tests/test_test_report.py</x:v>
       </x:c>
       <x:c r="C195" s="49" t="str">
-        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
+        <x:v>test_summarize_calculates_counts_rate_and_duration</x:v>
       </x:c>
       <x:c r="D195" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E195" s="49" t="str">
-        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
+        <x:v>验证测试报告总览的数量、通过率、耗时和退出码计算。</x:v>
       </x:c>
       <x:c r="F195" s="49" t="str">
-        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
+        <x:v>四个示例用例被汇总为 2 通过、1 失败、1 跳过、50% 通过率和 0.875 秒。</x:v>
       </x:c>
       <x:c r="G195" s="49" t="str">
-        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
+        <x:v>测试总览指标可能与明细不一致，导致质量判断错误。</x:v>
       </x:c>
       <x:c r="H195" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I195" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J195" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="196" ht="132" hidden="0" customHeight="1">
       <x:c r="A196" s="42" t="n">
         <x:v>192</x:v>
       </x:c>
@@ -12445,19 +12517,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C196" s="49" t="str">
-        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
+        <x:v>test_registry_registers_discovers_and_filters_tools</x:v>
       </x:c>
       <x:c r="D196" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E196" s="49" t="str">
-        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
+        <x:v>验证 Tool Registry 可以注册、按名称发现并按能力筛选工具。</x:v>
       </x:c>
       <x:c r="F196" s="49" t="str">
-        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
+        <x:v>工具注册顺序稳定，paper 等能力可以通过统一入口发现，不依赖业务节点直接导入。</x:v>
       </x:c>
       <x:c r="G196" s="49" t="str">
-        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
+        <x:v>后续多数据源或 MCP 工具可能无法可靠注册、发现或路由。</x:v>
       </x:c>
       <x:c r="H196" s="52" t="str">
         <x:v>通过</x:v>
@@ -12469,7 +12541,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="197" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A197" s="42" t="n">
         <x:v>193</x:v>
       </x:c>
@@ -12477,25 +12549,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C197" s="49" t="str">
-        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
+        <x:v>test_registry_rejects_duplicate_tool_names</x:v>
       </x:c>
       <x:c r="D197" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E197" s="49" t="str">
-        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
+        <x:v>验证 Registry 拒绝相同稳定名称的重复工具。</x:v>
       </x:c>
       <x:c r="F197" s="49" t="str">
-        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
+        <x:v>重复注册会明确报错，避免工具实现被静默覆盖。</x:v>
       </x:c>
       <x:c r="G197" s="49" t="str">
-        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
+        <x:v>同名工具可能覆盖旧实现，导致实际执行版本不可追踪。</x:v>
       </x:c>
       <x:c r="H197" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I197" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J197" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12509,19 +12581,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C198" s="49" t="str">
-        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
+        <x:v>test_executor_returns_structured_error_for_unknown_tool</x:v>
       </x:c>
       <x:c r="D198" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E198" s="49" t="str">
-        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
+        <x:v>验证执行不存在的工具时返回标准化错误而不是抛出未处理异常。</x:v>
       </x:c>
       <x:c r="F198" s="49" t="str">
-        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
+        <x:v>结果包含 TOOL_NOT_FOUND、零执行次数和可观测延迟。</x:v>
       </x:c>
       <x:c r="G198" s="49" t="str">
-        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
+        <x:v>错误路由可能让 LangGraph 整体崩溃或产生无法分类的失败。</x:v>
       </x:c>
       <x:c r="H198" s="52" t="str">
         <x:v>通过</x:v>
@@ -12541,31 +12613,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C199" s="49" t="str">
-        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
+        <x:v>test_executor_rejects_invalid_input_without_invoking_tool</x:v>
       </x:c>
       <x:c r="D199" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E199" s="49" t="str">
-        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
+        <x:v>验证 Tool Executor 在执行前使用 Pydantic 校验输入参数。</x:v>
       </x:c>
       <x:c r="F199" s="49" t="str">
-        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
+        <x:v>非法参数被 INVALID_INPUT 拦截，底层工具完全没有执行。</x:v>
       </x:c>
       <x:c r="G199" s="49" t="str">
-        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
+        <x:v>错误参数可能进入外部 API，浪费调用额度或触发不可控行为。</x:v>
       </x:c>
       <x:c r="H199" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I199" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J199" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" ht="105.5999984741211" hidden="0" customHeight="1">
+    <x:row r="200" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A200" s="42" t="n">
         <x:v>196</x:v>
       </x:c>
@@ -12573,31 +12645,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C200" s="49" t="str">
-        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
+        <x:v>test_executor_blocks_non_read_only_tool_before_invocation</x:v>
       </x:c>
       <x:c r="D200" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E200" s="49" t="str">
-        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
+        <x:v>验证默认 ToolPolicy 在调用前拒绝非只读工具。</x:v>
       </x:c>
       <x:c r="F200" s="49" t="str">
-        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
+        <x:v>写工具返回 PERMISSION_DENIED、执行次数为零，底层函数没有运行。</x:v>
       </x:c>
       <x:c r="G200" s="49" t="str">
-        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
+        <x:v>风险等级可能只被记录而未执行，导致未授权写操作进入外部系统。</x:v>
       </x:c>
       <x:c r="H200" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I200" s="55" t="n">
-        <x:v>0.003</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J200" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="201" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A201" s="42" t="n">
         <x:v>197</x:v>
       </x:c>
@@ -12605,31 +12677,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C201" s="49" t="str">
-        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
+        <x:v>test_executor_validates_output_and_records_execution_metadata</x:v>
       </x:c>
       <x:c r="D201" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E201" s="49" t="str">
-        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
+        <x:v>验证成功工具调用会校验输出并记录版本、来源、能力、风险和延迟。</x:v>
       </x:c>
       <x:c r="F201" s="49" t="str">
-        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
+        <x:v>标准数据、工具版本、一次执行和只读风险元数据全部准确返回。</x:v>
       </x:c>
       <x:c r="G201" s="49" t="str">
-        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
+        <x:v>下游可能收到不可信结构，或无法审计工具版本、来源和成本。</x:v>
       </x:c>
       <x:c r="H201" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I201" s="55" t="n">
-        <x:v>0.021</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J201" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="202" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A202" s="42" t="n">
         <x:v>198</x:v>
       </x:c>
@@ -12637,19 +12709,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C202" s="49" t="str">
-        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
+        <x:v>test_executor_retries_retryable_failure_then_returns_success</x:v>
       </x:c>
       <x:c r="D202" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E202" s="49" t="str">
-        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
+        <x:v>验证临时执行错误可以按照有限 RetryPolicy 重试。</x:v>
       </x:c>
       <x:c r="F202" s="49" t="str">
-        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
+        <x:v>第一次连接错误后只重试一次并成功，attempt_count 准确记录为 2。</x:v>
       </x:c>
       <x:c r="G202" s="49" t="str">
-        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
+        <x:v>临时错误可能无法恢复，或工具发生无上限重复调用。</x:v>
       </x:c>
       <x:c r="H202" s="52" t="str">
         <x:v>通过</x:v>
@@ -12661,7 +12733,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="203" ht="105.5999984741211" hidden="0" customHeight="1">
       <x:c r="A203" s="42" t="n">
         <x:v>199</x:v>
       </x:c>
@@ -12669,19 +12741,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C203" s="49" t="str">
-        <x:v>test_router_resolves_registered_capability_and_source</x:v>
+        <x:v>test_executor_returns_structured_rate_limit_after_finite_retries</x:v>
       </x:c>
       <x:c r="D203" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E203" s="49" t="str">
-        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
+        <x:v>验证数据源限流经过有限次数重试后返回独立标准错误码。</x:v>
       </x:c>
       <x:c r="F203" s="49" t="str">
-        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
+        <x:v>执行两次后停止并返回 RATE_LIMITED，不会无限消耗 API 额度。</x:v>
       </x:c>
       <x:c r="G203" s="49" t="str">
-        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
+        <x:v>429 可能被误记为普通异常、无法触发正确恢复，或产生无限重试。</x:v>
       </x:c>
       <x:c r="H203" s="52" t="str">
         <x:v>通过</x:v>
@@ -12701,31 +12773,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C204" s="49" t="str">
-        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
+        <x:v>test_executor_returns_timeout_after_bounded_wait</x:v>
       </x:c>
       <x:c r="D204" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E204" s="49" t="str">
-        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
+        <x:v>验证工具超过配置时间后返回结构化超时错误。</x:v>
       </x:c>
       <x:c r="F204" s="49" t="str">
-        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
+        <x:v>执行在有限等待后返回 TIMEOUT，并准确记录一次尝试。</x:v>
       </x:c>
       <x:c r="G204" s="49" t="str">
-        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
+        <x:v>外部工具可能无限阻塞请求，或超时无法被失败路由识别。</x:v>
       </x:c>
       <x:c r="H204" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I204" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="J204" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" ht="132" hidden="0" customHeight="1">
+    <x:row r="205" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A205" s="42" t="n">
         <x:v>201</x:v>
       </x:c>
@@ -12733,19 +12805,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C205" s="49" t="str">
-        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
+        <x:v>test_executor_rejects_output_that_breaks_tool_contract</x:v>
       </x:c>
       <x:c r="D205" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E205" s="49" t="str">
-        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
+        <x:v>验证工具返回值不符合输出 Schema 时被拒绝。</x:v>
       </x:c>
       <x:c r="F205" s="49" t="str">
-        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
+        <x:v>缺失 doubled 字段的输出返回 INVALID_OUTPUT，不会传给下游节点。</x:v>
       </x:c>
       <x:c r="G205" s="49" t="str">
-        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
+        <x:v>外部 API 或 MCP 结构变化可能静默污染 AgentState。</x:v>
       </x:c>
       <x:c r="H205" s="52" t="str">
         <x:v>通过</x:v>
@@ -12757,7 +12829,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="206" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A206" s="42" t="n">
         <x:v>202</x:v>
       </x:c>
@@ -12765,31 +12837,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C206" s="49" t="str">
-        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
+        <x:v>test_router_resolves_registered_capability_and_source</x:v>
       </x:c>
       <x:c r="D206" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E206" s="49" t="str">
-        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
+        <x:v>验证 Tool Router 根据能力与数据源选择稳定工具名称。</x:v>
       </x:c>
       <x:c r="F206" s="49" t="str">
-        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
+        <x:v>arXiv 路由正确，未注册的 OpenAlex 路由明确失败。</x:v>
       </x:c>
       <x:c r="G206" s="49" t="str">
-        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
+        <x:v>数据源选择可能错误或在无实现时静默调用其他工具。</x:v>
       </x:c>
       <x:c r="H206" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I206" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.004</x:v>
       </x:c>
       <x:c r="J206" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" ht="145.1999969482422" hidden="0" customHeight="1">
+    <x:row r="207" ht="92.4000015258789" hidden="0" customHeight="1">
       <x:c r="A207" s="42" t="n">
         <x:v>203</x:v>
       </x:c>
@@ -12797,25 +12869,25 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C207" s="49" t="str">
-        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_arxiv_adapter_preserves_native_search_behavior</x:v>
       </x:c>
       <x:c r="D207" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E207" s="49" t="str">
-        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+        <x:v>验证 arXiv Adapter 保留现有查询词、数量和论文字段。</x:v>
       </x:c>
       <x:c r="F207" s="49" t="str">
-        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+        <x:v>适配器把相同参数传给原生函数，并完整返回论文标识。</x:v>
       </x:c>
       <x:c r="G207" s="49" t="str">
-        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+        <x:v>工具层改造可能改变原有 arXiv 行为或丢失论文字段。</x:v>
       </x:c>
       <x:c r="H207" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I207" s="55" t="n">
-        <x:v>0.002</x:v>
+        <x:v>0.001</x:v>
       </x:c>
       <x:c r="J207" s="58" t="str">
         <x:v>已登记</x:v>
@@ -12829,19 +12901,19 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C208" s="49" t="str">
-        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+        <x:v>test_arxiv_lookup_adapter_uses_native_identity_contract</x:v>
       </x:c>
       <x:c r="D208" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E208" s="49" t="str">
-        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+        <x:v>验证工具层可以按 arXiv 原生 ID 查询单篇规范元数据，而不需要退化为关键词搜索。</x:v>
       </x:c>
       <x:c r="F208" s="49" t="str">
-        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+        <x:v>lookup 工具准确传递 ID，并通过统一 Pydantic 输出协议返回论文。</x:v>
       </x:c>
       <x:c r="G208" s="49" t="str">
-        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+        <x:v>身份校验可能误用相关性搜索结果，无法证明返回论文就是被声明的规范身份。</x:v>
       </x:c>
       <x:c r="H208" s="52" t="str">
         <x:v>通过</x:v>
@@ -12853,7 +12925,7 @@
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" ht="118.80000305175781" hidden="0" customHeight="1">
+    <x:row r="209" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A209" s="42" t="n">
         <x:v>205</x:v>
       </x:c>
@@ -12861,31 +12933,31 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C209" s="49" t="str">
-        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+        <x:v>test_crossref_client_normalizes_doi_metadata</x:v>
       </x:c>
       <x:c r="D209" s="49" t="str">
         <x:v>默认场景</x:v>
       </x:c>
       <x:c r="E209" s="49" t="str">
-        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+        <x:v>验证 Crossref 客户端正确编码 DOI，并把标题、作者、年份和链接归一为统一论文结构。</x:v>
       </x:c>
       <x:c r="F209" s="49" t="str">
-        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+        <x:v>带斜杠 DOI 被安全编码，Crossref 响应字段准确进入 PaperRecord。</x:v>
       </x:c>
       <x:c r="G209" s="49" t="str">
-        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+        <x:v>普通 DOI 查询可能因 URL 错误或字段映射错误产生伪冲突和错误修复。</x:v>
       </x:c>
       <x:c r="H209" s="52" t="str">
         <x:v>通过</x:v>
       </x:c>
       <x:c r="I209" s="55" t="n">
-        <x:v>0.001</x:v>
+        <x:v>0.002</x:v>
       </x:c>
       <x:c r="J209" s="58" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" ht="92.4000015258789" hidden="0" customHeight="1">
+    <x:row r="210" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A210" s="42" t="n">
         <x:v>206</x:v>
       </x:c>
@@ -12893,59 +12965,155 @@
         <x:v>tests/test_tool_layer.py</x:v>
       </x:c>
       <x:c r="C210" s="49" t="str">
+        <x:v>test_crossref_lookup_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D210" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E210" s="49" t="str">
+        <x:v>验证 Crossref 与 arXiv 共用 paper.lookup 工具能力和 Pydantic 输出契约。</x:v>
+      </x:c>
+      <x:c r="F210" s="49" t="str">
+        <x:v>同一 Router、Registry、Policy 和 Executor 可以替换 authority provider。</x:v>
+      </x:c>
+      <x:c r="G210" s="49" t="str">
+        <x:v>Crossref 可能变成绕过工具约束的特例，增加后续 MCP 接入和选型替换成本。</x:v>
+      </x:c>
+      <x:c r="H210" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I210" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J210" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" ht="132" hidden="0" customHeight="1">
+      <x:c r="A211" s="42" t="n">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B211" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C211" s="49" t="str">
+        <x:v>test_semantic_scholar_client_normalizes_doi_metadata</x:v>
+      </x:c>
+      <x:c r="D211" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E211" s="49" t="str">
+        <x:v>验证 Semantic Scholar DOI 精确查询、API Key 请求头和统一论文字段映射。</x:v>
+      </x:c>
+      <x:c r="F211" s="49" t="str">
+        <x:v>DOI 被安全编码，作者、年份、外部 DOI 与开放 PDF 进入 PaperRecord。</x:v>
+      </x:c>
+      <x:c r="G211" s="49" t="str">
+        <x:v>替代 provider 可能因 URL 或认证错误产生系统性失败。</x:v>
+      </x:c>
+      <x:c r="H211" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I211" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J211" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A212" s="42" t="n">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B212" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C212" s="49" t="str">
+        <x:v>test_semantic_scholar_adapter_uses_shared_lookup_contract</x:v>
+      </x:c>
+      <x:c r="D212" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E212" s="49" t="str">
+        <x:v>验证 Semantic Scholar 与 Crossref 共用 paper.lookup 工具契约。</x:v>
+      </x:c>
+      <x:c r="F212" s="49" t="str">
+        <x:v>Router 和 Executor 可以按 provider 替换实现而无需改动调用方。</x:v>
+      </x:c>
+      <x:c r="G212" s="49" t="str">
+        <x:v>第二候选源可能绕过 Registry、Policy 和输出校验，破坏工具层边界。</x:v>
+      </x:c>
+      <x:c r="H212" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I212" s="55" t="n">
+        <x:v>0.002</x:v>
+      </x:c>
+      <x:c r="J212" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A213" s="42" t="n">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B213" s="49" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C213" s="49" t="str">
         <x:v>test_semantic_scholar_client_maps_rate_limit_to_tool_error</x:v>
       </x:c>
-      <x:c r="D210" s="49" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E210" s="49" t="str">
+      <x:c r="D213" s="49" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E213" s="49" t="str">
         <x:v>验证 Semantic Scholar HTTP 429 被映射为 RATE_LIMITED。</x:v>
       </x:c>
-      <x:c r="F210" s="49" t="str">
+      <x:c r="F213" s="49" t="str">
         <x:v>限流进入可重试失败类别，不被误记为论文查无。</x:v>
       </x:c>
-      <x:c r="G210" s="49" t="str">
+      <x:c r="G213" s="49" t="str">
         <x:v>匿名访问限流可能污染覆盖率并错误触发论文隔离。</x:v>
       </x:c>
-      <x:c r="H210" s="52" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I210" s="55" t="n">
+      <x:c r="H213" s="52" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I213" s="55" t="n">
+        <x:v>0.001</x:v>
+      </x:c>
+      <x:c r="J213" s="58" t="str">
+        <x:v>已登记</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" ht="132" hidden="0" customHeight="1">
+      <x:c r="A214" s="45" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B214" s="50" t="str">
+        <x:v>tests/test_tool_layer.py</x:v>
+      </x:c>
+      <x:c r="C214" s="50" t="str">
+        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
+      </x:c>
+      <x:c r="D214" s="50" t="str">
+        <x:v>默认场景</x:v>
+      </x:c>
+      <x:c r="E214" s="50" t="str">
+        <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
+      </x:c>
+      <x:c r="F214" s="50" t="str">
+        <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
+      </x:c>
+      <x:c r="G214" s="50" t="str">
+        <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
+      </x:c>
+      <x:c r="H214" s="53" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="I214" s="56" t="n">
         <x:v>0.003</x:v>
       </x:c>
-      <x:c r="J210" s="58" t="str">
-        <x:v>已登记</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" ht="132" hidden="0" customHeight="1">
-      <x:c r="A211" s="45" t="n">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="B211" s="50" t="str">
-        <x:v>tests/test_tool_layer.py</x:v>
-      </x:c>
-      <x:c r="C211" s="50" t="str">
-        <x:v>test_metrics_reports_tool_execution_success_failure_and_latency</x:v>
-      </x:c>
-      <x:c r="D211" s="50" t="str">
-        <x:v>默认场景</x:v>
-      </x:c>
-      <x:c r="E211" s="50" t="str">
-        <x:v>验证 Metrics 汇总每次工具调用的成功、失败、耗时和错误明细。</x:v>
-      </x:c>
-      <x:c r="F211" s="50" t="str">
-        <x:v>两次调用准确统计为一成功、一失败、总耗时 2 秒，并保留 TIMEOUT。</x:v>
-      </x:c>
-      <x:c r="G211" s="50" t="str">
-        <x:v>工具观测数据可能漏记或汇总错误，无法支持多数据源和 MCP 评测。</x:v>
-      </x:c>
-      <x:c r="H211" s="53" t="str">
-        <x:v>通过</x:v>
-      </x:c>
-      <x:c r="I211" s="56" t="n">
-        <x:v>0.003</x:v>
-      </x:c>
-      <x:c r="J211" s="59" t="str">
+      <x:c r="J214" s="59" t="str">
         <x:v>已登记</x:v>
       </x:c>
     </x:row>
@@ -12954,18 +13122,18 @@
     <x:mergeCell ref="A1:J1"/>
     <x:mergeCell ref="A2:J2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="H5:H211">
+  <x:conditionalFormatting sqref="H5:H214">
     <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="通过"/>
     <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
     <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="错误"/>
     <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="跳过"/>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="J5:J211">
+  <x:conditionalFormatting sqref="J5:J214">
     <x:cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="未登记"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R474013acfb17436f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95a3641fc1b04ced"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14414,34 +14582,66 @@
       </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="128" t="n">
+      <x:c r="A45" s="127" t="n">
         <x:v>46247.482141203705</x:v>
       </x:c>
-      <x:c r="B45" s="24" t="str">
+      <x:c r="B45" s="23" t="str">
         <x:v>4a50f5528c4f</x:v>
       </x:c>
-      <x:c r="C45" s="24" t="n">
+      <x:c r="C45" s="23" t="n">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="D45" s="24" t="n">
+      <x:c r="D45" s="23" t="n">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="E45" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F45" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G45" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H45" s="131" t="n">
+      <x:c r="E45" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F45" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G45" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H45" s="130" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I45" s="30" t="n">
+      <x:c r="I45" s="29" t="n">
         <x:v>142.615</x:v>
       </x:c>
-      <x:c r="J45" s="24" t="n">
+      <x:c r="J45" s="23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="128" t="n">
+        <x:v>46247.49344907407</x:v>
+      </x:c>
+      <x:c r="B46" s="24" t="str">
+        <x:v>0fbbcbb04859</x:v>
+      </x:c>
+      <x:c r="C46" s="24" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D46" s="24" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="E46" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F46" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G46" s="24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H46" s="131" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I46" s="30" t="n">
+        <x:v>181.577</x:v>
+      </x:c>
+      <x:c r="J46" s="24" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -14451,7 +14651,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56d0c7ba455547db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78280e2828484c3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/latest_test_report.xlsx
+++ b/reports/latest_test_report.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R840acf28d9844883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="Rcf9c72b0f8cb4e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="R5040751c96d54361"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="R5c445ab6bdd44f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="Reb02fb5ea0f047b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试总览" sheetId="1" r:id="R140e3d78d8d14a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试明细" sheetId="2" r:id="R85d3c95914884c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="用例说明" sheetId="3" r:id="Rb064a7eca44448a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="失败明细" sheetId="4" r:id="Rcf0bdd9b951c4516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史趋势" sheetId="5" r:id="R6096d12e73974470"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -707,7 +707,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TestDetailsTable" displayName="TestDetailsTable" ref="A4:H217" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -723,7 +723,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J214" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TestExplanationsTable" displayName="TestExplanationsTable" ref="A4:J217" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="序号"/>
     <x:tableColumn id="2" name="测试文件"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TestHistoryTable" displayName="TestHistoryTable" ref="A3:J47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="运行时间"/>
     <x:tableColumn id="2" name="Git Commit"/>
@@ -977,7 +977,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T11:50:34+08:00  |  Git：0fbbcbb04859d5a43e681259eadaab9e08057c5e</x:v>
+        <x:v>运行时间：2026-08-13T12:04:31+08:00  |  Git：9bedb90dd9cd2459dd5d2c9c8d243d7ff664021f</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1007,22 +1007,22 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="74" t="n">
-        <x:f>COUNTA('测试明细'!$A$5:$A$214)</x:f>
-        <x:v>210</x:v>
+        <x:f>COUNTA('测试明细'!$A$5:$A$217)</x:f>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B5" s="75"/>
       <x:c r="C5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$214,"通过")</x:f>
-        <x:v>210</x:v>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$217,"通过")</x:f>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D5" s="75"/>
       <x:c r="E5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$214,"失败")+COUNTIF('测试明细'!$E$5:$E$214,"错误")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$217,"失败")+COUNTIF('测试明细'!$E$5:$E$217,"错误")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="75"/>
       <x:c r="G5" s="75" t="n">
-        <x:f>COUNTIF('测试明细'!$E$5:$E$214,"跳过")</x:f>
+        <x:f>COUNTIF('测试明细'!$E$5:$E$217,"跳过")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="76"/>
@@ -1062,8 +1062,8 @@
       </x:c>
       <x:c r="B9" s="108"/>
       <x:c r="C9" s="109" t="n">
-        <x:f>SUM('测试明细'!$F$5:$F$214)</x:f>
-        <x:v>181.57700000000014</x:v>
+        <x:f>SUM('测试明细'!$F$5:$F$217)</x:f>
+        <x:v>233.6440000000002</x:v>
       </x:c>
       <x:c r="D9" s="109"/>
       <x:c r="E9" s="110" t="n">
@@ -1071,7 +1071,7 @@
       </x:c>
       <x:c r="F9" s="110"/>
       <x:c r="G9" s="110" t="n">
-        <x:f>COUNTIF('用例说明'!$J$5:$J$214,"未登记")</x:f>
+        <x:f>COUNTIF('用例说明'!$J$5:$J$217,"未登记")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="111"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="str">
-        <x:v>运行时间：2026-08-13T11:50:34+08:00  |  Git：0fbbcbb04859d5a43e681259eadaab9e08057c5e</x:v>
+        <x:v>运行时间：2026-08-13T12:04:31+08:00  |  Git：9bedb90dd9cd2459dd5d2c9c8d243d7ff664021f</x:v>
       </x:c>
       <x:c r="B2" s="5"/>
       <x:c r="C2" s="5"/>
@@ -1280,7 +1280,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F5" s="31" t="n">
-        <x:v>0.013</x:v>
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="G5" s="34" t="str">
         <x:v>确认旧基线与当前候选实现使用完全相同的能力模块，保证能力对比口径一致。</x:v>
@@ -1304,7 +1304,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F6" s="32" t="n">
-        <x:v>0.01</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
         <x:v>确认当前实现相对旧基线确实提升关键确定性能力的准确率。</x:v>
@@ -1328,7 +1328,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="32" t="n">
-        <x:v>0.014</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>验证动态查询规划不会为简单问题创建多余检索词，同时保持规划准确。</x:v>
@@ -1352,7 +1352,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F8" s="32" t="n">
-        <x:v>0.022</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>验证基准报告能同时给出基线值、候选值和差值。</x:v>
@@ -1376,7 +1376,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F9" s="32" t="n">
-        <x:v>0.015</x:v>
+        <x:v>0.007</x:v>
       </x:c>
       <x:c r="G9" s="35" t="str">
         <x:v>验证离线基准能准确统计成功/失败调用以及输入、输出和总 Token。</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F10" s="32" t="n">
-        <x:v>0.017</x:v>
+        <x:v>0.009</x:v>
       </x:c>
       <x:c r="G10" s="35" t="str">
         <x:v>验证离线基准能够量化统一 Tool 层的协议、错误和恢复能力。</x:v>
@@ -1424,7 +1424,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F11" s="32" t="n">
-        <x:v>0.011</x:v>
+        <x:v>0.008</x:v>
       </x:c>
       <x:c r="G11" s="35" t="str">
         <x:v>验证离线 Benchmark 对比单源基线与多源候选的覆盖、去重和故障恢复。</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>通过</x:v>
       </x:c>
       <x:c r="F12" s="32" t="n">
-        <x:v>0.166</x:v>
+        <x:v>0.205</x:v>
       </x:c>
       <x:c r="G12" s="35" t="str">
         <x:v>验证完整能力基准报告可以用 UTF-8 JSON 保存并重新读取。</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>通过</x:v>
       </x:c>
 